--- a/tests/SqlAnalysisFormatter.OutputExpectations.xlsx
+++ b/tests/SqlAnalysisFormatter.OutputExpectations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Macro\SqlAnalyzerFormatter-feature\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE4A88F-1CBE-4AE1-BC06-70C37B7DBCE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA2F8A5-2DBC-4F24-993D-244F406887F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{41A826B0-B2A2-4DC8-9B04-8EFBE807DC37}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="60" activeTab="66" xr2:uid="{41A826B0-B2A2-4DC8-9B04-8EFBE807DC37}"/>
   </bookViews>
   <sheets>
     <sheet name="SEL-064" sheetId="66" r:id="rId1"/>
@@ -77,6 +77,9 @@
     <sheet name="SEL-003" sheetId="3" r:id="rId62"/>
     <sheet name="SEL-002" sheetId="2" r:id="rId63"/>
     <sheet name="SEL-001" sheetId="1" r:id="rId64"/>
+    <sheet name="SEL-065" sheetId="67" r:id="rId65"/>
+    <sheet name="SEL-066" sheetId="68" r:id="rId66"/>
+    <sheet name="SEL-067" sheetId="69" r:id="rId67"/>
   </sheets>
   <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
@@ -88,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="337">
   <si>
     <t>＜DB入出力項目定義＞</t>
     <rPh sb="3" eb="10">
@@ -1393,6 +1396,45 @@
   <si>
     <t>EXISTS (SQ1)</t>
   </si>
+  <si>
+    <t>参照テーブル: ユーザー[users]、注文[tb2]</t>
+  </si>
+  <si>
+    <t>tb2.注文ユーザーID = users.ユーザーID</t>
+  </si>
+  <si>
+    <t>tb2.状態 = 'CANCELLED'</t>
+  </si>
+  <si>
+    <t>参照テーブル: ユーザー[users]、SQ1</t>
+  </si>
+  <si>
+    <t>'INACTIVE'</t>
+  </si>
+  <si>
+    <t>average_amount</t>
+  </si>
+  <si>
+    <t>AVG(tb2.金額)</t>
+  </si>
+  <si>
+    <t>'REVIEW'</t>
+  </si>
+  <si>
+    <t>tb1.金額 &gt; (SQ1)</t>
+  </si>
+  <si>
+    <t>参照テーブル: 注文[tb2]</t>
+  </si>
+  <si>
+    <t>tb2.注文日時 &lt; @cutoff</t>
+  </si>
+  <si>
+    <t>'ARCHIVED'</t>
+  </si>
+  <si>
+    <t>tb1.ユーザーID IN (SQ1)</t>
+  </si>
 </sst>
 </file>
 
@@ -1733,7 +1775,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1936,6 +1978,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -45051,6 +45096,3010 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{125A3CC4-F32F-4AFC-B49F-2EB086F762F7}">
+  <dimension ref="A1:CL11"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="90" width="1.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
+      <c r="AQ1" s="1"/>
+      <c r="AR1" s="1"/>
+      <c r="AS1" s="1"/>
+      <c r="AT1" s="1"/>
+      <c r="AU1" s="1"/>
+      <c r="AV1" s="1"/>
+      <c r="AW1" s="1"/>
+      <c r="AX1" s="1"/>
+      <c r="AY1" s="1"/>
+      <c r="AZ1" s="1"/>
+      <c r="BA1" s="1"/>
+      <c r="BB1" s="1"/>
+      <c r="BC1" s="1"/>
+      <c r="BD1" s="1"/>
+      <c r="BE1" s="1"/>
+      <c r="BF1" s="1"/>
+      <c r="BG1" s="1"/>
+      <c r="BH1" s="1"/>
+      <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
+      <c r="BN1" s="1"/>
+      <c r="BO1" s="1"/>
+      <c r="BP1" s="1"/>
+      <c r="BQ1" s="1"/>
+      <c r="BR1" s="1"/>
+      <c r="BS1" s="1"/>
+      <c r="BT1" s="1"/>
+      <c r="BU1" s="1"/>
+      <c r="BV1" s="1"/>
+      <c r="BW1" s="1"/>
+      <c r="BX1" s="1"/>
+      <c r="BY1" s="1"/>
+      <c r="BZ1" s="1"/>
+      <c r="CA1" s="1"/>
+      <c r="CB1" s="1"/>
+      <c r="CC1" s="1"/>
+      <c r="CD1" s="1"/>
+      <c r="CE1" s="1"/>
+      <c r="CF1" s="1"/>
+      <c r="CG1" s="1"/>
+      <c r="CH1" s="1"/>
+      <c r="CI1" s="1"/>
+      <c r="CJ1" s="1"/>
+      <c r="CK1" s="1"/>
+      <c r="CL1" s="1"/>
+    </row>
+    <row r="2" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="56" t="s">
+        <v>324</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="1"/>
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="1"/>
+      <c r="BQ2" s="1"/>
+      <c r="BR2" s="1"/>
+      <c r="BS2" s="1"/>
+      <c r="BT2" s="1"/>
+      <c r="BU2" s="1"/>
+      <c r="BV2" s="1"/>
+      <c r="BW2" s="1"/>
+      <c r="BX2" s="1"/>
+      <c r="BY2" s="1"/>
+      <c r="BZ2" s="1"/>
+      <c r="CA2" s="1"/>
+      <c r="CB2" s="1"/>
+      <c r="CC2" s="1"/>
+      <c r="CD2" s="1"/>
+      <c r="CE2" s="1"/>
+      <c r="CF2" s="1"/>
+      <c r="CG2" s="1"/>
+      <c r="CH2" s="1"/>
+      <c r="CI2" s="1"/>
+      <c r="CJ2" s="1"/>
+      <c r="CK2" s="1"/>
+      <c r="CL2" s="1"/>
+    </row>
+    <row r="3" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="59" t="s">
+        <v>308</v>
+      </c>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="28"/>
+      <c r="X3" s="28"/>
+      <c r="Y3" s="28"/>
+      <c r="Z3" s="28"/>
+      <c r="AA3" s="28"/>
+      <c r="AB3" s="28"/>
+      <c r="AC3" s="28"/>
+      <c r="AD3" s="28"/>
+      <c r="AE3" s="28"/>
+      <c r="AF3" s="28"/>
+      <c r="AG3" s="28"/>
+      <c r="AH3" s="28"/>
+      <c r="AI3" s="28"/>
+      <c r="AJ3" s="28"/>
+      <c r="AK3" s="28"/>
+      <c r="AL3" s="28"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="28"/>
+      <c r="AO3" s="28"/>
+      <c r="AP3" s="28"/>
+      <c r="AQ3" s="28"/>
+      <c r="AR3" s="28"/>
+      <c r="AS3" s="28"/>
+      <c r="AT3" s="28"/>
+      <c r="AU3" s="28"/>
+      <c r="AV3" s="28"/>
+      <c r="AW3" s="28"/>
+      <c r="AX3" s="28"/>
+      <c r="AY3" s="28"/>
+      <c r="AZ3" s="28"/>
+      <c r="BA3" s="28"/>
+      <c r="BB3" s="28"/>
+      <c r="BC3" s="28"/>
+      <c r="BD3" s="28"/>
+      <c r="BE3" s="28"/>
+      <c r="BF3" s="28"/>
+      <c r="BG3" s="28"/>
+      <c r="BH3" s="28"/>
+      <c r="BI3" s="28"/>
+      <c r="BJ3" s="28"/>
+      <c r="BK3" s="28"/>
+      <c r="BL3" s="28"/>
+      <c r="BM3" s="28"/>
+      <c r="BN3" s="28"/>
+      <c r="BO3" s="28"/>
+      <c r="BP3" s="28"/>
+      <c r="BQ3" s="28"/>
+      <c r="BR3" s="28"/>
+      <c r="BS3" s="28"/>
+      <c r="BT3" s="28"/>
+      <c r="BU3" s="28"/>
+      <c r="BV3" s="28"/>
+      <c r="BW3" s="28"/>
+      <c r="BX3" s="28"/>
+      <c r="BY3" s="28"/>
+      <c r="BZ3" s="28"/>
+      <c r="CA3" s="28"/>
+      <c r="CB3" s="28"/>
+      <c r="CC3" s="28"/>
+      <c r="CD3" s="28"/>
+      <c r="CE3" s="28"/>
+      <c r="CF3" s="28"/>
+      <c r="CG3" s="28"/>
+      <c r="CH3" s="28"/>
+      <c r="CI3" s="28"/>
+      <c r="CJ3" s="28"/>
+      <c r="CK3" s="28"/>
+      <c r="CL3" s="29"/>
+    </row>
+    <row r="4" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="59" t="s">
+        <v>325</v>
+      </c>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="28"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="28"/>
+      <c r="AA4" s="28"/>
+      <c r="AB4" s="28"/>
+      <c r="AC4" s="28"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="28"/>
+      <c r="AG4" s="28"/>
+      <c r="AH4" s="28"/>
+      <c r="AI4" s="28"/>
+      <c r="AJ4" s="28"/>
+      <c r="AK4" s="28"/>
+      <c r="AL4" s="28"/>
+      <c r="AM4" s="28"/>
+      <c r="AN4" s="28"/>
+      <c r="AO4" s="28"/>
+      <c r="AP4" s="28"/>
+      <c r="AQ4" s="28"/>
+      <c r="AR4" s="28"/>
+      <c r="AS4" s="28"/>
+      <c r="AT4" s="28"/>
+      <c r="AU4" s="28"/>
+      <c r="AV4" s="28"/>
+      <c r="AW4" s="28"/>
+      <c r="AX4" s="28"/>
+      <c r="AY4" s="28"/>
+      <c r="AZ4" s="28"/>
+      <c r="BA4" s="28"/>
+      <c r="BB4" s="28"/>
+      <c r="BC4" s="28"/>
+      <c r="BD4" s="28"/>
+      <c r="BE4" s="28"/>
+      <c r="BF4" s="28"/>
+      <c r="BG4" s="28"/>
+      <c r="BH4" s="28"/>
+      <c r="BI4" s="28"/>
+      <c r="BJ4" s="28"/>
+      <c r="BK4" s="28"/>
+      <c r="BL4" s="28"/>
+      <c r="BM4" s="28"/>
+      <c r="BN4" s="28"/>
+      <c r="BO4" s="28"/>
+      <c r="BP4" s="28"/>
+      <c r="BQ4" s="28"/>
+      <c r="BR4" s="28"/>
+      <c r="BS4" s="28"/>
+      <c r="BT4" s="28"/>
+      <c r="BU4" s="28"/>
+      <c r="BV4" s="28"/>
+      <c r="BW4" s="28"/>
+      <c r="BX4" s="28"/>
+      <c r="BY4" s="28"/>
+      <c r="BZ4" s="28"/>
+      <c r="CA4" s="28"/>
+      <c r="CB4" s="28"/>
+      <c r="CC4" s="28"/>
+      <c r="CD4" s="28"/>
+      <c r="CE4" s="28"/>
+      <c r="CF4" s="28"/>
+      <c r="CG4" s="28"/>
+      <c r="CH4" s="28"/>
+      <c r="CI4" s="28"/>
+      <c r="CJ4" s="28"/>
+      <c r="CK4" s="28"/>
+      <c r="CL4" s="29"/>
+    </row>
+    <row r="5" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="33"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="65" t="s">
+        <v>209</v>
+      </c>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="64" t="s">
+        <v>326</v>
+      </c>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="36"/>
+      <c r="U5" s="36"/>
+      <c r="V5" s="36"/>
+      <c r="W5" s="36"/>
+      <c r="X5" s="36"/>
+      <c r="Y5" s="36"/>
+      <c r="Z5" s="36"/>
+      <c r="AA5" s="36"/>
+      <c r="AB5" s="36"/>
+      <c r="AC5" s="36"/>
+      <c r="AD5" s="36"/>
+      <c r="AE5" s="36"/>
+      <c r="AF5" s="36"/>
+      <c r="AG5" s="36"/>
+      <c r="AH5" s="36"/>
+      <c r="AI5" s="36"/>
+      <c r="AJ5" s="36"/>
+      <c r="AK5" s="36"/>
+      <c r="AL5" s="36"/>
+      <c r="AM5" s="36"/>
+      <c r="AN5" s="36"/>
+      <c r="AO5" s="36"/>
+      <c r="AP5" s="36"/>
+      <c r="AQ5" s="36"/>
+      <c r="AR5" s="36"/>
+      <c r="AS5" s="36"/>
+      <c r="AT5" s="36"/>
+      <c r="AU5" s="36"/>
+      <c r="AV5" s="36"/>
+      <c r="AW5" s="36"/>
+      <c r="AX5" s="36"/>
+      <c r="AY5" s="36"/>
+      <c r="AZ5" s="36"/>
+      <c r="BA5" s="36"/>
+      <c r="BB5" s="36"/>
+      <c r="BC5" s="36"/>
+      <c r="BD5" s="36"/>
+      <c r="BE5" s="36"/>
+      <c r="BF5" s="36"/>
+      <c r="BG5" s="36"/>
+      <c r="BH5" s="36"/>
+      <c r="BI5" s="36"/>
+      <c r="BJ5" s="36"/>
+      <c r="BK5" s="36"/>
+      <c r="BL5" s="36"/>
+      <c r="BM5" s="36"/>
+      <c r="BN5" s="36"/>
+      <c r="BO5" s="36"/>
+      <c r="BP5" s="36"/>
+      <c r="BQ5" s="36"/>
+      <c r="BR5" s="36"/>
+      <c r="BS5" s="36"/>
+      <c r="BT5" s="36"/>
+      <c r="BU5" s="36"/>
+      <c r="BV5" s="36"/>
+      <c r="BW5" s="36"/>
+      <c r="BX5" s="36"/>
+      <c r="BY5" s="36"/>
+      <c r="BZ5" s="36"/>
+      <c r="CA5" s="36"/>
+      <c r="CB5" s="36"/>
+      <c r="CC5" s="36"/>
+      <c r="CD5" s="36"/>
+      <c r="CE5" s="36"/>
+      <c r="CF5" s="36"/>
+      <c r="CG5" s="36"/>
+      <c r="CH5" s="36"/>
+      <c r="CI5" s="36"/>
+      <c r="CJ5" s="36"/>
+      <c r="CK5" s="36"/>
+      <c r="CL5" s="37"/>
+    </row>
+    <row r="6" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1"/>
+      <c r="AG6" s="1"/>
+      <c r="AH6" s="1"/>
+      <c r="AI6" s="1"/>
+      <c r="AJ6" s="1"/>
+      <c r="AK6" s="1"/>
+      <c r="AL6" s="1"/>
+      <c r="AM6" s="1"/>
+      <c r="AN6" s="1"/>
+      <c r="AO6" s="1"/>
+      <c r="AP6" s="1"/>
+      <c r="AQ6" s="1"/>
+      <c r="AR6" s="1"/>
+      <c r="AS6" s="1"/>
+      <c r="AT6" s="1"/>
+      <c r="AU6" s="1"/>
+      <c r="AV6" s="1"/>
+      <c r="AW6" s="1"/>
+      <c r="AX6" s="1"/>
+      <c r="AY6" s="1"/>
+      <c r="AZ6" s="1"/>
+      <c r="BA6" s="1"/>
+      <c r="BB6" s="1"/>
+      <c r="BC6" s="1"/>
+      <c r="BD6" s="1"/>
+      <c r="BE6" s="1"/>
+      <c r="BF6" s="1"/>
+      <c r="BG6" s="1"/>
+      <c r="BH6" s="1"/>
+      <c r="BI6" s="1"/>
+      <c r="BJ6" s="1"/>
+      <c r="BK6" s="1"/>
+      <c r="BL6" s="1"/>
+      <c r="BM6" s="1"/>
+      <c r="BN6" s="1"/>
+      <c r="BO6" s="1"/>
+      <c r="BP6" s="1"/>
+      <c r="BQ6" s="1"/>
+      <c r="BR6" s="1"/>
+      <c r="BS6" s="1"/>
+      <c r="BT6" s="1"/>
+      <c r="BU6" s="1"/>
+      <c r="BV6" s="1"/>
+      <c r="BW6" s="1"/>
+      <c r="BX6" s="1"/>
+      <c r="BY6" s="1"/>
+      <c r="BZ6" s="1"/>
+      <c r="CA6" s="1"/>
+      <c r="CB6" s="1"/>
+      <c r="CC6" s="1"/>
+      <c r="CD6" s="1"/>
+      <c r="CE6" s="1"/>
+      <c r="CF6" s="1"/>
+      <c r="CG6" s="1"/>
+      <c r="CH6" s="1"/>
+      <c r="CI6" s="1"/>
+      <c r="CJ6" s="1"/>
+      <c r="CK6" s="1"/>
+      <c r="CL6" s="1"/>
+    </row>
+    <row r="7" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="56" t="s">
+        <v>213</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="1"/>
+      <c r="AE7" s="1"/>
+      <c r="AF7" s="1"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="1"/>
+      <c r="AI7" s="1"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="1"/>
+      <c r="AL7" s="1"/>
+      <c r="AM7" s="1"/>
+      <c r="AN7" s="1"/>
+      <c r="AO7" s="1"/>
+      <c r="AP7" s="1"/>
+      <c r="AQ7" s="1"/>
+      <c r="AR7" s="1"/>
+      <c r="AS7" s="1"/>
+      <c r="AT7" s="1"/>
+      <c r="AU7" s="1"/>
+      <c r="AV7" s="1"/>
+      <c r="AW7" s="1"/>
+      <c r="AX7" s="1"/>
+      <c r="AY7" s="1"/>
+      <c r="AZ7" s="1"/>
+      <c r="BA7" s="1"/>
+      <c r="BB7" s="1"/>
+      <c r="BC7" s="1"/>
+      <c r="BD7" s="1"/>
+      <c r="BE7" s="1"/>
+      <c r="BF7" s="1"/>
+      <c r="BG7" s="1"/>
+      <c r="BH7" s="1"/>
+      <c r="BI7" s="1"/>
+      <c r="BJ7" s="1"/>
+      <c r="BK7" s="1"/>
+      <c r="BL7" s="1"/>
+      <c r="BM7" s="1"/>
+      <c r="BN7" s="1"/>
+      <c r="BO7" s="1"/>
+      <c r="BP7" s="1"/>
+      <c r="BQ7" s="1"/>
+      <c r="BR7" s="1"/>
+      <c r="BS7" s="1"/>
+      <c r="BT7" s="1"/>
+      <c r="BU7" s="1"/>
+      <c r="BV7" s="1"/>
+      <c r="BW7" s="1"/>
+      <c r="BX7" s="1"/>
+      <c r="BY7" s="1"/>
+      <c r="BZ7" s="1"/>
+      <c r="CA7" s="1"/>
+      <c r="CB7" s="1"/>
+      <c r="CC7" s="1"/>
+      <c r="CD7" s="1"/>
+      <c r="CE7" s="1"/>
+      <c r="CF7" s="1"/>
+      <c r="CG7" s="1"/>
+      <c r="CH7" s="1"/>
+      <c r="CI7" s="1"/>
+      <c r="CJ7" s="1"/>
+      <c r="CK7" s="1"/>
+      <c r="CL7" s="1"/>
+    </row>
+    <row r="8" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="56" t="s">
+        <v>327</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="1"/>
+      <c r="AD8" s="1"/>
+      <c r="AE8" s="1"/>
+      <c r="AF8" s="1"/>
+      <c r="AG8" s="1"/>
+      <c r="AH8" s="1"/>
+      <c r="AI8" s="1"/>
+      <c r="AJ8" s="1"/>
+      <c r="AK8" s="1"/>
+      <c r="AL8" s="1"/>
+      <c r="AM8" s="1"/>
+      <c r="AN8" s="1"/>
+      <c r="AO8" s="1"/>
+      <c r="AP8" s="1"/>
+      <c r="AQ8" s="1"/>
+      <c r="AR8" s="1"/>
+      <c r="AS8" s="1"/>
+      <c r="AT8" s="1"/>
+      <c r="AU8" s="1"/>
+      <c r="AV8" s="1"/>
+      <c r="AW8" s="1"/>
+      <c r="AX8" s="1"/>
+      <c r="AY8" s="1"/>
+      <c r="AZ8" s="1"/>
+      <c r="BA8" s="1"/>
+      <c r="BB8" s="1"/>
+      <c r="BC8" s="1"/>
+      <c r="BD8" s="1"/>
+      <c r="BE8" s="1"/>
+      <c r="BF8" s="1"/>
+      <c r="BG8" s="1"/>
+      <c r="BH8" s="1"/>
+      <c r="BI8" s="1"/>
+      <c r="BJ8" s="1"/>
+      <c r="BK8" s="1"/>
+      <c r="BL8" s="1"/>
+      <c r="BM8" s="1"/>
+      <c r="BN8" s="1"/>
+      <c r="BO8" s="1"/>
+      <c r="BP8" s="1"/>
+      <c r="BQ8" s="1"/>
+      <c r="BR8" s="1"/>
+      <c r="BS8" s="1"/>
+      <c r="BT8" s="1"/>
+      <c r="BU8" s="1"/>
+      <c r="BV8" s="1"/>
+      <c r="BW8" s="1"/>
+      <c r="BX8" s="1"/>
+      <c r="BY8" s="1"/>
+      <c r="BZ8" s="1"/>
+      <c r="CA8" s="1"/>
+      <c r="CB8" s="1"/>
+      <c r="CC8" s="1"/>
+      <c r="CD8" s="1"/>
+      <c r="CE8" s="1"/>
+      <c r="CF8" s="1"/>
+      <c r="CG8" s="1"/>
+      <c r="CH8" s="1"/>
+      <c r="CI8" s="1"/>
+      <c r="CJ8" s="1"/>
+      <c r="CK8" s="1"/>
+      <c r="CL8" s="1"/>
+    </row>
+    <row r="9" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="62" t="s">
+        <v>214</v>
+      </c>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="39"/>
+      <c r="N9" s="39"/>
+      <c r="O9" s="39"/>
+      <c r="P9" s="39"/>
+      <c r="Q9" s="39"/>
+      <c r="R9" s="39"/>
+      <c r="S9" s="62" t="s">
+        <v>215</v>
+      </c>
+      <c r="T9" s="39"/>
+      <c r="U9" s="39"/>
+      <c r="V9" s="39"/>
+      <c r="W9" s="39"/>
+      <c r="X9" s="39"/>
+      <c r="Y9" s="39"/>
+      <c r="Z9" s="39"/>
+      <c r="AA9" s="39"/>
+      <c r="AB9" s="39"/>
+      <c r="AC9" s="39"/>
+      <c r="AD9" s="39"/>
+      <c r="AE9" s="39"/>
+      <c r="AF9" s="39"/>
+      <c r="AG9" s="39"/>
+      <c r="AH9" s="39"/>
+      <c r="AI9" s="39"/>
+      <c r="AJ9" s="39"/>
+      <c r="AK9" s="62" t="s">
+        <v>216</v>
+      </c>
+      <c r="AL9" s="39"/>
+      <c r="AM9" s="39"/>
+      <c r="AN9" s="39"/>
+      <c r="AO9" s="39"/>
+      <c r="AP9" s="39"/>
+      <c r="AQ9" s="39"/>
+      <c r="AR9" s="39"/>
+      <c r="AS9" s="39"/>
+      <c r="AT9" s="39"/>
+      <c r="AU9" s="39"/>
+      <c r="AV9" s="39"/>
+      <c r="AW9" s="39"/>
+      <c r="AX9" s="39"/>
+      <c r="AY9" s="39"/>
+      <c r="AZ9" s="39"/>
+      <c r="BA9" s="39"/>
+      <c r="BB9" s="39"/>
+      <c r="BC9" s="39"/>
+      <c r="BD9" s="39"/>
+      <c r="BE9" s="39"/>
+      <c r="BF9" s="39"/>
+      <c r="BG9" s="39"/>
+      <c r="BH9" s="39"/>
+      <c r="BI9" s="39"/>
+      <c r="BJ9" s="39"/>
+      <c r="BK9" s="39"/>
+      <c r="BL9" s="39"/>
+      <c r="BM9" s="39"/>
+      <c r="BN9" s="39"/>
+      <c r="BO9" s="39"/>
+      <c r="BP9" s="39"/>
+      <c r="BQ9" s="39"/>
+      <c r="BR9" s="39"/>
+      <c r="BS9" s="39"/>
+      <c r="BT9" s="39"/>
+      <c r="BU9" s="39"/>
+      <c r="BV9" s="39"/>
+      <c r="BW9" s="39"/>
+      <c r="BX9" s="39"/>
+      <c r="BY9" s="39"/>
+      <c r="BZ9" s="39"/>
+      <c r="CA9" s="39"/>
+      <c r="CB9" s="39"/>
+      <c r="CC9" s="39"/>
+      <c r="CD9" s="39"/>
+      <c r="CE9" s="39"/>
+      <c r="CF9" s="39"/>
+      <c r="CG9" s="39"/>
+      <c r="CH9" s="39"/>
+      <c r="CI9" s="39"/>
+      <c r="CJ9" s="39"/>
+      <c r="CK9" s="39"/>
+      <c r="CL9" s="49"/>
+    </row>
+    <row r="10" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="60" t="s">
+        <v>301</v>
+      </c>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="24"/>
+      <c r="V10" s="24"/>
+      <c r="W10" s="24"/>
+      <c r="X10" s="24"/>
+      <c r="Y10" s="24"/>
+      <c r="Z10" s="24"/>
+      <c r="AA10" s="24"/>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="24"/>
+      <c r="AD10" s="24"/>
+      <c r="AE10" s="24"/>
+      <c r="AF10" s="24"/>
+      <c r="AG10" s="24"/>
+      <c r="AH10" s="24"/>
+      <c r="AI10" s="24"/>
+      <c r="AJ10" s="24"/>
+      <c r="AK10" s="68" t="s">
+        <v>328</v>
+      </c>
+      <c r="AL10" s="24"/>
+      <c r="AM10" s="24"/>
+      <c r="AN10" s="24"/>
+      <c r="AO10" s="24"/>
+      <c r="AP10" s="24"/>
+      <c r="AQ10" s="24"/>
+      <c r="AR10" s="24"/>
+      <c r="AS10" s="24"/>
+      <c r="AT10" s="24"/>
+      <c r="AU10" s="24"/>
+      <c r="AV10" s="24"/>
+      <c r="AW10" s="24"/>
+      <c r="AX10" s="24"/>
+      <c r="AY10" s="24"/>
+      <c r="AZ10" s="24"/>
+      <c r="BA10" s="24"/>
+      <c r="BB10" s="24"/>
+      <c r="BC10" s="24"/>
+      <c r="BD10" s="24"/>
+      <c r="BE10" s="24"/>
+      <c r="BF10" s="24"/>
+      <c r="BG10" s="24"/>
+      <c r="BH10" s="24"/>
+      <c r="BI10" s="24"/>
+      <c r="BJ10" s="24"/>
+      <c r="BK10" s="24"/>
+      <c r="BL10" s="24"/>
+      <c r="BM10" s="24"/>
+      <c r="BN10" s="24"/>
+      <c r="BO10" s="24"/>
+      <c r="BP10" s="24"/>
+      <c r="BQ10" s="24"/>
+      <c r="BR10" s="24"/>
+      <c r="BS10" s="24"/>
+      <c r="BT10" s="24"/>
+      <c r="BU10" s="24"/>
+      <c r="BV10" s="24"/>
+      <c r="BW10" s="24"/>
+      <c r="BX10" s="24"/>
+      <c r="BY10" s="24"/>
+      <c r="BZ10" s="24"/>
+      <c r="CA10" s="24"/>
+      <c r="CB10" s="24"/>
+      <c r="CC10" s="24"/>
+      <c r="CD10" s="24"/>
+      <c r="CE10" s="24"/>
+      <c r="CF10" s="24"/>
+      <c r="CG10" s="24"/>
+      <c r="CH10" s="24"/>
+      <c r="CI10" s="24"/>
+      <c r="CJ10" s="24"/>
+      <c r="CK10" s="24"/>
+      <c r="CL10" s="32"/>
+    </row>
+    <row r="11" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="62" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="41"/>
+      <c r="N11" s="41"/>
+      <c r="O11" s="41"/>
+      <c r="P11" s="41"/>
+      <c r="Q11" s="63" t="s">
+        <v>323</v>
+      </c>
+      <c r="R11" s="41"/>
+      <c r="S11" s="41"/>
+      <c r="T11" s="41"/>
+      <c r="U11" s="41"/>
+      <c r="V11" s="41"/>
+      <c r="W11" s="41"/>
+      <c r="X11" s="41"/>
+      <c r="Y11" s="41"/>
+      <c r="Z11" s="41"/>
+      <c r="AA11" s="41"/>
+      <c r="AB11" s="41"/>
+      <c r="AC11" s="41"/>
+      <c r="AD11" s="41"/>
+      <c r="AE11" s="41"/>
+      <c r="AF11" s="41"/>
+      <c r="AG11" s="41"/>
+      <c r="AH11" s="41"/>
+      <c r="AI11" s="41"/>
+      <c r="AJ11" s="41"/>
+      <c r="AK11" s="41"/>
+      <c r="AL11" s="41"/>
+      <c r="AM11" s="41"/>
+      <c r="AN11" s="41"/>
+      <c r="AO11" s="41"/>
+      <c r="AP11" s="41"/>
+      <c r="AQ11" s="41"/>
+      <c r="AR11" s="41"/>
+      <c r="AS11" s="41"/>
+      <c r="AT11" s="41"/>
+      <c r="AU11" s="41"/>
+      <c r="AV11" s="41"/>
+      <c r="AW11" s="41"/>
+      <c r="AX11" s="41"/>
+      <c r="AY11" s="41"/>
+      <c r="AZ11" s="41"/>
+      <c r="BA11" s="41"/>
+      <c r="BB11" s="41"/>
+      <c r="BC11" s="41"/>
+      <c r="BD11" s="41"/>
+      <c r="BE11" s="41"/>
+      <c r="BF11" s="41"/>
+      <c r="BG11" s="41"/>
+      <c r="BH11" s="41"/>
+      <c r="BI11" s="41"/>
+      <c r="BJ11" s="41"/>
+      <c r="BK11" s="41"/>
+      <c r="BL11" s="41"/>
+      <c r="BM11" s="41"/>
+      <c r="BN11" s="41"/>
+      <c r="BO11" s="41"/>
+      <c r="BP11" s="41"/>
+      <c r="BQ11" s="41"/>
+      <c r="BR11" s="41"/>
+      <c r="BS11" s="41"/>
+      <c r="BT11" s="41"/>
+      <c r="BU11" s="41"/>
+      <c r="BV11" s="41"/>
+      <c r="BW11" s="41"/>
+      <c r="BX11" s="41"/>
+      <c r="BY11" s="41"/>
+      <c r="BZ11" s="41"/>
+      <c r="CA11" s="41"/>
+      <c r="CB11" s="41"/>
+      <c r="CC11" s="41"/>
+      <c r="CD11" s="41"/>
+      <c r="CE11" s="41"/>
+      <c r="CF11" s="41"/>
+      <c r="CG11" s="41"/>
+      <c r="CH11" s="41"/>
+      <c r="CI11" s="41"/>
+      <c r="CJ11" s="41"/>
+      <c r="CK11" s="41"/>
+      <c r="CL11" s="42"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{177B7FDC-759C-4C00-BE29-1B3AB6C5E4C1}">
+  <dimension ref="A1:CL10"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="90" width="1.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
+      <c r="AQ1" s="1"/>
+      <c r="AR1" s="1"/>
+      <c r="AS1" s="1"/>
+      <c r="AT1" s="1"/>
+      <c r="AU1" s="1"/>
+      <c r="AV1" s="1"/>
+      <c r="AW1" s="1"/>
+      <c r="AX1" s="1"/>
+      <c r="AY1" s="1"/>
+      <c r="AZ1" s="1"/>
+      <c r="BA1" s="1"/>
+      <c r="BB1" s="1"/>
+      <c r="BC1" s="1"/>
+      <c r="BD1" s="1"/>
+      <c r="BE1" s="1"/>
+      <c r="BF1" s="1"/>
+      <c r="BG1" s="1"/>
+      <c r="BH1" s="1"/>
+      <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
+      <c r="BN1" s="1"/>
+      <c r="BO1" s="1"/>
+      <c r="BP1" s="1"/>
+      <c r="BQ1" s="1"/>
+      <c r="BR1" s="1"/>
+      <c r="BS1" s="1"/>
+      <c r="BT1" s="1"/>
+      <c r="BU1" s="1"/>
+      <c r="BV1" s="1"/>
+      <c r="BW1" s="1"/>
+      <c r="BX1" s="1"/>
+      <c r="BY1" s="1"/>
+      <c r="BZ1" s="1"/>
+      <c r="CA1" s="1"/>
+      <c r="CB1" s="1"/>
+      <c r="CC1" s="1"/>
+      <c r="CD1" s="1"/>
+      <c r="CE1" s="1"/>
+      <c r="CF1" s="1"/>
+      <c r="CG1" s="1"/>
+      <c r="CH1" s="1"/>
+      <c r="CI1" s="1"/>
+      <c r="CJ1" s="1"/>
+      <c r="CK1" s="1"/>
+      <c r="CL1" s="1"/>
+    </row>
+    <row r="2" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="56" t="s">
+        <v>273</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="1"/>
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="1"/>
+      <c r="BQ2" s="1"/>
+      <c r="BR2" s="1"/>
+      <c r="BS2" s="1"/>
+      <c r="BT2" s="1"/>
+      <c r="BU2" s="1"/>
+      <c r="BV2" s="1"/>
+      <c r="BW2" s="1"/>
+      <c r="BX2" s="1"/>
+      <c r="BY2" s="1"/>
+      <c r="BZ2" s="1"/>
+      <c r="CA2" s="1"/>
+      <c r="CB2" s="1"/>
+      <c r="CC2" s="1"/>
+      <c r="CD2" s="1"/>
+      <c r="CE2" s="1"/>
+      <c r="CF2" s="1"/>
+      <c r="CG2" s="1"/>
+      <c r="CH2" s="1"/>
+      <c r="CI2" s="1"/>
+      <c r="CJ2" s="1"/>
+      <c r="CK2" s="1"/>
+      <c r="CL2" s="1"/>
+    </row>
+    <row r="3" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="59" t="s">
+        <v>329</v>
+      </c>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="28"/>
+      <c r="X3" s="28"/>
+      <c r="Y3" s="28"/>
+      <c r="Z3" s="28"/>
+      <c r="AA3" s="28"/>
+      <c r="AB3" s="28"/>
+      <c r="AC3" s="28"/>
+      <c r="AD3" s="28"/>
+      <c r="AE3" s="59" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF3" s="59" t="s">
+        <v>330</v>
+      </c>
+      <c r="AG3" s="28"/>
+      <c r="AH3" s="28"/>
+      <c r="AI3" s="28"/>
+      <c r="AJ3" s="28"/>
+      <c r="AK3" s="28"/>
+      <c r="AL3" s="28"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="28"/>
+      <c r="AO3" s="28"/>
+      <c r="AP3" s="28"/>
+      <c r="AQ3" s="28"/>
+      <c r="AR3" s="28"/>
+      <c r="AS3" s="28"/>
+      <c r="AT3" s="28"/>
+      <c r="AU3" s="28"/>
+      <c r="AV3" s="28"/>
+      <c r="AW3" s="28"/>
+      <c r="AX3" s="28"/>
+      <c r="AY3" s="28"/>
+      <c r="AZ3" s="28"/>
+      <c r="BA3" s="28"/>
+      <c r="BB3" s="28"/>
+      <c r="BC3" s="28"/>
+      <c r="BD3" s="28"/>
+      <c r="BE3" s="28"/>
+      <c r="BF3" s="28"/>
+      <c r="BG3" s="28"/>
+      <c r="BH3" s="28"/>
+      <c r="BI3" s="28"/>
+      <c r="BJ3" s="28"/>
+      <c r="BK3" s="28"/>
+      <c r="BL3" s="28"/>
+      <c r="BM3" s="28"/>
+      <c r="BN3" s="28"/>
+      <c r="BO3" s="28"/>
+      <c r="BP3" s="28"/>
+      <c r="BQ3" s="28"/>
+      <c r="BR3" s="28"/>
+      <c r="BS3" s="28"/>
+      <c r="BT3" s="28"/>
+      <c r="BU3" s="28"/>
+      <c r="BV3" s="28"/>
+      <c r="BW3" s="28"/>
+      <c r="BX3" s="28"/>
+      <c r="BY3" s="28"/>
+      <c r="BZ3" s="28"/>
+      <c r="CA3" s="28"/>
+      <c r="CB3" s="28"/>
+      <c r="CC3" s="28"/>
+      <c r="CD3" s="28"/>
+      <c r="CE3" s="28"/>
+      <c r="CF3" s="28"/>
+      <c r="CG3" s="28"/>
+      <c r="CH3" s="28"/>
+      <c r="CI3" s="28"/>
+      <c r="CJ3" s="28"/>
+      <c r="CK3" s="28"/>
+      <c r="CL3" s="29"/>
+    </row>
+    <row r="4" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="62" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="63" t="s">
+        <v>208</v>
+      </c>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="41"/>
+      <c r="Z4" s="41"/>
+      <c r="AA4" s="41"/>
+      <c r="AB4" s="41"/>
+      <c r="AC4" s="41"/>
+      <c r="AD4" s="41"/>
+      <c r="AE4" s="41"/>
+      <c r="AF4" s="41"/>
+      <c r="AG4" s="41"/>
+      <c r="AH4" s="41"/>
+      <c r="AI4" s="41"/>
+      <c r="AJ4" s="41"/>
+      <c r="AK4" s="41"/>
+      <c r="AL4" s="41"/>
+      <c r="AM4" s="41"/>
+      <c r="AN4" s="41"/>
+      <c r="AO4" s="41"/>
+      <c r="AP4" s="41"/>
+      <c r="AQ4" s="41"/>
+      <c r="AR4" s="41"/>
+      <c r="AS4" s="41"/>
+      <c r="AT4" s="41"/>
+      <c r="AU4" s="41"/>
+      <c r="AV4" s="41"/>
+      <c r="AW4" s="41"/>
+      <c r="AX4" s="41"/>
+      <c r="AY4" s="41"/>
+      <c r="AZ4" s="41"/>
+      <c r="BA4" s="41"/>
+      <c r="BB4" s="41"/>
+      <c r="BC4" s="41"/>
+      <c r="BD4" s="41"/>
+      <c r="BE4" s="41"/>
+      <c r="BF4" s="41"/>
+      <c r="BG4" s="41"/>
+      <c r="BH4" s="41"/>
+      <c r="BI4" s="41"/>
+      <c r="BJ4" s="41"/>
+      <c r="BK4" s="41"/>
+      <c r="BL4" s="41"/>
+      <c r="BM4" s="41"/>
+      <c r="BN4" s="41"/>
+      <c r="BO4" s="41"/>
+      <c r="BP4" s="41"/>
+      <c r="BQ4" s="41"/>
+      <c r="BR4" s="41"/>
+      <c r="BS4" s="41"/>
+      <c r="BT4" s="41"/>
+      <c r="BU4" s="41"/>
+      <c r="BV4" s="41"/>
+      <c r="BW4" s="41"/>
+      <c r="BX4" s="41"/>
+      <c r="BY4" s="41"/>
+      <c r="BZ4" s="41"/>
+      <c r="CA4" s="41"/>
+      <c r="CB4" s="41"/>
+      <c r="CC4" s="41"/>
+      <c r="CD4" s="41"/>
+      <c r="CE4" s="41"/>
+      <c r="CF4" s="41"/>
+      <c r="CG4" s="41"/>
+      <c r="CH4" s="41"/>
+      <c r="CI4" s="41"/>
+      <c r="CJ4" s="41"/>
+      <c r="CK4" s="41"/>
+      <c r="CL4" s="42"/>
+    </row>
+    <row r="5" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="1"/>
+      <c r="AG5" s="1"/>
+      <c r="AH5" s="1"/>
+      <c r="AI5" s="1"/>
+      <c r="AJ5" s="1"/>
+      <c r="AK5" s="1"/>
+      <c r="AL5" s="1"/>
+      <c r="AM5" s="1"/>
+      <c r="AN5" s="1"/>
+      <c r="AO5" s="1"/>
+      <c r="AP5" s="1"/>
+      <c r="AQ5" s="1"/>
+      <c r="AR5" s="1"/>
+      <c r="AS5" s="1"/>
+      <c r="AT5" s="1"/>
+      <c r="AU5" s="1"/>
+      <c r="AV5" s="1"/>
+      <c r="AW5" s="1"/>
+      <c r="AX5" s="1"/>
+      <c r="AY5" s="1"/>
+      <c r="AZ5" s="1"/>
+      <c r="BA5" s="1"/>
+      <c r="BB5" s="1"/>
+      <c r="BC5" s="1"/>
+      <c r="BD5" s="1"/>
+      <c r="BE5" s="1"/>
+      <c r="BF5" s="1"/>
+      <c r="BG5" s="1"/>
+      <c r="BH5" s="1"/>
+      <c r="BI5" s="1"/>
+      <c r="BJ5" s="1"/>
+      <c r="BK5" s="1"/>
+      <c r="BL5" s="1"/>
+      <c r="BM5" s="1"/>
+      <c r="BN5" s="1"/>
+      <c r="BO5" s="1"/>
+      <c r="BP5" s="1"/>
+      <c r="BQ5" s="1"/>
+      <c r="BR5" s="1"/>
+      <c r="BS5" s="1"/>
+      <c r="BT5" s="1"/>
+      <c r="BU5" s="1"/>
+      <c r="BV5" s="1"/>
+      <c r="BW5" s="1"/>
+      <c r="BX5" s="1"/>
+      <c r="BY5" s="1"/>
+      <c r="BZ5" s="1"/>
+      <c r="CA5" s="1"/>
+      <c r="CB5" s="1"/>
+      <c r="CC5" s="1"/>
+      <c r="CD5" s="1"/>
+      <c r="CE5" s="1"/>
+      <c r="CF5" s="1"/>
+      <c r="CG5" s="1"/>
+      <c r="CH5" s="1"/>
+      <c r="CI5" s="1"/>
+      <c r="CJ5" s="1"/>
+      <c r="CK5" s="1"/>
+      <c r="CL5" s="1"/>
+    </row>
+    <row r="6" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="56" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1"/>
+      <c r="AG6" s="1"/>
+      <c r="AH6" s="1"/>
+      <c r="AI6" s="1"/>
+      <c r="AJ6" s="1"/>
+      <c r="AK6" s="1"/>
+      <c r="AL6" s="1"/>
+      <c r="AM6" s="1"/>
+      <c r="AN6" s="1"/>
+      <c r="AO6" s="1"/>
+      <c r="AP6" s="1"/>
+      <c r="AQ6" s="1"/>
+      <c r="AR6" s="1"/>
+      <c r="AS6" s="1"/>
+      <c r="AT6" s="1"/>
+      <c r="AU6" s="1"/>
+      <c r="AV6" s="1"/>
+      <c r="AW6" s="1"/>
+      <c r="AX6" s="1"/>
+      <c r="AY6" s="1"/>
+      <c r="AZ6" s="1"/>
+      <c r="BA6" s="1"/>
+      <c r="BB6" s="1"/>
+      <c r="BC6" s="1"/>
+      <c r="BD6" s="1"/>
+      <c r="BE6" s="1"/>
+      <c r="BF6" s="1"/>
+      <c r="BG6" s="1"/>
+      <c r="BH6" s="1"/>
+      <c r="BI6" s="1"/>
+      <c r="BJ6" s="1"/>
+      <c r="BK6" s="1"/>
+      <c r="BL6" s="1"/>
+      <c r="BM6" s="1"/>
+      <c r="BN6" s="1"/>
+      <c r="BO6" s="1"/>
+      <c r="BP6" s="1"/>
+      <c r="BQ6" s="1"/>
+      <c r="BR6" s="1"/>
+      <c r="BS6" s="1"/>
+      <c r="BT6" s="1"/>
+      <c r="BU6" s="1"/>
+      <c r="BV6" s="1"/>
+      <c r="BW6" s="1"/>
+      <c r="BX6" s="1"/>
+      <c r="BY6" s="1"/>
+      <c r="BZ6" s="1"/>
+      <c r="CA6" s="1"/>
+      <c r="CB6" s="1"/>
+      <c r="CC6" s="1"/>
+      <c r="CD6" s="1"/>
+      <c r="CE6" s="1"/>
+      <c r="CF6" s="1"/>
+      <c r="CG6" s="1"/>
+      <c r="CH6" s="1"/>
+      <c r="CI6" s="1"/>
+      <c r="CJ6" s="1"/>
+      <c r="CK6" s="1"/>
+      <c r="CL6" s="1"/>
+    </row>
+    <row r="7" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="56" t="s">
+        <v>311</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="1"/>
+      <c r="AE7" s="1"/>
+      <c r="AF7" s="1"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="1"/>
+      <c r="AI7" s="1"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="1"/>
+      <c r="AL7" s="1"/>
+      <c r="AM7" s="1"/>
+      <c r="AN7" s="1"/>
+      <c r="AO7" s="1"/>
+      <c r="AP7" s="1"/>
+      <c r="AQ7" s="1"/>
+      <c r="AR7" s="1"/>
+      <c r="AS7" s="1"/>
+      <c r="AT7" s="1"/>
+      <c r="AU7" s="1"/>
+      <c r="AV7" s="1"/>
+      <c r="AW7" s="1"/>
+      <c r="AX7" s="1"/>
+      <c r="AY7" s="1"/>
+      <c r="AZ7" s="1"/>
+      <c r="BA7" s="1"/>
+      <c r="BB7" s="1"/>
+      <c r="BC7" s="1"/>
+      <c r="BD7" s="1"/>
+      <c r="BE7" s="1"/>
+      <c r="BF7" s="1"/>
+      <c r="BG7" s="1"/>
+      <c r="BH7" s="1"/>
+      <c r="BI7" s="1"/>
+      <c r="BJ7" s="1"/>
+      <c r="BK7" s="1"/>
+      <c r="BL7" s="1"/>
+      <c r="BM7" s="1"/>
+      <c r="BN7" s="1"/>
+      <c r="BO7" s="1"/>
+      <c r="BP7" s="1"/>
+      <c r="BQ7" s="1"/>
+      <c r="BR7" s="1"/>
+      <c r="BS7" s="1"/>
+      <c r="BT7" s="1"/>
+      <c r="BU7" s="1"/>
+      <c r="BV7" s="1"/>
+      <c r="BW7" s="1"/>
+      <c r="BX7" s="1"/>
+      <c r="BY7" s="1"/>
+      <c r="BZ7" s="1"/>
+      <c r="CA7" s="1"/>
+      <c r="CB7" s="1"/>
+      <c r="CC7" s="1"/>
+      <c r="CD7" s="1"/>
+      <c r="CE7" s="1"/>
+      <c r="CF7" s="1"/>
+      <c r="CG7" s="1"/>
+      <c r="CH7" s="1"/>
+      <c r="CI7" s="1"/>
+      <c r="CJ7" s="1"/>
+      <c r="CK7" s="1"/>
+      <c r="CL7" s="1"/>
+    </row>
+    <row r="8" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="62" t="s">
+        <v>214</v>
+      </c>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="39"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="39"/>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="39"/>
+      <c r="S8" s="62" t="s">
+        <v>215</v>
+      </c>
+      <c r="T8" s="39"/>
+      <c r="U8" s="39"/>
+      <c r="V8" s="39"/>
+      <c r="W8" s="39"/>
+      <c r="X8" s="39"/>
+      <c r="Y8" s="39"/>
+      <c r="Z8" s="39"/>
+      <c r="AA8" s="39"/>
+      <c r="AB8" s="39"/>
+      <c r="AC8" s="39"/>
+      <c r="AD8" s="39"/>
+      <c r="AE8" s="39"/>
+      <c r="AF8" s="39"/>
+      <c r="AG8" s="39"/>
+      <c r="AH8" s="39"/>
+      <c r="AI8" s="39"/>
+      <c r="AJ8" s="39"/>
+      <c r="AK8" s="62" t="s">
+        <v>216</v>
+      </c>
+      <c r="AL8" s="39"/>
+      <c r="AM8" s="39"/>
+      <c r="AN8" s="39"/>
+      <c r="AO8" s="39"/>
+      <c r="AP8" s="39"/>
+      <c r="AQ8" s="39"/>
+      <c r="AR8" s="39"/>
+      <c r="AS8" s="39"/>
+      <c r="AT8" s="39"/>
+      <c r="AU8" s="39"/>
+      <c r="AV8" s="39"/>
+      <c r="AW8" s="39"/>
+      <c r="AX8" s="39"/>
+      <c r="AY8" s="39"/>
+      <c r="AZ8" s="39"/>
+      <c r="BA8" s="39"/>
+      <c r="BB8" s="39"/>
+      <c r="BC8" s="39"/>
+      <c r="BD8" s="39"/>
+      <c r="BE8" s="39"/>
+      <c r="BF8" s="39"/>
+      <c r="BG8" s="39"/>
+      <c r="BH8" s="39"/>
+      <c r="BI8" s="39"/>
+      <c r="BJ8" s="39"/>
+      <c r="BK8" s="39"/>
+      <c r="BL8" s="39"/>
+      <c r="BM8" s="39"/>
+      <c r="BN8" s="39"/>
+      <c r="BO8" s="39"/>
+      <c r="BP8" s="39"/>
+      <c r="BQ8" s="39"/>
+      <c r="BR8" s="39"/>
+      <c r="BS8" s="39"/>
+      <c r="BT8" s="39"/>
+      <c r="BU8" s="39"/>
+      <c r="BV8" s="39"/>
+      <c r="BW8" s="39"/>
+      <c r="BX8" s="39"/>
+      <c r="BY8" s="39"/>
+      <c r="BZ8" s="39"/>
+      <c r="CA8" s="39"/>
+      <c r="CB8" s="39"/>
+      <c r="CC8" s="39"/>
+      <c r="CD8" s="39"/>
+      <c r="CE8" s="39"/>
+      <c r="CF8" s="39"/>
+      <c r="CG8" s="39"/>
+      <c r="CH8" s="39"/>
+      <c r="CI8" s="39"/>
+      <c r="CJ8" s="39"/>
+      <c r="CK8" s="39"/>
+      <c r="CL8" s="49"/>
+    </row>
+    <row r="9" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="60" t="s">
+        <v>301</v>
+      </c>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="31"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="24"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="24"/>
+      <c r="X9" s="24"/>
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="24"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="24"/>
+      <c r="AD9" s="24"/>
+      <c r="AE9" s="24"/>
+      <c r="AF9" s="24"/>
+      <c r="AG9" s="24"/>
+      <c r="AH9" s="24"/>
+      <c r="AI9" s="24"/>
+      <c r="AJ9" s="24"/>
+      <c r="AK9" s="68" t="s">
+        <v>331</v>
+      </c>
+      <c r="AL9" s="24"/>
+      <c r="AM9" s="24"/>
+      <c r="AN9" s="24"/>
+      <c r="AO9" s="24"/>
+      <c r="AP9" s="24"/>
+      <c r="AQ9" s="24"/>
+      <c r="AR9" s="24"/>
+      <c r="AS9" s="24"/>
+      <c r="AT9" s="24"/>
+      <c r="AU9" s="24"/>
+      <c r="AV9" s="24"/>
+      <c r="AW9" s="24"/>
+      <c r="AX9" s="24"/>
+      <c r="AY9" s="24"/>
+      <c r="AZ9" s="24"/>
+      <c r="BA9" s="24"/>
+      <c r="BB9" s="24"/>
+      <c r="BC9" s="24"/>
+      <c r="BD9" s="24"/>
+      <c r="BE9" s="24"/>
+      <c r="BF9" s="24"/>
+      <c r="BG9" s="24"/>
+      <c r="BH9" s="24"/>
+      <c r="BI9" s="24"/>
+      <c r="BJ9" s="24"/>
+      <c r="BK9" s="24"/>
+      <c r="BL9" s="24"/>
+      <c r="BM9" s="24"/>
+      <c r="BN9" s="24"/>
+      <c r="BO9" s="24"/>
+      <c r="BP9" s="24"/>
+      <c r="BQ9" s="24"/>
+      <c r="BR9" s="24"/>
+      <c r="BS9" s="24"/>
+      <c r="BT9" s="24"/>
+      <c r="BU9" s="24"/>
+      <c r="BV9" s="24"/>
+      <c r="BW9" s="24"/>
+      <c r="BX9" s="24"/>
+      <c r="BY9" s="24"/>
+      <c r="BZ9" s="24"/>
+      <c r="CA9" s="24"/>
+      <c r="CB9" s="24"/>
+      <c r="CC9" s="24"/>
+      <c r="CD9" s="24"/>
+      <c r="CE9" s="24"/>
+      <c r="CF9" s="24"/>
+      <c r="CG9" s="24"/>
+      <c r="CH9" s="24"/>
+      <c r="CI9" s="24"/>
+      <c r="CJ9" s="24"/>
+      <c r="CK9" s="24"/>
+      <c r="CL9" s="32"/>
+    </row>
+    <row r="10" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="62" t="s">
+        <v>113</v>
+      </c>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="41"/>
+      <c r="Q10" s="63" t="s">
+        <v>332</v>
+      </c>
+      <c r="R10" s="41"/>
+      <c r="S10" s="41"/>
+      <c r="T10" s="41"/>
+      <c r="U10" s="41"/>
+      <c r="V10" s="41"/>
+      <c r="W10" s="41"/>
+      <c r="X10" s="41"/>
+      <c r="Y10" s="41"/>
+      <c r="Z10" s="41"/>
+      <c r="AA10" s="41"/>
+      <c r="AB10" s="41"/>
+      <c r="AC10" s="41"/>
+      <c r="AD10" s="41"/>
+      <c r="AE10" s="41"/>
+      <c r="AF10" s="41"/>
+      <c r="AG10" s="41"/>
+      <c r="AH10" s="41"/>
+      <c r="AI10" s="41"/>
+      <c r="AJ10" s="41"/>
+      <c r="AK10" s="41"/>
+      <c r="AL10" s="41"/>
+      <c r="AM10" s="41"/>
+      <c r="AN10" s="41"/>
+      <c r="AO10" s="41"/>
+      <c r="AP10" s="41"/>
+      <c r="AQ10" s="41"/>
+      <c r="AR10" s="41"/>
+      <c r="AS10" s="41"/>
+      <c r="AT10" s="41"/>
+      <c r="AU10" s="41"/>
+      <c r="AV10" s="41"/>
+      <c r="AW10" s="41"/>
+      <c r="AX10" s="41"/>
+      <c r="AY10" s="41"/>
+      <c r="AZ10" s="41"/>
+      <c r="BA10" s="41"/>
+      <c r="BB10" s="41"/>
+      <c r="BC10" s="41"/>
+      <c r="BD10" s="41"/>
+      <c r="BE10" s="41"/>
+      <c r="BF10" s="41"/>
+      <c r="BG10" s="41"/>
+      <c r="BH10" s="41"/>
+      <c r="BI10" s="41"/>
+      <c r="BJ10" s="41"/>
+      <c r="BK10" s="41"/>
+      <c r="BL10" s="41"/>
+      <c r="BM10" s="41"/>
+      <c r="BN10" s="41"/>
+      <c r="BO10" s="41"/>
+      <c r="BP10" s="41"/>
+      <c r="BQ10" s="41"/>
+      <c r="BR10" s="41"/>
+      <c r="BS10" s="41"/>
+      <c r="BT10" s="41"/>
+      <c r="BU10" s="41"/>
+      <c r="BV10" s="41"/>
+      <c r="BW10" s="41"/>
+      <c r="BX10" s="41"/>
+      <c r="BY10" s="41"/>
+      <c r="BZ10" s="41"/>
+      <c r="CA10" s="41"/>
+      <c r="CB10" s="41"/>
+      <c r="CC10" s="41"/>
+      <c r="CD10" s="41"/>
+      <c r="CE10" s="41"/>
+      <c r="CF10" s="41"/>
+      <c r="CG10" s="41"/>
+      <c r="CH10" s="41"/>
+      <c r="CI10" s="41"/>
+      <c r="CJ10" s="41"/>
+      <c r="CK10" s="41"/>
+      <c r="CL10" s="42"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{999AD117-9C89-46B1-8101-80FE48E37FB4}">
+  <dimension ref="A1:CL10"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="90" width="1.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
+      <c r="AQ1" s="1"/>
+      <c r="AR1" s="1"/>
+      <c r="AS1" s="1"/>
+      <c r="AT1" s="1"/>
+      <c r="AU1" s="1"/>
+      <c r="AV1" s="1"/>
+      <c r="AW1" s="1"/>
+      <c r="AX1" s="1"/>
+      <c r="AY1" s="1"/>
+      <c r="AZ1" s="1"/>
+      <c r="BA1" s="1"/>
+      <c r="BB1" s="1"/>
+      <c r="BC1" s="1"/>
+      <c r="BD1" s="1"/>
+      <c r="BE1" s="1"/>
+      <c r="BF1" s="1"/>
+      <c r="BG1" s="1"/>
+      <c r="BH1" s="1"/>
+      <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
+      <c r="BN1" s="1"/>
+      <c r="BO1" s="1"/>
+      <c r="BP1" s="1"/>
+      <c r="BQ1" s="1"/>
+      <c r="BR1" s="1"/>
+      <c r="BS1" s="1"/>
+      <c r="BT1" s="1"/>
+      <c r="BU1" s="1"/>
+      <c r="BV1" s="1"/>
+      <c r="BW1" s="1"/>
+      <c r="BX1" s="1"/>
+      <c r="BY1" s="1"/>
+      <c r="BZ1" s="1"/>
+      <c r="CA1" s="1"/>
+      <c r="CB1" s="1"/>
+      <c r="CC1" s="1"/>
+      <c r="CD1" s="1"/>
+      <c r="CE1" s="1"/>
+      <c r="CF1" s="1"/>
+      <c r="CG1" s="1"/>
+      <c r="CH1" s="1"/>
+      <c r="CI1" s="1"/>
+      <c r="CJ1" s="1"/>
+      <c r="CK1" s="1"/>
+      <c r="CL1" s="1"/>
+    </row>
+    <row r="2" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="56" t="s">
+        <v>333</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="1"/>
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="1"/>
+      <c r="BQ2" s="1"/>
+      <c r="BR2" s="1"/>
+      <c r="BS2" s="1"/>
+      <c r="BT2" s="1"/>
+      <c r="BU2" s="1"/>
+      <c r="BV2" s="1"/>
+      <c r="BW2" s="1"/>
+      <c r="BX2" s="1"/>
+      <c r="BY2" s="1"/>
+      <c r="BZ2" s="1"/>
+      <c r="CA2" s="1"/>
+      <c r="CB2" s="1"/>
+      <c r="CC2" s="1"/>
+      <c r="CD2" s="1"/>
+      <c r="CE2" s="1"/>
+      <c r="CF2" s="1"/>
+      <c r="CG2" s="1"/>
+      <c r="CH2" s="1"/>
+      <c r="CI2" s="1"/>
+      <c r="CJ2" s="1"/>
+      <c r="CK2" s="1"/>
+      <c r="CL2" s="1"/>
+    </row>
+    <row r="3" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="59" t="s">
+        <v>316</v>
+      </c>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="28"/>
+      <c r="X3" s="28"/>
+      <c r="Y3" s="28"/>
+      <c r="Z3" s="28"/>
+      <c r="AA3" s="28"/>
+      <c r="AB3" s="28"/>
+      <c r="AC3" s="28"/>
+      <c r="AD3" s="28"/>
+      <c r="AE3" s="28"/>
+      <c r="AF3" s="28"/>
+      <c r="AG3" s="28"/>
+      <c r="AH3" s="28"/>
+      <c r="AI3" s="28"/>
+      <c r="AJ3" s="28"/>
+      <c r="AK3" s="28"/>
+      <c r="AL3" s="28"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="28"/>
+      <c r="AO3" s="28"/>
+      <c r="AP3" s="28"/>
+      <c r="AQ3" s="28"/>
+      <c r="AR3" s="28"/>
+      <c r="AS3" s="28"/>
+      <c r="AT3" s="28"/>
+      <c r="AU3" s="28"/>
+      <c r="AV3" s="28"/>
+      <c r="AW3" s="28"/>
+      <c r="AX3" s="28"/>
+      <c r="AY3" s="28"/>
+      <c r="AZ3" s="28"/>
+      <c r="BA3" s="28"/>
+      <c r="BB3" s="28"/>
+      <c r="BC3" s="28"/>
+      <c r="BD3" s="28"/>
+      <c r="BE3" s="28"/>
+      <c r="BF3" s="28"/>
+      <c r="BG3" s="28"/>
+      <c r="BH3" s="28"/>
+      <c r="BI3" s="28"/>
+      <c r="BJ3" s="28"/>
+      <c r="BK3" s="28"/>
+      <c r="BL3" s="28"/>
+      <c r="BM3" s="28"/>
+      <c r="BN3" s="28"/>
+      <c r="BO3" s="28"/>
+      <c r="BP3" s="28"/>
+      <c r="BQ3" s="28"/>
+      <c r="BR3" s="28"/>
+      <c r="BS3" s="28"/>
+      <c r="BT3" s="28"/>
+      <c r="BU3" s="28"/>
+      <c r="BV3" s="28"/>
+      <c r="BW3" s="28"/>
+      <c r="BX3" s="28"/>
+      <c r="BY3" s="28"/>
+      <c r="BZ3" s="28"/>
+      <c r="CA3" s="28"/>
+      <c r="CB3" s="28"/>
+      <c r="CC3" s="28"/>
+      <c r="CD3" s="28"/>
+      <c r="CE3" s="28"/>
+      <c r="CF3" s="28"/>
+      <c r="CG3" s="28"/>
+      <c r="CH3" s="28"/>
+      <c r="CI3" s="28"/>
+      <c r="CJ3" s="28"/>
+      <c r="CK3" s="28"/>
+      <c r="CL3" s="29"/>
+    </row>
+    <row r="4" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="62" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="63" t="s">
+        <v>334</v>
+      </c>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="41"/>
+      <c r="Z4" s="41"/>
+      <c r="AA4" s="41"/>
+      <c r="AB4" s="41"/>
+      <c r="AC4" s="41"/>
+      <c r="AD4" s="41"/>
+      <c r="AE4" s="41"/>
+      <c r="AF4" s="41"/>
+      <c r="AG4" s="41"/>
+      <c r="AH4" s="41"/>
+      <c r="AI4" s="41"/>
+      <c r="AJ4" s="41"/>
+      <c r="AK4" s="41"/>
+      <c r="AL4" s="41"/>
+      <c r="AM4" s="41"/>
+      <c r="AN4" s="41"/>
+      <c r="AO4" s="41"/>
+      <c r="AP4" s="41"/>
+      <c r="AQ4" s="41"/>
+      <c r="AR4" s="41"/>
+      <c r="AS4" s="41"/>
+      <c r="AT4" s="41"/>
+      <c r="AU4" s="41"/>
+      <c r="AV4" s="41"/>
+      <c r="AW4" s="41"/>
+      <c r="AX4" s="41"/>
+      <c r="AY4" s="41"/>
+      <c r="AZ4" s="41"/>
+      <c r="BA4" s="41"/>
+      <c r="BB4" s="41"/>
+      <c r="BC4" s="41"/>
+      <c r="BD4" s="41"/>
+      <c r="BE4" s="41"/>
+      <c r="BF4" s="41"/>
+      <c r="BG4" s="41"/>
+      <c r="BH4" s="41"/>
+      <c r="BI4" s="41"/>
+      <c r="BJ4" s="41"/>
+      <c r="BK4" s="41"/>
+      <c r="BL4" s="41"/>
+      <c r="BM4" s="41"/>
+      <c r="BN4" s="41"/>
+      <c r="BO4" s="41"/>
+      <c r="BP4" s="41"/>
+      <c r="BQ4" s="41"/>
+      <c r="BR4" s="41"/>
+      <c r="BS4" s="41"/>
+      <c r="BT4" s="41"/>
+      <c r="BU4" s="41"/>
+      <c r="BV4" s="41"/>
+      <c r="BW4" s="41"/>
+      <c r="BX4" s="41"/>
+      <c r="BY4" s="41"/>
+      <c r="BZ4" s="41"/>
+      <c r="CA4" s="41"/>
+      <c r="CB4" s="41"/>
+      <c r="CC4" s="41"/>
+      <c r="CD4" s="41"/>
+      <c r="CE4" s="41"/>
+      <c r="CF4" s="41"/>
+      <c r="CG4" s="41"/>
+      <c r="CH4" s="41"/>
+      <c r="CI4" s="41"/>
+      <c r="CJ4" s="41"/>
+      <c r="CK4" s="41"/>
+      <c r="CL4" s="42"/>
+    </row>
+    <row r="5" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="1"/>
+      <c r="AG5" s="1"/>
+      <c r="AH5" s="1"/>
+      <c r="AI5" s="1"/>
+      <c r="AJ5" s="1"/>
+      <c r="AK5" s="1"/>
+      <c r="AL5" s="1"/>
+      <c r="AM5" s="1"/>
+      <c r="AN5" s="1"/>
+      <c r="AO5" s="1"/>
+      <c r="AP5" s="1"/>
+      <c r="AQ5" s="1"/>
+      <c r="AR5" s="1"/>
+      <c r="AS5" s="1"/>
+      <c r="AT5" s="1"/>
+      <c r="AU5" s="1"/>
+      <c r="AV5" s="1"/>
+      <c r="AW5" s="1"/>
+      <c r="AX5" s="1"/>
+      <c r="AY5" s="1"/>
+      <c r="AZ5" s="1"/>
+      <c r="BA5" s="1"/>
+      <c r="BB5" s="1"/>
+      <c r="BC5" s="1"/>
+      <c r="BD5" s="1"/>
+      <c r="BE5" s="1"/>
+      <c r="BF5" s="1"/>
+      <c r="BG5" s="1"/>
+      <c r="BH5" s="1"/>
+      <c r="BI5" s="1"/>
+      <c r="BJ5" s="1"/>
+      <c r="BK5" s="1"/>
+      <c r="BL5" s="1"/>
+      <c r="BM5" s="1"/>
+      <c r="BN5" s="1"/>
+      <c r="BO5" s="1"/>
+      <c r="BP5" s="1"/>
+      <c r="BQ5" s="1"/>
+      <c r="BR5" s="1"/>
+      <c r="BS5" s="1"/>
+      <c r="BT5" s="1"/>
+      <c r="BU5" s="1"/>
+      <c r="BV5" s="1"/>
+      <c r="BW5" s="1"/>
+      <c r="BX5" s="1"/>
+      <c r="BY5" s="1"/>
+      <c r="BZ5" s="1"/>
+      <c r="CA5" s="1"/>
+      <c r="CB5" s="1"/>
+      <c r="CC5" s="1"/>
+      <c r="CD5" s="1"/>
+      <c r="CE5" s="1"/>
+      <c r="CF5" s="1"/>
+      <c r="CG5" s="1"/>
+      <c r="CH5" s="1"/>
+      <c r="CI5" s="1"/>
+      <c r="CJ5" s="1"/>
+      <c r="CK5" s="1"/>
+      <c r="CL5" s="1"/>
+    </row>
+    <row r="6" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="56" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1"/>
+      <c r="AG6" s="1"/>
+      <c r="AH6" s="1"/>
+      <c r="AI6" s="1"/>
+      <c r="AJ6" s="1"/>
+      <c r="AK6" s="1"/>
+      <c r="AL6" s="1"/>
+      <c r="AM6" s="1"/>
+      <c r="AN6" s="1"/>
+      <c r="AO6" s="1"/>
+      <c r="AP6" s="1"/>
+      <c r="AQ6" s="1"/>
+      <c r="AR6" s="1"/>
+      <c r="AS6" s="1"/>
+      <c r="AT6" s="1"/>
+      <c r="AU6" s="1"/>
+      <c r="AV6" s="1"/>
+      <c r="AW6" s="1"/>
+      <c r="AX6" s="1"/>
+      <c r="AY6" s="1"/>
+      <c r="AZ6" s="1"/>
+      <c r="BA6" s="1"/>
+      <c r="BB6" s="1"/>
+      <c r="BC6" s="1"/>
+      <c r="BD6" s="1"/>
+      <c r="BE6" s="1"/>
+      <c r="BF6" s="1"/>
+      <c r="BG6" s="1"/>
+      <c r="BH6" s="1"/>
+      <c r="BI6" s="1"/>
+      <c r="BJ6" s="1"/>
+      <c r="BK6" s="1"/>
+      <c r="BL6" s="1"/>
+      <c r="BM6" s="1"/>
+      <c r="BN6" s="1"/>
+      <c r="BO6" s="1"/>
+      <c r="BP6" s="1"/>
+      <c r="BQ6" s="1"/>
+      <c r="BR6" s="1"/>
+      <c r="BS6" s="1"/>
+      <c r="BT6" s="1"/>
+      <c r="BU6" s="1"/>
+      <c r="BV6" s="1"/>
+      <c r="BW6" s="1"/>
+      <c r="BX6" s="1"/>
+      <c r="BY6" s="1"/>
+      <c r="BZ6" s="1"/>
+      <c r="CA6" s="1"/>
+      <c r="CB6" s="1"/>
+      <c r="CC6" s="1"/>
+      <c r="CD6" s="1"/>
+      <c r="CE6" s="1"/>
+      <c r="CF6" s="1"/>
+      <c r="CG6" s="1"/>
+      <c r="CH6" s="1"/>
+      <c r="CI6" s="1"/>
+      <c r="CJ6" s="1"/>
+      <c r="CK6" s="1"/>
+      <c r="CL6" s="1"/>
+    </row>
+    <row r="7" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="56" t="s">
+        <v>311</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="1"/>
+      <c r="AE7" s="1"/>
+      <c r="AF7" s="1"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="1"/>
+      <c r="AI7" s="1"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="1"/>
+      <c r="AL7" s="1"/>
+      <c r="AM7" s="1"/>
+      <c r="AN7" s="1"/>
+      <c r="AO7" s="1"/>
+      <c r="AP7" s="1"/>
+      <c r="AQ7" s="1"/>
+      <c r="AR7" s="1"/>
+      <c r="AS7" s="1"/>
+      <c r="AT7" s="1"/>
+      <c r="AU7" s="1"/>
+      <c r="AV7" s="1"/>
+      <c r="AW7" s="1"/>
+      <c r="AX7" s="1"/>
+      <c r="AY7" s="1"/>
+      <c r="AZ7" s="1"/>
+      <c r="BA7" s="1"/>
+      <c r="BB7" s="1"/>
+      <c r="BC7" s="1"/>
+      <c r="BD7" s="1"/>
+      <c r="BE7" s="1"/>
+      <c r="BF7" s="1"/>
+      <c r="BG7" s="1"/>
+      <c r="BH7" s="1"/>
+      <c r="BI7" s="1"/>
+      <c r="BJ7" s="1"/>
+      <c r="BK7" s="1"/>
+      <c r="BL7" s="1"/>
+      <c r="BM7" s="1"/>
+      <c r="BN7" s="1"/>
+      <c r="BO7" s="1"/>
+      <c r="BP7" s="1"/>
+      <c r="BQ7" s="1"/>
+      <c r="BR7" s="1"/>
+      <c r="BS7" s="1"/>
+      <c r="BT7" s="1"/>
+      <c r="BU7" s="1"/>
+      <c r="BV7" s="1"/>
+      <c r="BW7" s="1"/>
+      <c r="BX7" s="1"/>
+      <c r="BY7" s="1"/>
+      <c r="BZ7" s="1"/>
+      <c r="CA7" s="1"/>
+      <c r="CB7" s="1"/>
+      <c r="CC7" s="1"/>
+      <c r="CD7" s="1"/>
+      <c r="CE7" s="1"/>
+      <c r="CF7" s="1"/>
+      <c r="CG7" s="1"/>
+      <c r="CH7" s="1"/>
+      <c r="CI7" s="1"/>
+      <c r="CJ7" s="1"/>
+      <c r="CK7" s="1"/>
+      <c r="CL7" s="1"/>
+    </row>
+    <row r="8" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="62" t="s">
+        <v>214</v>
+      </c>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="39"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="39"/>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="39"/>
+      <c r="S8" s="62" t="s">
+        <v>215</v>
+      </c>
+      <c r="T8" s="39"/>
+      <c r="U8" s="39"/>
+      <c r="V8" s="39"/>
+      <c r="W8" s="39"/>
+      <c r="X8" s="39"/>
+      <c r="Y8" s="39"/>
+      <c r="Z8" s="39"/>
+      <c r="AA8" s="39"/>
+      <c r="AB8" s="39"/>
+      <c r="AC8" s="39"/>
+      <c r="AD8" s="39"/>
+      <c r="AE8" s="39"/>
+      <c r="AF8" s="39"/>
+      <c r="AG8" s="39"/>
+      <c r="AH8" s="39"/>
+      <c r="AI8" s="39"/>
+      <c r="AJ8" s="39"/>
+      <c r="AK8" s="62" t="s">
+        <v>216</v>
+      </c>
+      <c r="AL8" s="39"/>
+      <c r="AM8" s="39"/>
+      <c r="AN8" s="39"/>
+      <c r="AO8" s="39"/>
+      <c r="AP8" s="39"/>
+      <c r="AQ8" s="39"/>
+      <c r="AR8" s="39"/>
+      <c r="AS8" s="39"/>
+      <c r="AT8" s="39"/>
+      <c r="AU8" s="39"/>
+      <c r="AV8" s="39"/>
+      <c r="AW8" s="39"/>
+      <c r="AX8" s="39"/>
+      <c r="AY8" s="39"/>
+      <c r="AZ8" s="39"/>
+      <c r="BA8" s="39"/>
+      <c r="BB8" s="39"/>
+      <c r="BC8" s="39"/>
+      <c r="BD8" s="39"/>
+      <c r="BE8" s="39"/>
+      <c r="BF8" s="39"/>
+      <c r="BG8" s="39"/>
+      <c r="BH8" s="39"/>
+      <c r="BI8" s="39"/>
+      <c r="BJ8" s="39"/>
+      <c r="BK8" s="39"/>
+      <c r="BL8" s="39"/>
+      <c r="BM8" s="39"/>
+      <c r="BN8" s="39"/>
+      <c r="BO8" s="39"/>
+      <c r="BP8" s="39"/>
+      <c r="BQ8" s="39"/>
+      <c r="BR8" s="39"/>
+      <c r="BS8" s="39"/>
+      <c r="BT8" s="39"/>
+      <c r="BU8" s="39"/>
+      <c r="BV8" s="39"/>
+      <c r="BW8" s="39"/>
+      <c r="BX8" s="39"/>
+      <c r="BY8" s="39"/>
+      <c r="BZ8" s="39"/>
+      <c r="CA8" s="39"/>
+      <c r="CB8" s="39"/>
+      <c r="CC8" s="39"/>
+      <c r="CD8" s="39"/>
+      <c r="CE8" s="39"/>
+      <c r="CF8" s="39"/>
+      <c r="CG8" s="39"/>
+      <c r="CH8" s="39"/>
+      <c r="CI8" s="39"/>
+      <c r="CJ8" s="39"/>
+      <c r="CK8" s="39"/>
+      <c r="CL8" s="49"/>
+    </row>
+    <row r="9" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="60" t="s">
+        <v>301</v>
+      </c>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="31"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="24"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="24"/>
+      <c r="X9" s="24"/>
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="24"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="24"/>
+      <c r="AD9" s="24"/>
+      <c r="AE9" s="24"/>
+      <c r="AF9" s="24"/>
+      <c r="AG9" s="24"/>
+      <c r="AH9" s="24"/>
+      <c r="AI9" s="24"/>
+      <c r="AJ9" s="24"/>
+      <c r="AK9" s="68" t="s">
+        <v>335</v>
+      </c>
+      <c r="AL9" s="24"/>
+      <c r="AM9" s="24"/>
+      <c r="AN9" s="24"/>
+      <c r="AO9" s="24"/>
+      <c r="AP9" s="24"/>
+      <c r="AQ9" s="24"/>
+      <c r="AR9" s="24"/>
+      <c r="AS9" s="24"/>
+      <c r="AT9" s="24"/>
+      <c r="AU9" s="24"/>
+      <c r="AV9" s="24"/>
+      <c r="AW9" s="24"/>
+      <c r="AX9" s="24"/>
+      <c r="AY9" s="24"/>
+      <c r="AZ9" s="24"/>
+      <c r="BA9" s="24"/>
+      <c r="BB9" s="24"/>
+      <c r="BC9" s="24"/>
+      <c r="BD9" s="24"/>
+      <c r="BE9" s="24"/>
+      <c r="BF9" s="24"/>
+      <c r="BG9" s="24"/>
+      <c r="BH9" s="24"/>
+      <c r="BI9" s="24"/>
+      <c r="BJ9" s="24"/>
+      <c r="BK9" s="24"/>
+      <c r="BL9" s="24"/>
+      <c r="BM9" s="24"/>
+      <c r="BN9" s="24"/>
+      <c r="BO9" s="24"/>
+      <c r="BP9" s="24"/>
+      <c r="BQ9" s="24"/>
+      <c r="BR9" s="24"/>
+      <c r="BS9" s="24"/>
+      <c r="BT9" s="24"/>
+      <c r="BU9" s="24"/>
+      <c r="BV9" s="24"/>
+      <c r="BW9" s="24"/>
+      <c r="BX9" s="24"/>
+      <c r="BY9" s="24"/>
+      <c r="BZ9" s="24"/>
+      <c r="CA9" s="24"/>
+      <c r="CB9" s="24"/>
+      <c r="CC9" s="24"/>
+      <c r="CD9" s="24"/>
+      <c r="CE9" s="24"/>
+      <c r="CF9" s="24"/>
+      <c r="CG9" s="24"/>
+      <c r="CH9" s="24"/>
+      <c r="CI9" s="24"/>
+      <c r="CJ9" s="24"/>
+      <c r="CK9" s="24"/>
+      <c r="CL9" s="32"/>
+    </row>
+    <row r="10" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="62" t="s">
+        <v>113</v>
+      </c>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="41"/>
+      <c r="Q10" s="63" t="s">
+        <v>336</v>
+      </c>
+      <c r="R10" s="41"/>
+      <c r="S10" s="41"/>
+      <c r="T10" s="41"/>
+      <c r="U10" s="41"/>
+      <c r="V10" s="41"/>
+      <c r="W10" s="41"/>
+      <c r="X10" s="41"/>
+      <c r="Y10" s="41"/>
+      <c r="Z10" s="41"/>
+      <c r="AA10" s="41"/>
+      <c r="AB10" s="41"/>
+      <c r="AC10" s="41"/>
+      <c r="AD10" s="41"/>
+      <c r="AE10" s="41"/>
+      <c r="AF10" s="41"/>
+      <c r="AG10" s="41"/>
+      <c r="AH10" s="41"/>
+      <c r="AI10" s="41"/>
+      <c r="AJ10" s="41"/>
+      <c r="AK10" s="41"/>
+      <c r="AL10" s="41"/>
+      <c r="AM10" s="41"/>
+      <c r="AN10" s="41"/>
+      <c r="AO10" s="41"/>
+      <c r="AP10" s="41"/>
+      <c r="AQ10" s="41"/>
+      <c r="AR10" s="41"/>
+      <c r="AS10" s="41"/>
+      <c r="AT10" s="41"/>
+      <c r="AU10" s="41"/>
+      <c r="AV10" s="41"/>
+      <c r="AW10" s="41"/>
+      <c r="AX10" s="41"/>
+      <c r="AY10" s="41"/>
+      <c r="AZ10" s="41"/>
+      <c r="BA10" s="41"/>
+      <c r="BB10" s="41"/>
+      <c r="BC10" s="41"/>
+      <c r="BD10" s="41"/>
+      <c r="BE10" s="41"/>
+      <c r="BF10" s="41"/>
+      <c r="BG10" s="41"/>
+      <c r="BH10" s="41"/>
+      <c r="BI10" s="41"/>
+      <c r="BJ10" s="41"/>
+      <c r="BK10" s="41"/>
+      <c r="BL10" s="41"/>
+      <c r="BM10" s="41"/>
+      <c r="BN10" s="41"/>
+      <c r="BO10" s="41"/>
+      <c r="BP10" s="41"/>
+      <c r="BQ10" s="41"/>
+      <c r="BR10" s="41"/>
+      <c r="BS10" s="41"/>
+      <c r="BT10" s="41"/>
+      <c r="BU10" s="41"/>
+      <c r="BV10" s="41"/>
+      <c r="BW10" s="41"/>
+      <c r="BX10" s="41"/>
+      <c r="BY10" s="41"/>
+      <c r="BZ10" s="41"/>
+      <c r="CA10" s="41"/>
+      <c r="CB10" s="41"/>
+      <c r="CC10" s="41"/>
+      <c r="CD10" s="41"/>
+      <c r="CE10" s="41"/>
+      <c r="CF10" s="41"/>
+      <c r="CG10" s="41"/>
+      <c r="CH10" s="41"/>
+      <c r="CI10" s="41"/>
+      <c r="CJ10" s="41"/>
+      <c r="CK10" s="41"/>
+      <c r="CL10" s="42"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF9898D0-97E7-4BA1-9234-259483827CA2}">
   <sheetPr codeName="Sheet1"/>

--- a/tests/SqlAnalysisFormatter.OutputExpectations.xlsx
+++ b/tests/SqlAnalysisFormatter.OutputExpectations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Macro\SqlAnalyzerFormatter-feature\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E5C72A-2503-4A5D-82D1-23E55461E8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C06EDD-BFC2-4AE0-978A-2B3EB4587545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="63" activeTab="69" xr2:uid="{41A826B0-B2A2-4DC8-9B04-8EFBE807DC37}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="67" activeTab="73" xr2:uid="{41A826B0-B2A2-4DC8-9B04-8EFBE807DC37}"/>
   </bookViews>
   <sheets>
     <sheet name="SEL-064" sheetId="66" r:id="rId1"/>
@@ -83,6 +83,11 @@
     <sheet name="SEL-068" sheetId="71" r:id="rId68"/>
     <sheet name="SEL-069" sheetId="72" r:id="rId69"/>
     <sheet name="SEL-070" sheetId="73" r:id="rId70"/>
+    <sheet name="SEL-071" sheetId="74" r:id="rId71"/>
+    <sheet name="SEL-072" sheetId="75" r:id="rId72"/>
+    <sheet name="SEL-073" sheetId="76" r:id="rId73"/>
+    <sheet name="SEL-075" sheetId="78" r:id="rId74"/>
+    <sheet name="SEL-074" sheetId="77" r:id="rId75"/>
   </sheets>
   <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
@@ -94,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="355">
   <si>
     <t>＜DB入出力項目定義＞</t>
     <rPh sb="3" eb="10">
@@ -1465,6 +1470,33 @@
   <si>
     <t>eligible_flag</t>
   </si>
+  <si>
+    <t>tb1.削除日時 IS NULL</t>
+  </si>
+  <si>
+    <t>AND tb1.有効区分 = 1 → 'ACTIVE'</t>
+  </si>
+  <si>
+    <t>それ以外 → 'INACTIVE'</t>
+  </si>
+  <si>
+    <t>@active = 1 → 'ACTIVE'</t>
+  </si>
+  <si>
+    <t>@all_rows = 1 → 100</t>
+  </si>
+  <si>
+    <t>それ以外 → 10</t>
+  </si>
+  <si>
+    <t>offset (CASE結果) rows fetch next 20 rows only</t>
+  </si>
+  <si>
+    <t>@skip_rows = 1 → 10</t>
+  </si>
+  <si>
+    <t>tb1.状態 = 'ACTIVE' → 1</t>
+  </si>
 </sst>
 </file>
 
@@ -2327,6 +2359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8342C69F-C45D-427C-B3AA-1E8F3561DA3F}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:CL8"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -13185,6 +13218,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7594DDE4-F031-431B-9740-0D95F5F84FA4}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:CL13"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -21267,6 +21301,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C83768B-411E-4F12-B21D-9496B5CFD80D}">
+  <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:CL12"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -27441,6 +27476,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B8EFC88-B32B-464F-B271-9A0BD6A61532}">
+  <sheetPr codeName="Sheet61"/>
   <dimension ref="A1:CL7"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -32999,6 +33035,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A45D62D-68F5-47F4-82BD-406753D82392}">
+  <sheetPr codeName="Sheet62"/>
   <dimension ref="A1:CL24"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -41089,6 +41126,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4E52F0-775C-4BA3-8E6B-04DBE455867D}">
+  <sheetPr codeName="Sheet63"/>
   <dimension ref="A1:CL13"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -44341,6 +44379,7 @@
 
 <file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{125A3CC4-F32F-4AFC-B49F-2EB086F762F7}">
+  <sheetPr codeName="Sheet64"/>
   <dimension ref="A1:CL11"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -45405,6 +45444,7 @@
 
 <file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{177B7FDC-759C-4C00-BE29-1B3AB6C5E4C1}">
+  <sheetPr codeName="Sheet65"/>
   <dimension ref="A1:CL10"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -46377,6 +46417,7 @@
 
 <file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{999AD117-9C89-46B1-8101-80FE48E37FB4}">
+  <sheetPr codeName="Sheet66"/>
   <dimension ref="A1:CL10"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -47345,6 +47386,7 @@
 
 <file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB0D1930-9AB8-4E8B-A69C-E8A464241E29}">
+  <sheetPr codeName="Sheet67"/>
   <dimension ref="A1:CL10"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -48319,6 +48361,7 @@
 
 <file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98123E36-DEC7-4BA3-914F-651666C56468}">
+  <sheetPr codeName="Sheet68"/>
   <dimension ref="A1:CL4"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -48721,6 +48764,7 @@
 
 <file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D2694E-D810-4A8F-9E88-6BF6AE47836A}">
+  <sheetPr codeName="Sheet69"/>
   <dimension ref="A1:CL6"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -50758,6 +50802,7 @@
 
 <file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13E13F0B-BD68-436F-AC4B-0DE79A71FA29}">
+  <sheetPr codeName="Sheet70"/>
   <dimension ref="A1:CL5"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -51243,6 +51288,2584 @@
       <c r="CJ5" s="36"/>
       <c r="CK5" s="36"/>
       <c r="CL5" s="37"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30AB51C2-4CAF-40D2-90C0-05BD312EBAB8}">
+  <sheetPr codeName="Sheet71"/>
+  <dimension ref="A1:CL6"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="90" width="1.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="56" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
+      <c r="AQ1" s="1"/>
+      <c r="AR1" s="1"/>
+      <c r="AS1" s="1"/>
+      <c r="AT1" s="1"/>
+      <c r="AU1" s="1"/>
+      <c r="AV1" s="1"/>
+      <c r="AW1" s="1"/>
+      <c r="AX1" s="1"/>
+      <c r="AY1" s="1"/>
+      <c r="AZ1" s="1"/>
+      <c r="BA1" s="1"/>
+      <c r="BB1" s="1"/>
+      <c r="BC1" s="1"/>
+      <c r="BD1" s="1"/>
+      <c r="BE1" s="1"/>
+      <c r="BF1" s="1"/>
+      <c r="BG1" s="1"/>
+      <c r="BH1" s="1"/>
+      <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
+      <c r="BN1" s="1"/>
+      <c r="BO1" s="1"/>
+      <c r="BP1" s="1"/>
+      <c r="BQ1" s="1"/>
+      <c r="BR1" s="1"/>
+      <c r="BS1" s="1"/>
+      <c r="BT1" s="1"/>
+      <c r="BU1" s="1"/>
+      <c r="BV1" s="1"/>
+      <c r="BW1" s="1"/>
+      <c r="BX1" s="1"/>
+      <c r="BY1" s="1"/>
+      <c r="BZ1" s="1"/>
+      <c r="CA1" s="1"/>
+      <c r="CB1" s="1"/>
+      <c r="CC1" s="1"/>
+      <c r="CD1" s="1"/>
+      <c r="CE1" s="1"/>
+      <c r="CF1" s="1"/>
+      <c r="CG1" s="1"/>
+      <c r="CH1" s="1"/>
+      <c r="CI1" s="1"/>
+      <c r="CJ1" s="1"/>
+      <c r="CK1" s="1"/>
+      <c r="CL1" s="1"/>
+    </row>
+    <row r="2" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="56" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="1"/>
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="1"/>
+      <c r="BQ2" s="1"/>
+      <c r="BR2" s="1"/>
+      <c r="BS2" s="1"/>
+      <c r="BT2" s="1"/>
+      <c r="BU2" s="1"/>
+      <c r="BV2" s="1"/>
+      <c r="BW2" s="1"/>
+      <c r="BX2" s="1"/>
+      <c r="BY2" s="1"/>
+      <c r="BZ2" s="1"/>
+      <c r="CA2" s="1"/>
+      <c r="CB2" s="1"/>
+      <c r="CC2" s="1"/>
+      <c r="CD2" s="1"/>
+      <c r="CE2" s="1"/>
+      <c r="CF2" s="1"/>
+      <c r="CG2" s="1"/>
+      <c r="CH2" s="1"/>
+      <c r="CI2" s="1"/>
+      <c r="CJ2" s="1"/>
+      <c r="CK2" s="1"/>
+      <c r="CL2" s="1"/>
+    </row>
+    <row r="3" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="62" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="62" t="s">
+        <v>215</v>
+      </c>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="39"/>
+      <c r="AI3" s="39"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="62" t="s">
+        <v>216</v>
+      </c>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="39"/>
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="39"/>
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="39"/>
+      <c r="AR3" s="39"/>
+      <c r="AS3" s="39"/>
+      <c r="AT3" s="39"/>
+      <c r="AU3" s="39"/>
+      <c r="AV3" s="39"/>
+      <c r="AW3" s="39"/>
+      <c r="AX3" s="39"/>
+      <c r="AY3" s="39"/>
+      <c r="AZ3" s="39"/>
+      <c r="BA3" s="39"/>
+      <c r="BB3" s="39"/>
+      <c r="BC3" s="39"/>
+      <c r="BD3" s="39"/>
+      <c r="BE3" s="39"/>
+      <c r="BF3" s="39"/>
+      <c r="BG3" s="39"/>
+      <c r="BH3" s="39"/>
+      <c r="BI3" s="39"/>
+      <c r="BJ3" s="39"/>
+      <c r="BK3" s="39"/>
+      <c r="BL3" s="39"/>
+      <c r="BM3" s="39"/>
+      <c r="BN3" s="39"/>
+      <c r="BO3" s="39"/>
+      <c r="BP3" s="39"/>
+      <c r="BQ3" s="39"/>
+      <c r="BR3" s="39"/>
+      <c r="BS3" s="39"/>
+      <c r="BT3" s="39"/>
+      <c r="BU3" s="39"/>
+      <c r="BV3" s="39"/>
+      <c r="BW3" s="39"/>
+      <c r="BX3" s="39"/>
+      <c r="BY3" s="39"/>
+      <c r="BZ3" s="39"/>
+      <c r="CA3" s="39"/>
+      <c r="CB3" s="39"/>
+      <c r="CC3" s="39"/>
+      <c r="CD3" s="39"/>
+      <c r="CE3" s="39"/>
+      <c r="CF3" s="39"/>
+      <c r="CG3" s="39"/>
+      <c r="CH3" s="39"/>
+      <c r="CI3" s="39"/>
+      <c r="CJ3" s="39"/>
+      <c r="CK3" s="39"/>
+      <c r="CL3" s="49"/>
+    </row>
+    <row r="4" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="65" t="s">
+        <v>299</v>
+      </c>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="65" t="s">
+        <v>249</v>
+      </c>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="36"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="36"/>
+      <c r="AE4" s="36"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="36"/>
+      <c r="AH4" s="36"/>
+      <c r="AI4" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ4" s="36"/>
+      <c r="AK4" s="65" t="s">
+        <v>346</v>
+      </c>
+      <c r="AL4" s="36"/>
+      <c r="AM4" s="36"/>
+      <c r="AN4" s="36"/>
+      <c r="AO4" s="36"/>
+      <c r="AP4" s="36"/>
+      <c r="AQ4" s="36"/>
+      <c r="AR4" s="36"/>
+      <c r="AS4" s="36"/>
+      <c r="AT4" s="36"/>
+      <c r="AU4" s="36"/>
+      <c r="AV4" s="36"/>
+      <c r="AW4" s="36"/>
+      <c r="AX4" s="36"/>
+      <c r="AY4" s="36"/>
+      <c r="AZ4" s="36"/>
+      <c r="BA4" s="36"/>
+      <c r="BB4" s="36"/>
+      <c r="BC4" s="36"/>
+      <c r="BD4" s="36"/>
+      <c r="BE4" s="36"/>
+      <c r="BF4" s="36"/>
+      <c r="BG4" s="36"/>
+      <c r="BH4" s="36"/>
+      <c r="BI4" s="36"/>
+      <c r="BJ4" s="36"/>
+      <c r="BK4" s="36"/>
+      <c r="BL4" s="36"/>
+      <c r="BM4" s="36"/>
+      <c r="BN4" s="36"/>
+      <c r="BO4" s="36"/>
+      <c r="BP4" s="36"/>
+      <c r="BQ4" s="36"/>
+      <c r="BR4" s="36"/>
+      <c r="BS4" s="36"/>
+      <c r="BT4" s="36"/>
+      <c r="BU4" s="36"/>
+      <c r="BV4" s="36"/>
+      <c r="BW4" s="36"/>
+      <c r="BX4" s="36"/>
+      <c r="BY4" s="36"/>
+      <c r="BZ4" s="36"/>
+      <c r="CA4" s="36"/>
+      <c r="CB4" s="36"/>
+      <c r="CC4" s="36"/>
+      <c r="CD4" s="36"/>
+      <c r="CE4" s="36"/>
+      <c r="CF4" s="36"/>
+      <c r="CG4" s="36"/>
+      <c r="CH4" s="36"/>
+      <c r="CI4" s="36"/>
+      <c r="CJ4" s="36"/>
+      <c r="CK4" s="36"/>
+      <c r="CL4" s="37"/>
+    </row>
+    <row r="5" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="40"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41"/>
+      <c r="R5" s="41"/>
+      <c r="S5" s="40"/>
+      <c r="T5" s="41"/>
+      <c r="U5" s="41"/>
+      <c r="V5" s="41"/>
+      <c r="W5" s="41"/>
+      <c r="X5" s="41"/>
+      <c r="Y5" s="41"/>
+      <c r="Z5" s="41"/>
+      <c r="AA5" s="41"/>
+      <c r="AB5" s="41"/>
+      <c r="AC5" s="41"/>
+      <c r="AD5" s="41"/>
+      <c r="AE5" s="41"/>
+      <c r="AF5" s="41"/>
+      <c r="AG5" s="41"/>
+      <c r="AH5" s="41"/>
+      <c r="AI5" s="41"/>
+      <c r="AJ5" s="41"/>
+      <c r="AK5" s="43" t="s">
+        <v>347</v>
+      </c>
+      <c r="AL5" s="41"/>
+      <c r="AM5" s="41"/>
+      <c r="AN5" s="41"/>
+      <c r="AO5" s="41"/>
+      <c r="AP5" s="41"/>
+      <c r="AQ5" s="41"/>
+      <c r="AR5" s="41"/>
+      <c r="AS5" s="41"/>
+      <c r="AT5" s="41"/>
+      <c r="AU5" s="41"/>
+      <c r="AV5" s="41"/>
+      <c r="AW5" s="41"/>
+      <c r="AX5" s="41"/>
+      <c r="AY5" s="41"/>
+      <c r="AZ5" s="41"/>
+      <c r="BA5" s="41"/>
+      <c r="BB5" s="41"/>
+      <c r="BC5" s="41"/>
+      <c r="BD5" s="41"/>
+      <c r="BE5" s="41"/>
+      <c r="BF5" s="41"/>
+      <c r="BG5" s="41"/>
+      <c r="BH5" s="41"/>
+      <c r="BI5" s="41"/>
+      <c r="BJ5" s="41"/>
+      <c r="BK5" s="41"/>
+      <c r="BL5" s="41"/>
+      <c r="BM5" s="41"/>
+      <c r="BN5" s="41"/>
+      <c r="BO5" s="41"/>
+      <c r="BP5" s="41"/>
+      <c r="BQ5" s="41"/>
+      <c r="BR5" s="41"/>
+      <c r="BS5" s="41"/>
+      <c r="BT5" s="41"/>
+      <c r="BU5" s="41"/>
+      <c r="BV5" s="41"/>
+      <c r="BW5" s="41"/>
+      <c r="BX5" s="41"/>
+      <c r="BY5" s="41"/>
+      <c r="BZ5" s="41"/>
+      <c r="CA5" s="41"/>
+      <c r="CB5" s="41"/>
+      <c r="CC5" s="41"/>
+      <c r="CD5" s="41"/>
+      <c r="CE5" s="41"/>
+      <c r="CF5" s="41"/>
+      <c r="CG5" s="41"/>
+      <c r="CH5" s="41"/>
+      <c r="CI5" s="41"/>
+      <c r="CJ5" s="41"/>
+      <c r="CK5" s="41"/>
+      <c r="CL5" s="42"/>
+    </row>
+    <row r="6" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="40"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="41"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="41"/>
+      <c r="Z6" s="41"/>
+      <c r="AA6" s="41"/>
+      <c r="AB6" s="41"/>
+      <c r="AC6" s="41"/>
+      <c r="AD6" s="41"/>
+      <c r="AE6" s="41"/>
+      <c r="AF6" s="41"/>
+      <c r="AG6" s="41"/>
+      <c r="AH6" s="41"/>
+      <c r="AI6" s="41"/>
+      <c r="AJ6" s="41"/>
+      <c r="AK6" s="43" t="s">
+        <v>348</v>
+      </c>
+      <c r="AL6" s="41"/>
+      <c r="AM6" s="41"/>
+      <c r="AN6" s="41"/>
+      <c r="AO6" s="41"/>
+      <c r="AP6" s="41"/>
+      <c r="AQ6" s="41"/>
+      <c r="AR6" s="41"/>
+      <c r="AS6" s="41"/>
+      <c r="AT6" s="41"/>
+      <c r="AU6" s="41"/>
+      <c r="AV6" s="41"/>
+      <c r="AW6" s="41"/>
+      <c r="AX6" s="41"/>
+      <c r="AY6" s="41"/>
+      <c r="AZ6" s="41"/>
+      <c r="BA6" s="41"/>
+      <c r="BB6" s="41"/>
+      <c r="BC6" s="41"/>
+      <c r="BD6" s="41"/>
+      <c r="BE6" s="41"/>
+      <c r="BF6" s="41"/>
+      <c r="BG6" s="41"/>
+      <c r="BH6" s="41"/>
+      <c r="BI6" s="41"/>
+      <c r="BJ6" s="41"/>
+      <c r="BK6" s="41"/>
+      <c r="BL6" s="41"/>
+      <c r="BM6" s="41"/>
+      <c r="BN6" s="41"/>
+      <c r="BO6" s="41"/>
+      <c r="BP6" s="41"/>
+      <c r="BQ6" s="41"/>
+      <c r="BR6" s="41"/>
+      <c r="BS6" s="41"/>
+      <c r="BT6" s="41"/>
+      <c r="BU6" s="41"/>
+      <c r="BV6" s="41"/>
+      <c r="BW6" s="41"/>
+      <c r="BX6" s="41"/>
+      <c r="BY6" s="41"/>
+      <c r="BZ6" s="41"/>
+      <c r="CA6" s="41"/>
+      <c r="CB6" s="41"/>
+      <c r="CC6" s="41"/>
+      <c r="CD6" s="41"/>
+      <c r="CE6" s="41"/>
+      <c r="CF6" s="41"/>
+      <c r="CG6" s="41"/>
+      <c r="CH6" s="41"/>
+      <c r="CI6" s="41"/>
+      <c r="CJ6" s="41"/>
+      <c r="CK6" s="41"/>
+      <c r="CL6" s="42"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A2358E7-8911-407D-AA94-1AF2EC7340FC}">
+  <sheetPr codeName="Sheet72"/>
+  <dimension ref="A1:CL5"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="90" width="1.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="56" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
+      <c r="AQ1" s="1"/>
+      <c r="AR1" s="1"/>
+      <c r="AS1" s="1"/>
+      <c r="AT1" s="1"/>
+      <c r="AU1" s="1"/>
+      <c r="AV1" s="1"/>
+      <c r="AW1" s="1"/>
+      <c r="AX1" s="1"/>
+      <c r="AY1" s="1"/>
+      <c r="AZ1" s="1"/>
+      <c r="BA1" s="1"/>
+      <c r="BB1" s="1"/>
+      <c r="BC1" s="1"/>
+      <c r="BD1" s="1"/>
+      <c r="BE1" s="1"/>
+      <c r="BF1" s="1"/>
+      <c r="BG1" s="1"/>
+      <c r="BH1" s="1"/>
+      <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
+      <c r="BN1" s="1"/>
+      <c r="BO1" s="1"/>
+      <c r="BP1" s="1"/>
+      <c r="BQ1" s="1"/>
+      <c r="BR1" s="1"/>
+      <c r="BS1" s="1"/>
+      <c r="BT1" s="1"/>
+      <c r="BU1" s="1"/>
+      <c r="BV1" s="1"/>
+      <c r="BW1" s="1"/>
+      <c r="BX1" s="1"/>
+      <c r="BY1" s="1"/>
+      <c r="BZ1" s="1"/>
+      <c r="CA1" s="1"/>
+      <c r="CB1" s="1"/>
+      <c r="CC1" s="1"/>
+      <c r="CD1" s="1"/>
+      <c r="CE1" s="1"/>
+      <c r="CF1" s="1"/>
+      <c r="CG1" s="1"/>
+      <c r="CH1" s="1"/>
+      <c r="CI1" s="1"/>
+      <c r="CJ1" s="1"/>
+      <c r="CK1" s="1"/>
+      <c r="CL1" s="1"/>
+    </row>
+    <row r="2" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="56" t="s">
+        <v>302</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="1"/>
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="1"/>
+      <c r="BQ2" s="1"/>
+      <c r="BR2" s="1"/>
+      <c r="BS2" s="1"/>
+      <c r="BT2" s="1"/>
+      <c r="BU2" s="1"/>
+      <c r="BV2" s="1"/>
+      <c r="BW2" s="1"/>
+      <c r="BX2" s="1"/>
+      <c r="BY2" s="1"/>
+      <c r="BZ2" s="1"/>
+      <c r="CA2" s="1"/>
+      <c r="CB2" s="1"/>
+      <c r="CC2" s="1"/>
+      <c r="CD2" s="1"/>
+      <c r="CE2" s="1"/>
+      <c r="CF2" s="1"/>
+      <c r="CG2" s="1"/>
+      <c r="CH2" s="1"/>
+      <c r="CI2" s="1"/>
+      <c r="CJ2" s="1"/>
+      <c r="CK2" s="1"/>
+      <c r="CL2" s="1"/>
+    </row>
+    <row r="3" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="62" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="62" t="s">
+        <v>215</v>
+      </c>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="39"/>
+      <c r="AI3" s="39"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="62" t="s">
+        <v>216</v>
+      </c>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="39"/>
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="39"/>
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="39"/>
+      <c r="AR3" s="39"/>
+      <c r="AS3" s="39"/>
+      <c r="AT3" s="39"/>
+      <c r="AU3" s="39"/>
+      <c r="AV3" s="39"/>
+      <c r="AW3" s="39"/>
+      <c r="AX3" s="39"/>
+      <c r="AY3" s="39"/>
+      <c r="AZ3" s="39"/>
+      <c r="BA3" s="39"/>
+      <c r="BB3" s="39"/>
+      <c r="BC3" s="39"/>
+      <c r="BD3" s="39"/>
+      <c r="BE3" s="39"/>
+      <c r="BF3" s="39"/>
+      <c r="BG3" s="39"/>
+      <c r="BH3" s="39"/>
+      <c r="BI3" s="39"/>
+      <c r="BJ3" s="39"/>
+      <c r="BK3" s="39"/>
+      <c r="BL3" s="39"/>
+      <c r="BM3" s="39"/>
+      <c r="BN3" s="39"/>
+      <c r="BO3" s="39"/>
+      <c r="BP3" s="39"/>
+      <c r="BQ3" s="39"/>
+      <c r="BR3" s="39"/>
+      <c r="BS3" s="39"/>
+      <c r="BT3" s="39"/>
+      <c r="BU3" s="39"/>
+      <c r="BV3" s="39"/>
+      <c r="BW3" s="39"/>
+      <c r="BX3" s="39"/>
+      <c r="BY3" s="39"/>
+      <c r="BZ3" s="39"/>
+      <c r="CA3" s="39"/>
+      <c r="CB3" s="39"/>
+      <c r="CC3" s="39"/>
+      <c r="CD3" s="39"/>
+      <c r="CE3" s="39"/>
+      <c r="CF3" s="39"/>
+      <c r="CG3" s="39"/>
+      <c r="CH3" s="39"/>
+      <c r="CI3" s="39"/>
+      <c r="CJ3" s="39"/>
+      <c r="CK3" s="39"/>
+      <c r="CL3" s="49"/>
+    </row>
+    <row r="4" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="65" t="s">
+        <v>299</v>
+      </c>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="65" t="s">
+        <v>249</v>
+      </c>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="36"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="36"/>
+      <c r="AE4" s="36"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="36"/>
+      <c r="AH4" s="36"/>
+      <c r="AI4" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ4" s="36"/>
+      <c r="AK4" s="65" t="s">
+        <v>349</v>
+      </c>
+      <c r="AL4" s="36"/>
+      <c r="AM4" s="36"/>
+      <c r="AN4" s="36"/>
+      <c r="AO4" s="36"/>
+      <c r="AP4" s="36"/>
+      <c r="AQ4" s="36"/>
+      <c r="AR4" s="36"/>
+      <c r="AS4" s="36"/>
+      <c r="AT4" s="36"/>
+      <c r="AU4" s="36"/>
+      <c r="AV4" s="36"/>
+      <c r="AW4" s="36"/>
+      <c r="AX4" s="36"/>
+      <c r="AY4" s="36"/>
+      <c r="AZ4" s="36"/>
+      <c r="BA4" s="36"/>
+      <c r="BB4" s="36"/>
+      <c r="BC4" s="36"/>
+      <c r="BD4" s="36"/>
+      <c r="BE4" s="36"/>
+      <c r="BF4" s="36"/>
+      <c r="BG4" s="36"/>
+      <c r="BH4" s="36"/>
+      <c r="BI4" s="36"/>
+      <c r="BJ4" s="36"/>
+      <c r="BK4" s="36"/>
+      <c r="BL4" s="36"/>
+      <c r="BM4" s="36"/>
+      <c r="BN4" s="36"/>
+      <c r="BO4" s="36"/>
+      <c r="BP4" s="36"/>
+      <c r="BQ4" s="36"/>
+      <c r="BR4" s="36"/>
+      <c r="BS4" s="36"/>
+      <c r="BT4" s="36"/>
+      <c r="BU4" s="36"/>
+      <c r="BV4" s="36"/>
+      <c r="BW4" s="36"/>
+      <c r="BX4" s="36"/>
+      <c r="BY4" s="36"/>
+      <c r="BZ4" s="36"/>
+      <c r="CA4" s="36"/>
+      <c r="CB4" s="36"/>
+      <c r="CC4" s="36"/>
+      <c r="CD4" s="36"/>
+      <c r="CE4" s="36"/>
+      <c r="CF4" s="36"/>
+      <c r="CG4" s="36"/>
+      <c r="CH4" s="36"/>
+      <c r="CI4" s="36"/>
+      <c r="CJ4" s="36"/>
+      <c r="CK4" s="36"/>
+      <c r="CL4" s="37"/>
+    </row>
+    <row r="5" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="40"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41"/>
+      <c r="R5" s="41"/>
+      <c r="S5" s="40"/>
+      <c r="T5" s="41"/>
+      <c r="U5" s="41"/>
+      <c r="V5" s="41"/>
+      <c r="W5" s="41"/>
+      <c r="X5" s="41"/>
+      <c r="Y5" s="41"/>
+      <c r="Z5" s="41"/>
+      <c r="AA5" s="41"/>
+      <c r="AB5" s="41"/>
+      <c r="AC5" s="41"/>
+      <c r="AD5" s="41"/>
+      <c r="AE5" s="41"/>
+      <c r="AF5" s="41"/>
+      <c r="AG5" s="41"/>
+      <c r="AH5" s="41"/>
+      <c r="AI5" s="41"/>
+      <c r="AJ5" s="41"/>
+      <c r="AK5" s="43" t="s">
+        <v>348</v>
+      </c>
+      <c r="AL5" s="41"/>
+      <c r="AM5" s="41"/>
+      <c r="AN5" s="41"/>
+      <c r="AO5" s="41"/>
+      <c r="AP5" s="41"/>
+      <c r="AQ5" s="41"/>
+      <c r="AR5" s="41"/>
+      <c r="AS5" s="41"/>
+      <c r="AT5" s="41"/>
+      <c r="AU5" s="41"/>
+      <c r="AV5" s="41"/>
+      <c r="AW5" s="41"/>
+      <c r="AX5" s="41"/>
+      <c r="AY5" s="41"/>
+      <c r="AZ5" s="41"/>
+      <c r="BA5" s="41"/>
+      <c r="BB5" s="41"/>
+      <c r="BC5" s="41"/>
+      <c r="BD5" s="41"/>
+      <c r="BE5" s="41"/>
+      <c r="BF5" s="41"/>
+      <c r="BG5" s="41"/>
+      <c r="BH5" s="41"/>
+      <c r="BI5" s="41"/>
+      <c r="BJ5" s="41"/>
+      <c r="BK5" s="41"/>
+      <c r="BL5" s="41"/>
+      <c r="BM5" s="41"/>
+      <c r="BN5" s="41"/>
+      <c r="BO5" s="41"/>
+      <c r="BP5" s="41"/>
+      <c r="BQ5" s="41"/>
+      <c r="BR5" s="41"/>
+      <c r="BS5" s="41"/>
+      <c r="BT5" s="41"/>
+      <c r="BU5" s="41"/>
+      <c r="BV5" s="41"/>
+      <c r="BW5" s="41"/>
+      <c r="BX5" s="41"/>
+      <c r="BY5" s="41"/>
+      <c r="BZ5" s="41"/>
+      <c r="CA5" s="41"/>
+      <c r="CB5" s="41"/>
+      <c r="CC5" s="41"/>
+      <c r="CD5" s="41"/>
+      <c r="CE5" s="41"/>
+      <c r="CF5" s="41"/>
+      <c r="CG5" s="41"/>
+      <c r="CH5" s="41"/>
+      <c r="CI5" s="41"/>
+      <c r="CJ5" s="41"/>
+      <c r="CK5" s="41"/>
+      <c r="CL5" s="42"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{956EFD9A-0444-473E-BD83-6FED68498CDD}">
+  <sheetPr codeName="Sheet73"/>
+  <dimension ref="A1:CL5"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="90" width="1.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
+      <c r="AQ1" s="1"/>
+      <c r="AR1" s="1"/>
+      <c r="AS1" s="1"/>
+      <c r="AT1" s="1"/>
+      <c r="AU1" s="1"/>
+      <c r="AV1" s="1"/>
+      <c r="AW1" s="1"/>
+      <c r="AX1" s="1"/>
+      <c r="AY1" s="1"/>
+      <c r="AZ1" s="1"/>
+      <c r="BA1" s="1"/>
+      <c r="BB1" s="1"/>
+      <c r="BC1" s="1"/>
+      <c r="BD1" s="1"/>
+      <c r="BE1" s="1"/>
+      <c r="BF1" s="1"/>
+      <c r="BG1" s="1"/>
+      <c r="BH1" s="1"/>
+      <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
+      <c r="BN1" s="1"/>
+      <c r="BO1" s="1"/>
+      <c r="BP1" s="1"/>
+      <c r="BQ1" s="1"/>
+      <c r="BR1" s="1"/>
+      <c r="BS1" s="1"/>
+      <c r="BT1" s="1"/>
+      <c r="BU1" s="1"/>
+      <c r="BV1" s="1"/>
+      <c r="BW1" s="1"/>
+      <c r="BX1" s="1"/>
+      <c r="BY1" s="1"/>
+      <c r="BZ1" s="1"/>
+      <c r="CA1" s="1"/>
+      <c r="CB1" s="1"/>
+      <c r="CC1" s="1"/>
+      <c r="CD1" s="1"/>
+      <c r="CE1" s="1"/>
+      <c r="CF1" s="1"/>
+      <c r="CG1" s="1"/>
+      <c r="CH1" s="1"/>
+      <c r="CI1" s="1"/>
+      <c r="CJ1" s="1"/>
+      <c r="CK1" s="1"/>
+      <c r="CL1" s="1"/>
+    </row>
+    <row r="2" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="56" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="1"/>
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="1"/>
+      <c r="BQ2" s="1"/>
+      <c r="BR2" s="1"/>
+      <c r="BS2" s="1"/>
+      <c r="BT2" s="1"/>
+      <c r="BU2" s="1"/>
+      <c r="BV2" s="1"/>
+      <c r="BW2" s="1"/>
+      <c r="BX2" s="1"/>
+      <c r="BY2" s="1"/>
+      <c r="BZ2" s="1"/>
+      <c r="CA2" s="1"/>
+      <c r="CB2" s="1"/>
+      <c r="CC2" s="1"/>
+      <c r="CD2" s="1"/>
+      <c r="CE2" s="1"/>
+      <c r="CF2" s="1"/>
+      <c r="CG2" s="1"/>
+      <c r="CH2" s="1"/>
+      <c r="CI2" s="1"/>
+      <c r="CJ2" s="1"/>
+      <c r="CK2" s="1"/>
+      <c r="CL2" s="1"/>
+    </row>
+    <row r="3" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="57" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="58" t="s">
+        <v>249</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="59" t="s">
+        <v>60</v>
+      </c>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="59" t="s">
+        <v>350</v>
+      </c>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="28"/>
+      <c r="X3" s="28"/>
+      <c r="Y3" s="28"/>
+      <c r="Z3" s="28"/>
+      <c r="AA3" s="28"/>
+      <c r="AB3" s="28"/>
+      <c r="AC3" s="28"/>
+      <c r="AD3" s="28"/>
+      <c r="AE3" s="28"/>
+      <c r="AF3" s="28"/>
+      <c r="AG3" s="28"/>
+      <c r="AH3" s="28"/>
+      <c r="AI3" s="28"/>
+      <c r="AJ3" s="28"/>
+      <c r="AK3" s="28"/>
+      <c r="AL3" s="28"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="28"/>
+      <c r="AO3" s="28"/>
+      <c r="AP3" s="28"/>
+      <c r="AQ3" s="28"/>
+      <c r="AR3" s="28"/>
+      <c r="AS3" s="28"/>
+      <c r="AT3" s="28"/>
+      <c r="AU3" s="28"/>
+      <c r="AV3" s="28"/>
+      <c r="AW3" s="28"/>
+      <c r="AX3" s="28"/>
+      <c r="AY3" s="28"/>
+      <c r="AZ3" s="28"/>
+      <c r="BA3" s="28"/>
+      <c r="BB3" s="28"/>
+      <c r="BC3" s="28"/>
+      <c r="BD3" s="28"/>
+      <c r="BE3" s="28"/>
+      <c r="BF3" s="28"/>
+      <c r="BG3" s="28"/>
+      <c r="BH3" s="28"/>
+      <c r="BI3" s="28"/>
+      <c r="BJ3" s="28"/>
+      <c r="BK3" s="28"/>
+      <c r="BL3" s="28"/>
+      <c r="BM3" s="28"/>
+      <c r="BN3" s="28"/>
+      <c r="BO3" s="28"/>
+      <c r="BP3" s="28"/>
+      <c r="BQ3" s="28"/>
+      <c r="BR3" s="28"/>
+      <c r="BS3" s="28"/>
+      <c r="BT3" s="28"/>
+      <c r="BU3" s="28"/>
+      <c r="BV3" s="28"/>
+      <c r="BW3" s="28"/>
+      <c r="BX3" s="28"/>
+      <c r="BY3" s="28"/>
+      <c r="BZ3" s="28"/>
+      <c r="CA3" s="28"/>
+      <c r="CB3" s="28"/>
+      <c r="CC3" s="28"/>
+      <c r="CD3" s="28"/>
+      <c r="CE3" s="28"/>
+      <c r="CF3" s="28"/>
+      <c r="CG3" s="28"/>
+      <c r="CH3" s="28"/>
+      <c r="CI3" s="28"/>
+      <c r="CJ3" s="28"/>
+      <c r="CK3" s="28"/>
+      <c r="CL3" s="29"/>
+    </row>
+    <row r="4" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="30"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="61" t="s">
+        <v>351</v>
+      </c>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="24"/>
+      <c r="V4" s="24"/>
+      <c r="W4" s="24"/>
+      <c r="X4" s="24"/>
+      <c r="Y4" s="24"/>
+      <c r="Z4" s="24"/>
+      <c r="AA4" s="24"/>
+      <c r="AB4" s="24"/>
+      <c r="AC4" s="24"/>
+      <c r="AD4" s="24"/>
+      <c r="AE4" s="24"/>
+      <c r="AF4" s="24"/>
+      <c r="AG4" s="24"/>
+      <c r="AH4" s="24"/>
+      <c r="AI4" s="24"/>
+      <c r="AJ4" s="24"/>
+      <c r="AK4" s="24"/>
+      <c r="AL4" s="24"/>
+      <c r="AM4" s="24"/>
+      <c r="AN4" s="24"/>
+      <c r="AO4" s="24"/>
+      <c r="AP4" s="24"/>
+      <c r="AQ4" s="24"/>
+      <c r="AR4" s="24"/>
+      <c r="AS4" s="24"/>
+      <c r="AT4" s="24"/>
+      <c r="AU4" s="24"/>
+      <c r="AV4" s="24"/>
+      <c r="AW4" s="24"/>
+      <c r="AX4" s="24"/>
+      <c r="AY4" s="24"/>
+      <c r="AZ4" s="24"/>
+      <c r="BA4" s="24"/>
+      <c r="BB4" s="24"/>
+      <c r="BC4" s="24"/>
+      <c r="BD4" s="24"/>
+      <c r="BE4" s="24"/>
+      <c r="BF4" s="24"/>
+      <c r="BG4" s="24"/>
+      <c r="BH4" s="24"/>
+      <c r="BI4" s="24"/>
+      <c r="BJ4" s="24"/>
+      <c r="BK4" s="24"/>
+      <c r="BL4" s="24"/>
+      <c r="BM4" s="24"/>
+      <c r="BN4" s="24"/>
+      <c r="BO4" s="24"/>
+      <c r="BP4" s="24"/>
+      <c r="BQ4" s="24"/>
+      <c r="BR4" s="24"/>
+      <c r="BS4" s="24"/>
+      <c r="BT4" s="24"/>
+      <c r="BU4" s="24"/>
+      <c r="BV4" s="24"/>
+      <c r="BW4" s="24"/>
+      <c r="BX4" s="24"/>
+      <c r="BY4" s="24"/>
+      <c r="BZ4" s="24"/>
+      <c r="CA4" s="24"/>
+      <c r="CB4" s="24"/>
+      <c r="CC4" s="24"/>
+      <c r="CD4" s="24"/>
+      <c r="CE4" s="24"/>
+      <c r="CF4" s="24"/>
+      <c r="CG4" s="24"/>
+      <c r="CH4" s="24"/>
+      <c r="CI4" s="24"/>
+      <c r="CJ4" s="24"/>
+      <c r="CK4" s="24"/>
+      <c r="CL4" s="32"/>
+    </row>
+    <row r="5" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="63" t="s">
+        <v>58</v>
+      </c>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="41"/>
+      <c r="S5" s="41"/>
+      <c r="T5" s="41"/>
+      <c r="U5" s="41"/>
+      <c r="V5" s="41"/>
+      <c r="W5" s="41"/>
+      <c r="X5" s="41"/>
+      <c r="Y5" s="41"/>
+      <c r="Z5" s="41"/>
+      <c r="AA5" s="41"/>
+      <c r="AB5" s="41"/>
+      <c r="AC5" s="41"/>
+      <c r="AD5" s="41"/>
+      <c r="AE5" s="41"/>
+      <c r="AF5" s="41"/>
+      <c r="AG5" s="41"/>
+      <c r="AH5" s="41"/>
+      <c r="AI5" s="41"/>
+      <c r="AJ5" s="41"/>
+      <c r="AK5" s="41"/>
+      <c r="AL5" s="41"/>
+      <c r="AM5" s="41"/>
+      <c r="AN5" s="41"/>
+      <c r="AO5" s="41"/>
+      <c r="AP5" s="41"/>
+      <c r="AQ5" s="41"/>
+      <c r="AR5" s="41"/>
+      <c r="AS5" s="41"/>
+      <c r="AT5" s="41"/>
+      <c r="AU5" s="41"/>
+      <c r="AV5" s="41"/>
+      <c r="AW5" s="41"/>
+      <c r="AX5" s="41"/>
+      <c r="AY5" s="41"/>
+      <c r="AZ5" s="41"/>
+      <c r="BA5" s="41"/>
+      <c r="BB5" s="41"/>
+      <c r="BC5" s="41"/>
+      <c r="BD5" s="41"/>
+      <c r="BE5" s="41"/>
+      <c r="BF5" s="41"/>
+      <c r="BG5" s="41"/>
+      <c r="BH5" s="41"/>
+      <c r="BI5" s="41"/>
+      <c r="BJ5" s="41"/>
+      <c r="BK5" s="41"/>
+      <c r="BL5" s="41"/>
+      <c r="BM5" s="41"/>
+      <c r="BN5" s="41"/>
+      <c r="BO5" s="41"/>
+      <c r="BP5" s="41"/>
+      <c r="BQ5" s="41"/>
+      <c r="BR5" s="41"/>
+      <c r="BS5" s="41"/>
+      <c r="BT5" s="41"/>
+      <c r="BU5" s="41"/>
+      <c r="BV5" s="41"/>
+      <c r="BW5" s="41"/>
+      <c r="BX5" s="41"/>
+      <c r="BY5" s="41"/>
+      <c r="BZ5" s="41"/>
+      <c r="CA5" s="41"/>
+      <c r="CB5" s="41"/>
+      <c r="CC5" s="41"/>
+      <c r="CD5" s="41"/>
+      <c r="CE5" s="41"/>
+      <c r="CF5" s="41"/>
+      <c r="CG5" s="41"/>
+      <c r="CH5" s="41"/>
+      <c r="CI5" s="41"/>
+      <c r="CJ5" s="41"/>
+      <c r="CK5" s="41"/>
+      <c r="CL5" s="42"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55C79228-10C5-406A-9C26-30FF8F9FEFED}">
+  <dimension ref="A1:CL4"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="90" width="1.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
+      <c r="AQ1" s="1"/>
+      <c r="AR1" s="1"/>
+      <c r="AS1" s="1"/>
+      <c r="AT1" s="1"/>
+      <c r="AU1" s="1"/>
+      <c r="AV1" s="1"/>
+      <c r="AW1" s="1"/>
+      <c r="AX1" s="1"/>
+      <c r="AY1" s="1"/>
+      <c r="AZ1" s="1"/>
+      <c r="BA1" s="1"/>
+      <c r="BB1" s="1"/>
+      <c r="BC1" s="1"/>
+      <c r="BD1" s="1"/>
+      <c r="BE1" s="1"/>
+      <c r="BF1" s="1"/>
+      <c r="BG1" s="1"/>
+      <c r="BH1" s="1"/>
+      <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
+      <c r="BN1" s="1"/>
+      <c r="BO1" s="1"/>
+      <c r="BP1" s="1"/>
+      <c r="BQ1" s="1"/>
+      <c r="BR1" s="1"/>
+      <c r="BS1" s="1"/>
+      <c r="BT1" s="1"/>
+      <c r="BU1" s="1"/>
+      <c r="BV1" s="1"/>
+      <c r="BW1" s="1"/>
+      <c r="BX1" s="1"/>
+      <c r="BY1" s="1"/>
+      <c r="BZ1" s="1"/>
+      <c r="CA1" s="1"/>
+      <c r="CB1" s="1"/>
+      <c r="CC1" s="1"/>
+      <c r="CD1" s="1"/>
+      <c r="CE1" s="1"/>
+      <c r="CF1" s="1"/>
+      <c r="CG1" s="1"/>
+      <c r="CH1" s="1"/>
+      <c r="CI1" s="1"/>
+      <c r="CJ1" s="1"/>
+      <c r="CK1" s="1"/>
+      <c r="CL1" s="1"/>
+    </row>
+    <row r="2" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="56" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="1"/>
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="1"/>
+      <c r="BQ2" s="1"/>
+      <c r="BR2" s="1"/>
+      <c r="BS2" s="1"/>
+      <c r="BT2" s="1"/>
+      <c r="BU2" s="1"/>
+      <c r="BV2" s="1"/>
+      <c r="BW2" s="1"/>
+      <c r="BX2" s="1"/>
+      <c r="BY2" s="1"/>
+      <c r="BZ2" s="1"/>
+      <c r="CA2" s="1"/>
+      <c r="CB2" s="1"/>
+      <c r="CC2" s="1"/>
+      <c r="CD2" s="1"/>
+      <c r="CE2" s="1"/>
+      <c r="CF2" s="1"/>
+      <c r="CG2" s="1"/>
+      <c r="CH2" s="1"/>
+      <c r="CI2" s="1"/>
+      <c r="CJ2" s="1"/>
+      <c r="CK2" s="1"/>
+      <c r="CL2" s="1"/>
+    </row>
+    <row r="3" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="59" t="s">
+        <v>249</v>
+      </c>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="28"/>
+      <c r="X3" s="28"/>
+      <c r="Y3" s="28"/>
+      <c r="Z3" s="28"/>
+      <c r="AA3" s="28"/>
+      <c r="AB3" s="28"/>
+      <c r="AC3" s="28"/>
+      <c r="AD3" s="28"/>
+      <c r="AE3" s="59" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF3" s="59" t="s">
+        <v>354</v>
+      </c>
+      <c r="AG3" s="28"/>
+      <c r="AH3" s="28"/>
+      <c r="AI3" s="28"/>
+      <c r="AJ3" s="28"/>
+      <c r="AK3" s="28"/>
+      <c r="AL3" s="28"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="28"/>
+      <c r="AO3" s="28"/>
+      <c r="AP3" s="28"/>
+      <c r="AQ3" s="28"/>
+      <c r="AR3" s="28"/>
+      <c r="AS3" s="28"/>
+      <c r="AT3" s="28"/>
+      <c r="AU3" s="28"/>
+      <c r="AV3" s="28"/>
+      <c r="AW3" s="28"/>
+      <c r="AX3" s="28"/>
+      <c r="AY3" s="28"/>
+      <c r="AZ3" s="28"/>
+      <c r="BA3" s="28"/>
+      <c r="BB3" s="28"/>
+      <c r="BC3" s="28"/>
+      <c r="BD3" s="28"/>
+      <c r="BE3" s="28"/>
+      <c r="BF3" s="28"/>
+      <c r="BG3" s="28"/>
+      <c r="BH3" s="28"/>
+      <c r="BI3" s="28"/>
+      <c r="BJ3" s="28"/>
+      <c r="BK3" s="28"/>
+      <c r="BL3" s="28"/>
+      <c r="BM3" s="28"/>
+      <c r="BN3" s="28"/>
+      <c r="BO3" s="28"/>
+      <c r="BP3" s="28"/>
+      <c r="BQ3" s="28"/>
+      <c r="BR3" s="28"/>
+      <c r="BS3" s="28"/>
+      <c r="BT3" s="28"/>
+      <c r="BU3" s="28"/>
+      <c r="BV3" s="28"/>
+      <c r="BW3" s="28"/>
+      <c r="BX3" s="28"/>
+      <c r="BY3" s="28"/>
+      <c r="BZ3" s="28"/>
+      <c r="CA3" s="28"/>
+      <c r="CB3" s="28"/>
+      <c r="CC3" s="28"/>
+      <c r="CD3" s="28"/>
+      <c r="CE3" s="28"/>
+      <c r="CF3" s="28"/>
+      <c r="CG3" s="28"/>
+      <c r="CH3" s="28"/>
+      <c r="CI3" s="28"/>
+      <c r="CJ3" s="28"/>
+      <c r="CK3" s="28"/>
+      <c r="CL3" s="29"/>
+    </row>
+    <row r="4" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="33"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="36"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="36"/>
+      <c r="AE4" s="36"/>
+      <c r="AF4" s="64" t="s">
+        <v>236</v>
+      </c>
+      <c r="AG4" s="36"/>
+      <c r="AH4" s="36"/>
+      <c r="AI4" s="36"/>
+      <c r="AJ4" s="36"/>
+      <c r="AK4" s="36"/>
+      <c r="AL4" s="36"/>
+      <c r="AM4" s="36"/>
+      <c r="AN4" s="36"/>
+      <c r="AO4" s="36"/>
+      <c r="AP4" s="36"/>
+      <c r="AQ4" s="36"/>
+      <c r="AR4" s="36"/>
+      <c r="AS4" s="36"/>
+      <c r="AT4" s="36"/>
+      <c r="AU4" s="36"/>
+      <c r="AV4" s="36"/>
+      <c r="AW4" s="36"/>
+      <c r="AX4" s="36"/>
+      <c r="AY4" s="36"/>
+      <c r="AZ4" s="36"/>
+      <c r="BA4" s="36"/>
+      <c r="BB4" s="36"/>
+      <c r="BC4" s="36"/>
+      <c r="BD4" s="36"/>
+      <c r="BE4" s="36"/>
+      <c r="BF4" s="36"/>
+      <c r="BG4" s="36"/>
+      <c r="BH4" s="36"/>
+      <c r="BI4" s="36"/>
+      <c r="BJ4" s="36"/>
+      <c r="BK4" s="36"/>
+      <c r="BL4" s="36"/>
+      <c r="BM4" s="36"/>
+      <c r="BN4" s="36"/>
+      <c r="BO4" s="36"/>
+      <c r="BP4" s="36"/>
+      <c r="BQ4" s="36"/>
+      <c r="BR4" s="36"/>
+      <c r="BS4" s="36"/>
+      <c r="BT4" s="36"/>
+      <c r="BU4" s="36"/>
+      <c r="BV4" s="36"/>
+      <c r="BW4" s="36"/>
+      <c r="BX4" s="36"/>
+      <c r="BY4" s="36"/>
+      <c r="BZ4" s="36"/>
+      <c r="CA4" s="36"/>
+      <c r="CB4" s="36"/>
+      <c r="CC4" s="36"/>
+      <c r="CD4" s="36"/>
+      <c r="CE4" s="36"/>
+      <c r="CF4" s="36"/>
+      <c r="CG4" s="36"/>
+      <c r="CH4" s="36"/>
+      <c r="CI4" s="36"/>
+      <c r="CJ4" s="36"/>
+      <c r="CK4" s="36"/>
+      <c r="CL4" s="37"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{274F91F3-4FA3-4162-9351-46CAD6674E97}">
+  <sheetPr codeName="Sheet74"/>
+  <dimension ref="A1:CL6"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="90" width="1.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
+      <c r="AQ1" s="1"/>
+      <c r="AR1" s="1"/>
+      <c r="AS1" s="1"/>
+      <c r="AT1" s="1"/>
+      <c r="AU1" s="1"/>
+      <c r="AV1" s="1"/>
+      <c r="AW1" s="1"/>
+      <c r="AX1" s="1"/>
+      <c r="AY1" s="1"/>
+      <c r="AZ1" s="1"/>
+      <c r="BA1" s="1"/>
+      <c r="BB1" s="1"/>
+      <c r="BC1" s="1"/>
+      <c r="BD1" s="1"/>
+      <c r="BE1" s="1"/>
+      <c r="BF1" s="1"/>
+      <c r="BG1" s="1"/>
+      <c r="BH1" s="1"/>
+      <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
+      <c r="BN1" s="1"/>
+      <c r="BO1" s="1"/>
+      <c r="BP1" s="1"/>
+      <c r="BQ1" s="1"/>
+      <c r="BR1" s="1"/>
+      <c r="BS1" s="1"/>
+      <c r="BT1" s="1"/>
+      <c r="BU1" s="1"/>
+      <c r="BV1" s="1"/>
+      <c r="BW1" s="1"/>
+      <c r="BX1" s="1"/>
+      <c r="BY1" s="1"/>
+      <c r="BZ1" s="1"/>
+      <c r="CA1" s="1"/>
+      <c r="CB1" s="1"/>
+      <c r="CC1" s="1"/>
+      <c r="CD1" s="1"/>
+      <c r="CE1" s="1"/>
+      <c r="CF1" s="1"/>
+      <c r="CG1" s="1"/>
+      <c r="CH1" s="1"/>
+      <c r="CI1" s="1"/>
+      <c r="CJ1" s="1"/>
+      <c r="CK1" s="1"/>
+      <c r="CL1" s="1"/>
+    </row>
+    <row r="2" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="56" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="1"/>
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="1"/>
+      <c r="BQ2" s="1"/>
+      <c r="BR2" s="1"/>
+      <c r="BS2" s="1"/>
+      <c r="BT2" s="1"/>
+      <c r="BU2" s="1"/>
+      <c r="BV2" s="1"/>
+      <c r="BW2" s="1"/>
+      <c r="BX2" s="1"/>
+      <c r="BY2" s="1"/>
+      <c r="BZ2" s="1"/>
+      <c r="CA2" s="1"/>
+      <c r="CB2" s="1"/>
+      <c r="CC2" s="1"/>
+      <c r="CD2" s="1"/>
+      <c r="CE2" s="1"/>
+      <c r="CF2" s="1"/>
+      <c r="CG2" s="1"/>
+      <c r="CH2" s="1"/>
+      <c r="CI2" s="1"/>
+      <c r="CJ2" s="1"/>
+      <c r="CK2" s="1"/>
+      <c r="CL2" s="1"/>
+    </row>
+    <row r="3" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="58" t="s">
+        <v>352</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="59" t="s">
+        <v>60</v>
+      </c>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="59" t="s">
+        <v>353</v>
+      </c>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="28"/>
+      <c r="X3" s="28"/>
+      <c r="Y3" s="28"/>
+      <c r="Z3" s="28"/>
+      <c r="AA3" s="28"/>
+      <c r="AB3" s="28"/>
+      <c r="AC3" s="28"/>
+      <c r="AD3" s="28"/>
+      <c r="AE3" s="28"/>
+      <c r="AF3" s="28"/>
+      <c r="AG3" s="28"/>
+      <c r="AH3" s="28"/>
+      <c r="AI3" s="28"/>
+      <c r="AJ3" s="28"/>
+      <c r="AK3" s="28"/>
+      <c r="AL3" s="28"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="28"/>
+      <c r="AO3" s="28"/>
+      <c r="AP3" s="28"/>
+      <c r="AQ3" s="28"/>
+      <c r="AR3" s="28"/>
+      <c r="AS3" s="28"/>
+      <c r="AT3" s="28"/>
+      <c r="AU3" s="28"/>
+      <c r="AV3" s="28"/>
+      <c r="AW3" s="28"/>
+      <c r="AX3" s="28"/>
+      <c r="AY3" s="28"/>
+      <c r="AZ3" s="28"/>
+      <c r="BA3" s="28"/>
+      <c r="BB3" s="28"/>
+      <c r="BC3" s="28"/>
+      <c r="BD3" s="28"/>
+      <c r="BE3" s="28"/>
+      <c r="BF3" s="28"/>
+      <c r="BG3" s="28"/>
+      <c r="BH3" s="28"/>
+      <c r="BI3" s="28"/>
+      <c r="BJ3" s="28"/>
+      <c r="BK3" s="28"/>
+      <c r="BL3" s="28"/>
+      <c r="BM3" s="28"/>
+      <c r="BN3" s="28"/>
+      <c r="BO3" s="28"/>
+      <c r="BP3" s="28"/>
+      <c r="BQ3" s="28"/>
+      <c r="BR3" s="28"/>
+      <c r="BS3" s="28"/>
+      <c r="BT3" s="28"/>
+      <c r="BU3" s="28"/>
+      <c r="BV3" s="28"/>
+      <c r="BW3" s="28"/>
+      <c r="BX3" s="28"/>
+      <c r="BY3" s="28"/>
+      <c r="BZ3" s="28"/>
+      <c r="CA3" s="28"/>
+      <c r="CB3" s="28"/>
+      <c r="CC3" s="28"/>
+      <c r="CD3" s="28"/>
+      <c r="CE3" s="28"/>
+      <c r="CF3" s="28"/>
+      <c r="CG3" s="28"/>
+      <c r="CH3" s="28"/>
+      <c r="CI3" s="28"/>
+      <c r="CJ3" s="28"/>
+      <c r="CK3" s="28"/>
+      <c r="CL3" s="29"/>
+    </row>
+    <row r="4" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="30"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="61" t="s">
+        <v>236</v>
+      </c>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="24"/>
+      <c r="V4" s="24"/>
+      <c r="W4" s="24"/>
+      <c r="X4" s="24"/>
+      <c r="Y4" s="24"/>
+      <c r="Z4" s="24"/>
+      <c r="AA4" s="24"/>
+      <c r="AB4" s="24"/>
+      <c r="AC4" s="24"/>
+      <c r="AD4" s="24"/>
+      <c r="AE4" s="24"/>
+      <c r="AF4" s="24"/>
+      <c r="AG4" s="24"/>
+      <c r="AH4" s="24"/>
+      <c r="AI4" s="24"/>
+      <c r="AJ4" s="24"/>
+      <c r="AK4" s="24"/>
+      <c r="AL4" s="24"/>
+      <c r="AM4" s="24"/>
+      <c r="AN4" s="24"/>
+      <c r="AO4" s="24"/>
+      <c r="AP4" s="24"/>
+      <c r="AQ4" s="24"/>
+      <c r="AR4" s="24"/>
+      <c r="AS4" s="24"/>
+      <c r="AT4" s="24"/>
+      <c r="AU4" s="24"/>
+      <c r="AV4" s="24"/>
+      <c r="AW4" s="24"/>
+      <c r="AX4" s="24"/>
+      <c r="AY4" s="24"/>
+      <c r="AZ4" s="24"/>
+      <c r="BA4" s="24"/>
+      <c r="BB4" s="24"/>
+      <c r="BC4" s="24"/>
+      <c r="BD4" s="24"/>
+      <c r="BE4" s="24"/>
+      <c r="BF4" s="24"/>
+      <c r="BG4" s="24"/>
+      <c r="BH4" s="24"/>
+      <c r="BI4" s="24"/>
+      <c r="BJ4" s="24"/>
+      <c r="BK4" s="24"/>
+      <c r="BL4" s="24"/>
+      <c r="BM4" s="24"/>
+      <c r="BN4" s="24"/>
+      <c r="BO4" s="24"/>
+      <c r="BP4" s="24"/>
+      <c r="BQ4" s="24"/>
+      <c r="BR4" s="24"/>
+      <c r="BS4" s="24"/>
+      <c r="BT4" s="24"/>
+      <c r="BU4" s="24"/>
+      <c r="BV4" s="24"/>
+      <c r="BW4" s="24"/>
+      <c r="BX4" s="24"/>
+      <c r="BY4" s="24"/>
+      <c r="BZ4" s="24"/>
+      <c r="CA4" s="24"/>
+      <c r="CB4" s="24"/>
+      <c r="CC4" s="24"/>
+      <c r="CD4" s="24"/>
+      <c r="CE4" s="24"/>
+      <c r="CF4" s="24"/>
+      <c r="CG4" s="24"/>
+      <c r="CH4" s="24"/>
+      <c r="CI4" s="24"/>
+      <c r="CJ4" s="24"/>
+      <c r="CK4" s="24"/>
+      <c r="CL4" s="32"/>
+    </row>
+    <row r="5" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="59" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="28"/>
+      <c r="W5" s="28"/>
+      <c r="X5" s="28"/>
+      <c r="Y5" s="28"/>
+      <c r="Z5" s="28"/>
+      <c r="AA5" s="28"/>
+      <c r="AB5" s="28"/>
+      <c r="AC5" s="28"/>
+      <c r="AD5" s="28"/>
+      <c r="AE5" s="28"/>
+      <c r="AF5" s="28"/>
+      <c r="AG5" s="28"/>
+      <c r="AH5" s="28"/>
+      <c r="AI5" s="28"/>
+      <c r="AJ5" s="28"/>
+      <c r="AK5" s="28"/>
+      <c r="AL5" s="28"/>
+      <c r="AM5" s="28"/>
+      <c r="AN5" s="28"/>
+      <c r="AO5" s="28"/>
+      <c r="AP5" s="28"/>
+      <c r="AQ5" s="28"/>
+      <c r="AR5" s="28"/>
+      <c r="AS5" s="28"/>
+      <c r="AT5" s="28"/>
+      <c r="AU5" s="28"/>
+      <c r="AV5" s="28"/>
+      <c r="AW5" s="28"/>
+      <c r="AX5" s="28"/>
+      <c r="AY5" s="28"/>
+      <c r="AZ5" s="28"/>
+      <c r="BA5" s="28"/>
+      <c r="BB5" s="28"/>
+      <c r="BC5" s="28"/>
+      <c r="BD5" s="28"/>
+      <c r="BE5" s="28"/>
+      <c r="BF5" s="28"/>
+      <c r="BG5" s="28"/>
+      <c r="BH5" s="28"/>
+      <c r="BI5" s="28"/>
+      <c r="BJ5" s="28"/>
+      <c r="BK5" s="28"/>
+      <c r="BL5" s="28"/>
+      <c r="BM5" s="28"/>
+      <c r="BN5" s="28"/>
+      <c r="BO5" s="28"/>
+      <c r="BP5" s="28"/>
+      <c r="BQ5" s="28"/>
+      <c r="BR5" s="28"/>
+      <c r="BS5" s="28"/>
+      <c r="BT5" s="28"/>
+      <c r="BU5" s="28"/>
+      <c r="BV5" s="28"/>
+      <c r="BW5" s="28"/>
+      <c r="BX5" s="28"/>
+      <c r="BY5" s="28"/>
+      <c r="BZ5" s="28"/>
+      <c r="CA5" s="28"/>
+      <c r="CB5" s="28"/>
+      <c r="CC5" s="28"/>
+      <c r="CD5" s="28"/>
+      <c r="CE5" s="28"/>
+      <c r="CF5" s="28"/>
+      <c r="CG5" s="28"/>
+      <c r="CH5" s="28"/>
+      <c r="CI5" s="28"/>
+      <c r="CJ5" s="28"/>
+      <c r="CK5" s="28"/>
+      <c r="CL5" s="29"/>
+    </row>
+    <row r="6" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="62" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="63" t="s">
+        <v>58</v>
+      </c>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="41"/>
+      <c r="X6" s="41"/>
+      <c r="Y6" s="41"/>
+      <c r="Z6" s="41"/>
+      <c r="AA6" s="41"/>
+      <c r="AB6" s="41"/>
+      <c r="AC6" s="41"/>
+      <c r="AD6" s="41"/>
+      <c r="AE6" s="41"/>
+      <c r="AF6" s="41"/>
+      <c r="AG6" s="41"/>
+      <c r="AH6" s="41"/>
+      <c r="AI6" s="41"/>
+      <c r="AJ6" s="41"/>
+      <c r="AK6" s="41"/>
+      <c r="AL6" s="41"/>
+      <c r="AM6" s="41"/>
+      <c r="AN6" s="41"/>
+      <c r="AO6" s="41"/>
+      <c r="AP6" s="41"/>
+      <c r="AQ6" s="41"/>
+      <c r="AR6" s="41"/>
+      <c r="AS6" s="41"/>
+      <c r="AT6" s="41"/>
+      <c r="AU6" s="41"/>
+      <c r="AV6" s="41"/>
+      <c r="AW6" s="41"/>
+      <c r="AX6" s="41"/>
+      <c r="AY6" s="41"/>
+      <c r="AZ6" s="41"/>
+      <c r="BA6" s="41"/>
+      <c r="BB6" s="41"/>
+      <c r="BC6" s="41"/>
+      <c r="BD6" s="41"/>
+      <c r="BE6" s="41"/>
+      <c r="BF6" s="41"/>
+      <c r="BG6" s="41"/>
+      <c r="BH6" s="41"/>
+      <c r="BI6" s="41"/>
+      <c r="BJ6" s="41"/>
+      <c r="BK6" s="41"/>
+      <c r="BL6" s="41"/>
+      <c r="BM6" s="41"/>
+      <c r="BN6" s="41"/>
+      <c r="BO6" s="41"/>
+      <c r="BP6" s="41"/>
+      <c r="BQ6" s="41"/>
+      <c r="BR6" s="41"/>
+      <c r="BS6" s="41"/>
+      <c r="BT6" s="41"/>
+      <c r="BU6" s="41"/>
+      <c r="BV6" s="41"/>
+      <c r="BW6" s="41"/>
+      <c r="BX6" s="41"/>
+      <c r="BY6" s="41"/>
+      <c r="BZ6" s="41"/>
+      <c r="CA6" s="41"/>
+      <c r="CB6" s="41"/>
+      <c r="CC6" s="41"/>
+      <c r="CD6" s="41"/>
+      <c r="CE6" s="41"/>
+      <c r="CF6" s="41"/>
+      <c r="CG6" s="41"/>
+      <c r="CH6" s="41"/>
+      <c r="CI6" s="41"/>
+      <c r="CJ6" s="41"/>
+      <c r="CK6" s="41"/>
+      <c r="CL6" s="42"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/tests/SqlAnalysisFormatter.OutputExpectations.xlsx
+++ b/tests/SqlAnalysisFormatter.OutputExpectations.xlsx
@@ -2,81 +2,81 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-001" sheetId="1" r:id="Re3d60d232002441c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-002" sheetId="2" r:id="Reaff004d4fb54bad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-003" sheetId="3" r:id="R8838b10aed8a4616"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-004" sheetId="4" r:id="R31dceb04a79b41d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-005" sheetId="5" r:id="R45a8515e4def4173"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-006" sheetId="6" r:id="R6de82e3aa9e74108"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-007" sheetId="7" r:id="R45efd9e865d14a0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-008" sheetId="8" r:id="Rc51e5a0284ce4359"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-009" sheetId="9" r:id="Rca106a0fa9f04f82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-010" sheetId="10" r:id="R2ef531694d804715"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-011" sheetId="11" r:id="Rd376e3bc62464cdb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-012" sheetId="12" r:id="R11e36c15d7c24576"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-013" sheetId="13" r:id="Rc0840a5829504498"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-014" sheetId="14" r:id="R92491fb6435f4e14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-015" sheetId="15" r:id="R507f6ad758c54f3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-016" sheetId="16" r:id="R3a7422a324b0465a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-017" sheetId="17" r:id="Rbc4b27f61b0c4a63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-018" sheetId="18" r:id="R5b5a4242ebfe46a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-019" sheetId="19" r:id="Rdf26e27e817647df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-020" sheetId="20" r:id="Rf0bf0f6b94ba4768"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-021" sheetId="21" r:id="Radc2a298fb244a93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-022" sheetId="22" r:id="Ra9b02ae62bf94948"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-023" sheetId="23" r:id="R16f20d6d462b45c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-024" sheetId="24" r:id="Rbb003898dba74f8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-025" sheetId="25" r:id="R1a92c8ba899a4a81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-026" sheetId="26" r:id="Ra814fa2a3f8b4b0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-027" sheetId="37" r:id="Reb05a109f9834fb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-028" sheetId="27" r:id="R6b104ccc23564c78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-029" sheetId="28" r:id="R97afb3f8d90c4c41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-030" sheetId="29" r:id="Rf1ab75245c8c4110"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-031" sheetId="30" r:id="R80e2754764a54786"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-032" sheetId="31" r:id="Re4899ecf53d04210"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-033" sheetId="32" r:id="R2d90060736284376"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-034" sheetId="33" r:id="R0c4ebd46480247bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-035" sheetId="34" r:id="R91fc92cb87c74b65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-036" sheetId="35" r:id="R74df7aedc09c4dd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-037" sheetId="36" r:id="Ra0c5f2e3f9d74b6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-038" sheetId="38" r:id="R214c4806c4804a64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-039" sheetId="39" r:id="Raea840452a2a4e95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-040" sheetId="40" r:id="R505193ec7b414332"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-041" sheetId="41" r:id="R976252189c7641a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-042" sheetId="42" r:id="R8cc3e6f82a2e43b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-043" sheetId="43" r:id="Re32586e690aa45e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-044" sheetId="44" r:id="Rda52f2d3a38441ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-045" sheetId="79" r:id="R1f27c28613974eb2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-046" sheetId="46" r:id="Rc3ad41954f084760"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-047" sheetId="47" r:id="R2cf387e2f06d46b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-048" sheetId="52" r:id="R5d432b69f0df476e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-049" sheetId="53" r:id="R2ce1a1c77a3b4206"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-050" sheetId="54" r:id="Re3e536489c3e4549"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-051" sheetId="55" r:id="Rb502b55cdcf64086"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-052" sheetId="56" r:id="R11fd0812c4cd45ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-053" sheetId="57" r:id="R18acae09662e4b65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-054" sheetId="48" r:id="R088b5890b4f34bd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-055" sheetId="49" r:id="Rd7d20d56caa74cff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-056" sheetId="80" r:id="R7eeabb56c43b4b61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-057" sheetId="70" r:id="R07d2e82871dc4335"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-058" sheetId="58" r:id="R1aef3219c29347a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-059" sheetId="81" r:id="Ra2ad9d2e80f24ee2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-060" sheetId="63" r:id="R9295ca66ffc94eb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-061" sheetId="82" r:id="R251969822bfa464a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-062" sheetId="64" r:id="R1d7753a6c8594db0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-063" sheetId="65" r:id="R5dff84819d864e32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-064" sheetId="66" r:id="Rafc64599ef564a3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-065" sheetId="67" r:id="R914316d04df241c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-066" sheetId="68" r:id="R091c0dd69f6a44fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-067" sheetId="69" r:id="R0c1829c8420f493c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-068" sheetId="71" r:id="R622a1dab730948c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-069" sheetId="72" r:id="Rbd1bc953bf6a4a23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-070" sheetId="73" r:id="Rebf606570b6f4575"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-071" sheetId="74" r:id="Rf42a2c2145da41ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-072" sheetId="75" r:id="R1fa9348c73dc40dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-073" sheetId="76" r:id="R672cd6701c8d4dcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-074" sheetId="77" r:id="Rc0f2959263c64354"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-075" sheetId="78" r:id="R6fa511d7a3e44119"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-001" sheetId="1" r:id="Rf686810751fe4d68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-002" sheetId="2" r:id="Ra8011ad2fb864d89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-003" sheetId="3" r:id="Rffd839c4de9649fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-004" sheetId="4" r:id="Rf1d4ae1f86774a6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-005" sheetId="5" r:id="R67a879a598374ee1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-006" sheetId="6" r:id="R856a947654fd47fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-007" sheetId="7" r:id="Rbbe8367cb8e9404e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-008" sheetId="8" r:id="R6a2463e8b88649bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-009" sheetId="9" r:id="Rd6d10fca3cc2413f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-010" sheetId="10" r:id="Rc9577af229544780"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-011" sheetId="11" r:id="R1bad759e45764704"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-012" sheetId="12" r:id="R798648c165074af0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-013" sheetId="13" r:id="R72ed89b42d4d4e9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-014" sheetId="14" r:id="R659aed7c8a65441b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-015" sheetId="15" r:id="R2ffdf17dddf944f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-016" sheetId="16" r:id="R7ce821e416dc45e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-017" sheetId="17" r:id="R316bce1dee824e74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-018" sheetId="18" r:id="R591a234213f64c37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-019" sheetId="19" r:id="R57a9330b0c0f4289"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-020" sheetId="20" r:id="R3991a239326d4630"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-021" sheetId="21" r:id="Rce57e1f3bb4c497e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-022" sheetId="22" r:id="R33b74155f2924354"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-023" sheetId="23" r:id="Ra10fd05be90442ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-024" sheetId="24" r:id="Re4dbdfb9dbd14ec4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-025" sheetId="25" r:id="R043a8422f1794809"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-026" sheetId="26" r:id="R3d6ffc678d4a486b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-027" sheetId="37" r:id="R7a6cd80f98a84f7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-028" sheetId="27" r:id="Rffd96d3bbf7649a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-029" sheetId="28" r:id="Raf1e07e377084a8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-030" sheetId="29" r:id="R7d46c0ee8a414c76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-031" sheetId="30" r:id="Rc8738514743f4a90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-032" sheetId="31" r:id="R8708216bc321499d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-033" sheetId="32" r:id="Rab7130daa005447c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-034" sheetId="33" r:id="R4f1d196ec7a44b7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-035" sheetId="34" r:id="Re99af788f1354b3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-036" sheetId="35" r:id="R406ab449c7c74922"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-037" sheetId="36" r:id="Rcd3f99b5ee4c4565"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-038" sheetId="38" r:id="R410e33190db4407e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-039" sheetId="39" r:id="R4e49618187424b0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-040" sheetId="40" r:id="R76d7dac6ecab4608"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-041" sheetId="41" r:id="Rc3b8501ac0e2472c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-042" sheetId="42" r:id="Rc741462d1047443a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-043" sheetId="43" r:id="R9fad8dd7ed7943b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-044" sheetId="44" r:id="Rd5d531fd49754f94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-045" sheetId="79" r:id="Rc016684d579649dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-046" sheetId="46" r:id="R3add21420b2d4e29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-047" sheetId="47" r:id="Rba84b9c179ad4340"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-048" sheetId="52" r:id="R503eebaf238e482a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-049" sheetId="53" r:id="R509e172818f14cd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-050" sheetId="54" r:id="Raf7f88a22fa446a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-051" sheetId="55" r:id="Rcff2e1bc2fc1472e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-052" sheetId="56" r:id="R4d0c73cb80fd4846"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-053" sheetId="57" r:id="R2a13f7f5e6694a1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-054" sheetId="48" r:id="Rbee5a001ef9e4a7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-055" sheetId="49" r:id="R502f0d51c28941fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-056" sheetId="80" r:id="R54bfd7f31c2445d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-057" sheetId="70" r:id="Rd9440d6dffbd46f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-058" sheetId="58" r:id="R5c7a13eb95194e54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-059" sheetId="81" r:id="R8151e5f210a8495f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-060" sheetId="63" r:id="R84f48c47f8404f35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-061" sheetId="82" r:id="R60f6b69d9f7a495b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-062" sheetId="64" r:id="Rde9348b969dd489b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-063" sheetId="65" r:id="R7610585d4d184198"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-064" sheetId="66" r:id="Re7cfa79e9c4b47c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-065" sheetId="67" r:id="Ra03a08e139fa4f86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-066" sheetId="68" r:id="Rd2d3e69b40c24dd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-067" sheetId="69" r:id="R58200b61814343f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-068" sheetId="71" r:id="R1a81ccfd03df44d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-069" sheetId="72" r:id="Rc8b19ed7e3e54756"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-070" sheetId="73" r:id="R04b675fe77974344"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-071" sheetId="74" r:id="Rce21db7d5f6b47a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-072" sheetId="75" r:id="R98594971f23f4c22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-073" sheetId="76" r:id="Raeee1dbf3f35424b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-074" sheetId="77" r:id="R79dde9fdad034be4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-075" sheetId="78" r:id="R4107ca8b06d94454"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -36146,8 +36146,8 @@
       <x:c r="P21" s="18"/>
       <x:c r="Q21" s="18"/>
       <x:c r="R21" s="18"/>
-      <x:c r="S21" s="20" t="s">
-        <x:v>208</x:v>
+      <x:c r="S21" s="20" t="str">
+        <x:v>tb1.氏名、tb1.メール</x:v>
       </x:c>
       <x:c r="T21" s="18"/>
       <x:c r="U21" s="18"/>
@@ -36166,7 +36166,9 @@
       <x:c r="AH21" s="18"/>
       <x:c r="AI21" s="18"/>
       <x:c r="AJ21" s="18"/>
-      <x:c r="AK21" s="17"/>
+      <x:c r="AK21" s="17" t="str">
+        <x:v>COALESCE(tb1.氏名, tb1.メール)</x:v>
+      </x:c>
       <x:c r="AL21" s="18"/>
       <x:c r="AM21" s="18"/>
       <x:c r="AN21" s="18"/>
@@ -36242,8 +36244,8 @@
       <x:c r="P22" s="18"/>
       <x:c r="Q22" s="18"/>
       <x:c r="R22" s="18"/>
-      <x:c r="S22" s="20" t="s">
-        <x:v>209</x:v>
+      <x:c r="S22" s="20" t="str">
+        <x:v>tb2.注文ID</x:v>
       </x:c>
       <x:c r="T22" s="18"/>
       <x:c r="U22" s="18"/>
@@ -36262,7 +36264,9 @@
       <x:c r="AH22" s="18"/>
       <x:c r="AI22" s="18"/>
       <x:c r="AJ22" s="18"/>
-      <x:c r="AK22" s="17"/>
+      <x:c r="AK22" s="17" t="str">
+        <x:v>COUNT(tb2.注文ID)</x:v>
+      </x:c>
       <x:c r="AL22" s="18"/>
       <x:c r="AM22" s="18"/>
       <x:c r="AN22" s="18"/>
@@ -42494,8 +42498,8 @@
       <x:c r="P24" s="18"/>
       <x:c r="Q24" s="18"/>
       <x:c r="R24" s="18"/>
-      <x:c r="S24" s="20" t="s">
-        <x:v>208</x:v>
+      <x:c r="S24" s="20" t="str">
+        <x:v>tb1.氏名、tb1.メール</x:v>
       </x:c>
       <x:c r="T24" s="18"/>
       <x:c r="U24" s="18"/>
@@ -42514,7 +42518,9 @@
       <x:c r="AH24" s="18"/>
       <x:c r="AI24" s="18"/>
       <x:c r="AJ24" s="18"/>
-      <x:c r="AK24" s="17"/>
+      <x:c r="AK24" s="17" t="str">
+        <x:v>COALESCE(tb1.氏名, tb1.メール)</x:v>
+      </x:c>
       <x:c r="AL24" s="18"/>
       <x:c r="AM24" s="18"/>
       <x:c r="AN24" s="18"/>
@@ -42590,8 +42596,8 @@
       <x:c r="P25" s="18"/>
       <x:c r="Q25" s="18"/>
       <x:c r="R25" s="18"/>
-      <x:c r="S25" s="20" t="s">
-        <x:v>209</x:v>
+      <x:c r="S25" s="20" t="str">
+        <x:v>tb2.注文ID</x:v>
       </x:c>
       <x:c r="T25" s="18"/>
       <x:c r="U25" s="18"/>
@@ -42610,7 +42616,9 @@
       <x:c r="AH25" s="18"/>
       <x:c r="AI25" s="18"/>
       <x:c r="AJ25" s="18"/>
-      <x:c r="AK25" s="17"/>
+      <x:c r="AK25" s="17" t="str">
+        <x:v>COUNT(tb2.注文ID)</x:v>
+      </x:c>
       <x:c r="AL25" s="18"/>
       <x:c r="AM25" s="18"/>
       <x:c r="AN25" s="18"/>

--- a/tests/SqlAnalysisFormatter.OutputExpectations.xlsx
+++ b/tests/SqlAnalysisFormatter.OutputExpectations.xlsx
@@ -2,83 +2,83 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-001" sheetId="1" r:id="R90522b0d9b3046f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-002" sheetId="2" r:id="R2f580149777549a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-003" sheetId="3" r:id="R5a9596d56a294bed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-004" sheetId="4" r:id="R63c32d0dbda2420b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-005" sheetId="5" r:id="R821d4f9bd2fb4104"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-006" sheetId="6" r:id="Reb793db6563f4eb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-007" sheetId="7" r:id="R2f5485cee91f4f92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-008" sheetId="8" r:id="R7ea4b9c4ac8c432a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-009" sheetId="9" r:id="R443b55cf0b0c4891"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-010" sheetId="10" r:id="R1f4b9bbc1c404629"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-011" sheetId="11" r:id="R4487c9fa764847b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-012" sheetId="12" r:id="Rd2e39118cbbc4242"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-013" sheetId="13" r:id="Rbebbc9167cfb4b7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-014" sheetId="14" r:id="R49b03ec6231944ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-015" sheetId="15" r:id="Rbe22d6b94766448d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-016" sheetId="16" r:id="R99b325f2c6614f89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-017" sheetId="17" r:id="R8180eda84f6543d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-018" sheetId="18" r:id="R8c84f33331e74cfd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-019" sheetId="19" r:id="R222bd4dce1114a58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-020" sheetId="20" r:id="R6e8a38f666804bbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-021" sheetId="21" r:id="R914cab2b3baa4132"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-022" sheetId="22" r:id="Readea579412b4f7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-023" sheetId="23" r:id="R5a32e5cb303340eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-024" sheetId="24" r:id="R72ea034dc2e64263"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-025" sheetId="25" r:id="R55d542803e4f407c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-026" sheetId="26" r:id="Rec4f8650793849e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-027" sheetId="37" r:id="R2715f25b66f54378"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-028" sheetId="27" r:id="R55f117de58fc4d6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-029" sheetId="28" r:id="Re99d349348644416"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-030" sheetId="29" r:id="Rb58c9ca6a8ef4027"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-031" sheetId="30" r:id="R555408f05bbe4b6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-032" sheetId="31" r:id="Rd425e53b8eae45a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-033" sheetId="32" r:id="Rba529a6d16c44931"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-034" sheetId="33" r:id="Rb79284f1fdae446a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-035" sheetId="34" r:id="Rf581733061e244c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-036" sheetId="35" r:id="Rfec22ff4c41f41ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-037" sheetId="36" r:id="R26c80b031f4a420e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-038" sheetId="38" r:id="R4d4d050bd3154297"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-039" sheetId="39" r:id="Rde2eb570d97e4c13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-040" sheetId="40" r:id="R220f963822fc48df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-041" sheetId="41" r:id="R345fb4f00558481c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-042" sheetId="42" r:id="R93d2f1c78f9a4cff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-043" sheetId="43" r:id="Rd23883b40c024de0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-044" sheetId="44" r:id="Rd4cd261b865d4679"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-045" sheetId="79" r:id="Rb9e92253910743da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-046" sheetId="46" r:id="R1142a2e82f5e4b55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-047" sheetId="47" r:id="R90a5c7b8d0d94907"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-048" sheetId="52" r:id="Ra8b511cc1a404e38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-049" sheetId="53" r:id="R00ba6cfcc1d34c5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-050" sheetId="54" r:id="R31dc0a7e09f949ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-051" sheetId="55" r:id="R3250861511a6418f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-052" sheetId="56" r:id="R80676cbeaa104554"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-053" sheetId="57" r:id="R4c02ad32ecf14484"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-054" sheetId="48" r:id="R1c51b935f07b41ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-055" sheetId="49" r:id="Re7031591db684831"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-056" sheetId="80" r:id="Rdecaea7f738a4e66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-057" sheetId="70" r:id="R590b917de9544387"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-058" sheetId="58" r:id="Rad350a3fc5184c33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-059" sheetId="81" r:id="Rd84c5d71bdb74870"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-060" sheetId="63" r:id="Re87660ded3524994"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-061" sheetId="82" r:id="Rf2369ef8ba394fe6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-062" sheetId="64" r:id="R3a62405d1ae34adf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-063" sheetId="65" r:id="Rc0bb938c60f04754"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-064" sheetId="66" r:id="R6031ae8f15fa451f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-065" sheetId="67" r:id="R6fb8f183be9b4ad7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-066" sheetId="68" r:id="Rce181c168a984261"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-067" sheetId="69" r:id="R27963fd5d85143e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-068" sheetId="71" r:id="Rf85843c9c9714948"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-069" sheetId="72" r:id="Rdde18e46e328408f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-070" sheetId="73" r:id="R795178ccde074e86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-071" sheetId="74" r:id="R4fcb7d917aa64fba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-072" sheetId="75" r:id="Rac00426f96a64e3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-073" sheetId="76" r:id="R61faed93ae344ca0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-074" sheetId="77" r:id="R1e1a2bbf2a6b4b36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-075" sheetId="78" r:id="R97c4463a2ec841c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-076" sheetId="83" r:id="R29df998fd1e64d00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-077" sheetId="84" r:id="Rfa60a475ad564d36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-001" sheetId="1" r:id="Re8cc6367cadb468a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-002" sheetId="2" r:id="Ra6aa173c11874eb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-003" sheetId="3" r:id="R23e05e832a2a438a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-004" sheetId="4" r:id="R2616ba582a6e4841"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-005" sheetId="5" r:id="Rbc92f1e6e7644664"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-006" sheetId="6" r:id="R2e631fa6f52d423e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-007" sheetId="7" r:id="R986d4677c6e44f6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-008" sheetId="8" r:id="R472bb021b2db4cba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-009" sheetId="9" r:id="Refe46be8114d43b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-010" sheetId="10" r:id="Rcaf93847564a4387"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-011" sheetId="11" r:id="Rdad09afbbbc74623"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-012" sheetId="12" r:id="R0304d5b240a54f42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-013" sheetId="13" r:id="R8c54992a7ea441c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-014" sheetId="14" r:id="Rc4b33685c09f475d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-015" sheetId="15" r:id="R5f39288d505646ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-016" sheetId="16" r:id="R11262d4b28be4b40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-017" sheetId="17" r:id="R5a01a5f9243d494b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-018" sheetId="18" r:id="R0a60f39ac92a4a56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-019" sheetId="19" r:id="R8fa0ac62ef564e7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-020" sheetId="20" r:id="Rb377f18f40fe4b2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-021" sheetId="21" r:id="Ra11c8e652aa14b58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-022" sheetId="22" r:id="R4a0d1453be10482a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-023" sheetId="23" r:id="Rb057381b703b43c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-024" sheetId="24" r:id="Rfe321699ea5844eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-025" sheetId="25" r:id="Rca2d57cdcbe54574"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-026" sheetId="26" r:id="Rc9db76e7a35643e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-027" sheetId="37" r:id="R035cc205f3d14b73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-028" sheetId="27" r:id="R55076a7ba6cb4055"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-029" sheetId="28" r:id="R33a4b540b75c46b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-030" sheetId="29" r:id="R6a503962d13d4275"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-031" sheetId="30" r:id="Reaac6f884c6e42df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-032" sheetId="31" r:id="Re69a66039c2e409c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-033" sheetId="32" r:id="R99c7c9f75a944263"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-034" sheetId="33" r:id="R59364af4d96043f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-035" sheetId="34" r:id="R53cadddf077e46ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-036" sheetId="35" r:id="Rde5bb3591ddd455a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-037" sheetId="36" r:id="R35a2919a124a4a13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-038" sheetId="38" r:id="Rbff6ad4955fb4c59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-039" sheetId="39" r:id="Rdb69d605facf420e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-040" sheetId="40" r:id="R3302bffc83144cf4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-041" sheetId="41" r:id="R5f5c6ccb29ea49f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-042" sheetId="42" r:id="Rc3d9b4703ed94668"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-043" sheetId="43" r:id="R9183cb0150a946e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-044" sheetId="44" r:id="R89b1dc9cd22e4aef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-045" sheetId="79" r:id="Rc9cf75528e484873"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-046" sheetId="46" r:id="R77785c467db64945"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-047" sheetId="47" r:id="Re39a1a30735346c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-048" sheetId="52" r:id="R65e9133444df44de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-049" sheetId="53" r:id="Rdd1766288b1f4dcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-050" sheetId="54" r:id="Rf42d273e22ff490a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-051" sheetId="55" r:id="Rb33a6bd3d0f04069"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-052" sheetId="56" r:id="R36b5b8ad13724277"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-053" sheetId="57" r:id="R9979a20fe4e149fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-054" sheetId="48" r:id="Rd1e6d4cbb9664e76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-055" sheetId="49" r:id="R821e284697674be1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-056" sheetId="80" r:id="R87ce4183a7484df8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-057" sheetId="70" r:id="Rbe03d408ec744837"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-058" sheetId="58" r:id="R256e5caa22b84021"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-059" sheetId="81" r:id="R85dc8864325c4b24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-060" sheetId="63" r:id="R89f12f6e5d6e44d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-061" sheetId="82" r:id="Rd6b55f3f1eee4d81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-062" sheetId="64" r:id="R9cd29edbb17a4ce3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-063" sheetId="65" r:id="R475e57af146b417e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-064" sheetId="66" r:id="Re22d909f1fb44e71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-065" sheetId="67" r:id="R40c8922c57504637"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-066" sheetId="68" r:id="Rab29bdc5e7b34de0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-067" sheetId="69" r:id="R999e183a7e854126"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-068" sheetId="71" r:id="R1761ed956e204f4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-069" sheetId="72" r:id="R0a366b6f4fa44d9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-070" sheetId="73" r:id="R356224734e154655"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-071" sheetId="74" r:id="R3229cd251ebe4521"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-072" sheetId="75" r:id="Rc58a887196df43bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-073" sheetId="76" r:id="R2d45fe446db34f18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-074" sheetId="77" r:id="R004f3ea88c1244eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-075" sheetId="78" r:id="Ra18cfac5e9e04c59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-076" sheetId="83" r:id="R2e377d9fd4ae46f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEL-077" sheetId="84" r:id="R263556a746c14d4f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -743,6 +743,9 @@
     <x:t xml:space="preserve">表示名</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">tb1.氏名、tb1.メール</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">注文件数</x:t>
   </x:si>
   <x:si>
@@ -893,6 +896,12 @@
     <x:t xml:space="preserve">eligible_flag</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">(tb1.状態 = 'ACTIVE'</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tb1.削除日時 IS NULL) → 1</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">tb1.有効区分 = 1 → 'ACTIVE'</x:t>
   </x:si>
   <x:si>
@@ -916,6 +925,42 @@
   <x:si>
     <x:t xml:space="preserve">tb1.状態 = 'ACTIVE' → 1</x:t>
   </x:si>
+  <x:si>
+    <x:t xml:space="preserve">＜VALUES 1行目＞</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">@user_id_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">@name_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">＜VALUES 2行目＞</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">@user_id_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">@name_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">'PENDING'</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">＜UNION ALL＞</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">TRIM(tb2.氏名)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tb2.状態 = 'INACTIVE'</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">＜移送パターン1＞</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">＜移送パターン2＞</x:t>
+  </x:si>
 </x:sst>
 </file>
 
@@ -934,7 +979,7 @@
     </x:font>
     <x:font>
       <x:sz val="6"/>
-      <x:name val="游ゴシック"/>
+      <x:name val="ＭＳ Ｐゴシック"/>
     </x:font>
   </x:fonts>
   <x:fills count="6">
@@ -1056,13 +1101,11 @@
       <x:top style="thin">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="none"/>
     </x:border>
     <x:border>
       <x:top style="thin">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="none"/>
     </x:border>
     <x:border>
       <x:right style="thin">
@@ -1071,37 +1114,27 @@
       <x:top style="thin">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="none"/>
     </x:border>
     <x:border>
       <x:left style="thin">
         <x:color rgb="FF000000"/>
       </x:left>
-      <x:top style="none"/>
-      <x:bottom style="none"/>
     </x:border>
-    <x:border>
-      <x:top style="none"/>
-      <x:bottom style="none"/>
-    </x:border>
+    <x:border/>
     <x:border>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="none"/>
-      <x:bottom style="none"/>
     </x:border>
     <x:border>
       <x:left style="thin">
         <x:color rgb="FF000000"/>
       </x:left>
-      <x:top style="none"/>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
-      <x:top style="none"/>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -1110,7 +1143,6 @@
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="none"/>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -1121,7 +1153,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="85">
+  <x:cellXfs count="63">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -1218,164 +1250,98 @@
     <x:xf numFmtId="49" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="49" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="49" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="49" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="49" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="49" fontId="1" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="49" fontId="1" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="49" fontId="1" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="49" fontId="1" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="49" fontId="1" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="49" fontId="1" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="49" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="49" fontId="1" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="49" fontId="1" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="49" fontId="1" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -34887,7 +34853,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="P7" s="3"/>
-      <x:c r="Q7" s="32" t="s">
+      <x:c r="Q7" s="27" t="s">
         <x:v>211</x:v>
       </x:c>
       <x:c r="R7" s="3"/>
@@ -36233,8 +36199,8 @@
       <x:c r="P21" s="18"/>
       <x:c r="Q21" s="18"/>
       <x:c r="R21" s="18"/>
-      <x:c r="S21" s="20" t="str">
-        <x:v>tb1.氏名、tb1.メール</x:v>
+      <x:c r="S21" s="20" t="s">
+        <x:v>219</x:v>
       </x:c>
       <x:c r="T21" s="18"/>
       <x:c r="U21" s="18"/>
@@ -36253,8 +36219,8 @@
       <x:c r="AH21" s="18"/>
       <x:c r="AI21" s="18"/>
       <x:c r="AJ21" s="18"/>
-      <x:c r="AK21" s="17" t="str">
-        <x:v>COALESCE(tb1.氏名, tb1.メール)</x:v>
+      <x:c r="AK21" s="17" t="s">
+        <x:v>208</x:v>
       </x:c>
       <x:c r="AL21" s="18"/>
       <x:c r="AM21" s="18"/>
@@ -36312,7 +36278,7 @@
     </x:row>
     <x:row r="22" ht="13.5" customHeight="1">
       <x:c r="A22" s="20" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B22" s="18"/>
       <x:c r="C22" s="18"/>
@@ -36331,8 +36297,8 @@
       <x:c r="P22" s="18"/>
       <x:c r="Q22" s="18"/>
       <x:c r="R22" s="18"/>
-      <x:c r="S22" s="20" t="str">
-        <x:v>tb2.注文ID</x:v>
+      <x:c r="S22" s="20" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="T22" s="18"/>
       <x:c r="U22" s="18"/>
@@ -36351,8 +36317,8 @@
       <x:c r="AH22" s="18"/>
       <x:c r="AI22" s="18"/>
       <x:c r="AJ22" s="18"/>
-      <x:c r="AK22" s="17" t="str">
-        <x:v>COUNT(tb2.注文ID)</x:v>
+      <x:c r="AK22" s="17" t="s">
+        <x:v>209</x:v>
       </x:c>
       <x:c r="AL22" s="18"/>
       <x:c r="AM22" s="18"/>
@@ -36410,7 +36376,7 @@
     </x:row>
     <x:row r="23" ht="13.5" customHeight="1">
       <x:c r="A23" s="20" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B23" s="18"/>
       <x:c r="C23" s="18"/>
@@ -36506,7 +36472,7 @@
     </x:row>
     <x:row r="24" ht="13.5" customHeight="1">
       <x:c r="A24" s="20" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B24" s="18"/>
       <x:c r="C24" s="18"/>
@@ -36543,7 +36509,7 @@
       <x:c r="AH24" s="18"/>
       <x:c r="AI24" s="18"/>
       <x:c r="AJ24" s="18"/>
-      <x:c r="AK24" s="33" t="s">
+      <x:c r="AK24" s="20" t="s">
         <x:v>211</x:v>
       </x:c>
       <x:c r="AL24" s="18"/>
@@ -37116,7 +37082,7 @@
       <x:c r="O6" s="6"/>
       <x:c r="P6" s="6"/>
       <x:c r="Q6" s="25" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="R6" s="6"/>
       <x:c r="S6" s="6"/>
@@ -37233,7 +37199,7 @@
       </x:c>
       <x:c r="AG7" s="3"/>
       <x:c r="AH7" s="27" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="AI7" s="3"/>
       <x:c r="AJ7" s="3"/>
@@ -37423,7 +37389,7 @@
       </x:c>
       <x:c r="AG9" s="3"/>
       <x:c r="AH9" s="27" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="AI9" s="3"/>
       <x:c r="AJ9" s="3"/>
@@ -37515,7 +37481,7 @@
       <x:c r="AD10" s="14"/>
       <x:c r="AE10" s="14"/>
       <x:c r="AF10" s="30" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="AG10" s="14"/>
       <x:c r="AH10" s="14"/>
@@ -37778,7 +37744,7 @@
     </x:row>
     <x:row r="3" ht="13.5" customHeight="1">
       <x:c r="A3" s="23" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B3" s="4"/>
       <x:c r="C3" s="4"/>
@@ -37786,7 +37752,7 @@
       <x:c r="E3" s="4"/>
       <x:c r="F3" s="4"/>
       <x:c r="G3" s="24" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H3" s="6"/>
       <x:c r="I3" s="6"/>
@@ -38658,7 +38624,7 @@
     </x:row>
     <x:row r="7" ht="13.5" customHeight="1">
       <x:c r="A7" s="22" t="s">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B7" s="1"/>
       <x:c r="C7" s="1"/>
@@ -38946,7 +38912,7 @@
     </x:row>
     <x:row r="10" ht="13.5" customHeight="1">
       <x:c r="A10" s="20" t="s">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B10" s="18"/>
       <x:c r="C10" s="18"/>
@@ -39744,7 +39710,7 @@
     </x:row>
     <x:row r="2" ht="13.5" customHeight="1">
       <x:c r="A2" s="22" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -39974,7 +39940,7 @@
       <x:c r="AI4" s="14"/>
       <x:c r="AJ4" s="14"/>
       <x:c r="AK4" s="31" t="s">
-        <x:v>231</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="AL4" s="14"/>
       <x:c r="AM4" s="14"/>
@@ -40070,7 +40036,7 @@
       <x:c r="AI5" s="18"/>
       <x:c r="AJ5" s="18"/>
       <x:c r="AK5" s="20" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="AL5" s="18"/>
       <x:c r="AM5" s="18"/>
@@ -40165,8 +40131,8 @@
       <x:c r="AH6" s="18"/>
       <x:c r="AI6" s="18"/>
       <x:c r="AJ6" s="18"/>
-      <x:c r="AK6" s="33" t="s">
-        <x:v>233</x:v>
+      <x:c r="AK6" s="20" t="s">
+        <x:v>234</x:v>
       </x:c>
       <x:c r="AL6" s="18"/>
       <x:c r="AM6" s="18"/>
@@ -40224,7 +40190,7 @@
     </x:row>
     <x:row r="7" ht="13.5" customHeight="1">
       <x:c r="A7" s="20" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B7" s="18"/>
       <x:c r="C7" s="18"/>
@@ -40844,7 +40810,7 @@
       </x:c>
       <x:c r="P6" s="3"/>
       <x:c r="Q6" s="27" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="R6" s="3"/>
       <x:c r="S6" s="3"/>
@@ -40863,7 +40829,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AF6" s="27" t="s">
-        <x:v>235</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="AG6" s="3"/>
       <x:c r="AH6" s="3"/>
@@ -40957,7 +40923,7 @@
       <x:c r="AD7" s="3"/>
       <x:c r="AE7" s="3"/>
       <x:c r="AF7" s="27" t="s">
-        <x:v>236</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="AG7" s="3"/>
       <x:c r="AH7" s="3"/>
@@ -41051,7 +41017,7 @@
       <x:c r="AD8" s="3"/>
       <x:c r="AE8" s="3"/>
       <x:c r="AF8" s="27" t="s">
-        <x:v>237</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="AG8" s="3"/>
       <x:c r="AH8" s="3"/>
@@ -41134,7 +41100,7 @@
       </x:c>
       <x:c r="P9" s="3"/>
       <x:c r="Q9" s="27" t="s">
-        <x:v>238</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="R9" s="3"/>
       <x:c r="S9" s="3"/>
@@ -41222,7 +41188,7 @@
       <x:c r="E10" s="2"/>
       <x:c r="F10" s="2"/>
       <x:c r="G10" s="26" t="s">
-        <x:v>239</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="H10" s="3"/>
       <x:c r="I10" s="3"/>
@@ -41236,7 +41202,7 @@
       </x:c>
       <x:c r="P10" s="3"/>
       <x:c r="Q10" s="27" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="R10" s="3"/>
       <x:c r="S10" s="3"/>
@@ -41254,7 +41220,7 @@
       <x:c r="AE10" s="27" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="AF10" s="32" t="s">
+      <x:c r="AF10" s="27" t="s">
         <x:v>211</x:v>
       </x:c>
       <x:c r="AG10" s="3"/>
@@ -42585,8 +42551,8 @@
       <x:c r="P24" s="18"/>
       <x:c r="Q24" s="18"/>
       <x:c r="R24" s="18"/>
-      <x:c r="S24" s="20" t="str">
-        <x:v>tb1.氏名、tb1.メール</x:v>
+      <x:c r="S24" s="20" t="s">
+        <x:v>219</x:v>
       </x:c>
       <x:c r="T24" s="18"/>
       <x:c r="U24" s="18"/>
@@ -42605,8 +42571,8 @@
       <x:c r="AH24" s="18"/>
       <x:c r="AI24" s="18"/>
       <x:c r="AJ24" s="18"/>
-      <x:c r="AK24" s="17" t="str">
-        <x:v>COALESCE(tb1.氏名, tb1.メール)</x:v>
+      <x:c r="AK24" s="17" t="s">
+        <x:v>208</x:v>
       </x:c>
       <x:c r="AL24" s="18"/>
       <x:c r="AM24" s="18"/>
@@ -42664,7 +42630,7 @@
     </x:row>
     <x:row r="25" ht="13.5" customHeight="1">
       <x:c r="A25" s="20" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B25" s="18"/>
       <x:c r="C25" s="18"/>
@@ -42683,8 +42649,8 @@
       <x:c r="P25" s="18"/>
       <x:c r="Q25" s="18"/>
       <x:c r="R25" s="18"/>
-      <x:c r="S25" s="20" t="str">
-        <x:v>tb2.注文ID</x:v>
+      <x:c r="S25" s="20" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="T25" s="18"/>
       <x:c r="U25" s="18"/>
@@ -42703,8 +42669,8 @@
       <x:c r="AH25" s="18"/>
       <x:c r="AI25" s="18"/>
       <x:c r="AJ25" s="18"/>
-      <x:c r="AK25" s="17" t="str">
-        <x:v>COUNT(tb2.注文ID)</x:v>
+      <x:c r="AK25" s="17" t="s">
+        <x:v>209</x:v>
       </x:c>
       <x:c r="AL25" s="18"/>
       <x:c r="AM25" s="18"/>
@@ -42761,296 +42727,296 @@
       <x:c r="CL25" s="19"/>
     </x:row>
     <x:row r="26" ht="13.5" customHeight="1">
-      <x:c r="A26" s="48" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="B26" s="49"/>
-      <x:c r="C26" s="49"/>
-      <x:c r="D26" s="49"/>
-      <x:c r="E26" s="49"/>
-      <x:c r="F26" s="49"/>
-      <x:c r="G26" s="49"/>
-      <x:c r="H26" s="49"/>
-      <x:c r="I26" s="49"/>
-      <x:c r="J26" s="49"/>
-      <x:c r="K26" s="49"/>
-      <x:c r="L26" s="49"/>
-      <x:c r="M26" s="49"/>
-      <x:c r="N26" s="49"/>
-      <x:c r="O26" s="49"/>
-      <x:c r="P26" s="49"/>
-      <x:c r="Q26" s="49"/>
-      <x:c r="R26" s="50"/>
-      <x:c r="S26" s="48"/>
-      <x:c r="T26" s="49"/>
-      <x:c r="U26" s="49"/>
-      <x:c r="V26" s="49"/>
-      <x:c r="W26" s="49"/>
-      <x:c r="X26" s="49"/>
-      <x:c r="Y26" s="49"/>
-      <x:c r="Z26" s="49"/>
-      <x:c r="AA26" s="49"/>
-      <x:c r="AB26" s="49"/>
-      <x:c r="AC26" s="49"/>
-      <x:c r="AD26" s="49"/>
-      <x:c r="AE26" s="49"/>
-      <x:c r="AF26" s="49"/>
-      <x:c r="AG26" s="49"/>
-      <x:c r="AH26" s="49"/>
-      <x:c r="AI26" s="51"/>
-      <x:c r="AJ26" s="50"/>
-      <x:c r="AK26" s="48" t="str">
-        <x:v>CASE結果</x:v>
-      </x:c>
-      <x:c r="AL26" s="49"/>
-      <x:c r="AM26" s="49"/>
-      <x:c r="AN26" s="49"/>
-      <x:c r="AO26" s="49"/>
-      <x:c r="AP26" s="49"/>
-      <x:c r="AQ26" s="49"/>
-      <x:c r="AR26" s="49"/>
-      <x:c r="AS26" s="49"/>
-      <x:c r="AT26" s="49"/>
-      <x:c r="AU26" s="49"/>
-      <x:c r="AV26" s="49"/>
-      <x:c r="AW26" s="49"/>
-      <x:c r="AX26" s="49"/>
-      <x:c r="AY26" s="49" t="str">
-        <x:v>※</x:v>
-      </x:c>
-      <x:c r="AZ26" s="49" t="str">
-        <x:v>COUNT(tb2.注文ID) &gt;= @priority_order_count → 'PRIORITY'</x:v>
-      </x:c>
-      <x:c r="BA26" s="49"/>
-      <x:c r="BB26" s="49"/>
-      <x:c r="BC26" s="49"/>
-      <x:c r="BD26" s="49"/>
-      <x:c r="BE26" s="49"/>
-      <x:c r="BF26" s="49"/>
-      <x:c r="BG26" s="49"/>
-      <x:c r="BH26" s="49"/>
-      <x:c r="BI26" s="49"/>
-      <x:c r="BJ26" s="49"/>
-      <x:c r="BK26" s="49"/>
-      <x:c r="BL26" s="49"/>
-      <x:c r="BM26" s="49"/>
-      <x:c r="BN26" s="49"/>
-      <x:c r="BO26" s="49"/>
-      <x:c r="BP26" s="49"/>
-      <x:c r="BQ26" s="49"/>
-      <x:c r="BR26" s="49"/>
-      <x:c r="BS26" s="49"/>
-      <x:c r="BT26" s="49"/>
-      <x:c r="BU26" s="49"/>
-      <x:c r="BV26" s="49"/>
-      <x:c r="BW26" s="49"/>
-      <x:c r="BX26" s="49"/>
-      <x:c r="BY26" s="49"/>
-      <x:c r="BZ26" s="49"/>
-      <x:c r="CA26" s="49"/>
-      <x:c r="CB26" s="49"/>
-      <x:c r="CC26" s="49"/>
-      <x:c r="CD26" s="49"/>
-      <x:c r="CE26" s="49"/>
-      <x:c r="CF26" s="49"/>
-      <x:c r="CG26" s="49"/>
-      <x:c r="CH26" s="49"/>
-      <x:c r="CI26" s="49"/>
-      <x:c r="CJ26" s="49"/>
-      <x:c r="CK26" s="49"/>
-      <x:c r="CL26" s="50"/>
+      <x:c r="A26" s="33" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="B26" s="34"/>
+      <x:c r="C26" s="34"/>
+      <x:c r="D26" s="34"/>
+      <x:c r="E26" s="34"/>
+      <x:c r="F26" s="34"/>
+      <x:c r="G26" s="34"/>
+      <x:c r="H26" s="34"/>
+      <x:c r="I26" s="34"/>
+      <x:c r="J26" s="34"/>
+      <x:c r="K26" s="34"/>
+      <x:c r="L26" s="34"/>
+      <x:c r="M26" s="34"/>
+      <x:c r="N26" s="34"/>
+      <x:c r="O26" s="34"/>
+      <x:c r="P26" s="34"/>
+      <x:c r="Q26" s="34"/>
+      <x:c r="R26" s="35"/>
+      <x:c r="S26" s="33"/>
+      <x:c r="T26" s="34"/>
+      <x:c r="U26" s="34"/>
+      <x:c r="V26" s="34"/>
+      <x:c r="W26" s="34"/>
+      <x:c r="X26" s="34"/>
+      <x:c r="Y26" s="34"/>
+      <x:c r="Z26" s="34"/>
+      <x:c r="AA26" s="34"/>
+      <x:c r="AB26" s="34"/>
+      <x:c r="AC26" s="34"/>
+      <x:c r="AD26" s="34"/>
+      <x:c r="AE26" s="34"/>
+      <x:c r="AF26" s="34"/>
+      <x:c r="AG26" s="34"/>
+      <x:c r="AH26" s="34"/>
+      <x:c r="AI26" s="42"/>
+      <x:c r="AJ26" s="35"/>
+      <x:c r="AK26" s="33" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="AL26" s="34"/>
+      <x:c r="AM26" s="34"/>
+      <x:c r="AN26" s="34"/>
+      <x:c r="AO26" s="34"/>
+      <x:c r="AP26" s="34"/>
+      <x:c r="AQ26" s="34"/>
+      <x:c r="AR26" s="34"/>
+      <x:c r="AS26" s="34"/>
+      <x:c r="AT26" s="34"/>
+      <x:c r="AU26" s="34"/>
+      <x:c r="AV26" s="34"/>
+      <x:c r="AW26" s="34"/>
+      <x:c r="AX26" s="34"/>
+      <x:c r="AY26" s="34" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="AZ26" s="34" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="BA26" s="34"/>
+      <x:c r="BB26" s="34"/>
+      <x:c r="BC26" s="34"/>
+      <x:c r="BD26" s="34"/>
+      <x:c r="BE26" s="34"/>
+      <x:c r="BF26" s="34"/>
+      <x:c r="BG26" s="34"/>
+      <x:c r="BH26" s="34"/>
+      <x:c r="BI26" s="34"/>
+      <x:c r="BJ26" s="34"/>
+      <x:c r="BK26" s="34"/>
+      <x:c r="BL26" s="34"/>
+      <x:c r="BM26" s="34"/>
+      <x:c r="BN26" s="34"/>
+      <x:c r="BO26" s="34"/>
+      <x:c r="BP26" s="34"/>
+      <x:c r="BQ26" s="34"/>
+      <x:c r="BR26" s="34"/>
+      <x:c r="BS26" s="34"/>
+      <x:c r="BT26" s="34"/>
+      <x:c r="BU26" s="34"/>
+      <x:c r="BV26" s="34"/>
+      <x:c r="BW26" s="34"/>
+      <x:c r="BX26" s="34"/>
+      <x:c r="BY26" s="34"/>
+      <x:c r="BZ26" s="34"/>
+      <x:c r="CA26" s="34"/>
+      <x:c r="CB26" s="34"/>
+      <x:c r="CC26" s="34"/>
+      <x:c r="CD26" s="34"/>
+      <x:c r="CE26" s="34"/>
+      <x:c r="CF26" s="34"/>
+      <x:c r="CG26" s="34"/>
+      <x:c r="CH26" s="34"/>
+      <x:c r="CI26" s="34"/>
+      <x:c r="CJ26" s="34"/>
+      <x:c r="CK26" s="34"/>
+      <x:c r="CL26" s="35"/>
     </x:row>
     <x:row r="27" ht="13.5" customHeight="1">
-      <x:c r="A27" s="52"/>
-      <x:c r="B27" s="53"/>
-      <x:c r="C27" s="53"/>
-      <x:c r="D27" s="53"/>
-      <x:c r="E27" s="53"/>
-      <x:c r="F27" s="53"/>
-      <x:c r="G27" s="53"/>
-      <x:c r="H27" s="53"/>
-      <x:c r="I27" s="53"/>
-      <x:c r="J27" s="53"/>
-      <x:c r="K27" s="53"/>
-      <x:c r="L27" s="53"/>
-      <x:c r="M27" s="53"/>
-      <x:c r="N27" s="53"/>
-      <x:c r="O27" s="53"/>
-      <x:c r="P27" s="53"/>
-      <x:c r="Q27" s="53"/>
-      <x:c r="R27" s="54"/>
-      <x:c r="S27" s="52"/>
-      <x:c r="T27" s="53"/>
-      <x:c r="U27" s="53"/>
-      <x:c r="V27" s="53"/>
-      <x:c r="W27" s="53"/>
-      <x:c r="X27" s="53"/>
-      <x:c r="Y27" s="53"/>
-      <x:c r="Z27" s="53"/>
-      <x:c r="AA27" s="53"/>
-      <x:c r="AB27" s="53"/>
-      <x:c r="AC27" s="53"/>
-      <x:c r="AD27" s="53"/>
-      <x:c r="AE27" s="53"/>
-      <x:c r="AF27" s="53"/>
-      <x:c r="AG27" s="53"/>
-      <x:c r="AH27" s="53"/>
-      <x:c r="AI27" s="53"/>
-      <x:c r="AJ27" s="54"/>
-      <x:c r="AK27" s="55"/>
-      <x:c r="AL27" s="53"/>
-      <x:c r="AM27" s="53"/>
-      <x:c r="AN27" s="53"/>
-      <x:c r="AO27" s="53"/>
-      <x:c r="AP27" s="53"/>
-      <x:c r="AQ27" s="53"/>
-      <x:c r="AR27" s="53"/>
-      <x:c r="AS27" s="53"/>
-      <x:c r="AT27" s="53"/>
-      <x:c r="AU27" s="53"/>
-      <x:c r="AV27" s="53"/>
-      <x:c r="AW27" s="53"/>
-      <x:c r="AX27" s="53"/>
-      <x:c r="AY27" s="53"/>
-      <x:c r="AZ27" s="53" t="str">
-        <x:v>COUNT(tb2.注文ID) &gt; 0 → 'STANDARD'</x:v>
-      </x:c>
-      <x:c r="BA27" s="53"/>
-      <x:c r="BB27" s="53"/>
-      <x:c r="BC27" s="53"/>
-      <x:c r="BD27" s="53"/>
-      <x:c r="BE27" s="53"/>
-      <x:c r="BF27" s="53"/>
-      <x:c r="BG27" s="53"/>
-      <x:c r="BH27" s="53"/>
-      <x:c r="BI27" s="53"/>
-      <x:c r="BJ27" s="53"/>
-      <x:c r="BK27" s="53"/>
-      <x:c r="BL27" s="53"/>
-      <x:c r="BM27" s="53"/>
-      <x:c r="BN27" s="53"/>
-      <x:c r="BO27" s="53"/>
-      <x:c r="BP27" s="53"/>
-      <x:c r="BQ27" s="53"/>
-      <x:c r="BR27" s="53"/>
-      <x:c r="BS27" s="53"/>
-      <x:c r="BT27" s="53"/>
-      <x:c r="BU27" s="53"/>
-      <x:c r="BV27" s="53"/>
-      <x:c r="BW27" s="53"/>
-      <x:c r="BX27" s="53"/>
-      <x:c r="BY27" s="53"/>
-      <x:c r="BZ27" s="53"/>
-      <x:c r="CA27" s="53"/>
-      <x:c r="CB27" s="53"/>
-      <x:c r="CC27" s="53"/>
-      <x:c r="CD27" s="53"/>
-      <x:c r="CE27" s="53"/>
-      <x:c r="CF27" s="53"/>
-      <x:c r="CG27" s="53"/>
-      <x:c r="CH27" s="53"/>
-      <x:c r="CI27" s="53"/>
-      <x:c r="CJ27" s="53"/>
-      <x:c r="CK27" s="53"/>
-      <x:c r="CL27" s="54"/>
+      <x:c r="A27" s="36"/>
+      <x:c r="B27" s="37"/>
+      <x:c r="C27" s="37"/>
+      <x:c r="D27" s="37"/>
+      <x:c r="E27" s="37"/>
+      <x:c r="F27" s="37"/>
+      <x:c r="G27" s="37"/>
+      <x:c r="H27" s="37"/>
+      <x:c r="I27" s="37"/>
+      <x:c r="J27" s="37"/>
+      <x:c r="K27" s="37"/>
+      <x:c r="L27" s="37"/>
+      <x:c r="M27" s="37"/>
+      <x:c r="N27" s="37"/>
+      <x:c r="O27" s="37"/>
+      <x:c r="P27" s="37"/>
+      <x:c r="Q27" s="37"/>
+      <x:c r="R27" s="38"/>
+      <x:c r="S27" s="36"/>
+      <x:c r="T27" s="37"/>
+      <x:c r="U27" s="37"/>
+      <x:c r="V27" s="37"/>
+      <x:c r="W27" s="37"/>
+      <x:c r="X27" s="37"/>
+      <x:c r="Y27" s="37"/>
+      <x:c r="Z27" s="37"/>
+      <x:c r="AA27" s="37"/>
+      <x:c r="AB27" s="37"/>
+      <x:c r="AC27" s="37"/>
+      <x:c r="AD27" s="37"/>
+      <x:c r="AE27" s="37"/>
+      <x:c r="AF27" s="37"/>
+      <x:c r="AG27" s="37"/>
+      <x:c r="AH27" s="37"/>
+      <x:c r="AI27" s="37"/>
+      <x:c r="AJ27" s="38"/>
+      <x:c r="AK27" s="43"/>
+      <x:c r="AL27" s="37"/>
+      <x:c r="AM27" s="37"/>
+      <x:c r="AN27" s="37"/>
+      <x:c r="AO27" s="37"/>
+      <x:c r="AP27" s="37"/>
+      <x:c r="AQ27" s="37"/>
+      <x:c r="AR27" s="37"/>
+      <x:c r="AS27" s="37"/>
+      <x:c r="AT27" s="37"/>
+      <x:c r="AU27" s="37"/>
+      <x:c r="AV27" s="37"/>
+      <x:c r="AW27" s="37"/>
+      <x:c r="AX27" s="37"/>
+      <x:c r="AY27" s="37"/>
+      <x:c r="AZ27" s="37" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="BA27" s="37"/>
+      <x:c r="BB27" s="37"/>
+      <x:c r="BC27" s="37"/>
+      <x:c r="BD27" s="37"/>
+      <x:c r="BE27" s="37"/>
+      <x:c r="BF27" s="37"/>
+      <x:c r="BG27" s="37"/>
+      <x:c r="BH27" s="37"/>
+      <x:c r="BI27" s="37"/>
+      <x:c r="BJ27" s="37"/>
+      <x:c r="BK27" s="37"/>
+      <x:c r="BL27" s="37"/>
+      <x:c r="BM27" s="37"/>
+      <x:c r="BN27" s="37"/>
+      <x:c r="BO27" s="37"/>
+      <x:c r="BP27" s="37"/>
+      <x:c r="BQ27" s="37"/>
+      <x:c r="BR27" s="37"/>
+      <x:c r="BS27" s="37"/>
+      <x:c r="BT27" s="37"/>
+      <x:c r="BU27" s="37"/>
+      <x:c r="BV27" s="37"/>
+      <x:c r="BW27" s="37"/>
+      <x:c r="BX27" s="37"/>
+      <x:c r="BY27" s="37"/>
+      <x:c r="BZ27" s="37"/>
+      <x:c r="CA27" s="37"/>
+      <x:c r="CB27" s="37"/>
+      <x:c r="CC27" s="37"/>
+      <x:c r="CD27" s="37"/>
+      <x:c r="CE27" s="37"/>
+      <x:c r="CF27" s="37"/>
+      <x:c r="CG27" s="37"/>
+      <x:c r="CH27" s="37"/>
+      <x:c r="CI27" s="37"/>
+      <x:c r="CJ27" s="37"/>
+      <x:c r="CK27" s="37"/>
+      <x:c r="CL27" s="38"/>
     </x:row>
     <x:row r="28" ht="13.5" customHeight="1">
-      <x:c r="A28" s="56"/>
-      <x:c r="B28" s="57"/>
-      <x:c r="C28" s="57"/>
-      <x:c r="D28" s="57"/>
-      <x:c r="E28" s="57"/>
-      <x:c r="F28" s="57"/>
-      <x:c r="G28" s="57"/>
-      <x:c r="H28" s="57"/>
-      <x:c r="I28" s="57"/>
-      <x:c r="J28" s="57"/>
-      <x:c r="K28" s="57"/>
-      <x:c r="L28" s="57"/>
-      <x:c r="M28" s="57"/>
-      <x:c r="N28" s="57"/>
-      <x:c r="O28" s="57"/>
-      <x:c r="P28" s="57"/>
-      <x:c r="Q28" s="57"/>
-      <x:c r="R28" s="58"/>
-      <x:c r="S28" s="56"/>
-      <x:c r="T28" s="57"/>
-      <x:c r="U28" s="57"/>
-      <x:c r="V28" s="57"/>
-      <x:c r="W28" s="57"/>
-      <x:c r="X28" s="57"/>
-      <x:c r="Y28" s="57"/>
-      <x:c r="Z28" s="57"/>
-      <x:c r="AA28" s="57"/>
-      <x:c r="AB28" s="57"/>
-      <x:c r="AC28" s="57"/>
-      <x:c r="AD28" s="57"/>
-      <x:c r="AE28" s="57"/>
-      <x:c r="AF28" s="57"/>
-      <x:c r="AG28" s="57"/>
-      <x:c r="AH28" s="57"/>
-      <x:c r="AI28" s="57"/>
-      <x:c r="AJ28" s="58"/>
-      <x:c r="AK28" s="59"/>
-      <x:c r="AL28" s="57"/>
-      <x:c r="AM28" s="57"/>
-      <x:c r="AN28" s="57"/>
-      <x:c r="AO28" s="57"/>
-      <x:c r="AP28" s="57"/>
-      <x:c r="AQ28" s="57"/>
-      <x:c r="AR28" s="57"/>
-      <x:c r="AS28" s="57"/>
-      <x:c r="AT28" s="57"/>
-      <x:c r="AU28" s="57"/>
-      <x:c r="AV28" s="57"/>
-      <x:c r="AW28" s="57"/>
-      <x:c r="AX28" s="57"/>
-      <x:c r="AY28" s="57"/>
-      <x:c r="AZ28" s="57" t="str">
-        <x:v>ELSE → 'NONE'</x:v>
-      </x:c>
-      <x:c r="BA28" s="57"/>
-      <x:c r="BB28" s="57"/>
-      <x:c r="BC28" s="57"/>
-      <x:c r="BD28" s="57"/>
-      <x:c r="BE28" s="57"/>
-      <x:c r="BF28" s="57"/>
-      <x:c r="BG28" s="57"/>
-      <x:c r="BH28" s="57"/>
-      <x:c r="BI28" s="57"/>
-      <x:c r="BJ28" s="57"/>
-      <x:c r="BK28" s="57"/>
-      <x:c r="BL28" s="57"/>
-      <x:c r="BM28" s="57"/>
-      <x:c r="BN28" s="57"/>
-      <x:c r="BO28" s="57"/>
-      <x:c r="BP28" s="57"/>
-      <x:c r="BQ28" s="57"/>
-      <x:c r="BR28" s="57"/>
-      <x:c r="BS28" s="57"/>
-      <x:c r="BT28" s="57"/>
-      <x:c r="BU28" s="57"/>
-      <x:c r="BV28" s="57"/>
-      <x:c r="BW28" s="57"/>
-      <x:c r="BX28" s="57"/>
-      <x:c r="BY28" s="57"/>
-      <x:c r="BZ28" s="57"/>
-      <x:c r="CA28" s="57"/>
-      <x:c r="CB28" s="57"/>
-      <x:c r="CC28" s="57"/>
-      <x:c r="CD28" s="57"/>
-      <x:c r="CE28" s="57"/>
-      <x:c r="CF28" s="57"/>
-      <x:c r="CG28" s="57"/>
-      <x:c r="CH28" s="57"/>
-      <x:c r="CI28" s="57"/>
-      <x:c r="CJ28" s="57"/>
-      <x:c r="CK28" s="57"/>
-      <x:c r="CL28" s="58"/>
+      <x:c r="A28" s="39"/>
+      <x:c r="B28" s="40"/>
+      <x:c r="C28" s="40"/>
+      <x:c r="D28" s="40"/>
+      <x:c r="E28" s="40"/>
+      <x:c r="F28" s="40"/>
+      <x:c r="G28" s="40"/>
+      <x:c r="H28" s="40"/>
+      <x:c r="I28" s="40"/>
+      <x:c r="J28" s="40"/>
+      <x:c r="K28" s="40"/>
+      <x:c r="L28" s="40"/>
+      <x:c r="M28" s="40"/>
+      <x:c r="N28" s="40"/>
+      <x:c r="O28" s="40"/>
+      <x:c r="P28" s="40"/>
+      <x:c r="Q28" s="40"/>
+      <x:c r="R28" s="41"/>
+      <x:c r="S28" s="39"/>
+      <x:c r="T28" s="40"/>
+      <x:c r="U28" s="40"/>
+      <x:c r="V28" s="40"/>
+      <x:c r="W28" s="40"/>
+      <x:c r="X28" s="40"/>
+      <x:c r="Y28" s="40"/>
+      <x:c r="Z28" s="40"/>
+      <x:c r="AA28" s="40"/>
+      <x:c r="AB28" s="40"/>
+      <x:c r="AC28" s="40"/>
+      <x:c r="AD28" s="40"/>
+      <x:c r="AE28" s="40"/>
+      <x:c r="AF28" s="40"/>
+      <x:c r="AG28" s="40"/>
+      <x:c r="AH28" s="40"/>
+      <x:c r="AI28" s="40"/>
+      <x:c r="AJ28" s="41"/>
+      <x:c r="AK28" s="44"/>
+      <x:c r="AL28" s="40"/>
+      <x:c r="AM28" s="40"/>
+      <x:c r="AN28" s="40"/>
+      <x:c r="AO28" s="40"/>
+      <x:c r="AP28" s="40"/>
+      <x:c r="AQ28" s="40"/>
+      <x:c r="AR28" s="40"/>
+      <x:c r="AS28" s="40"/>
+      <x:c r="AT28" s="40"/>
+      <x:c r="AU28" s="40"/>
+      <x:c r="AV28" s="40"/>
+      <x:c r="AW28" s="40"/>
+      <x:c r="AX28" s="40"/>
+      <x:c r="AY28" s="40"/>
+      <x:c r="AZ28" s="40" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="BA28" s="40"/>
+      <x:c r="BB28" s="40"/>
+      <x:c r="BC28" s="40"/>
+      <x:c r="BD28" s="40"/>
+      <x:c r="BE28" s="40"/>
+      <x:c r="BF28" s="40"/>
+      <x:c r="BG28" s="40"/>
+      <x:c r="BH28" s="40"/>
+      <x:c r="BI28" s="40"/>
+      <x:c r="BJ28" s="40"/>
+      <x:c r="BK28" s="40"/>
+      <x:c r="BL28" s="40"/>
+      <x:c r="BM28" s="40"/>
+      <x:c r="BN28" s="40"/>
+      <x:c r="BO28" s="40"/>
+      <x:c r="BP28" s="40"/>
+      <x:c r="BQ28" s="40"/>
+      <x:c r="BR28" s="40"/>
+      <x:c r="BS28" s="40"/>
+      <x:c r="BT28" s="40"/>
+      <x:c r="BU28" s="40"/>
+      <x:c r="BV28" s="40"/>
+      <x:c r="BW28" s="40"/>
+      <x:c r="BX28" s="40"/>
+      <x:c r="BY28" s="40"/>
+      <x:c r="BZ28" s="40"/>
+      <x:c r="CA28" s="40"/>
+      <x:c r="CB28" s="40"/>
+      <x:c r="CC28" s="40"/>
+      <x:c r="CD28" s="40"/>
+      <x:c r="CE28" s="40"/>
+      <x:c r="CF28" s="40"/>
+      <x:c r="CG28" s="40"/>
+      <x:c r="CH28" s="40"/>
+      <x:c r="CI28" s="40"/>
+      <x:c r="CJ28" s="40"/>
+      <x:c r="CK28" s="40"/>
+      <x:c r="CL28" s="41"/>
     </x:row>
     <x:row r="29" ht="13.5" customHeight="1">
       <x:c r="A29" s="20" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B29" s="18"/>
       <x:c r="C29" s="18"/>
@@ -43146,7 +43112,7 @@
     </x:row>
     <x:row r="30" ht="13.5" customHeight="1">
       <x:c r="A30" s="20" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B30" s="18"/>
       <x:c r="C30" s="18"/>
@@ -43183,7 +43149,7 @@
       <x:c r="AH30" s="18"/>
       <x:c r="AI30" s="18"/>
       <x:c r="AJ30" s="18"/>
-      <x:c r="AK30" s="33" t="s">
+      <x:c r="AK30" s="20" t="s">
         <x:v>211</x:v>
       </x:c>
       <x:c r="AL30" s="18"/>
@@ -43756,7 +43722,7 @@
       </x:c>
       <x:c r="P6" s="18"/>
       <x:c r="Q6" s="29" t="s">
-        <x:v>242</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="R6" s="18"/>
       <x:c r="S6" s="18"/>
@@ -44212,7 +44178,7 @@
     </x:row>
     <x:row r="11" ht="13.5" customHeight="1">
       <x:c r="A11" s="26" t="s">
-        <x:v>243</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B11" s="3"/>
       <x:c r="C11" s="3"/>
@@ -44232,7 +44198,7 @@
       <x:c r="Q11" s="3"/>
       <x:c r="R11" s="3"/>
       <x:c r="S11" s="26" t="s">
-        <x:v>244</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="T11" s="3"/>
       <x:c r="U11" s="3"/>
@@ -44510,7 +44476,7 @@
     </x:row>
     <x:row r="2" ht="13.5" customHeight="1">
       <x:c r="A2" s="22" t="s">
-        <x:v>245</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -44724,7 +44690,7 @@
       </x:c>
       <x:c r="P4" s="3"/>
       <x:c r="Q4" s="27" t="s">
-        <x:v>246</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="R4" s="3"/>
       <x:c r="S4" s="3"/>
@@ -44743,7 +44709,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AF4" s="27" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="AG4" s="3"/>
       <x:c r="AH4" s="3"/>
@@ -45304,7 +45270,7 @@
       <x:c r="Q10" s="3"/>
       <x:c r="R10" s="3"/>
       <x:c r="S10" s="26" t="s">
-        <x:v>248</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="T10" s="3"/>
       <x:c r="U10" s="3"/>
@@ -46360,7 +46326,7 @@
       <x:c r="O8" s="18"/>
       <x:c r="P8" s="18"/>
       <x:c r="Q8" s="29" t="s">
-        <x:v>249</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="R8" s="18"/>
       <x:c r="S8" s="18"/>
@@ -46544,7 +46510,7 @@
     </x:row>
     <x:row r="2" ht="13.5" customHeight="1">
       <x:c r="A2" s="22" t="s">
-        <x:v>250</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -46756,7 +46722,7 @@
       <x:c r="O4" s="6"/>
       <x:c r="P4" s="6"/>
       <x:c r="Q4" s="25" t="s">
-        <x:v>251</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="R4" s="6"/>
       <x:c r="S4" s="6"/>
@@ -46852,7 +46818,7 @@
       <x:c r="O5" s="14"/>
       <x:c r="P5" s="14"/>
       <x:c r="Q5" s="30" t="s">
-        <x:v>252</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="R5" s="14"/>
       <x:c r="S5" s="14"/>
@@ -47116,7 +47082,7 @@
     </x:row>
     <x:row r="8" ht="13.5" customHeight="1">
       <x:c r="A8" s="22" t="s">
-        <x:v>253</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B8" s="1"/>
       <x:c r="C8" s="1"/>
@@ -47345,8 +47311,8 @@
       <x:c r="AH10" s="3"/>
       <x:c r="AI10" s="3"/>
       <x:c r="AJ10" s="3"/>
-      <x:c r="AK10" s="34" t="s">
-        <x:v>254</x:v>
+      <x:c r="AK10" s="26" t="s">
+        <x:v>255</x:v>
       </x:c>
       <x:c r="AL10" s="3"/>
       <x:c r="AM10" s="3"/>
@@ -47422,7 +47388,7 @@
       <x:c r="O11" s="18"/>
       <x:c r="P11" s="18"/>
       <x:c r="Q11" s="29" t="s">
-        <x:v>249</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="R11" s="18"/>
       <x:c r="S11" s="18"/>
@@ -47722,7 +47688,7 @@
       </x:c>
       <x:c r="P3" s="6"/>
       <x:c r="Q3" s="25" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="R3" s="6"/>
       <x:c r="S3" s="6"/>
@@ -47741,7 +47707,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AF3" s="25" t="s">
-        <x:v>256</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="AG3" s="6"/>
       <x:c r="AH3" s="6"/>
@@ -48315,8 +48281,8 @@
       <x:c r="AH9" s="3"/>
       <x:c r="AI9" s="3"/>
       <x:c r="AJ9" s="3"/>
-      <x:c r="AK9" s="34" t="s">
-        <x:v>257</x:v>
+      <x:c r="AK9" s="26" t="s">
+        <x:v>258</x:v>
       </x:c>
       <x:c r="AL9" s="3"/>
       <x:c r="AM9" s="3"/>
@@ -48392,7 +48358,7 @@
       <x:c r="O10" s="18"/>
       <x:c r="P10" s="18"/>
       <x:c r="Q10" s="29" t="s">
-        <x:v>258</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="R10" s="18"/>
       <x:c r="S10" s="18"/>
@@ -48788,7 +48754,7 @@
       <x:c r="O4" s="18"/>
       <x:c r="P4" s="18"/>
       <x:c r="Q4" s="29" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="R4" s="18"/>
       <x:c r="S4" s="18"/>
@@ -49281,8 +49247,8 @@
       <x:c r="AH9" s="3"/>
       <x:c r="AI9" s="3"/>
       <x:c r="AJ9" s="3"/>
-      <x:c r="AK9" s="34" t="s">
-        <x:v>260</x:v>
+      <x:c r="AK9" s="26" t="s">
+        <x:v>261</x:v>
       </x:c>
       <x:c r="AL9" s="3"/>
       <x:c r="AM9" s="3"/>
@@ -49658,7 +49624,7 @@
       </x:c>
       <x:c r="P3" s="6"/>
       <x:c r="Q3" s="25" t="s">
-        <x:v>261</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="R3" s="6"/>
       <x:c r="S3" s="6"/>
@@ -49677,11 +49643,11 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AF3" s="25" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="AG3" s="6"/>
       <x:c r="AH3" s="25" t="s">
-        <x:v>263</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="AI3" s="6"/>
       <x:c r="AJ3" s="6"/>
@@ -49775,7 +49741,7 @@
       <x:c r="AF4" s="14"/>
       <x:c r="AG4" s="14"/>
       <x:c r="AH4" s="30" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="AI4" s="14"/>
       <x:c r="AJ4" s="14"/>
@@ -50058,7 +50024,7 @@
       </x:c>
       <x:c r="P3" s="6"/>
       <x:c r="Q3" s="25" t="s">
-        <x:v>264</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="R3" s="6"/>
       <x:c r="S3" s="6"/>
@@ -50077,7 +50043,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AF3" s="25" t="s">
-        <x:v>265</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="AG3" s="6"/>
       <x:c r="AH3" s="6"/>
@@ -50171,7 +50137,7 @@
       <x:c r="AD4" s="3"/>
       <x:c r="AE4" s="3"/>
       <x:c r="AF4" s="27" t="s">
-        <x:v>266</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="AG4" s="3"/>
       <x:c r="AH4" s="3"/>
@@ -50267,7 +50233,7 @@
       <x:c r="AF5" s="14"/>
       <x:c r="AG5" s="14"/>
       <x:c r="AH5" s="30" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="AI5" s="14"/>
       <x:c r="AJ5" s="14"/>
@@ -51236,7 +51202,7 @@
       </x:c>
       <x:c r="P3" s="6"/>
       <x:c r="Q3" s="25" t="s">
-        <x:v>268</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="R3" s="6"/>
       <x:c r="S3" s="6"/>
@@ -51256,8 +51222,8 @@
       </x:c>
       <x:c r="AF3" s="6"/>
       <x:c r="AG3" s="6"/>
-      <x:c r="AH3" s="25" t="str">
-        <x:v>(tb1.状態 = 'ACTIVE'</x:v>
+      <x:c r="AH3" s="25" t="s">
+        <x:v>270</x:v>
       </x:c>
       <x:c r="AI3" s="6"/>
       <x:c r="AJ3" s="6"/>
@@ -51352,8 +51318,8 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AG4" s="3"/>
-      <x:c r="AH4" s="27" t="str">
-        <x:v>tb1.削除日時 IS NULL) → 1</x:v>
+      <x:c r="AH4" s="27" t="s">
+        <x:v>271</x:v>
       </x:c>
       <x:c r="AI4" s="3"/>
       <x:c r="AJ4" s="3"/>
@@ -51445,7 +51411,7 @@
       <x:c r="AD5" s="14"/>
       <x:c r="AE5" s="14"/>
       <x:c r="AF5" s="30" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="AG5" s="14"/>
       <x:c r="AH5" s="14"/>
@@ -51802,7 +51768,7 @@
       <x:c r="CI3" s="4"/>
       <x:c r="CJ3" s="4"/>
       <x:c r="CK3" s="4"/>
-      <x:c r="CL3" s="35"/>
+      <x:c r="CL3" s="32"/>
     </x:row>
     <x:row r="4" ht="13.5" customHeight="1">
       <x:c r="A4" s="24" t="s">
@@ -51961,7 +51927,7 @@
       </x:c>
       <x:c r="BA5" s="3"/>
       <x:c r="BB5" s="27" t="s">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="BC5" s="3"/>
       <x:c r="BD5" s="3"/>
@@ -52053,7 +52019,7 @@
       <x:c r="AX6" s="14"/>
       <x:c r="AY6" s="14"/>
       <x:c r="AZ6" s="30" t="s">
-        <x:v>270</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="BA6" s="14"/>
       <x:c r="BB6" s="14"/>
@@ -52202,7 +52168,7 @@
     </x:row>
     <x:row r="2" ht="13.5" customHeight="1">
       <x:c r="A2" s="22" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -52390,7 +52356,7 @@
       <x:c r="CI3" s="4"/>
       <x:c r="CJ3" s="4"/>
       <x:c r="CK3" s="4"/>
-      <x:c r="CL3" s="35"/>
+      <x:c r="CL3" s="32"/>
     </x:row>
     <x:row r="4" ht="13.5" customHeight="1">
       <x:c r="A4" s="24" t="s">
@@ -52451,7 +52417,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AZ4" s="25" t="s">
-        <x:v>271</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="BA4" s="6"/>
       <x:c r="BB4" s="6"/>
@@ -52545,7 +52511,7 @@
       <x:c r="AX5" s="14"/>
       <x:c r="AY5" s="14"/>
       <x:c r="AZ5" s="30" t="s">
-        <x:v>270</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="BA5" s="14"/>
       <x:c r="BB5" s="14"/>
@@ -52810,7 +52776,7 @@
       </x:c>
       <x:c r="P3" s="6"/>
       <x:c r="Q3" s="25" t="s">
-        <x:v>272</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="R3" s="6"/>
       <x:c r="S3" s="6"/>
@@ -52904,7 +52870,7 @@
       <x:c r="O4" s="3"/>
       <x:c r="P4" s="3"/>
       <x:c r="Q4" s="27" t="s">
-        <x:v>273</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="R4" s="3"/>
       <x:c r="S4" s="3"/>
@@ -53290,7 +53256,7 @@
       <x:c r="E3" s="4"/>
       <x:c r="F3" s="4"/>
       <x:c r="G3" s="24" t="s">
-        <x:v>274</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="H3" s="6"/>
       <x:c r="I3" s="6"/>
@@ -53304,7 +53270,7 @@
       </x:c>
       <x:c r="P3" s="6"/>
       <x:c r="Q3" s="25" t="s">
-        <x:v>275</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="R3" s="6"/>
       <x:c r="S3" s="6"/>
@@ -53398,7 +53364,7 @@
       <x:c r="O4" s="3"/>
       <x:c r="P4" s="3"/>
       <x:c r="Q4" s="27" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="R4" s="3"/>
       <x:c r="S4" s="3"/>
@@ -53917,7 +53883,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AF3" s="25" t="s">
-        <x:v>276</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="AG3" s="6"/>
       <x:c r="AH3" s="6"/>
@@ -54011,7 +53977,7 @@
       <x:c r="AD4" s="14"/>
       <x:c r="AE4" s="14"/>
       <x:c r="AF4" s="30" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="AG4" s="14"/>
       <x:c r="AH4" s="14"/>
@@ -54079,1439 +54045,1350 @@
 
 <file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultRowHeight="18.75"/>
   <x:cols>
-    <x:col min="1" max="1" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="22" max="22" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="24" max="24" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="25" max="25" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="26" max="26" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="27" max="27" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="28" max="28" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="29" max="29" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="30" max="30" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="31" max="31" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="32" max="32" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="33" max="33" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="34" max="34" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="35" max="35" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="36" max="36" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="37" max="37" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="38" max="38" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="39" max="39" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="40" max="40" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="41" max="41" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="42" max="42" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="43" max="43" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="44" max="44" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="45" max="45" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="46" max="46" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="47" max="47" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="48" max="48" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="49" max="49" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="50" max="50" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="51" max="51" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="52" max="52" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="53" max="53" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="54" max="54" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="55" max="55" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="56" max="56" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="57" max="57" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="58" max="58" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="59" max="59" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="60" max="60" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="61" max="61" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="62" max="62" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="63" max="63" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="64" max="64" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="65" max="65" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="66" max="66" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="67" max="67" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="68" max="68" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="69" max="69" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="70" max="70" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="71" max="71" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="72" max="72" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="73" max="73" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="74" max="74" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="75" max="75" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="76" max="76" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="77" max="77" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="78" max="78" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="79" max="79" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="80" max="80" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="81" max="81" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="82" max="82" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="83" max="83" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="84" max="84" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="85" max="85" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="86" max="86" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="87" max="87" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="88" max="88" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="89" max="89" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="90" max="90" width="1.1399999856948853" hidden="0" customWidth="1"/>
+    <x:col min="1" max="90" width="1.125" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="13.5" customHeight="1">
-      <x:c r="A1" s="61" t="s">
+      <x:c r="A1" s="1" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="B1" s="61"/>
-      <x:c r="C1" s="61"/>
-      <x:c r="D1" s="61"/>
-      <x:c r="E1" s="61"/>
-      <x:c r="F1" s="61"/>
-      <x:c r="G1" s="61"/>
-      <x:c r="H1" s="61"/>
-      <x:c r="I1" s="61"/>
-      <x:c r="J1" s="61"/>
-      <x:c r="K1" s="61"/>
-      <x:c r="L1" s="61"/>
-      <x:c r="M1" s="61"/>
-      <x:c r="N1" s="61"/>
-      <x:c r="O1" s="61"/>
-      <x:c r="P1" s="61"/>
-      <x:c r="Q1" s="61"/>
-      <x:c r="R1" s="61"/>
-      <x:c r="S1" s="61"/>
-      <x:c r="T1" s="61"/>
-      <x:c r="U1" s="61"/>
-      <x:c r="V1" s="61"/>
-      <x:c r="W1" s="61"/>
-      <x:c r="X1" s="61"/>
-      <x:c r="Y1" s="61"/>
-      <x:c r="Z1" s="61"/>
-      <x:c r="AA1" s="61"/>
-      <x:c r="AB1" s="61"/>
-      <x:c r="AC1" s="61"/>
-      <x:c r="AD1" s="61"/>
-      <x:c r="AE1" s="61"/>
-      <x:c r="AF1" s="61"/>
-      <x:c r="AG1" s="61"/>
-      <x:c r="AH1" s="61"/>
-      <x:c r="AI1" s="61"/>
-      <x:c r="AJ1" s="61"/>
-      <x:c r="AK1" s="61"/>
-      <x:c r="AL1" s="61"/>
-      <x:c r="AM1" s="61"/>
-      <x:c r="AN1" s="61"/>
-      <x:c r="AO1" s="61"/>
-      <x:c r="AP1" s="61"/>
-      <x:c r="AQ1" s="61"/>
-      <x:c r="AR1" s="61"/>
-      <x:c r="AS1" s="61"/>
-      <x:c r="AT1" s="61"/>
-      <x:c r="AU1" s="61"/>
-      <x:c r="AV1" s="61"/>
-      <x:c r="AW1" s="61"/>
-      <x:c r="AX1" s="61"/>
-      <x:c r="AY1" s="61"/>
-      <x:c r="AZ1" s="61"/>
-      <x:c r="BA1" s="61"/>
-      <x:c r="BB1" s="61"/>
-      <x:c r="BC1" s="61"/>
-      <x:c r="BD1" s="61"/>
-      <x:c r="BE1" s="61"/>
-      <x:c r="BF1" s="61"/>
-      <x:c r="BG1" s="61"/>
-      <x:c r="BH1" s="61"/>
-      <x:c r="BI1" s="61"/>
-      <x:c r="BJ1" s="61"/>
-      <x:c r="BK1" s="61"/>
-      <x:c r="BL1" s="61"/>
-      <x:c r="BM1" s="61"/>
-      <x:c r="BN1" s="61"/>
-      <x:c r="BO1" s="61"/>
-      <x:c r="BP1" s="61"/>
-      <x:c r="BQ1" s="61"/>
-      <x:c r="BR1" s="61"/>
-      <x:c r="BS1" s="61"/>
-      <x:c r="BT1" s="61"/>
-      <x:c r="BU1" s="61"/>
-      <x:c r="BV1" s="61"/>
-      <x:c r="BW1" s="61"/>
-      <x:c r="BX1" s="61"/>
-      <x:c r="BY1" s="61"/>
-      <x:c r="BZ1" s="61"/>
-      <x:c r="CA1" s="61"/>
-      <x:c r="CB1" s="61"/>
-      <x:c r="CC1" s="61"/>
-      <x:c r="CD1" s="61"/>
-      <x:c r="CE1" s="61"/>
-      <x:c r="CF1" s="61"/>
-      <x:c r="CG1" s="61"/>
-      <x:c r="CH1" s="61"/>
-      <x:c r="CI1" s="61"/>
-      <x:c r="CJ1" s="61"/>
-      <x:c r="CK1" s="61"/>
-      <x:c r="CL1" s="61"/>
+      <x:c r="B1" s="1"/>
+      <x:c r="C1" s="1"/>
+      <x:c r="D1" s="1"/>
+      <x:c r="E1" s="1"/>
+      <x:c r="F1" s="1"/>
+      <x:c r="G1" s="1"/>
+      <x:c r="H1" s="1"/>
+      <x:c r="I1" s="1"/>
+      <x:c r="J1" s="1"/>
+      <x:c r="K1" s="1"/>
+      <x:c r="L1" s="1"/>
+      <x:c r="M1" s="1"/>
+      <x:c r="N1" s="1"/>
+      <x:c r="O1" s="1"/>
+      <x:c r="P1" s="1"/>
+      <x:c r="Q1" s="1"/>
+      <x:c r="R1" s="1"/>
+      <x:c r="S1" s="1"/>
+      <x:c r="T1" s="1"/>
+      <x:c r="U1" s="1"/>
+      <x:c r="V1" s="1"/>
+      <x:c r="W1" s="1"/>
+      <x:c r="X1" s="1"/>
+      <x:c r="Y1" s="1"/>
+      <x:c r="Z1" s="1"/>
+      <x:c r="AA1" s="1"/>
+      <x:c r="AB1" s="1"/>
+      <x:c r="AC1" s="1"/>
+      <x:c r="AD1" s="1"/>
+      <x:c r="AE1" s="1"/>
+      <x:c r="AF1" s="1"/>
+      <x:c r="AG1" s="1"/>
+      <x:c r="AH1" s="1"/>
+      <x:c r="AI1" s="1"/>
+      <x:c r="AJ1" s="1"/>
+      <x:c r="AK1" s="1"/>
+      <x:c r="AL1" s="1"/>
+      <x:c r="AM1" s="1"/>
+      <x:c r="AN1" s="1"/>
+      <x:c r="AO1" s="1"/>
+      <x:c r="AP1" s="1"/>
+      <x:c r="AQ1" s="1"/>
+      <x:c r="AR1" s="1"/>
+      <x:c r="AS1" s="1"/>
+      <x:c r="AT1" s="1"/>
+      <x:c r="AU1" s="1"/>
+      <x:c r="AV1" s="1"/>
+      <x:c r="AW1" s="1"/>
+      <x:c r="AX1" s="1"/>
+      <x:c r="AY1" s="1"/>
+      <x:c r="AZ1" s="1"/>
+      <x:c r="BA1" s="1"/>
+      <x:c r="BB1" s="1"/>
+      <x:c r="BC1" s="1"/>
+      <x:c r="BD1" s="1"/>
+      <x:c r="BE1" s="1"/>
+      <x:c r="BF1" s="1"/>
+      <x:c r="BG1" s="1"/>
+      <x:c r="BH1" s="1"/>
+      <x:c r="BI1" s="1"/>
+      <x:c r="BJ1" s="1"/>
+      <x:c r="BK1" s="1"/>
+      <x:c r="BL1" s="1"/>
+      <x:c r="BM1" s="1"/>
+      <x:c r="BN1" s="1"/>
+      <x:c r="BO1" s="1"/>
+      <x:c r="BP1" s="1"/>
+      <x:c r="BQ1" s="1"/>
+      <x:c r="BR1" s="1"/>
+      <x:c r="BS1" s="1"/>
+      <x:c r="BT1" s="1"/>
+      <x:c r="BU1" s="1"/>
+      <x:c r="BV1" s="1"/>
+      <x:c r="BW1" s="1"/>
+      <x:c r="BX1" s="1"/>
+      <x:c r="BY1" s="1"/>
+      <x:c r="BZ1" s="1"/>
+      <x:c r="CA1" s="1"/>
+      <x:c r="CB1" s="1"/>
+      <x:c r="CC1" s="1"/>
+      <x:c r="CD1" s="1"/>
+      <x:c r="CE1" s="1"/>
+      <x:c r="CF1" s="1"/>
+      <x:c r="CG1" s="1"/>
+      <x:c r="CH1" s="1"/>
+      <x:c r="CI1" s="1"/>
+      <x:c r="CJ1" s="1"/>
+      <x:c r="CK1" s="1"/>
+      <x:c r="CL1" s="1"/>
     </x:row>
     <x:row r="2" ht="13.5" customHeight="1">
-      <x:c r="A2" s="61" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="B2" s="61"/>
-      <x:c r="C2" s="61"/>
-      <x:c r="D2" s="61"/>
-      <x:c r="E2" s="61"/>
-      <x:c r="F2" s="61"/>
-      <x:c r="G2" s="61"/>
-      <x:c r="H2" s="61"/>
-      <x:c r="I2" s="61"/>
-      <x:c r="J2" s="61"/>
-      <x:c r="K2" s="61"/>
-      <x:c r="L2" s="61"/>
-      <x:c r="M2" s="61"/>
-      <x:c r="N2" s="61"/>
-      <x:c r="O2" s="61"/>
-      <x:c r="P2" s="61"/>
-      <x:c r="Q2" s="61"/>
-      <x:c r="R2" s="61"/>
-      <x:c r="S2" s="61"/>
-      <x:c r="T2" s="61"/>
-      <x:c r="U2" s="61"/>
-      <x:c r="V2" s="61"/>
-      <x:c r="W2" s="61"/>
-      <x:c r="X2" s="61"/>
-      <x:c r="Y2" s="61"/>
-      <x:c r="Z2" s="61"/>
-      <x:c r="AA2" s="61"/>
-      <x:c r="AB2" s="61"/>
-      <x:c r="AC2" s="61"/>
-      <x:c r="AD2" s="61"/>
-      <x:c r="AE2" s="61"/>
-      <x:c r="AF2" s="61"/>
-      <x:c r="AG2" s="61"/>
-      <x:c r="AH2" s="61"/>
-      <x:c r="AI2" s="61"/>
-      <x:c r="AJ2" s="61"/>
-      <x:c r="AK2" s="61"/>
-      <x:c r="AL2" s="61"/>
-      <x:c r="AM2" s="61"/>
-      <x:c r="AN2" s="61"/>
-      <x:c r="AO2" s="61"/>
-      <x:c r="AP2" s="61"/>
-      <x:c r="AQ2" s="61"/>
-      <x:c r="AR2" s="61"/>
-      <x:c r="AS2" s="61"/>
-      <x:c r="AT2" s="61"/>
-      <x:c r="AU2" s="61"/>
-      <x:c r="AV2" s="61"/>
-      <x:c r="AW2" s="61"/>
-      <x:c r="AX2" s="61"/>
-      <x:c r="AY2" s="61"/>
-      <x:c r="AZ2" s="61"/>
-      <x:c r="BA2" s="61"/>
-      <x:c r="BB2" s="61"/>
-      <x:c r="BC2" s="61"/>
-      <x:c r="BD2" s="61"/>
-      <x:c r="BE2" s="61"/>
-      <x:c r="BF2" s="61"/>
-      <x:c r="BG2" s="61"/>
-      <x:c r="BH2" s="61"/>
-      <x:c r="BI2" s="61"/>
-      <x:c r="BJ2" s="61"/>
-      <x:c r="BK2" s="61"/>
-      <x:c r="BL2" s="61"/>
-      <x:c r="BM2" s="61"/>
-      <x:c r="BN2" s="61"/>
-      <x:c r="BO2" s="61"/>
-      <x:c r="BP2" s="61"/>
-      <x:c r="BQ2" s="61"/>
-      <x:c r="BR2" s="61"/>
-      <x:c r="BS2" s="61"/>
-      <x:c r="BT2" s="61"/>
-      <x:c r="BU2" s="61"/>
-      <x:c r="BV2" s="61"/>
-      <x:c r="BW2" s="61"/>
-      <x:c r="BX2" s="61"/>
-      <x:c r="BY2" s="61"/>
-      <x:c r="BZ2" s="61"/>
-      <x:c r="CA2" s="61"/>
-      <x:c r="CB2" s="61"/>
-      <x:c r="CC2" s="61"/>
-      <x:c r="CD2" s="61"/>
-      <x:c r="CE2" s="61"/>
-      <x:c r="CF2" s="61"/>
-      <x:c r="CG2" s="61"/>
-      <x:c r="CH2" s="61"/>
-      <x:c r="CI2" s="61"/>
-      <x:c r="CJ2" s="61"/>
-      <x:c r="CK2" s="61"/>
-      <x:c r="CL2" s="61"/>
+      <x:c r="A2" s="1" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="B2" s="1"/>
+      <x:c r="C2" s="1"/>
+      <x:c r="D2" s="1"/>
+      <x:c r="E2" s="1"/>
+      <x:c r="F2" s="1"/>
+      <x:c r="G2" s="1"/>
+      <x:c r="H2" s="1"/>
+      <x:c r="I2" s="1"/>
+      <x:c r="J2" s="1"/>
+      <x:c r="K2" s="1"/>
+      <x:c r="L2" s="1"/>
+      <x:c r="M2" s="1"/>
+      <x:c r="N2" s="1"/>
+      <x:c r="O2" s="1"/>
+      <x:c r="P2" s="1"/>
+      <x:c r="Q2" s="1"/>
+      <x:c r="R2" s="1"/>
+      <x:c r="S2" s="1"/>
+      <x:c r="T2" s="1"/>
+      <x:c r="U2" s="1"/>
+      <x:c r="V2" s="1"/>
+      <x:c r="W2" s="1"/>
+      <x:c r="X2" s="1"/>
+      <x:c r="Y2" s="1"/>
+      <x:c r="Z2" s="1"/>
+      <x:c r="AA2" s="1"/>
+      <x:c r="AB2" s="1"/>
+      <x:c r="AC2" s="1"/>
+      <x:c r="AD2" s="1"/>
+      <x:c r="AE2" s="1"/>
+      <x:c r="AF2" s="1"/>
+      <x:c r="AG2" s="1"/>
+      <x:c r="AH2" s="1"/>
+      <x:c r="AI2" s="1"/>
+      <x:c r="AJ2" s="1"/>
+      <x:c r="AK2" s="1"/>
+      <x:c r="AL2" s="1"/>
+      <x:c r="AM2" s="1"/>
+      <x:c r="AN2" s="1"/>
+      <x:c r="AO2" s="1"/>
+      <x:c r="AP2" s="1"/>
+      <x:c r="AQ2" s="1"/>
+      <x:c r="AR2" s="1"/>
+      <x:c r="AS2" s="1"/>
+      <x:c r="AT2" s="1"/>
+      <x:c r="AU2" s="1"/>
+      <x:c r="AV2" s="1"/>
+      <x:c r="AW2" s="1"/>
+      <x:c r="AX2" s="1"/>
+      <x:c r="AY2" s="1"/>
+      <x:c r="AZ2" s="1"/>
+      <x:c r="BA2" s="1"/>
+      <x:c r="BB2" s="1"/>
+      <x:c r="BC2" s="1"/>
+      <x:c r="BD2" s="1"/>
+      <x:c r="BE2" s="1"/>
+      <x:c r="BF2" s="1"/>
+      <x:c r="BG2" s="1"/>
+      <x:c r="BH2" s="1"/>
+      <x:c r="BI2" s="1"/>
+      <x:c r="BJ2" s="1"/>
+      <x:c r="BK2" s="1"/>
+      <x:c r="BL2" s="1"/>
+      <x:c r="BM2" s="1"/>
+      <x:c r="BN2" s="1"/>
+      <x:c r="BO2" s="1"/>
+      <x:c r="BP2" s="1"/>
+      <x:c r="BQ2" s="1"/>
+      <x:c r="BR2" s="1"/>
+      <x:c r="BS2" s="1"/>
+      <x:c r="BT2" s="1"/>
+      <x:c r="BU2" s="1"/>
+      <x:c r="BV2" s="1"/>
+      <x:c r="BW2" s="1"/>
+      <x:c r="BX2" s="1"/>
+      <x:c r="BY2" s="1"/>
+      <x:c r="BZ2" s="1"/>
+      <x:c r="CA2" s="1"/>
+      <x:c r="CB2" s="1"/>
+      <x:c r="CC2" s="1"/>
+      <x:c r="CD2" s="1"/>
+      <x:c r="CE2" s="1"/>
+      <x:c r="CF2" s="1"/>
+      <x:c r="CG2" s="1"/>
+      <x:c r="CH2" s="1"/>
+      <x:c r="CI2" s="1"/>
+      <x:c r="CJ2" s="1"/>
+      <x:c r="CK2" s="1"/>
+      <x:c r="CL2" s="1"/>
     </x:row>
     <x:row r="3" ht="13.5" customHeight="1">
-      <x:c r="A3" s="63" t="str">
-        <x:v>＜VALUES 1行目＞</x:v>
-      </x:c>
-      <x:c r="B3" s="63"/>
-      <x:c r="C3" s="63"/>
-      <x:c r="D3" s="63"/>
-      <x:c r="E3" s="63"/>
-      <x:c r="F3" s="63"/>
-      <x:c r="G3" s="63"/>
-      <x:c r="H3" s="63"/>
-      <x:c r="I3" s="63"/>
-      <x:c r="J3" s="63"/>
-      <x:c r="K3" s="63"/>
-      <x:c r="L3" s="63"/>
-      <x:c r="M3" s="63"/>
-      <x:c r="N3" s="63"/>
-      <x:c r="O3" s="63"/>
-      <x:c r="P3" s="63"/>
-      <x:c r="Q3" s="63"/>
-      <x:c r="R3" s="63"/>
-      <x:c r="S3" s="63"/>
-      <x:c r="T3" s="63"/>
-      <x:c r="U3" s="63"/>
-      <x:c r="V3" s="63"/>
-      <x:c r="W3" s="63"/>
-      <x:c r="X3" s="63"/>
-      <x:c r="Y3" s="63"/>
-      <x:c r="Z3" s="63"/>
-      <x:c r="AA3" s="63"/>
-      <x:c r="AB3" s="63"/>
-      <x:c r="AC3" s="63"/>
-      <x:c r="AD3" s="63"/>
-      <x:c r="AE3" s="63"/>
-      <x:c r="AF3" s="63"/>
-      <x:c r="AG3" s="63"/>
-      <x:c r="AH3" s="63"/>
-      <x:c r="AI3" s="63"/>
-      <x:c r="AJ3" s="63"/>
-      <x:c r="AK3" s="63"/>
-      <x:c r="AL3" s="63"/>
-      <x:c r="AM3" s="63"/>
-      <x:c r="AN3" s="63"/>
-      <x:c r="AO3" s="63"/>
-      <x:c r="AP3" s="63"/>
-      <x:c r="AQ3" s="63"/>
-      <x:c r="AR3" s="63"/>
-      <x:c r="AS3" s="63"/>
-      <x:c r="AT3" s="63"/>
-      <x:c r="AU3" s="63"/>
-      <x:c r="AV3" s="63"/>
-      <x:c r="AW3" s="63"/>
-      <x:c r="AX3" s="63"/>
-      <x:c r="AY3" s="63"/>
-      <x:c r="AZ3" s="63"/>
-      <x:c r="BA3" s="63"/>
-      <x:c r="BB3" s="63"/>
-      <x:c r="BC3" s="63"/>
-      <x:c r="BD3" s="63"/>
-      <x:c r="BE3" s="63"/>
-      <x:c r="BF3" s="63"/>
-      <x:c r="BG3" s="63"/>
-      <x:c r="BH3" s="63"/>
-      <x:c r="BI3" s="63"/>
-      <x:c r="BJ3" s="63"/>
-      <x:c r="BK3" s="63"/>
-      <x:c r="BL3" s="63"/>
-      <x:c r="BM3" s="63"/>
-      <x:c r="BN3" s="63"/>
-      <x:c r="BO3" s="63"/>
-      <x:c r="BP3" s="63"/>
-      <x:c r="BQ3" s="63"/>
-      <x:c r="BR3" s="63"/>
-      <x:c r="BS3" s="63"/>
-      <x:c r="BT3" s="63"/>
-      <x:c r="BU3" s="63"/>
-      <x:c r="BV3" s="63"/>
-      <x:c r="BW3" s="63"/>
-      <x:c r="BX3" s="63"/>
-      <x:c r="BY3" s="63"/>
-      <x:c r="BZ3" s="63"/>
-      <x:c r="CA3" s="63"/>
-      <x:c r="CB3" s="63"/>
-      <x:c r="CC3" s="63"/>
-      <x:c r="CD3" s="63"/>
-      <x:c r="CE3" s="63"/>
-      <x:c r="CF3" s="63"/>
-      <x:c r="CG3" s="63"/>
-      <x:c r="CH3" s="63"/>
-      <x:c r="CI3" s="63"/>
-      <x:c r="CJ3" s="63"/>
-      <x:c r="CK3" s="63"/>
-      <x:c r="CL3" s="63"/>
+      <x:c r="A3" s="61" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="B3" s="61"/>
+      <x:c r="C3" s="61"/>
+      <x:c r="D3" s="61"/>
+      <x:c r="E3" s="61"/>
+      <x:c r="F3" s="61"/>
+      <x:c r="G3" s="61"/>
+      <x:c r="H3" s="61"/>
+      <x:c r="I3" s="61"/>
+      <x:c r="J3" s="61"/>
+      <x:c r="K3" s="61"/>
+      <x:c r="L3" s="61"/>
+      <x:c r="M3" s="61"/>
+      <x:c r="N3" s="61"/>
+      <x:c r="O3" s="61"/>
+      <x:c r="P3" s="61"/>
+      <x:c r="Q3" s="61"/>
+      <x:c r="R3" s="61"/>
+      <x:c r="S3" s="61"/>
+      <x:c r="T3" s="61"/>
+      <x:c r="U3" s="61"/>
+      <x:c r="V3" s="61"/>
+      <x:c r="W3" s="61"/>
+      <x:c r="X3" s="61"/>
+      <x:c r="Y3" s="61"/>
+      <x:c r="Z3" s="61"/>
+      <x:c r="AA3" s="61"/>
+      <x:c r="AB3" s="61"/>
+      <x:c r="AC3" s="61"/>
+      <x:c r="AD3" s="61"/>
+      <x:c r="AE3" s="61"/>
+      <x:c r="AF3" s="61"/>
+      <x:c r="AG3" s="61"/>
+      <x:c r="AH3" s="61"/>
+      <x:c r="AI3" s="61"/>
+      <x:c r="AJ3" s="61"/>
+      <x:c r="AK3" s="61"/>
+      <x:c r="AL3" s="61"/>
+      <x:c r="AM3" s="61"/>
+      <x:c r="AN3" s="61"/>
+      <x:c r="AO3" s="61"/>
+      <x:c r="AP3" s="61"/>
+      <x:c r="AQ3" s="61"/>
+      <x:c r="AR3" s="61"/>
+      <x:c r="AS3" s="61"/>
+      <x:c r="AT3" s="61"/>
+      <x:c r="AU3" s="61"/>
+      <x:c r="AV3" s="61"/>
+      <x:c r="AW3" s="61"/>
+      <x:c r="AX3" s="61"/>
+      <x:c r="AY3" s="61"/>
+      <x:c r="AZ3" s="61"/>
+      <x:c r="BA3" s="61"/>
+      <x:c r="BB3" s="61"/>
+      <x:c r="BC3" s="61"/>
+      <x:c r="BD3" s="61"/>
+      <x:c r="BE3" s="61"/>
+      <x:c r="BF3" s="61"/>
+      <x:c r="BG3" s="61"/>
+      <x:c r="BH3" s="61"/>
+      <x:c r="BI3" s="61"/>
+      <x:c r="BJ3" s="61"/>
+      <x:c r="BK3" s="61"/>
+      <x:c r="BL3" s="61"/>
+      <x:c r="BM3" s="61"/>
+      <x:c r="BN3" s="61"/>
+      <x:c r="BO3" s="61"/>
+      <x:c r="BP3" s="61"/>
+      <x:c r="BQ3" s="61"/>
+      <x:c r="BR3" s="61"/>
+      <x:c r="BS3" s="61"/>
+      <x:c r="BT3" s="61"/>
+      <x:c r="BU3" s="61"/>
+      <x:c r="BV3" s="61"/>
+      <x:c r="BW3" s="61"/>
+      <x:c r="BX3" s="61"/>
+      <x:c r="BY3" s="61"/>
+      <x:c r="BZ3" s="61"/>
+      <x:c r="CA3" s="61"/>
+      <x:c r="CB3" s="61"/>
+      <x:c r="CC3" s="61"/>
+      <x:c r="CD3" s="61"/>
+      <x:c r="CE3" s="61"/>
+      <x:c r="CF3" s="61"/>
+      <x:c r="CG3" s="61"/>
+      <x:c r="CH3" s="61"/>
+      <x:c r="CI3" s="61"/>
+      <x:c r="CJ3" s="61"/>
+      <x:c r="CK3" s="61"/>
+      <x:c r="CL3" s="61"/>
     </x:row>
     <x:row r="4" ht="13.5" customHeight="1">
-      <x:c r="A4" s="67" t="s">
+      <x:c r="A4" s="50" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="B4" s="68"/>
-      <x:c r="C4" s="68"/>
-      <x:c r="D4" s="68"/>
-      <x:c r="E4" s="68"/>
-      <x:c r="F4" s="68"/>
-      <x:c r="G4" s="68"/>
-      <x:c r="H4" s="68"/>
-      <x:c r="I4" s="68"/>
-      <x:c r="J4" s="68"/>
-      <x:c r="K4" s="68"/>
-      <x:c r="L4" s="68"/>
-      <x:c r="M4" s="68"/>
-      <x:c r="N4" s="68"/>
-      <x:c r="O4" s="68"/>
-      <x:c r="P4" s="68"/>
-      <x:c r="Q4" s="68"/>
-      <x:c r="R4" s="68"/>
-      <x:c r="S4" s="67" t="s">
+      <x:c r="B4" s="51"/>
+      <x:c r="C4" s="51"/>
+      <x:c r="D4" s="51"/>
+      <x:c r="E4" s="51"/>
+      <x:c r="F4" s="51"/>
+      <x:c r="G4" s="51"/>
+      <x:c r="H4" s="51"/>
+      <x:c r="I4" s="51"/>
+      <x:c r="J4" s="51"/>
+      <x:c r="K4" s="51"/>
+      <x:c r="L4" s="51"/>
+      <x:c r="M4" s="51"/>
+      <x:c r="N4" s="51"/>
+      <x:c r="O4" s="51"/>
+      <x:c r="P4" s="51"/>
+      <x:c r="Q4" s="51"/>
+      <x:c r="R4" s="51"/>
+      <x:c r="S4" s="50" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="T4" s="68"/>
-      <x:c r="U4" s="68"/>
-      <x:c r="V4" s="68"/>
-      <x:c r="W4" s="68"/>
-      <x:c r="X4" s="68"/>
-      <x:c r="Y4" s="68"/>
-      <x:c r="Z4" s="68"/>
-      <x:c r="AA4" s="68"/>
-      <x:c r="AB4" s="68"/>
-      <x:c r="AC4" s="68"/>
-      <x:c r="AD4" s="68"/>
-      <x:c r="AE4" s="68"/>
-      <x:c r="AF4" s="68"/>
-      <x:c r="AG4" s="68"/>
-      <x:c r="AH4" s="68"/>
-      <x:c r="AI4" s="68"/>
-      <x:c r="AJ4" s="68"/>
-      <x:c r="AK4" s="67" t="str">
-        <x:v>移送方法ほか</x:v>
-      </x:c>
-      <x:c r="AL4" s="68"/>
-      <x:c r="AM4" s="68"/>
-      <x:c r="AN4" s="68"/>
-      <x:c r="AO4" s="68"/>
-      <x:c r="AP4" s="68"/>
-      <x:c r="AQ4" s="68"/>
-      <x:c r="AR4" s="68"/>
-      <x:c r="AS4" s="68"/>
-      <x:c r="AT4" s="68"/>
-      <x:c r="AU4" s="68"/>
-      <x:c r="AV4" s="68"/>
-      <x:c r="AW4" s="68"/>
-      <x:c r="AX4" s="68"/>
-      <x:c r="AY4" s="68"/>
-      <x:c r="AZ4" s="68"/>
-      <x:c r="BA4" s="68"/>
-      <x:c r="BB4" s="68"/>
-      <x:c r="BC4" s="68"/>
-      <x:c r="BD4" s="68"/>
-      <x:c r="BE4" s="68"/>
-      <x:c r="BF4" s="68"/>
-      <x:c r="BG4" s="68"/>
-      <x:c r="BH4" s="68"/>
-      <x:c r="BI4" s="68"/>
-      <x:c r="BJ4" s="68"/>
-      <x:c r="BK4" s="68"/>
-      <x:c r="BL4" s="68"/>
-      <x:c r="BM4" s="68"/>
-      <x:c r="BN4" s="68"/>
-      <x:c r="BO4" s="68"/>
-      <x:c r="BP4" s="68"/>
-      <x:c r="BQ4" s="68"/>
-      <x:c r="BR4" s="68"/>
-      <x:c r="BS4" s="68"/>
-      <x:c r="BT4" s="68"/>
-      <x:c r="BU4" s="68"/>
-      <x:c r="BV4" s="68"/>
-      <x:c r="BW4" s="68"/>
-      <x:c r="BX4" s="68"/>
-      <x:c r="BY4" s="68"/>
-      <x:c r="BZ4" s="68"/>
-      <x:c r="CA4" s="68"/>
-      <x:c r="CB4" s="68"/>
-      <x:c r="CC4" s="68"/>
-      <x:c r="CD4" s="68"/>
-      <x:c r="CE4" s="68"/>
-      <x:c r="CF4" s="68"/>
-      <x:c r="CG4" s="68"/>
-      <x:c r="CH4" s="68"/>
-      <x:c r="CI4" s="68"/>
-      <x:c r="CJ4" s="68"/>
-      <x:c r="CK4" s="68"/>
-      <x:c r="CL4" s="69"/>
+      <x:c r="T4" s="51"/>
+      <x:c r="U4" s="51"/>
+      <x:c r="V4" s="51"/>
+      <x:c r="W4" s="51"/>
+      <x:c r="X4" s="51"/>
+      <x:c r="Y4" s="51"/>
+      <x:c r="Z4" s="51"/>
+      <x:c r="AA4" s="51"/>
+      <x:c r="AB4" s="51"/>
+      <x:c r="AC4" s="51"/>
+      <x:c r="AD4" s="51"/>
+      <x:c r="AE4" s="51"/>
+      <x:c r="AF4" s="51"/>
+      <x:c r="AG4" s="51"/>
+      <x:c r="AH4" s="51"/>
+      <x:c r="AI4" s="51"/>
+      <x:c r="AJ4" s="51"/>
+      <x:c r="AK4" s="50" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="AL4" s="51"/>
+      <x:c r="AM4" s="51"/>
+      <x:c r="AN4" s="51"/>
+      <x:c r="AO4" s="51"/>
+      <x:c r="AP4" s="51"/>
+      <x:c r="AQ4" s="51"/>
+      <x:c r="AR4" s="51"/>
+      <x:c r="AS4" s="51"/>
+      <x:c r="AT4" s="51"/>
+      <x:c r="AU4" s="51"/>
+      <x:c r="AV4" s="51"/>
+      <x:c r="AW4" s="51"/>
+      <x:c r="AX4" s="51"/>
+      <x:c r="AY4" s="51"/>
+      <x:c r="AZ4" s="51"/>
+      <x:c r="BA4" s="51"/>
+      <x:c r="BB4" s="51"/>
+      <x:c r="BC4" s="51"/>
+      <x:c r="BD4" s="51"/>
+      <x:c r="BE4" s="51"/>
+      <x:c r="BF4" s="51"/>
+      <x:c r="BG4" s="51"/>
+      <x:c r="BH4" s="51"/>
+      <x:c r="BI4" s="51"/>
+      <x:c r="BJ4" s="51"/>
+      <x:c r="BK4" s="51"/>
+      <x:c r="BL4" s="51"/>
+      <x:c r="BM4" s="51"/>
+      <x:c r="BN4" s="51"/>
+      <x:c r="BO4" s="51"/>
+      <x:c r="BP4" s="51"/>
+      <x:c r="BQ4" s="51"/>
+      <x:c r="BR4" s="51"/>
+      <x:c r="BS4" s="51"/>
+      <x:c r="BT4" s="51"/>
+      <x:c r="BU4" s="51"/>
+      <x:c r="BV4" s="51"/>
+      <x:c r="BW4" s="51"/>
+      <x:c r="BX4" s="51"/>
+      <x:c r="BY4" s="51"/>
+      <x:c r="BZ4" s="51"/>
+      <x:c r="CA4" s="51"/>
+      <x:c r="CB4" s="51"/>
+      <x:c r="CC4" s="51"/>
+      <x:c r="CD4" s="51"/>
+      <x:c r="CE4" s="51"/>
+      <x:c r="CF4" s="51"/>
+      <x:c r="CG4" s="51"/>
+      <x:c r="CH4" s="51"/>
+      <x:c r="CI4" s="51"/>
+      <x:c r="CJ4" s="51"/>
+      <x:c r="CK4" s="51"/>
+      <x:c r="CL4" s="52"/>
     </x:row>
     <x:row r="5" ht="13.5" customHeight="1">
-      <x:c r="A5" s="64" t="s">
+      <x:c r="A5" s="47" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="B5" s="65"/>
-      <x:c r="C5" s="65"/>
-      <x:c r="D5" s="65"/>
-      <x:c r="E5" s="65"/>
-      <x:c r="F5" s="65"/>
-      <x:c r="G5" s="65"/>
-      <x:c r="H5" s="65"/>
-      <x:c r="I5" s="65"/>
-      <x:c r="J5" s="65"/>
-      <x:c r="K5" s="65"/>
-      <x:c r="L5" s="65"/>
-      <x:c r="M5" s="65"/>
-      <x:c r="N5" s="65"/>
-      <x:c r="O5" s="65"/>
-      <x:c r="P5" s="65"/>
-      <x:c r="Q5" s="65"/>
-      <x:c r="R5" s="65"/>
-      <x:c r="S5" s="64"/>
-      <x:c r="T5" s="65"/>
-      <x:c r="U5" s="65"/>
-      <x:c r="V5" s="65"/>
-      <x:c r="W5" s="65"/>
-      <x:c r="X5" s="65"/>
-      <x:c r="Y5" s="65"/>
-      <x:c r="Z5" s="65"/>
-      <x:c r="AA5" s="65"/>
-      <x:c r="AB5" s="65"/>
-      <x:c r="AC5" s="65"/>
-      <x:c r="AD5" s="65"/>
-      <x:c r="AE5" s="65"/>
-      <x:c r="AF5" s="65"/>
-      <x:c r="AG5" s="65"/>
-      <x:c r="AH5" s="65"/>
-      <x:c r="AI5" s="65"/>
-      <x:c r="AJ5" s="65"/>
-      <x:c r="AK5" s="64" t="str">
-        <x:v>@user_id_1</x:v>
-      </x:c>
-      <x:c r="AL5" s="65"/>
-      <x:c r="AM5" s="65"/>
-      <x:c r="AN5" s="65"/>
-      <x:c r="AO5" s="65"/>
-      <x:c r="AP5" s="65"/>
-      <x:c r="AQ5" s="65"/>
-      <x:c r="AR5" s="65"/>
-      <x:c r="AS5" s="65"/>
-      <x:c r="AT5" s="65"/>
-      <x:c r="AU5" s="65"/>
-      <x:c r="AV5" s="65"/>
-      <x:c r="AW5" s="65"/>
-      <x:c r="AX5" s="65"/>
-      <x:c r="AY5" s="65"/>
-      <x:c r="AZ5" s="65"/>
-      <x:c r="BA5" s="65"/>
-      <x:c r="BB5" s="65"/>
-      <x:c r="BC5" s="65"/>
-      <x:c r="BD5" s="65"/>
-      <x:c r="BE5" s="65"/>
-      <x:c r="BF5" s="65"/>
-      <x:c r="BG5" s="65"/>
-      <x:c r="BH5" s="65"/>
-      <x:c r="BI5" s="65"/>
-      <x:c r="BJ5" s="65"/>
-      <x:c r="BK5" s="65"/>
-      <x:c r="BL5" s="65"/>
-      <x:c r="BM5" s="65"/>
-      <x:c r="BN5" s="65"/>
-      <x:c r="BO5" s="65"/>
-      <x:c r="BP5" s="65"/>
-      <x:c r="BQ5" s="65"/>
-      <x:c r="BR5" s="65"/>
-      <x:c r="BS5" s="65"/>
-      <x:c r="BT5" s="65"/>
-      <x:c r="BU5" s="65"/>
-      <x:c r="BV5" s="65"/>
-      <x:c r="BW5" s="65"/>
-      <x:c r="BX5" s="65"/>
-      <x:c r="BY5" s="65"/>
-      <x:c r="BZ5" s="65"/>
-      <x:c r="CA5" s="65"/>
-      <x:c r="CB5" s="65"/>
-      <x:c r="CC5" s="65"/>
-      <x:c r="CD5" s="65"/>
-      <x:c r="CE5" s="65"/>
-      <x:c r="CF5" s="65"/>
-      <x:c r="CG5" s="65"/>
-      <x:c r="CH5" s="65"/>
-      <x:c r="CI5" s="65"/>
-      <x:c r="CJ5" s="65"/>
-      <x:c r="CK5" s="65"/>
-      <x:c r="CL5" s="66"/>
+      <x:c r="B5" s="48"/>
+      <x:c r="C5" s="48"/>
+      <x:c r="D5" s="48"/>
+      <x:c r="E5" s="48"/>
+      <x:c r="F5" s="48"/>
+      <x:c r="G5" s="48"/>
+      <x:c r="H5" s="48"/>
+      <x:c r="I5" s="48"/>
+      <x:c r="J5" s="48"/>
+      <x:c r="K5" s="48"/>
+      <x:c r="L5" s="48"/>
+      <x:c r="M5" s="48"/>
+      <x:c r="N5" s="48"/>
+      <x:c r="O5" s="48"/>
+      <x:c r="P5" s="48"/>
+      <x:c r="Q5" s="48"/>
+      <x:c r="R5" s="48"/>
+      <x:c r="S5" s="47"/>
+      <x:c r="T5" s="48"/>
+      <x:c r="U5" s="48"/>
+      <x:c r="V5" s="48"/>
+      <x:c r="W5" s="48"/>
+      <x:c r="X5" s="48"/>
+      <x:c r="Y5" s="48"/>
+      <x:c r="Z5" s="48"/>
+      <x:c r="AA5" s="48"/>
+      <x:c r="AB5" s="48"/>
+      <x:c r="AC5" s="48"/>
+      <x:c r="AD5" s="48"/>
+      <x:c r="AE5" s="48"/>
+      <x:c r="AF5" s="48"/>
+      <x:c r="AG5" s="48"/>
+      <x:c r="AH5" s="48"/>
+      <x:c r="AI5" s="48"/>
+      <x:c r="AJ5" s="48"/>
+      <x:c r="AK5" s="47" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="AL5" s="48"/>
+      <x:c r="AM5" s="48"/>
+      <x:c r="AN5" s="48"/>
+      <x:c r="AO5" s="48"/>
+      <x:c r="AP5" s="48"/>
+      <x:c r="AQ5" s="48"/>
+      <x:c r="AR5" s="48"/>
+      <x:c r="AS5" s="48"/>
+      <x:c r="AT5" s="48"/>
+      <x:c r="AU5" s="48"/>
+      <x:c r="AV5" s="48"/>
+      <x:c r="AW5" s="48"/>
+      <x:c r="AX5" s="48"/>
+      <x:c r="AY5" s="48"/>
+      <x:c r="AZ5" s="48"/>
+      <x:c r="BA5" s="48"/>
+      <x:c r="BB5" s="48"/>
+      <x:c r="BC5" s="48"/>
+      <x:c r="BD5" s="48"/>
+      <x:c r="BE5" s="48"/>
+      <x:c r="BF5" s="48"/>
+      <x:c r="BG5" s="48"/>
+      <x:c r="BH5" s="48"/>
+      <x:c r="BI5" s="48"/>
+      <x:c r="BJ5" s="48"/>
+      <x:c r="BK5" s="48"/>
+      <x:c r="BL5" s="48"/>
+      <x:c r="BM5" s="48"/>
+      <x:c r="BN5" s="48"/>
+      <x:c r="BO5" s="48"/>
+      <x:c r="BP5" s="48"/>
+      <x:c r="BQ5" s="48"/>
+      <x:c r="BR5" s="48"/>
+      <x:c r="BS5" s="48"/>
+      <x:c r="BT5" s="48"/>
+      <x:c r="BU5" s="48"/>
+      <x:c r="BV5" s="48"/>
+      <x:c r="BW5" s="48"/>
+      <x:c r="BX5" s="48"/>
+      <x:c r="BY5" s="48"/>
+      <x:c r="BZ5" s="48"/>
+      <x:c r="CA5" s="48"/>
+      <x:c r="CB5" s="48"/>
+      <x:c r="CC5" s="48"/>
+      <x:c r="CD5" s="48"/>
+      <x:c r="CE5" s="48"/>
+      <x:c r="CF5" s="48"/>
+      <x:c r="CG5" s="48"/>
+      <x:c r="CH5" s="48"/>
+      <x:c r="CI5" s="48"/>
+      <x:c r="CJ5" s="48"/>
+      <x:c r="CK5" s="48"/>
+      <x:c r="CL5" s="49"/>
     </x:row>
     <x:row r="6" ht="13.5" customHeight="1">
-      <x:c r="A6" s="64" t="s">
+      <x:c r="A6" s="47" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="B6" s="65"/>
-      <x:c r="C6" s="65"/>
-      <x:c r="D6" s="65"/>
-      <x:c r="E6" s="65"/>
-      <x:c r="F6" s="65"/>
-      <x:c r="G6" s="65"/>
-      <x:c r="H6" s="65"/>
-      <x:c r="I6" s="65"/>
-      <x:c r="J6" s="65"/>
-      <x:c r="K6" s="65"/>
-      <x:c r="L6" s="65"/>
-      <x:c r="M6" s="65"/>
-      <x:c r="N6" s="65"/>
-      <x:c r="O6" s="65"/>
-      <x:c r="P6" s="65"/>
-      <x:c r="Q6" s="65"/>
-      <x:c r="R6" s="65"/>
-      <x:c r="S6" s="64"/>
-      <x:c r="T6" s="65"/>
-      <x:c r="U6" s="65"/>
-      <x:c r="V6" s="65"/>
-      <x:c r="W6" s="65"/>
-      <x:c r="X6" s="65"/>
-      <x:c r="Y6" s="65"/>
-      <x:c r="Z6" s="65"/>
-      <x:c r="AA6" s="65"/>
-      <x:c r="AB6" s="65"/>
-      <x:c r="AC6" s="65"/>
-      <x:c r="AD6" s="65"/>
-      <x:c r="AE6" s="65"/>
-      <x:c r="AF6" s="65"/>
-      <x:c r="AG6" s="65"/>
-      <x:c r="AH6" s="65"/>
-      <x:c r="AI6" s="65"/>
-      <x:c r="AJ6" s="65"/>
-      <x:c r="AK6" s="64" t="str">
-        <x:v>@name_1</x:v>
-      </x:c>
-      <x:c r="AL6" s="65"/>
-      <x:c r="AM6" s="65"/>
-      <x:c r="AN6" s="65"/>
-      <x:c r="AO6" s="65"/>
-      <x:c r="AP6" s="65"/>
-      <x:c r="AQ6" s="65"/>
-      <x:c r="AR6" s="65"/>
-      <x:c r="AS6" s="65"/>
-      <x:c r="AT6" s="65"/>
-      <x:c r="AU6" s="65"/>
-      <x:c r="AV6" s="65"/>
-      <x:c r="AW6" s="65"/>
-      <x:c r="AX6" s="65"/>
-      <x:c r="AY6" s="65"/>
-      <x:c r="AZ6" s="65"/>
-      <x:c r="BA6" s="65"/>
-      <x:c r="BB6" s="65"/>
-      <x:c r="BC6" s="65"/>
-      <x:c r="BD6" s="65"/>
-      <x:c r="BE6" s="65"/>
-      <x:c r="BF6" s="65"/>
-      <x:c r="BG6" s="65"/>
-      <x:c r="BH6" s="65"/>
-      <x:c r="BI6" s="65"/>
-      <x:c r="BJ6" s="65"/>
-      <x:c r="BK6" s="65"/>
-      <x:c r="BL6" s="65"/>
-      <x:c r="BM6" s="65"/>
-      <x:c r="BN6" s="65"/>
-      <x:c r="BO6" s="65"/>
-      <x:c r="BP6" s="65"/>
-      <x:c r="BQ6" s="65"/>
-      <x:c r="BR6" s="65"/>
-      <x:c r="BS6" s="65"/>
-      <x:c r="BT6" s="65"/>
-      <x:c r="BU6" s="65"/>
-      <x:c r="BV6" s="65"/>
-      <x:c r="BW6" s="65"/>
-      <x:c r="BX6" s="65"/>
-      <x:c r="BY6" s="65"/>
-      <x:c r="BZ6" s="65"/>
-      <x:c r="CA6" s="65"/>
-      <x:c r="CB6" s="65"/>
-      <x:c r="CC6" s="65"/>
-      <x:c r="CD6" s="65"/>
-      <x:c r="CE6" s="65"/>
-      <x:c r="CF6" s="65"/>
-      <x:c r="CG6" s="65"/>
-      <x:c r="CH6" s="65"/>
-      <x:c r="CI6" s="65"/>
-      <x:c r="CJ6" s="65"/>
-      <x:c r="CK6" s="65"/>
-      <x:c r="CL6" s="66"/>
+      <x:c r="B6" s="48"/>
+      <x:c r="C6" s="48"/>
+      <x:c r="D6" s="48"/>
+      <x:c r="E6" s="48"/>
+      <x:c r="F6" s="48"/>
+      <x:c r="G6" s="48"/>
+      <x:c r="H6" s="48"/>
+      <x:c r="I6" s="48"/>
+      <x:c r="J6" s="48"/>
+      <x:c r="K6" s="48"/>
+      <x:c r="L6" s="48"/>
+      <x:c r="M6" s="48"/>
+      <x:c r="N6" s="48"/>
+      <x:c r="O6" s="48"/>
+      <x:c r="P6" s="48"/>
+      <x:c r="Q6" s="48"/>
+      <x:c r="R6" s="48"/>
+      <x:c r="S6" s="47"/>
+      <x:c r="T6" s="48"/>
+      <x:c r="U6" s="48"/>
+      <x:c r="V6" s="48"/>
+      <x:c r="W6" s="48"/>
+      <x:c r="X6" s="48"/>
+      <x:c r="Y6" s="48"/>
+      <x:c r="Z6" s="48"/>
+      <x:c r="AA6" s="48"/>
+      <x:c r="AB6" s="48"/>
+      <x:c r="AC6" s="48"/>
+      <x:c r="AD6" s="48"/>
+      <x:c r="AE6" s="48"/>
+      <x:c r="AF6" s="48"/>
+      <x:c r="AG6" s="48"/>
+      <x:c r="AH6" s="48"/>
+      <x:c r="AI6" s="48"/>
+      <x:c r="AJ6" s="48"/>
+      <x:c r="AK6" s="47" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="AL6" s="48"/>
+      <x:c r="AM6" s="48"/>
+      <x:c r="AN6" s="48"/>
+      <x:c r="AO6" s="48"/>
+      <x:c r="AP6" s="48"/>
+      <x:c r="AQ6" s="48"/>
+      <x:c r="AR6" s="48"/>
+      <x:c r="AS6" s="48"/>
+      <x:c r="AT6" s="48"/>
+      <x:c r="AU6" s="48"/>
+      <x:c r="AV6" s="48"/>
+      <x:c r="AW6" s="48"/>
+      <x:c r="AX6" s="48"/>
+      <x:c r="AY6" s="48"/>
+      <x:c r="AZ6" s="48"/>
+      <x:c r="BA6" s="48"/>
+      <x:c r="BB6" s="48"/>
+      <x:c r="BC6" s="48"/>
+      <x:c r="BD6" s="48"/>
+      <x:c r="BE6" s="48"/>
+      <x:c r="BF6" s="48"/>
+      <x:c r="BG6" s="48"/>
+      <x:c r="BH6" s="48"/>
+      <x:c r="BI6" s="48"/>
+      <x:c r="BJ6" s="48"/>
+      <x:c r="BK6" s="48"/>
+      <x:c r="BL6" s="48"/>
+      <x:c r="BM6" s="48"/>
+      <x:c r="BN6" s="48"/>
+      <x:c r="BO6" s="48"/>
+      <x:c r="BP6" s="48"/>
+      <x:c r="BQ6" s="48"/>
+      <x:c r="BR6" s="48"/>
+      <x:c r="BS6" s="48"/>
+      <x:c r="BT6" s="48"/>
+      <x:c r="BU6" s="48"/>
+      <x:c r="BV6" s="48"/>
+      <x:c r="BW6" s="48"/>
+      <x:c r="BX6" s="48"/>
+      <x:c r="BY6" s="48"/>
+      <x:c r="BZ6" s="48"/>
+      <x:c r="CA6" s="48"/>
+      <x:c r="CB6" s="48"/>
+      <x:c r="CC6" s="48"/>
+      <x:c r="CD6" s="48"/>
+      <x:c r="CE6" s="48"/>
+      <x:c r="CF6" s="48"/>
+      <x:c r="CG6" s="48"/>
+      <x:c r="CH6" s="48"/>
+      <x:c r="CI6" s="48"/>
+      <x:c r="CJ6" s="48"/>
+      <x:c r="CK6" s="48"/>
+      <x:c r="CL6" s="49"/>
     </x:row>
     <x:row r="7" ht="13.5" customHeight="1">
-      <x:c r="A7" s="64" t="s">
+      <x:c r="A7" s="47" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="B7" s="65"/>
-      <x:c r="C7" s="65"/>
-      <x:c r="D7" s="65"/>
-      <x:c r="E7" s="65"/>
-      <x:c r="F7" s="65"/>
-      <x:c r="G7" s="65"/>
-      <x:c r="H7" s="65"/>
-      <x:c r="I7" s="65"/>
-      <x:c r="J7" s="65"/>
-      <x:c r="K7" s="65"/>
-      <x:c r="L7" s="65"/>
-      <x:c r="M7" s="65"/>
-      <x:c r="N7" s="65"/>
-      <x:c r="O7" s="65"/>
-      <x:c r="P7" s="65"/>
-      <x:c r="Q7" s="65"/>
-      <x:c r="R7" s="65"/>
-      <x:c r="S7" s="64"/>
-      <x:c r="T7" s="65"/>
-      <x:c r="U7" s="65"/>
-      <x:c r="V7" s="65"/>
-      <x:c r="W7" s="65"/>
-      <x:c r="X7" s="65"/>
-      <x:c r="Y7" s="65"/>
-      <x:c r="Z7" s="65"/>
-      <x:c r="AA7" s="65"/>
-      <x:c r="AB7" s="65"/>
-      <x:c r="AC7" s="65"/>
-      <x:c r="AD7" s="65"/>
-      <x:c r="AE7" s="65"/>
-      <x:c r="AF7" s="65"/>
-      <x:c r="AG7" s="65"/>
-      <x:c r="AH7" s="65"/>
-      <x:c r="AI7" s="65"/>
-      <x:c r="AJ7" s="65"/>
-      <x:c r="AK7" s="64" t="str">
-        <x:v>'ACTIVE'</x:v>
-      </x:c>
-      <x:c r="AL7" s="65"/>
-      <x:c r="AM7" s="65"/>
-      <x:c r="AN7" s="65"/>
-      <x:c r="AO7" s="65"/>
-      <x:c r="AP7" s="65"/>
-      <x:c r="AQ7" s="65"/>
-      <x:c r="AR7" s="65"/>
-      <x:c r="AS7" s="65"/>
-      <x:c r="AT7" s="65"/>
-      <x:c r="AU7" s="65"/>
-      <x:c r="AV7" s="65"/>
-      <x:c r="AW7" s="65"/>
-      <x:c r="AX7" s="65"/>
-      <x:c r="AY7" s="65"/>
-      <x:c r="AZ7" s="65"/>
-      <x:c r="BA7" s="65"/>
-      <x:c r="BB7" s="65"/>
-      <x:c r="BC7" s="65"/>
-      <x:c r="BD7" s="65"/>
-      <x:c r="BE7" s="65"/>
-      <x:c r="BF7" s="65"/>
-      <x:c r="BG7" s="65"/>
-      <x:c r="BH7" s="65"/>
-      <x:c r="BI7" s="65"/>
-      <x:c r="BJ7" s="65"/>
-      <x:c r="BK7" s="65"/>
-      <x:c r="BL7" s="65"/>
-      <x:c r="BM7" s="65"/>
-      <x:c r="BN7" s="65"/>
-      <x:c r="BO7" s="65"/>
-      <x:c r="BP7" s="65"/>
-      <x:c r="BQ7" s="65"/>
-      <x:c r="BR7" s="65"/>
-      <x:c r="BS7" s="65"/>
-      <x:c r="BT7" s="65"/>
-      <x:c r="BU7" s="65"/>
-      <x:c r="BV7" s="65"/>
-      <x:c r="BW7" s="65"/>
-      <x:c r="BX7" s="65"/>
-      <x:c r="BY7" s="65"/>
-      <x:c r="BZ7" s="65"/>
-      <x:c r="CA7" s="65"/>
-      <x:c r="CB7" s="65"/>
-      <x:c r="CC7" s="65"/>
-      <x:c r="CD7" s="65"/>
-      <x:c r="CE7" s="65"/>
-      <x:c r="CF7" s="65"/>
-      <x:c r="CG7" s="65"/>
-      <x:c r="CH7" s="65"/>
-      <x:c r="CI7" s="65"/>
-      <x:c r="CJ7" s="65"/>
-      <x:c r="CK7" s="65"/>
-      <x:c r="CL7" s="66"/>
+      <x:c r="B7" s="48"/>
+      <x:c r="C7" s="48"/>
+      <x:c r="D7" s="48"/>
+      <x:c r="E7" s="48"/>
+      <x:c r="F7" s="48"/>
+      <x:c r="G7" s="48"/>
+      <x:c r="H7" s="48"/>
+      <x:c r="I7" s="48"/>
+      <x:c r="J7" s="48"/>
+      <x:c r="K7" s="48"/>
+      <x:c r="L7" s="48"/>
+      <x:c r="M7" s="48"/>
+      <x:c r="N7" s="48"/>
+      <x:c r="O7" s="48"/>
+      <x:c r="P7" s="48"/>
+      <x:c r="Q7" s="48"/>
+      <x:c r="R7" s="48"/>
+      <x:c r="S7" s="47"/>
+      <x:c r="T7" s="48"/>
+      <x:c r="U7" s="48"/>
+      <x:c r="V7" s="48"/>
+      <x:c r="W7" s="48"/>
+      <x:c r="X7" s="48"/>
+      <x:c r="Y7" s="48"/>
+      <x:c r="Z7" s="48"/>
+      <x:c r="AA7" s="48"/>
+      <x:c r="AB7" s="48"/>
+      <x:c r="AC7" s="48"/>
+      <x:c r="AD7" s="48"/>
+      <x:c r="AE7" s="48"/>
+      <x:c r="AF7" s="48"/>
+      <x:c r="AG7" s="48"/>
+      <x:c r="AH7" s="48"/>
+      <x:c r="AI7" s="48"/>
+      <x:c r="AJ7" s="48"/>
+      <x:c r="AK7" s="47" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="AL7" s="48"/>
+      <x:c r="AM7" s="48"/>
+      <x:c r="AN7" s="48"/>
+      <x:c r="AO7" s="48"/>
+      <x:c r="AP7" s="48"/>
+      <x:c r="AQ7" s="48"/>
+      <x:c r="AR7" s="48"/>
+      <x:c r="AS7" s="48"/>
+      <x:c r="AT7" s="48"/>
+      <x:c r="AU7" s="48"/>
+      <x:c r="AV7" s="48"/>
+      <x:c r="AW7" s="48"/>
+      <x:c r="AX7" s="48"/>
+      <x:c r="AY7" s="48"/>
+      <x:c r="AZ7" s="48"/>
+      <x:c r="BA7" s="48"/>
+      <x:c r="BB7" s="48"/>
+      <x:c r="BC7" s="48"/>
+      <x:c r="BD7" s="48"/>
+      <x:c r="BE7" s="48"/>
+      <x:c r="BF7" s="48"/>
+      <x:c r="BG7" s="48"/>
+      <x:c r="BH7" s="48"/>
+      <x:c r="BI7" s="48"/>
+      <x:c r="BJ7" s="48"/>
+      <x:c r="BK7" s="48"/>
+      <x:c r="BL7" s="48"/>
+      <x:c r="BM7" s="48"/>
+      <x:c r="BN7" s="48"/>
+      <x:c r="BO7" s="48"/>
+      <x:c r="BP7" s="48"/>
+      <x:c r="BQ7" s="48"/>
+      <x:c r="BR7" s="48"/>
+      <x:c r="BS7" s="48"/>
+      <x:c r="BT7" s="48"/>
+      <x:c r="BU7" s="48"/>
+      <x:c r="BV7" s="48"/>
+      <x:c r="BW7" s="48"/>
+      <x:c r="BX7" s="48"/>
+      <x:c r="BY7" s="48"/>
+      <x:c r="BZ7" s="48"/>
+      <x:c r="CA7" s="48"/>
+      <x:c r="CB7" s="48"/>
+      <x:c r="CC7" s="48"/>
+      <x:c r="CD7" s="48"/>
+      <x:c r="CE7" s="48"/>
+      <x:c r="CF7" s="48"/>
+      <x:c r="CG7" s="48"/>
+      <x:c r="CH7" s="48"/>
+      <x:c r="CI7" s="48"/>
+      <x:c r="CJ7" s="48"/>
+      <x:c r="CK7" s="48"/>
+      <x:c r="CL7" s="49"/>
     </x:row>
     <x:row r="8" ht="13.5" customHeight="1">
-      <x:c r="A8" s="64" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="B8" s="65"/>
-      <x:c r="C8" s="65"/>
-      <x:c r="D8" s="65"/>
-      <x:c r="E8" s="65"/>
-      <x:c r="F8" s="65"/>
-      <x:c r="G8" s="65"/>
-      <x:c r="H8" s="65"/>
-      <x:c r="I8" s="65"/>
-      <x:c r="J8" s="65"/>
-      <x:c r="K8" s="65"/>
-      <x:c r="L8" s="65"/>
-      <x:c r="M8" s="65"/>
-      <x:c r="N8" s="65"/>
-      <x:c r="O8" s="65"/>
-      <x:c r="P8" s="65"/>
-      <x:c r="Q8" s="65"/>
-      <x:c r="R8" s="65"/>
-      <x:c r="S8" s="64"/>
-      <x:c r="T8" s="65"/>
-      <x:c r="U8" s="65"/>
-      <x:c r="V8" s="65"/>
-      <x:c r="W8" s="65"/>
-      <x:c r="X8" s="65"/>
-      <x:c r="Y8" s="65"/>
-      <x:c r="Z8" s="65"/>
-      <x:c r="AA8" s="65"/>
-      <x:c r="AB8" s="65"/>
-      <x:c r="AC8" s="65"/>
-      <x:c r="AD8" s="65"/>
-      <x:c r="AE8" s="65"/>
-      <x:c r="AF8" s="65"/>
-      <x:c r="AG8" s="65"/>
-      <x:c r="AH8" s="65"/>
-      <x:c r="AI8" s="65"/>
-      <x:c r="AJ8" s="65"/>
-      <x:c r="AK8" s="64" t="str">
-        <x:v>SYSDATETIME()</x:v>
-      </x:c>
-      <x:c r="AL8" s="65"/>
-      <x:c r="AM8" s="65"/>
-      <x:c r="AN8" s="65"/>
-      <x:c r="AO8" s="65"/>
-      <x:c r="AP8" s="65"/>
-      <x:c r="AQ8" s="65"/>
-      <x:c r="AR8" s="65"/>
-      <x:c r="AS8" s="65"/>
-      <x:c r="AT8" s="65"/>
-      <x:c r="AU8" s="65"/>
-      <x:c r="AV8" s="65"/>
-      <x:c r="AW8" s="65"/>
-      <x:c r="AX8" s="65"/>
-      <x:c r="AY8" s="65"/>
-      <x:c r="AZ8" s="65"/>
-      <x:c r="BA8" s="65"/>
-      <x:c r="BB8" s="65"/>
-      <x:c r="BC8" s="65"/>
-      <x:c r="BD8" s="65"/>
-      <x:c r="BE8" s="65"/>
-      <x:c r="BF8" s="65"/>
-      <x:c r="BG8" s="65"/>
-      <x:c r="BH8" s="65"/>
-      <x:c r="BI8" s="65"/>
-      <x:c r="BJ8" s="65"/>
-      <x:c r="BK8" s="65"/>
-      <x:c r="BL8" s="65"/>
-      <x:c r="BM8" s="65"/>
-      <x:c r="BN8" s="65"/>
-      <x:c r="BO8" s="65"/>
-      <x:c r="BP8" s="65"/>
-      <x:c r="BQ8" s="65"/>
-      <x:c r="BR8" s="65"/>
-      <x:c r="BS8" s="65"/>
-      <x:c r="BT8" s="65"/>
-      <x:c r="BU8" s="65"/>
-      <x:c r="BV8" s="65"/>
-      <x:c r="BW8" s="65"/>
-      <x:c r="BX8" s="65"/>
-      <x:c r="BY8" s="65"/>
-      <x:c r="BZ8" s="65"/>
-      <x:c r="CA8" s="65"/>
-      <x:c r="CB8" s="65"/>
-      <x:c r="CC8" s="65"/>
-      <x:c r="CD8" s="65"/>
-      <x:c r="CE8" s="65"/>
-      <x:c r="CF8" s="65"/>
-      <x:c r="CG8" s="65"/>
-      <x:c r="CH8" s="65"/>
-      <x:c r="CI8" s="65"/>
-      <x:c r="CJ8" s="65"/>
-      <x:c r="CK8" s="65"/>
-      <x:c r="CL8" s="66"/>
+      <x:c r="A8" s="47" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="B8" s="48"/>
+      <x:c r="C8" s="48"/>
+      <x:c r="D8" s="48"/>
+      <x:c r="E8" s="48"/>
+      <x:c r="F8" s="48"/>
+      <x:c r="G8" s="48"/>
+      <x:c r="H8" s="48"/>
+      <x:c r="I8" s="48"/>
+      <x:c r="J8" s="48"/>
+      <x:c r="K8" s="48"/>
+      <x:c r="L8" s="48"/>
+      <x:c r="M8" s="48"/>
+      <x:c r="N8" s="48"/>
+      <x:c r="O8" s="48"/>
+      <x:c r="P8" s="48"/>
+      <x:c r="Q8" s="48"/>
+      <x:c r="R8" s="48"/>
+      <x:c r="S8" s="47"/>
+      <x:c r="T8" s="48"/>
+      <x:c r="U8" s="48"/>
+      <x:c r="V8" s="48"/>
+      <x:c r="W8" s="48"/>
+      <x:c r="X8" s="48"/>
+      <x:c r="Y8" s="48"/>
+      <x:c r="Z8" s="48"/>
+      <x:c r="AA8" s="48"/>
+      <x:c r="AB8" s="48"/>
+      <x:c r="AC8" s="48"/>
+      <x:c r="AD8" s="48"/>
+      <x:c r="AE8" s="48"/>
+      <x:c r="AF8" s="48"/>
+      <x:c r="AG8" s="48"/>
+      <x:c r="AH8" s="48"/>
+      <x:c r="AI8" s="48"/>
+      <x:c r="AJ8" s="48"/>
+      <x:c r="AK8" s="47" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="AL8" s="48"/>
+      <x:c r="AM8" s="48"/>
+      <x:c r="AN8" s="48"/>
+      <x:c r="AO8" s="48"/>
+      <x:c r="AP8" s="48"/>
+      <x:c r="AQ8" s="48"/>
+      <x:c r="AR8" s="48"/>
+      <x:c r="AS8" s="48"/>
+      <x:c r="AT8" s="48"/>
+      <x:c r="AU8" s="48"/>
+      <x:c r="AV8" s="48"/>
+      <x:c r="AW8" s="48"/>
+      <x:c r="AX8" s="48"/>
+      <x:c r="AY8" s="48"/>
+      <x:c r="AZ8" s="48"/>
+      <x:c r="BA8" s="48"/>
+      <x:c r="BB8" s="48"/>
+      <x:c r="BC8" s="48"/>
+      <x:c r="BD8" s="48"/>
+      <x:c r="BE8" s="48"/>
+      <x:c r="BF8" s="48"/>
+      <x:c r="BG8" s="48"/>
+      <x:c r="BH8" s="48"/>
+      <x:c r="BI8" s="48"/>
+      <x:c r="BJ8" s="48"/>
+      <x:c r="BK8" s="48"/>
+      <x:c r="BL8" s="48"/>
+      <x:c r="BM8" s="48"/>
+      <x:c r="BN8" s="48"/>
+      <x:c r="BO8" s="48"/>
+      <x:c r="BP8" s="48"/>
+      <x:c r="BQ8" s="48"/>
+      <x:c r="BR8" s="48"/>
+      <x:c r="BS8" s="48"/>
+      <x:c r="BT8" s="48"/>
+      <x:c r="BU8" s="48"/>
+      <x:c r="BV8" s="48"/>
+      <x:c r="BW8" s="48"/>
+      <x:c r="BX8" s="48"/>
+      <x:c r="BY8" s="48"/>
+      <x:c r="BZ8" s="48"/>
+      <x:c r="CA8" s="48"/>
+      <x:c r="CB8" s="48"/>
+      <x:c r="CC8" s="48"/>
+      <x:c r="CD8" s="48"/>
+      <x:c r="CE8" s="48"/>
+      <x:c r="CF8" s="48"/>
+      <x:c r="CG8" s="48"/>
+      <x:c r="CH8" s="48"/>
+      <x:c r="CI8" s="48"/>
+      <x:c r="CJ8" s="48"/>
+      <x:c r="CK8" s="48"/>
+      <x:c r="CL8" s="49"/>
     </x:row>
     <x:row r="9" ht="13.5" customHeight="1">
-      <x:c r="A9" s="63" t="str">
-        <x:v>＜VALUES 2行目＞</x:v>
-      </x:c>
-      <x:c r="B9" s="63"/>
-      <x:c r="C9" s="63"/>
-      <x:c r="D9" s="63"/>
-      <x:c r="E9" s="63"/>
-      <x:c r="F9" s="63"/>
-      <x:c r="G9" s="63"/>
-      <x:c r="H9" s="63"/>
-      <x:c r="I9" s="63"/>
-      <x:c r="J9" s="63"/>
-      <x:c r="K9" s="63"/>
-      <x:c r="L9" s="63"/>
-      <x:c r="M9" s="63"/>
-      <x:c r="N9" s="63"/>
-      <x:c r="O9" s="63"/>
-      <x:c r="P9" s="63"/>
-      <x:c r="Q9" s="63"/>
-      <x:c r="R9" s="63"/>
-      <x:c r="S9" s="63"/>
-      <x:c r="T9" s="63"/>
-      <x:c r="U9" s="63"/>
-      <x:c r="V9" s="63"/>
-      <x:c r="W9" s="63"/>
-      <x:c r="X9" s="63"/>
-      <x:c r="Y9" s="63"/>
-      <x:c r="Z9" s="63"/>
-      <x:c r="AA9" s="63"/>
-      <x:c r="AB9" s="63"/>
-      <x:c r="AC9" s="63"/>
-      <x:c r="AD9" s="63"/>
-      <x:c r="AE9" s="63"/>
-      <x:c r="AF9" s="63"/>
-      <x:c r="AG9" s="63"/>
-      <x:c r="AH9" s="63"/>
-      <x:c r="AI9" s="63"/>
-      <x:c r="AJ9" s="63"/>
-      <x:c r="AK9" s="63"/>
-      <x:c r="AL9" s="63"/>
-      <x:c r="AM9" s="63"/>
-      <x:c r="AN9" s="63"/>
-      <x:c r="AO9" s="63"/>
-      <x:c r="AP9" s="63"/>
-      <x:c r="AQ9" s="63"/>
-      <x:c r="AR9" s="63"/>
-      <x:c r="AS9" s="63"/>
-      <x:c r="AT9" s="63"/>
-      <x:c r="AU9" s="63"/>
-      <x:c r="AV9" s="63"/>
-      <x:c r="AW9" s="63"/>
-      <x:c r="AX9" s="63"/>
-      <x:c r="AY9" s="63"/>
-      <x:c r="AZ9" s="63"/>
-      <x:c r="BA9" s="63"/>
-      <x:c r="BB9" s="63"/>
-      <x:c r="BC9" s="63"/>
-      <x:c r="BD9" s="63"/>
-      <x:c r="BE9" s="63"/>
-      <x:c r="BF9" s="63"/>
-      <x:c r="BG9" s="63"/>
-      <x:c r="BH9" s="63"/>
-      <x:c r="BI9" s="63"/>
-      <x:c r="BJ9" s="63"/>
-      <x:c r="BK9" s="63"/>
-      <x:c r="BL9" s="63"/>
-      <x:c r="BM9" s="63"/>
-      <x:c r="BN9" s="63"/>
-      <x:c r="BO9" s="63"/>
-      <x:c r="BP9" s="63"/>
-      <x:c r="BQ9" s="63"/>
-      <x:c r="BR9" s="63"/>
-      <x:c r="BS9" s="63"/>
-      <x:c r="BT9" s="63"/>
-      <x:c r="BU9" s="63"/>
-      <x:c r="BV9" s="63"/>
-      <x:c r="BW9" s="63"/>
-      <x:c r="BX9" s="63"/>
-      <x:c r="BY9" s="63"/>
-      <x:c r="BZ9" s="63"/>
-      <x:c r="CA9" s="63"/>
-      <x:c r="CB9" s="63"/>
-      <x:c r="CC9" s="63"/>
-      <x:c r="CD9" s="63"/>
-      <x:c r="CE9" s="63"/>
-      <x:c r="CF9" s="63"/>
-      <x:c r="CG9" s="63"/>
-      <x:c r="CH9" s="63"/>
-      <x:c r="CI9" s="63"/>
-      <x:c r="CJ9" s="63"/>
-      <x:c r="CK9" s="63"/>
-      <x:c r="CL9" s="63"/>
+      <x:c r="A9" s="46" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="B9" s="46"/>
+      <x:c r="C9" s="46"/>
+      <x:c r="D9" s="46"/>
+      <x:c r="E9" s="46"/>
+      <x:c r="F9" s="46"/>
+      <x:c r="G9" s="46"/>
+      <x:c r="H9" s="46"/>
+      <x:c r="I9" s="46"/>
+      <x:c r="J9" s="46"/>
+      <x:c r="K9" s="46"/>
+      <x:c r="L9" s="46"/>
+      <x:c r="M9" s="46"/>
+      <x:c r="N9" s="46"/>
+      <x:c r="O9" s="46"/>
+      <x:c r="P9" s="46"/>
+      <x:c r="Q9" s="46"/>
+      <x:c r="R9" s="46"/>
+      <x:c r="S9" s="46"/>
+      <x:c r="T9" s="46"/>
+      <x:c r="U9" s="46"/>
+      <x:c r="V9" s="46"/>
+      <x:c r="W9" s="46"/>
+      <x:c r="X9" s="46"/>
+      <x:c r="Y9" s="46"/>
+      <x:c r="Z9" s="46"/>
+      <x:c r="AA9" s="46"/>
+      <x:c r="AB9" s="46"/>
+      <x:c r="AC9" s="46"/>
+      <x:c r="AD9" s="46"/>
+      <x:c r="AE9" s="46"/>
+      <x:c r="AF9" s="46"/>
+      <x:c r="AG9" s="46"/>
+      <x:c r="AH9" s="46"/>
+      <x:c r="AI9" s="46"/>
+      <x:c r="AJ9" s="46"/>
+      <x:c r="AK9" s="46"/>
+      <x:c r="AL9" s="46"/>
+      <x:c r="AM9" s="46"/>
+      <x:c r="AN9" s="46"/>
+      <x:c r="AO9" s="46"/>
+      <x:c r="AP9" s="46"/>
+      <x:c r="AQ9" s="46"/>
+      <x:c r="AR9" s="46"/>
+      <x:c r="AS9" s="46"/>
+      <x:c r="AT9" s="46"/>
+      <x:c r="AU9" s="46"/>
+      <x:c r="AV9" s="46"/>
+      <x:c r="AW9" s="46"/>
+      <x:c r="AX9" s="46"/>
+      <x:c r="AY9" s="46"/>
+      <x:c r="AZ9" s="46"/>
+      <x:c r="BA9" s="46"/>
+      <x:c r="BB9" s="46"/>
+      <x:c r="BC9" s="46"/>
+      <x:c r="BD9" s="46"/>
+      <x:c r="BE9" s="46"/>
+      <x:c r="BF9" s="46"/>
+      <x:c r="BG9" s="46"/>
+      <x:c r="BH9" s="46"/>
+      <x:c r="BI9" s="46"/>
+      <x:c r="BJ9" s="46"/>
+      <x:c r="BK9" s="46"/>
+      <x:c r="BL9" s="46"/>
+      <x:c r="BM9" s="46"/>
+      <x:c r="BN9" s="46"/>
+      <x:c r="BO9" s="46"/>
+      <x:c r="BP9" s="46"/>
+      <x:c r="BQ9" s="46"/>
+      <x:c r="BR9" s="46"/>
+      <x:c r="BS9" s="46"/>
+      <x:c r="BT9" s="46"/>
+      <x:c r="BU9" s="46"/>
+      <x:c r="BV9" s="46"/>
+      <x:c r="BW9" s="46"/>
+      <x:c r="BX9" s="46"/>
+      <x:c r="BY9" s="46"/>
+      <x:c r="BZ9" s="46"/>
+      <x:c r="CA9" s="46"/>
+      <x:c r="CB9" s="46"/>
+      <x:c r="CC9" s="46"/>
+      <x:c r="CD9" s="46"/>
+      <x:c r="CE9" s="46"/>
+      <x:c r="CF9" s="46"/>
+      <x:c r="CG9" s="46"/>
+      <x:c r="CH9" s="46"/>
+      <x:c r="CI9" s="46"/>
+      <x:c r="CJ9" s="46"/>
+      <x:c r="CK9" s="46"/>
+      <x:c r="CL9" s="46"/>
     </x:row>
     <x:row r="10" ht="13.5" customHeight="1">
-      <x:c r="A10" s="67" t="s">
+      <x:c r="A10" s="50" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="B10" s="68"/>
-      <x:c r="C10" s="68"/>
-      <x:c r="D10" s="68"/>
-      <x:c r="E10" s="68"/>
-      <x:c r="F10" s="68"/>
-      <x:c r="G10" s="68"/>
-      <x:c r="H10" s="68"/>
-      <x:c r="I10" s="68"/>
-      <x:c r="J10" s="68"/>
-      <x:c r="K10" s="68"/>
-      <x:c r="L10" s="68"/>
-      <x:c r="M10" s="68"/>
-      <x:c r="N10" s="68"/>
-      <x:c r="O10" s="68"/>
-      <x:c r="P10" s="68"/>
-      <x:c r="Q10" s="68"/>
-      <x:c r="R10" s="68"/>
-      <x:c r="S10" s="67" t="s">
+      <x:c r="B10" s="51"/>
+      <x:c r="C10" s="51"/>
+      <x:c r="D10" s="51"/>
+      <x:c r="E10" s="51"/>
+      <x:c r="F10" s="51"/>
+      <x:c r="G10" s="51"/>
+      <x:c r="H10" s="51"/>
+      <x:c r="I10" s="51"/>
+      <x:c r="J10" s="51"/>
+      <x:c r="K10" s="51"/>
+      <x:c r="L10" s="51"/>
+      <x:c r="M10" s="51"/>
+      <x:c r="N10" s="51"/>
+      <x:c r="O10" s="51"/>
+      <x:c r="P10" s="51"/>
+      <x:c r="Q10" s="51"/>
+      <x:c r="R10" s="51"/>
+      <x:c r="S10" s="50" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="T10" s="68"/>
-      <x:c r="U10" s="68"/>
-      <x:c r="V10" s="68"/>
-      <x:c r="W10" s="68"/>
-      <x:c r="X10" s="68"/>
-      <x:c r="Y10" s="68"/>
-      <x:c r="Z10" s="68"/>
-      <x:c r="AA10" s="68"/>
-      <x:c r="AB10" s="68"/>
-      <x:c r="AC10" s="68"/>
-      <x:c r="AD10" s="68"/>
-      <x:c r="AE10" s="68"/>
-      <x:c r="AF10" s="68"/>
-      <x:c r="AG10" s="68"/>
-      <x:c r="AH10" s="68"/>
-      <x:c r="AI10" s="68"/>
-      <x:c r="AJ10" s="68"/>
-      <x:c r="AK10" s="67" t="str">
-        <x:v>移送方法ほか</x:v>
-      </x:c>
-      <x:c r="AL10" s="68"/>
-      <x:c r="AM10" s="68"/>
-      <x:c r="AN10" s="68"/>
-      <x:c r="AO10" s="68"/>
-      <x:c r="AP10" s="68"/>
-      <x:c r="AQ10" s="68"/>
-      <x:c r="AR10" s="68"/>
-      <x:c r="AS10" s="68"/>
-      <x:c r="AT10" s="68"/>
-      <x:c r="AU10" s="68"/>
-      <x:c r="AV10" s="68"/>
-      <x:c r="AW10" s="68"/>
-      <x:c r="AX10" s="68"/>
-      <x:c r="AY10" s="68"/>
-      <x:c r="AZ10" s="68"/>
-      <x:c r="BA10" s="68"/>
-      <x:c r="BB10" s="68"/>
-      <x:c r="BC10" s="68"/>
-      <x:c r="BD10" s="68"/>
-      <x:c r="BE10" s="68"/>
-      <x:c r="BF10" s="68"/>
-      <x:c r="BG10" s="68"/>
-      <x:c r="BH10" s="68"/>
-      <x:c r="BI10" s="68"/>
-      <x:c r="BJ10" s="68"/>
-      <x:c r="BK10" s="68"/>
-      <x:c r="BL10" s="68"/>
-      <x:c r="BM10" s="68"/>
-      <x:c r="BN10" s="68"/>
-      <x:c r="BO10" s="68"/>
-      <x:c r="BP10" s="68"/>
-      <x:c r="BQ10" s="68"/>
-      <x:c r="BR10" s="68"/>
-      <x:c r="BS10" s="68"/>
-      <x:c r="BT10" s="68"/>
-      <x:c r="BU10" s="68"/>
-      <x:c r="BV10" s="68"/>
-      <x:c r="BW10" s="68"/>
-      <x:c r="BX10" s="68"/>
-      <x:c r="BY10" s="68"/>
-      <x:c r="BZ10" s="68"/>
-      <x:c r="CA10" s="68"/>
-      <x:c r="CB10" s="68"/>
-      <x:c r="CC10" s="68"/>
-      <x:c r="CD10" s="68"/>
-      <x:c r="CE10" s="68"/>
-      <x:c r="CF10" s="68"/>
-      <x:c r="CG10" s="68"/>
-      <x:c r="CH10" s="68"/>
-      <x:c r="CI10" s="68"/>
-      <x:c r="CJ10" s="68"/>
-      <x:c r="CK10" s="68"/>
-      <x:c r="CL10" s="69"/>
+      <x:c r="T10" s="51"/>
+      <x:c r="U10" s="51"/>
+      <x:c r="V10" s="51"/>
+      <x:c r="W10" s="51"/>
+      <x:c r="X10" s="51"/>
+      <x:c r="Y10" s="51"/>
+      <x:c r="Z10" s="51"/>
+      <x:c r="AA10" s="51"/>
+      <x:c r="AB10" s="51"/>
+      <x:c r="AC10" s="51"/>
+      <x:c r="AD10" s="51"/>
+      <x:c r="AE10" s="51"/>
+      <x:c r="AF10" s="51"/>
+      <x:c r="AG10" s="51"/>
+      <x:c r="AH10" s="51"/>
+      <x:c r="AI10" s="51"/>
+      <x:c r="AJ10" s="51"/>
+      <x:c r="AK10" s="50" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="AL10" s="51"/>
+      <x:c r="AM10" s="51"/>
+      <x:c r="AN10" s="51"/>
+      <x:c r="AO10" s="51"/>
+      <x:c r="AP10" s="51"/>
+      <x:c r="AQ10" s="51"/>
+      <x:c r="AR10" s="51"/>
+      <x:c r="AS10" s="51"/>
+      <x:c r="AT10" s="51"/>
+      <x:c r="AU10" s="51"/>
+      <x:c r="AV10" s="51"/>
+      <x:c r="AW10" s="51"/>
+      <x:c r="AX10" s="51"/>
+      <x:c r="AY10" s="51"/>
+      <x:c r="AZ10" s="51"/>
+      <x:c r="BA10" s="51"/>
+      <x:c r="BB10" s="51"/>
+      <x:c r="BC10" s="51"/>
+      <x:c r="BD10" s="51"/>
+      <x:c r="BE10" s="51"/>
+      <x:c r="BF10" s="51"/>
+      <x:c r="BG10" s="51"/>
+      <x:c r="BH10" s="51"/>
+      <x:c r="BI10" s="51"/>
+      <x:c r="BJ10" s="51"/>
+      <x:c r="BK10" s="51"/>
+      <x:c r="BL10" s="51"/>
+      <x:c r="BM10" s="51"/>
+      <x:c r="BN10" s="51"/>
+      <x:c r="BO10" s="51"/>
+      <x:c r="BP10" s="51"/>
+      <x:c r="BQ10" s="51"/>
+      <x:c r="BR10" s="51"/>
+      <x:c r="BS10" s="51"/>
+      <x:c r="BT10" s="51"/>
+      <x:c r="BU10" s="51"/>
+      <x:c r="BV10" s="51"/>
+      <x:c r="BW10" s="51"/>
+      <x:c r="BX10" s="51"/>
+      <x:c r="BY10" s="51"/>
+      <x:c r="BZ10" s="51"/>
+      <x:c r="CA10" s="51"/>
+      <x:c r="CB10" s="51"/>
+      <x:c r="CC10" s="51"/>
+      <x:c r="CD10" s="51"/>
+      <x:c r="CE10" s="51"/>
+      <x:c r="CF10" s="51"/>
+      <x:c r="CG10" s="51"/>
+      <x:c r="CH10" s="51"/>
+      <x:c r="CI10" s="51"/>
+      <x:c r="CJ10" s="51"/>
+      <x:c r="CK10" s="51"/>
+      <x:c r="CL10" s="52"/>
     </x:row>
     <x:row r="11" ht="13.5" customHeight="1">
-      <x:c r="A11" s="64" t="s">
+      <x:c r="A11" s="47" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="B11" s="65"/>
-      <x:c r="C11" s="65"/>
-      <x:c r="D11" s="65"/>
-      <x:c r="E11" s="65"/>
-      <x:c r="F11" s="65"/>
-      <x:c r="G11" s="65"/>
-      <x:c r="H11" s="65"/>
-      <x:c r="I11" s="65"/>
-      <x:c r="J11" s="65"/>
-      <x:c r="K11" s="65"/>
-      <x:c r="L11" s="65"/>
-      <x:c r="M11" s="65"/>
-      <x:c r="N11" s="65"/>
-      <x:c r="O11" s="65"/>
-      <x:c r="P11" s="65"/>
-      <x:c r="Q11" s="65"/>
-      <x:c r="R11" s="65"/>
-      <x:c r="S11" s="64"/>
-      <x:c r="T11" s="65"/>
-      <x:c r="U11" s="65"/>
-      <x:c r="V11" s="65"/>
-      <x:c r="W11" s="65"/>
-      <x:c r="X11" s="65"/>
-      <x:c r="Y11" s="65"/>
-      <x:c r="Z11" s="65"/>
-      <x:c r="AA11" s="65"/>
-      <x:c r="AB11" s="65"/>
-      <x:c r="AC11" s="65"/>
-      <x:c r="AD11" s="65"/>
-      <x:c r="AE11" s="65"/>
-      <x:c r="AF11" s="65"/>
-      <x:c r="AG11" s="65"/>
-      <x:c r="AH11" s="65"/>
-      <x:c r="AI11" s="65"/>
-      <x:c r="AJ11" s="65"/>
-      <x:c r="AK11" s="64" t="str">
-        <x:v>@user_id_2</x:v>
-      </x:c>
-      <x:c r="AL11" s="65"/>
-      <x:c r="AM11" s="65"/>
-      <x:c r="AN11" s="65"/>
-      <x:c r="AO11" s="65"/>
-      <x:c r="AP11" s="65"/>
-      <x:c r="AQ11" s="65"/>
-      <x:c r="AR11" s="65"/>
-      <x:c r="AS11" s="65"/>
-      <x:c r="AT11" s="65"/>
-      <x:c r="AU11" s="65"/>
-      <x:c r="AV11" s="65"/>
-      <x:c r="AW11" s="65"/>
-      <x:c r="AX11" s="65"/>
-      <x:c r="AY11" s="65"/>
-      <x:c r="AZ11" s="65"/>
-      <x:c r="BA11" s="65"/>
-      <x:c r="BB11" s="65"/>
-      <x:c r="BC11" s="65"/>
-      <x:c r="BD11" s="65"/>
-      <x:c r="BE11" s="65"/>
-      <x:c r="BF11" s="65"/>
-      <x:c r="BG11" s="65"/>
-      <x:c r="BH11" s="65"/>
-      <x:c r="BI11" s="65"/>
-      <x:c r="BJ11" s="65"/>
-      <x:c r="BK11" s="65"/>
-      <x:c r="BL11" s="65"/>
-      <x:c r="BM11" s="65"/>
-      <x:c r="BN11" s="65"/>
-      <x:c r="BO11" s="65"/>
-      <x:c r="BP11" s="65"/>
-      <x:c r="BQ11" s="65"/>
-      <x:c r="BR11" s="65"/>
-      <x:c r="BS11" s="65"/>
-      <x:c r="BT11" s="65"/>
-      <x:c r="BU11" s="65"/>
-      <x:c r="BV11" s="65"/>
-      <x:c r="BW11" s="65"/>
-      <x:c r="BX11" s="65"/>
-      <x:c r="BY11" s="65"/>
-      <x:c r="BZ11" s="65"/>
-      <x:c r="CA11" s="65"/>
-      <x:c r="CB11" s="65"/>
-      <x:c r="CC11" s="65"/>
-      <x:c r="CD11" s="65"/>
-      <x:c r="CE11" s="65"/>
-      <x:c r="CF11" s="65"/>
-      <x:c r="CG11" s="65"/>
-      <x:c r="CH11" s="65"/>
-      <x:c r="CI11" s="65"/>
-      <x:c r="CJ11" s="65"/>
-      <x:c r="CK11" s="65"/>
-      <x:c r="CL11" s="66"/>
+      <x:c r="B11" s="48"/>
+      <x:c r="C11" s="48"/>
+      <x:c r="D11" s="48"/>
+      <x:c r="E11" s="48"/>
+      <x:c r="F11" s="48"/>
+      <x:c r="G11" s="48"/>
+      <x:c r="H11" s="48"/>
+      <x:c r="I11" s="48"/>
+      <x:c r="J11" s="48"/>
+      <x:c r="K11" s="48"/>
+      <x:c r="L11" s="48"/>
+      <x:c r="M11" s="48"/>
+      <x:c r="N11" s="48"/>
+      <x:c r="O11" s="48"/>
+      <x:c r="P11" s="48"/>
+      <x:c r="Q11" s="48"/>
+      <x:c r="R11" s="48"/>
+      <x:c r="S11" s="47"/>
+      <x:c r="T11" s="48"/>
+      <x:c r="U11" s="48"/>
+      <x:c r="V11" s="48"/>
+      <x:c r="W11" s="48"/>
+      <x:c r="X11" s="48"/>
+      <x:c r="Y11" s="48"/>
+      <x:c r="Z11" s="48"/>
+      <x:c r="AA11" s="48"/>
+      <x:c r="AB11" s="48"/>
+      <x:c r="AC11" s="48"/>
+      <x:c r="AD11" s="48"/>
+      <x:c r="AE11" s="48"/>
+      <x:c r="AF11" s="48"/>
+      <x:c r="AG11" s="48"/>
+      <x:c r="AH11" s="48"/>
+      <x:c r="AI11" s="48"/>
+      <x:c r="AJ11" s="48"/>
+      <x:c r="AK11" s="47" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="AL11" s="48"/>
+      <x:c r="AM11" s="48"/>
+      <x:c r="AN11" s="48"/>
+      <x:c r="AO11" s="48"/>
+      <x:c r="AP11" s="48"/>
+      <x:c r="AQ11" s="48"/>
+      <x:c r="AR11" s="48"/>
+      <x:c r="AS11" s="48"/>
+      <x:c r="AT11" s="48"/>
+      <x:c r="AU11" s="48"/>
+      <x:c r="AV11" s="48"/>
+      <x:c r="AW11" s="48"/>
+      <x:c r="AX11" s="48"/>
+      <x:c r="AY11" s="48"/>
+      <x:c r="AZ11" s="48"/>
+      <x:c r="BA11" s="48"/>
+      <x:c r="BB11" s="48"/>
+      <x:c r="BC11" s="48"/>
+      <x:c r="BD11" s="48"/>
+      <x:c r="BE11" s="48"/>
+      <x:c r="BF11" s="48"/>
+      <x:c r="BG11" s="48"/>
+      <x:c r="BH11" s="48"/>
+      <x:c r="BI11" s="48"/>
+      <x:c r="BJ11" s="48"/>
+      <x:c r="BK11" s="48"/>
+      <x:c r="BL11" s="48"/>
+      <x:c r="BM11" s="48"/>
+      <x:c r="BN11" s="48"/>
+      <x:c r="BO11" s="48"/>
+      <x:c r="BP11" s="48"/>
+      <x:c r="BQ11" s="48"/>
+      <x:c r="BR11" s="48"/>
+      <x:c r="BS11" s="48"/>
+      <x:c r="BT11" s="48"/>
+      <x:c r="BU11" s="48"/>
+      <x:c r="BV11" s="48"/>
+      <x:c r="BW11" s="48"/>
+      <x:c r="BX11" s="48"/>
+      <x:c r="BY11" s="48"/>
+      <x:c r="BZ11" s="48"/>
+      <x:c r="CA11" s="48"/>
+      <x:c r="CB11" s="48"/>
+      <x:c r="CC11" s="48"/>
+      <x:c r="CD11" s="48"/>
+      <x:c r="CE11" s="48"/>
+      <x:c r="CF11" s="48"/>
+      <x:c r="CG11" s="48"/>
+      <x:c r="CH11" s="48"/>
+      <x:c r="CI11" s="48"/>
+      <x:c r="CJ11" s="48"/>
+      <x:c r="CK11" s="48"/>
+      <x:c r="CL11" s="49"/>
     </x:row>
     <x:row r="12" ht="13.5" customHeight="1">
-      <x:c r="A12" s="64" t="s">
+      <x:c r="A12" s="47" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="B12" s="65"/>
-      <x:c r="C12" s="65"/>
-      <x:c r="D12" s="65"/>
-      <x:c r="E12" s="65"/>
-      <x:c r="F12" s="65"/>
-      <x:c r="G12" s="65"/>
-      <x:c r="H12" s="65"/>
-      <x:c r="I12" s="65"/>
-      <x:c r="J12" s="65"/>
-      <x:c r="K12" s="65"/>
-      <x:c r="L12" s="65"/>
-      <x:c r="M12" s="65"/>
-      <x:c r="N12" s="65"/>
-      <x:c r="O12" s="65"/>
-      <x:c r="P12" s="65"/>
-      <x:c r="Q12" s="65"/>
-      <x:c r="R12" s="65"/>
-      <x:c r="S12" s="64"/>
-      <x:c r="T12" s="65"/>
-      <x:c r="U12" s="65"/>
-      <x:c r="V12" s="65"/>
-      <x:c r="W12" s="65"/>
-      <x:c r="X12" s="65"/>
-      <x:c r="Y12" s="65"/>
-      <x:c r="Z12" s="65"/>
-      <x:c r="AA12" s="65"/>
-      <x:c r="AB12" s="65"/>
-      <x:c r="AC12" s="65"/>
-      <x:c r="AD12" s="65"/>
-      <x:c r="AE12" s="65"/>
-      <x:c r="AF12" s="65"/>
-      <x:c r="AG12" s="65"/>
-      <x:c r="AH12" s="65"/>
-      <x:c r="AI12" s="65"/>
-      <x:c r="AJ12" s="65"/>
-      <x:c r="AK12" s="64" t="str">
-        <x:v>@name_2</x:v>
-      </x:c>
-      <x:c r="AL12" s="65"/>
-      <x:c r="AM12" s="65"/>
-      <x:c r="AN12" s="65"/>
-      <x:c r="AO12" s="65"/>
-      <x:c r="AP12" s="65"/>
-      <x:c r="AQ12" s="65"/>
-      <x:c r="AR12" s="65"/>
-      <x:c r="AS12" s="65"/>
-      <x:c r="AT12" s="65"/>
-      <x:c r="AU12" s="65"/>
-      <x:c r="AV12" s="65"/>
-      <x:c r="AW12" s="65"/>
-      <x:c r="AX12" s="65"/>
-      <x:c r="AY12" s="65"/>
-      <x:c r="AZ12" s="65"/>
-      <x:c r="BA12" s="65"/>
-      <x:c r="BB12" s="65"/>
-      <x:c r="BC12" s="65"/>
-      <x:c r="BD12" s="65"/>
-      <x:c r="BE12" s="65"/>
-      <x:c r="BF12" s="65"/>
-      <x:c r="BG12" s="65"/>
-      <x:c r="BH12" s="65"/>
-      <x:c r="BI12" s="65"/>
-      <x:c r="BJ12" s="65"/>
-      <x:c r="BK12" s="65"/>
-      <x:c r="BL12" s="65"/>
-      <x:c r="BM12" s="65"/>
-      <x:c r="BN12" s="65"/>
-      <x:c r="BO12" s="65"/>
-      <x:c r="BP12" s="65"/>
-      <x:c r="BQ12" s="65"/>
-      <x:c r="BR12" s="65"/>
-      <x:c r="BS12" s="65"/>
-      <x:c r="BT12" s="65"/>
-      <x:c r="BU12" s="65"/>
-      <x:c r="BV12" s="65"/>
-      <x:c r="BW12" s="65"/>
-      <x:c r="BX12" s="65"/>
-      <x:c r="BY12" s="65"/>
-      <x:c r="BZ12" s="65"/>
-      <x:c r="CA12" s="65"/>
-      <x:c r="CB12" s="65"/>
-      <x:c r="CC12" s="65"/>
-      <x:c r="CD12" s="65"/>
-      <x:c r="CE12" s="65"/>
-      <x:c r="CF12" s="65"/>
-      <x:c r="CG12" s="65"/>
-      <x:c r="CH12" s="65"/>
-      <x:c r="CI12" s="65"/>
-      <x:c r="CJ12" s="65"/>
-      <x:c r="CK12" s="65"/>
-      <x:c r="CL12" s="66"/>
+      <x:c r="B12" s="48"/>
+      <x:c r="C12" s="48"/>
+      <x:c r="D12" s="48"/>
+      <x:c r="E12" s="48"/>
+      <x:c r="F12" s="48"/>
+      <x:c r="G12" s="48"/>
+      <x:c r="H12" s="48"/>
+      <x:c r="I12" s="48"/>
+      <x:c r="J12" s="48"/>
+      <x:c r="K12" s="48"/>
+      <x:c r="L12" s="48"/>
+      <x:c r="M12" s="48"/>
+      <x:c r="N12" s="48"/>
+      <x:c r="O12" s="48"/>
+      <x:c r="P12" s="48"/>
+      <x:c r="Q12" s="48"/>
+      <x:c r="R12" s="48"/>
+      <x:c r="S12" s="47"/>
+      <x:c r="T12" s="48"/>
+      <x:c r="U12" s="48"/>
+      <x:c r="V12" s="48"/>
+      <x:c r="W12" s="48"/>
+      <x:c r="X12" s="48"/>
+      <x:c r="Y12" s="48"/>
+      <x:c r="Z12" s="48"/>
+      <x:c r="AA12" s="48"/>
+      <x:c r="AB12" s="48"/>
+      <x:c r="AC12" s="48"/>
+      <x:c r="AD12" s="48"/>
+      <x:c r="AE12" s="48"/>
+      <x:c r="AF12" s="48"/>
+      <x:c r="AG12" s="48"/>
+      <x:c r="AH12" s="48"/>
+      <x:c r="AI12" s="48"/>
+      <x:c r="AJ12" s="48"/>
+      <x:c r="AK12" s="47" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="AL12" s="48"/>
+      <x:c r="AM12" s="48"/>
+      <x:c r="AN12" s="48"/>
+      <x:c r="AO12" s="48"/>
+      <x:c r="AP12" s="48"/>
+      <x:c r="AQ12" s="48"/>
+      <x:c r="AR12" s="48"/>
+      <x:c r="AS12" s="48"/>
+      <x:c r="AT12" s="48"/>
+      <x:c r="AU12" s="48"/>
+      <x:c r="AV12" s="48"/>
+      <x:c r="AW12" s="48"/>
+      <x:c r="AX12" s="48"/>
+      <x:c r="AY12" s="48"/>
+      <x:c r="AZ12" s="48"/>
+      <x:c r="BA12" s="48"/>
+      <x:c r="BB12" s="48"/>
+      <x:c r="BC12" s="48"/>
+      <x:c r="BD12" s="48"/>
+      <x:c r="BE12" s="48"/>
+      <x:c r="BF12" s="48"/>
+      <x:c r="BG12" s="48"/>
+      <x:c r="BH12" s="48"/>
+      <x:c r="BI12" s="48"/>
+      <x:c r="BJ12" s="48"/>
+      <x:c r="BK12" s="48"/>
+      <x:c r="BL12" s="48"/>
+      <x:c r="BM12" s="48"/>
+      <x:c r="BN12" s="48"/>
+      <x:c r="BO12" s="48"/>
+      <x:c r="BP12" s="48"/>
+      <x:c r="BQ12" s="48"/>
+      <x:c r="BR12" s="48"/>
+      <x:c r="BS12" s="48"/>
+      <x:c r="BT12" s="48"/>
+      <x:c r="BU12" s="48"/>
+      <x:c r="BV12" s="48"/>
+      <x:c r="BW12" s="48"/>
+      <x:c r="BX12" s="48"/>
+      <x:c r="BY12" s="48"/>
+      <x:c r="BZ12" s="48"/>
+      <x:c r="CA12" s="48"/>
+      <x:c r="CB12" s="48"/>
+      <x:c r="CC12" s="48"/>
+      <x:c r="CD12" s="48"/>
+      <x:c r="CE12" s="48"/>
+      <x:c r="CF12" s="48"/>
+      <x:c r="CG12" s="48"/>
+      <x:c r="CH12" s="48"/>
+      <x:c r="CI12" s="48"/>
+      <x:c r="CJ12" s="48"/>
+      <x:c r="CK12" s="48"/>
+      <x:c r="CL12" s="49"/>
     </x:row>
     <x:row r="13" ht="13.5" customHeight="1">
-      <x:c r="A13" s="64" t="s">
+      <x:c r="A13" s="47" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="B13" s="65"/>
-      <x:c r="C13" s="65"/>
-      <x:c r="D13" s="65"/>
-      <x:c r="E13" s="65"/>
-      <x:c r="F13" s="65"/>
-      <x:c r="G13" s="65"/>
-      <x:c r="H13" s="65"/>
-      <x:c r="I13" s="65"/>
-      <x:c r="J13" s="65"/>
-      <x:c r="K13" s="65"/>
-      <x:c r="L13" s="65"/>
-      <x:c r="M13" s="65"/>
-      <x:c r="N13" s="65"/>
-      <x:c r="O13" s="65"/>
-      <x:c r="P13" s="65"/>
-      <x:c r="Q13" s="65"/>
-      <x:c r="R13" s="65"/>
-      <x:c r="S13" s="64"/>
-      <x:c r="T13" s="65"/>
-      <x:c r="U13" s="65"/>
-      <x:c r="V13" s="65"/>
-      <x:c r="W13" s="65"/>
-      <x:c r="X13" s="65"/>
-      <x:c r="Y13" s="65"/>
-      <x:c r="Z13" s="65"/>
-      <x:c r="AA13" s="65"/>
-      <x:c r="AB13" s="65"/>
-      <x:c r="AC13" s="65"/>
-      <x:c r="AD13" s="65"/>
-      <x:c r="AE13" s="65"/>
-      <x:c r="AF13" s="65"/>
-      <x:c r="AG13" s="65"/>
-      <x:c r="AH13" s="65"/>
-      <x:c r="AI13" s="65"/>
-      <x:c r="AJ13" s="65"/>
-      <x:c r="AK13" s="64" t="str">
-        <x:v>'PENDING'</x:v>
-      </x:c>
-      <x:c r="AL13" s="65"/>
-      <x:c r="AM13" s="65"/>
-      <x:c r="AN13" s="65"/>
-      <x:c r="AO13" s="65"/>
-      <x:c r="AP13" s="65"/>
-      <x:c r="AQ13" s="65"/>
-      <x:c r="AR13" s="65"/>
-      <x:c r="AS13" s="65"/>
-      <x:c r="AT13" s="65"/>
-      <x:c r="AU13" s="65"/>
-      <x:c r="AV13" s="65"/>
-      <x:c r="AW13" s="65"/>
-      <x:c r="AX13" s="65"/>
-      <x:c r="AY13" s="65"/>
-      <x:c r="AZ13" s="65"/>
-      <x:c r="BA13" s="65"/>
-      <x:c r="BB13" s="65"/>
-      <x:c r="BC13" s="65"/>
-      <x:c r="BD13" s="65"/>
-      <x:c r="BE13" s="65"/>
-      <x:c r="BF13" s="65"/>
-      <x:c r="BG13" s="65"/>
-      <x:c r="BH13" s="65"/>
-      <x:c r="BI13" s="65"/>
-      <x:c r="BJ13" s="65"/>
-      <x:c r="BK13" s="65"/>
-      <x:c r="BL13" s="65"/>
-      <x:c r="BM13" s="65"/>
-      <x:c r="BN13" s="65"/>
-      <x:c r="BO13" s="65"/>
-      <x:c r="BP13" s="65"/>
-      <x:c r="BQ13" s="65"/>
-      <x:c r="BR13" s="65"/>
-      <x:c r="BS13" s="65"/>
-      <x:c r="BT13" s="65"/>
-      <x:c r="BU13" s="65"/>
-      <x:c r="BV13" s="65"/>
-      <x:c r="BW13" s="65"/>
-      <x:c r="BX13" s="65"/>
-      <x:c r="BY13" s="65"/>
-      <x:c r="BZ13" s="65"/>
-      <x:c r="CA13" s="65"/>
-      <x:c r="CB13" s="65"/>
-      <x:c r="CC13" s="65"/>
-      <x:c r="CD13" s="65"/>
-      <x:c r="CE13" s="65"/>
-      <x:c r="CF13" s="65"/>
-      <x:c r="CG13" s="65"/>
-      <x:c r="CH13" s="65"/>
-      <x:c r="CI13" s="65"/>
-      <x:c r="CJ13" s="65"/>
-      <x:c r="CK13" s="65"/>
-      <x:c r="CL13" s="66"/>
+      <x:c r="B13" s="48"/>
+      <x:c r="C13" s="48"/>
+      <x:c r="D13" s="48"/>
+      <x:c r="E13" s="48"/>
+      <x:c r="F13" s="48"/>
+      <x:c r="G13" s="48"/>
+      <x:c r="H13" s="48"/>
+      <x:c r="I13" s="48"/>
+      <x:c r="J13" s="48"/>
+      <x:c r="K13" s="48"/>
+      <x:c r="L13" s="48"/>
+      <x:c r="M13" s="48"/>
+      <x:c r="N13" s="48"/>
+      <x:c r="O13" s="48"/>
+      <x:c r="P13" s="48"/>
+      <x:c r="Q13" s="48"/>
+      <x:c r="R13" s="48"/>
+      <x:c r="S13" s="47"/>
+      <x:c r="T13" s="48"/>
+      <x:c r="U13" s="48"/>
+      <x:c r="V13" s="48"/>
+      <x:c r="W13" s="48"/>
+      <x:c r="X13" s="48"/>
+      <x:c r="Y13" s="48"/>
+      <x:c r="Z13" s="48"/>
+      <x:c r="AA13" s="48"/>
+      <x:c r="AB13" s="48"/>
+      <x:c r="AC13" s="48"/>
+      <x:c r="AD13" s="48"/>
+      <x:c r="AE13" s="48"/>
+      <x:c r="AF13" s="48"/>
+      <x:c r="AG13" s="48"/>
+      <x:c r="AH13" s="48"/>
+      <x:c r="AI13" s="48"/>
+      <x:c r="AJ13" s="48"/>
+      <x:c r="AK13" s="47" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="AL13" s="48"/>
+      <x:c r="AM13" s="48"/>
+      <x:c r="AN13" s="48"/>
+      <x:c r="AO13" s="48"/>
+      <x:c r="AP13" s="48"/>
+      <x:c r="AQ13" s="48"/>
+      <x:c r="AR13" s="48"/>
+      <x:c r="AS13" s="48"/>
+      <x:c r="AT13" s="48"/>
+      <x:c r="AU13" s="48"/>
+      <x:c r="AV13" s="48"/>
+      <x:c r="AW13" s="48"/>
+      <x:c r="AX13" s="48"/>
+      <x:c r="AY13" s="48"/>
+      <x:c r="AZ13" s="48"/>
+      <x:c r="BA13" s="48"/>
+      <x:c r="BB13" s="48"/>
+      <x:c r="BC13" s="48"/>
+      <x:c r="BD13" s="48"/>
+      <x:c r="BE13" s="48"/>
+      <x:c r="BF13" s="48"/>
+      <x:c r="BG13" s="48"/>
+      <x:c r="BH13" s="48"/>
+      <x:c r="BI13" s="48"/>
+      <x:c r="BJ13" s="48"/>
+      <x:c r="BK13" s="48"/>
+      <x:c r="BL13" s="48"/>
+      <x:c r="BM13" s="48"/>
+      <x:c r="BN13" s="48"/>
+      <x:c r="BO13" s="48"/>
+      <x:c r="BP13" s="48"/>
+      <x:c r="BQ13" s="48"/>
+      <x:c r="BR13" s="48"/>
+      <x:c r="BS13" s="48"/>
+      <x:c r="BT13" s="48"/>
+      <x:c r="BU13" s="48"/>
+      <x:c r="BV13" s="48"/>
+      <x:c r="BW13" s="48"/>
+      <x:c r="BX13" s="48"/>
+      <x:c r="BY13" s="48"/>
+      <x:c r="BZ13" s="48"/>
+      <x:c r="CA13" s="48"/>
+      <x:c r="CB13" s="48"/>
+      <x:c r="CC13" s="48"/>
+      <x:c r="CD13" s="48"/>
+      <x:c r="CE13" s="48"/>
+      <x:c r="CF13" s="48"/>
+      <x:c r="CG13" s="48"/>
+      <x:c r="CH13" s="48"/>
+      <x:c r="CI13" s="48"/>
+      <x:c r="CJ13" s="48"/>
+      <x:c r="CK13" s="48"/>
+      <x:c r="CL13" s="49"/>
     </x:row>
     <x:row r="14" ht="13.5" customHeight="1">
-      <x:c r="A14" s="64" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="B14" s="65"/>
-      <x:c r="C14" s="65"/>
-      <x:c r="D14" s="65"/>
-      <x:c r="E14" s="65"/>
-      <x:c r="F14" s="65"/>
-      <x:c r="G14" s="65"/>
-      <x:c r="H14" s="65"/>
-      <x:c r="I14" s="65"/>
-      <x:c r="J14" s="65"/>
-      <x:c r="K14" s="65"/>
-      <x:c r="L14" s="65"/>
-      <x:c r="M14" s="65"/>
-      <x:c r="N14" s="65"/>
-      <x:c r="O14" s="65"/>
-      <x:c r="P14" s="65"/>
-      <x:c r="Q14" s="65"/>
-      <x:c r="R14" s="65"/>
-      <x:c r="S14" s="64"/>
-      <x:c r="T14" s="65"/>
-      <x:c r="U14" s="65"/>
-      <x:c r="V14" s="65"/>
-      <x:c r="W14" s="65"/>
-      <x:c r="X14" s="65"/>
-      <x:c r="Y14" s="65"/>
-      <x:c r="Z14" s="65"/>
-      <x:c r="AA14" s="65"/>
-      <x:c r="AB14" s="65"/>
-      <x:c r="AC14" s="65"/>
-      <x:c r="AD14" s="65"/>
-      <x:c r="AE14" s="65"/>
-      <x:c r="AF14" s="65"/>
-      <x:c r="AG14" s="65"/>
-      <x:c r="AH14" s="65"/>
-      <x:c r="AI14" s="65"/>
-      <x:c r="AJ14" s="65"/>
-      <x:c r="AK14" s="64" t="str">
-        <x:v>SYSDATETIME()</x:v>
-      </x:c>
-      <x:c r="AL14" s="65"/>
-      <x:c r="AM14" s="65"/>
-      <x:c r="AN14" s="65"/>
-      <x:c r="AO14" s="65"/>
-      <x:c r="AP14" s="65"/>
-      <x:c r="AQ14" s="65"/>
-      <x:c r="AR14" s="65"/>
-      <x:c r="AS14" s="65"/>
-      <x:c r="AT14" s="65"/>
-      <x:c r="AU14" s="65"/>
-      <x:c r="AV14" s="65"/>
-      <x:c r="AW14" s="65"/>
-      <x:c r="AX14" s="65"/>
-      <x:c r="AY14" s="65"/>
-      <x:c r="AZ14" s="65"/>
-      <x:c r="BA14" s="65"/>
-      <x:c r="BB14" s="65"/>
-      <x:c r="BC14" s="65"/>
-      <x:c r="BD14" s="65"/>
-      <x:c r="BE14" s="65"/>
-      <x:c r="BF14" s="65"/>
-      <x:c r="BG14" s="65"/>
-      <x:c r="BH14" s="65"/>
-      <x:c r="BI14" s="65"/>
-      <x:c r="BJ14" s="65"/>
-      <x:c r="BK14" s="65"/>
-      <x:c r="BL14" s="65"/>
-      <x:c r="BM14" s="65"/>
-      <x:c r="BN14" s="65"/>
-      <x:c r="BO14" s="65"/>
-      <x:c r="BP14" s="65"/>
-      <x:c r="BQ14" s="65"/>
-      <x:c r="BR14" s="65"/>
-      <x:c r="BS14" s="65"/>
-      <x:c r="BT14" s="65"/>
-      <x:c r="BU14" s="65"/>
-      <x:c r="BV14" s="65"/>
-      <x:c r="BW14" s="65"/>
-      <x:c r="BX14" s="65"/>
-      <x:c r="BY14" s="65"/>
-      <x:c r="BZ14" s="65"/>
-      <x:c r="CA14" s="65"/>
-      <x:c r="CB14" s="65"/>
-      <x:c r="CC14" s="65"/>
-      <x:c r="CD14" s="65"/>
-      <x:c r="CE14" s="65"/>
-      <x:c r="CF14" s="65"/>
-      <x:c r="CG14" s="65"/>
-      <x:c r="CH14" s="65"/>
-      <x:c r="CI14" s="65"/>
-      <x:c r="CJ14" s="65"/>
-      <x:c r="CK14" s="65"/>
-      <x:c r="CL14" s="66"/>
+      <x:c r="A14" s="47" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="B14" s="48"/>
+      <x:c r="C14" s="48"/>
+      <x:c r="D14" s="48"/>
+      <x:c r="E14" s="48"/>
+      <x:c r="F14" s="48"/>
+      <x:c r="G14" s="48"/>
+      <x:c r="H14" s="48"/>
+      <x:c r="I14" s="48"/>
+      <x:c r="J14" s="48"/>
+      <x:c r="K14" s="48"/>
+      <x:c r="L14" s="48"/>
+      <x:c r="M14" s="48"/>
+      <x:c r="N14" s="48"/>
+      <x:c r="O14" s="48"/>
+      <x:c r="P14" s="48"/>
+      <x:c r="Q14" s="48"/>
+      <x:c r="R14" s="48"/>
+      <x:c r="S14" s="47"/>
+      <x:c r="T14" s="48"/>
+      <x:c r="U14" s="48"/>
+      <x:c r="V14" s="48"/>
+      <x:c r="W14" s="48"/>
+      <x:c r="X14" s="48"/>
+      <x:c r="Y14" s="48"/>
+      <x:c r="Z14" s="48"/>
+      <x:c r="AA14" s="48"/>
+      <x:c r="AB14" s="48"/>
+      <x:c r="AC14" s="48"/>
+      <x:c r="AD14" s="48"/>
+      <x:c r="AE14" s="48"/>
+      <x:c r="AF14" s="48"/>
+      <x:c r="AG14" s="48"/>
+      <x:c r="AH14" s="48"/>
+      <x:c r="AI14" s="48"/>
+      <x:c r="AJ14" s="48"/>
+      <x:c r="AK14" s="47" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="AL14" s="48"/>
+      <x:c r="AM14" s="48"/>
+      <x:c r="AN14" s="48"/>
+      <x:c r="AO14" s="48"/>
+      <x:c r="AP14" s="48"/>
+      <x:c r="AQ14" s="48"/>
+      <x:c r="AR14" s="48"/>
+      <x:c r="AS14" s="48"/>
+      <x:c r="AT14" s="48"/>
+      <x:c r="AU14" s="48"/>
+      <x:c r="AV14" s="48"/>
+      <x:c r="AW14" s="48"/>
+      <x:c r="AX14" s="48"/>
+      <x:c r="AY14" s="48"/>
+      <x:c r="AZ14" s="48"/>
+      <x:c r="BA14" s="48"/>
+      <x:c r="BB14" s="48"/>
+      <x:c r="BC14" s="48"/>
+      <x:c r="BD14" s="48"/>
+      <x:c r="BE14" s="48"/>
+      <x:c r="BF14" s="48"/>
+      <x:c r="BG14" s="48"/>
+      <x:c r="BH14" s="48"/>
+      <x:c r="BI14" s="48"/>
+      <x:c r="BJ14" s="48"/>
+      <x:c r="BK14" s="48"/>
+      <x:c r="BL14" s="48"/>
+      <x:c r="BM14" s="48"/>
+      <x:c r="BN14" s="48"/>
+      <x:c r="BO14" s="48"/>
+      <x:c r="BP14" s="48"/>
+      <x:c r="BQ14" s="48"/>
+      <x:c r="BR14" s="48"/>
+      <x:c r="BS14" s="48"/>
+      <x:c r="BT14" s="48"/>
+      <x:c r="BU14" s="48"/>
+      <x:c r="BV14" s="48"/>
+      <x:c r="BW14" s="48"/>
+      <x:c r="BX14" s="48"/>
+      <x:c r="BY14" s="48"/>
+      <x:c r="BZ14" s="48"/>
+      <x:c r="CA14" s="48"/>
+      <x:c r="CB14" s="48"/>
+      <x:c r="CC14" s="48"/>
+      <x:c r="CD14" s="48"/>
+      <x:c r="CE14" s="48"/>
+      <x:c r="CF14" s="48"/>
+      <x:c r="CG14" s="48"/>
+      <x:c r="CH14" s="48"/>
+      <x:c r="CI14" s="48"/>
+      <x:c r="CJ14" s="48"/>
+      <x:c r="CK14" s="48"/>
+      <x:c r="CL14" s="49"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -55520,2019 +55397,2020 @@
 
 <file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultRowHeight="18.75"/>
   <x:cols>
-    <x:col min="1" max="1" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="22" max="22" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="24" max="24" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="25" max="25" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="26" max="26" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="27" max="27" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="28" max="28" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="29" max="29" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="30" max="30" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="31" max="31" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="32" max="32" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="33" max="33" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="34" max="34" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="35" max="35" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="36" max="36" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="37" max="37" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="38" max="38" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="39" max="39" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="40" max="40" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="41" max="41" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="42" max="42" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="43" max="43" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="44" max="44" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="45" max="45" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="46" max="46" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="47" max="47" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="48" max="48" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="49" max="49" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="50" max="50" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="51" max="51" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="52" max="52" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="53" max="53" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="54" max="54" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="55" max="55" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="56" max="56" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="57" max="57" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="58" max="58" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="59" max="59" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="60" max="60" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="61" max="61" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="62" max="62" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="63" max="63" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="64" max="64" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="65" max="65" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="66" max="66" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="67" max="67" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="68" max="68" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="69" max="69" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="70" max="70" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="71" max="71" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="72" max="72" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="73" max="73" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="74" max="74" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="75" max="75" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="76" max="76" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="77" max="77" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="78" max="78" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="79" max="79" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="80" max="80" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="81" max="81" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="82" max="82" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="83" max="83" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="84" max="84" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="85" max="85" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="86" max="86" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="87" max="87" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="88" max="88" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="89" max="89" width="1.1399999856948853" hidden="0" customWidth="1"/>
-    <x:col min="90" max="90" width="1.1399999856948853" hidden="0" customWidth="1"/>
+    <x:col min="1" max="90" width="1.125" customWidth="1"/>
+    <x:col min="1" max="1" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="29" max="29" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="30" max="30" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="33" max="33" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="34" max="34" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="35" max="35" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="36" max="36" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="37" max="37" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="38" max="38" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="39" max="39" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="40" max="40" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="41" max="41" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="42" max="42" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="43" max="43" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="44" max="44" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="45" max="45" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="46" max="46" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="47" max="47" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="48" max="48" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="49" max="49" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="50" max="50" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="51" max="51" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="52" max="52" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="53" max="53" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="54" max="54" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="55" max="55" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="56" max="56" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="57" max="57" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="58" max="58" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="59" max="59" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="60" max="60" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="61" max="61" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="62" max="62" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="63" max="63" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="64" max="64" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="65" max="65" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="66" max="66" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="67" max="67" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="68" max="68" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="69" max="69" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="70" max="70" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="71" max="71" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="72" max="72" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="73" max="73" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="74" max="74" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="75" max="75" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="76" max="76" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="77" max="77" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="78" max="78" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="79" max="79" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="80" max="80" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="81" max="81" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="82" max="82" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="83" max="83" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="84" max="84" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="85" max="85" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="86" max="86" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="87" max="87" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="88" max="88" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="89" max="89" width="1.7799999713897705" hidden="0" customWidth="1"/>
+    <x:col min="90" max="90" width="1.7799999713897705" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="13.5" customHeight="1">
-      <x:c r="A1" s="61" t="s">
+      <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="61"/>
-      <x:c r="C1" s="61"/>
-      <x:c r="D1" s="61"/>
-      <x:c r="E1" s="61"/>
-      <x:c r="F1" s="61"/>
-      <x:c r="G1" s="61"/>
-      <x:c r="H1" s="61"/>
-      <x:c r="I1" s="61"/>
-      <x:c r="J1" s="61"/>
-      <x:c r="K1" s="61"/>
-      <x:c r="L1" s="61"/>
-      <x:c r="M1" s="61"/>
-      <x:c r="N1" s="61"/>
-      <x:c r="O1" s="61"/>
-      <x:c r="P1" s="61"/>
-      <x:c r="Q1" s="61"/>
-      <x:c r="R1" s="61"/>
-      <x:c r="S1" s="61"/>
-      <x:c r="T1" s="61"/>
-      <x:c r="U1" s="61"/>
-      <x:c r="V1" s="61"/>
-      <x:c r="W1" s="61"/>
-      <x:c r="X1" s="61"/>
-      <x:c r="Y1" s="61"/>
-      <x:c r="Z1" s="61"/>
-      <x:c r="AA1" s="61"/>
-      <x:c r="AB1" s="61"/>
-      <x:c r="AC1" s="61"/>
-      <x:c r="AD1" s="61"/>
-      <x:c r="AE1" s="61"/>
-      <x:c r="AF1" s="61"/>
-      <x:c r="AG1" s="61"/>
-      <x:c r="AH1" s="61"/>
-      <x:c r="AI1" s="61"/>
-      <x:c r="AJ1" s="61"/>
-      <x:c r="AK1" s="61"/>
-      <x:c r="AL1" s="61"/>
-      <x:c r="AM1" s="61"/>
-      <x:c r="AN1" s="61"/>
-      <x:c r="AO1" s="61"/>
-      <x:c r="AP1" s="61"/>
-      <x:c r="AQ1" s="61"/>
-      <x:c r="AR1" s="61"/>
-      <x:c r="AS1" s="61"/>
-      <x:c r="AT1" s="61"/>
-      <x:c r="AU1" s="61"/>
-      <x:c r="AV1" s="61"/>
-      <x:c r="AW1" s="61"/>
-      <x:c r="AX1" s="61"/>
-      <x:c r="AY1" s="61"/>
-      <x:c r="AZ1" s="61"/>
-      <x:c r="BA1" s="61"/>
-      <x:c r="BB1" s="61"/>
-      <x:c r="BC1" s="61"/>
-      <x:c r="BD1" s="61"/>
-      <x:c r="BE1" s="61"/>
-      <x:c r="BF1" s="61"/>
-      <x:c r="BG1" s="61"/>
-      <x:c r="BH1" s="61"/>
-      <x:c r="BI1" s="61"/>
-      <x:c r="BJ1" s="61"/>
-      <x:c r="BK1" s="61"/>
-      <x:c r="BL1" s="61"/>
-      <x:c r="BM1" s="61"/>
-      <x:c r="BN1" s="61"/>
-      <x:c r="BO1" s="61"/>
-      <x:c r="BP1" s="61"/>
-      <x:c r="BQ1" s="61"/>
-      <x:c r="BR1" s="61"/>
-      <x:c r="BS1" s="61"/>
-      <x:c r="BT1" s="61"/>
-      <x:c r="BU1" s="61"/>
-      <x:c r="BV1" s="61"/>
-      <x:c r="BW1" s="61"/>
-      <x:c r="BX1" s="61"/>
-      <x:c r="BY1" s="61"/>
-      <x:c r="BZ1" s="61"/>
-      <x:c r="CA1" s="61"/>
-      <x:c r="CB1" s="61"/>
-      <x:c r="CC1" s="61"/>
-      <x:c r="CD1" s="61"/>
-      <x:c r="CE1" s="61"/>
-      <x:c r="CF1" s="61"/>
-      <x:c r="CG1" s="61"/>
-      <x:c r="CH1" s="61"/>
-      <x:c r="CI1" s="61"/>
-      <x:c r="CJ1" s="61"/>
-      <x:c r="CK1" s="61"/>
-      <x:c r="CL1" s="61"/>
+      <x:c r="B1" s="1"/>
+      <x:c r="C1" s="1"/>
+      <x:c r="D1" s="1"/>
+      <x:c r="E1" s="1"/>
+      <x:c r="F1" s="1"/>
+      <x:c r="G1" s="1"/>
+      <x:c r="H1" s="1"/>
+      <x:c r="I1" s="1"/>
+      <x:c r="J1" s="1"/>
+      <x:c r="K1" s="1"/>
+      <x:c r="L1" s="1"/>
+      <x:c r="M1" s="1"/>
+      <x:c r="N1" s="1"/>
+      <x:c r="O1" s="1"/>
+      <x:c r="P1" s="1"/>
+      <x:c r="Q1" s="1"/>
+      <x:c r="R1" s="1"/>
+      <x:c r="S1" s="1"/>
+      <x:c r="T1" s="1"/>
+      <x:c r="U1" s="1"/>
+      <x:c r="V1" s="1"/>
+      <x:c r="W1" s="1"/>
+      <x:c r="X1" s="1"/>
+      <x:c r="Y1" s="1"/>
+      <x:c r="Z1" s="1"/>
+      <x:c r="AA1" s="1"/>
+      <x:c r="AB1" s="1"/>
+      <x:c r="AC1" s="1"/>
+      <x:c r="AD1" s="1"/>
+      <x:c r="AE1" s="1"/>
+      <x:c r="AF1" s="1"/>
+      <x:c r="AG1" s="1"/>
+      <x:c r="AH1" s="1"/>
+      <x:c r="AI1" s="1"/>
+      <x:c r="AJ1" s="1"/>
+      <x:c r="AK1" s="1"/>
+      <x:c r="AL1" s="1"/>
+      <x:c r="AM1" s="1"/>
+      <x:c r="AN1" s="1"/>
+      <x:c r="AO1" s="1"/>
+      <x:c r="AP1" s="1"/>
+      <x:c r="AQ1" s="1"/>
+      <x:c r="AR1" s="1"/>
+      <x:c r="AS1" s="1"/>
+      <x:c r="AT1" s="1"/>
+      <x:c r="AU1" s="1"/>
+      <x:c r="AV1" s="1"/>
+      <x:c r="AW1" s="1"/>
+      <x:c r="AX1" s="1"/>
+      <x:c r="AY1" s="1"/>
+      <x:c r="AZ1" s="1"/>
+      <x:c r="BA1" s="1"/>
+      <x:c r="BB1" s="1"/>
+      <x:c r="BC1" s="1"/>
+      <x:c r="BD1" s="1"/>
+      <x:c r="BE1" s="1"/>
+      <x:c r="BF1" s="1"/>
+      <x:c r="BG1" s="1"/>
+      <x:c r="BH1" s="1"/>
+      <x:c r="BI1" s="1"/>
+      <x:c r="BJ1" s="1"/>
+      <x:c r="BK1" s="1"/>
+      <x:c r="BL1" s="1"/>
+      <x:c r="BM1" s="1"/>
+      <x:c r="BN1" s="1"/>
+      <x:c r="BO1" s="1"/>
+      <x:c r="BP1" s="1"/>
+      <x:c r="BQ1" s="1"/>
+      <x:c r="BR1" s="1"/>
+      <x:c r="BS1" s="1"/>
+      <x:c r="BT1" s="1"/>
+      <x:c r="BU1" s="1"/>
+      <x:c r="BV1" s="1"/>
+      <x:c r="BW1" s="1"/>
+      <x:c r="BX1" s="1"/>
+      <x:c r="BY1" s="1"/>
+      <x:c r="BZ1" s="1"/>
+      <x:c r="CA1" s="1"/>
+      <x:c r="CB1" s="1"/>
+      <x:c r="CC1" s="1"/>
+      <x:c r="CD1" s="1"/>
+      <x:c r="CE1" s="1"/>
+      <x:c r="CF1" s="1"/>
+      <x:c r="CG1" s="1"/>
+      <x:c r="CH1" s="1"/>
+      <x:c r="CI1" s="1"/>
+      <x:c r="CJ1" s="1"/>
+      <x:c r="CK1" s="1"/>
+      <x:c r="CL1" s="1"/>
     </x:row>
     <x:row r="2" ht="13.5" customHeight="1">
-      <x:c r="A2" s="61" t="s">
+      <x:c r="A2" s="1" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="B2" s="61"/>
-      <x:c r="C2" s="61"/>
-      <x:c r="D2" s="61"/>
-      <x:c r="E2" s="61"/>
-      <x:c r="F2" s="61"/>
-      <x:c r="G2" s="61"/>
-      <x:c r="H2" s="61"/>
-      <x:c r="I2" s="61"/>
-      <x:c r="J2" s="61"/>
-      <x:c r="K2" s="61"/>
-      <x:c r="L2" s="61"/>
-      <x:c r="M2" s="61"/>
-      <x:c r="N2" s="61"/>
-      <x:c r="O2" s="61"/>
-      <x:c r="P2" s="61"/>
-      <x:c r="Q2" s="61"/>
-      <x:c r="R2" s="61"/>
-      <x:c r="S2" s="61"/>
-      <x:c r="T2" s="61"/>
-      <x:c r="U2" s="61"/>
-      <x:c r="V2" s="61"/>
-      <x:c r="W2" s="61"/>
-      <x:c r="X2" s="61"/>
-      <x:c r="Y2" s="61"/>
-      <x:c r="Z2" s="61"/>
-      <x:c r="AA2" s="61"/>
-      <x:c r="AB2" s="61"/>
-      <x:c r="AC2" s="61"/>
-      <x:c r="AD2" s="61"/>
-      <x:c r="AE2" s="61"/>
-      <x:c r="AF2" s="61"/>
-      <x:c r="AG2" s="61"/>
-      <x:c r="AH2" s="61"/>
-      <x:c r="AI2" s="61"/>
-      <x:c r="AJ2" s="61"/>
-      <x:c r="AK2" s="61"/>
-      <x:c r="AL2" s="61"/>
-      <x:c r="AM2" s="61"/>
-      <x:c r="AN2" s="61"/>
-      <x:c r="AO2" s="61"/>
-      <x:c r="AP2" s="61"/>
-      <x:c r="AQ2" s="61"/>
-      <x:c r="AR2" s="61"/>
-      <x:c r="AS2" s="61"/>
-      <x:c r="AT2" s="61"/>
-      <x:c r="AU2" s="61"/>
-      <x:c r="AV2" s="61"/>
-      <x:c r="AW2" s="61"/>
-      <x:c r="AX2" s="61"/>
-      <x:c r="AY2" s="61"/>
-      <x:c r="AZ2" s="61"/>
-      <x:c r="BA2" s="61"/>
-      <x:c r="BB2" s="61"/>
-      <x:c r="BC2" s="61"/>
-      <x:c r="BD2" s="61"/>
-      <x:c r="BE2" s="61"/>
-      <x:c r="BF2" s="61"/>
-      <x:c r="BG2" s="61"/>
-      <x:c r="BH2" s="61"/>
-      <x:c r="BI2" s="61"/>
-      <x:c r="BJ2" s="61"/>
-      <x:c r="BK2" s="61"/>
-      <x:c r="BL2" s="61"/>
-      <x:c r="BM2" s="61"/>
-      <x:c r="BN2" s="61"/>
-      <x:c r="BO2" s="61"/>
-      <x:c r="BP2" s="61"/>
-      <x:c r="BQ2" s="61"/>
-      <x:c r="BR2" s="61"/>
-      <x:c r="BS2" s="61"/>
-      <x:c r="BT2" s="61"/>
-      <x:c r="BU2" s="61"/>
-      <x:c r="BV2" s="61"/>
-      <x:c r="BW2" s="61"/>
-      <x:c r="BX2" s="61"/>
-      <x:c r="BY2" s="61"/>
-      <x:c r="BZ2" s="61"/>
-      <x:c r="CA2" s="61"/>
-      <x:c r="CB2" s="61"/>
-      <x:c r="CC2" s="61"/>
-      <x:c r="CD2" s="61"/>
-      <x:c r="CE2" s="61"/>
-      <x:c r="CF2" s="61"/>
-      <x:c r="CG2" s="61"/>
-      <x:c r="CH2" s="61"/>
-      <x:c r="CI2" s="61"/>
-      <x:c r="CJ2" s="61"/>
-      <x:c r="CK2" s="61"/>
-      <x:c r="CL2" s="61"/>
+      <x:c r="B2" s="1"/>
+      <x:c r="C2" s="1"/>
+      <x:c r="D2" s="1"/>
+      <x:c r="E2" s="1"/>
+      <x:c r="F2" s="1"/>
+      <x:c r="G2" s="1"/>
+      <x:c r="H2" s="1"/>
+      <x:c r="I2" s="1"/>
+      <x:c r="J2" s="1"/>
+      <x:c r="K2" s="1"/>
+      <x:c r="L2" s="1"/>
+      <x:c r="M2" s="1"/>
+      <x:c r="N2" s="1"/>
+      <x:c r="O2" s="1"/>
+      <x:c r="P2" s="1"/>
+      <x:c r="Q2" s="1"/>
+      <x:c r="R2" s="1"/>
+      <x:c r="S2" s="1"/>
+      <x:c r="T2" s="1"/>
+      <x:c r="U2" s="1"/>
+      <x:c r="V2" s="1"/>
+      <x:c r="W2" s="1"/>
+      <x:c r="X2" s="1"/>
+      <x:c r="Y2" s="1"/>
+      <x:c r="Z2" s="1"/>
+      <x:c r="AA2" s="1"/>
+      <x:c r="AB2" s="1"/>
+      <x:c r="AC2" s="1"/>
+      <x:c r="AD2" s="1"/>
+      <x:c r="AE2" s="1"/>
+      <x:c r="AF2" s="1"/>
+      <x:c r="AG2" s="1"/>
+      <x:c r="AH2" s="1"/>
+      <x:c r="AI2" s="1"/>
+      <x:c r="AJ2" s="1"/>
+      <x:c r="AK2" s="1"/>
+      <x:c r="AL2" s="1"/>
+      <x:c r="AM2" s="1"/>
+      <x:c r="AN2" s="1"/>
+      <x:c r="AO2" s="1"/>
+      <x:c r="AP2" s="1"/>
+      <x:c r="AQ2" s="1"/>
+      <x:c r="AR2" s="1"/>
+      <x:c r="AS2" s="1"/>
+      <x:c r="AT2" s="1"/>
+      <x:c r="AU2" s="1"/>
+      <x:c r="AV2" s="1"/>
+      <x:c r="AW2" s="1"/>
+      <x:c r="AX2" s="1"/>
+      <x:c r="AY2" s="1"/>
+      <x:c r="AZ2" s="1"/>
+      <x:c r="BA2" s="1"/>
+      <x:c r="BB2" s="1"/>
+      <x:c r="BC2" s="1"/>
+      <x:c r="BD2" s="1"/>
+      <x:c r="BE2" s="1"/>
+      <x:c r="BF2" s="1"/>
+      <x:c r="BG2" s="1"/>
+      <x:c r="BH2" s="1"/>
+      <x:c r="BI2" s="1"/>
+      <x:c r="BJ2" s="1"/>
+      <x:c r="BK2" s="1"/>
+      <x:c r="BL2" s="1"/>
+      <x:c r="BM2" s="1"/>
+      <x:c r="BN2" s="1"/>
+      <x:c r="BO2" s="1"/>
+      <x:c r="BP2" s="1"/>
+      <x:c r="BQ2" s="1"/>
+      <x:c r="BR2" s="1"/>
+      <x:c r="BS2" s="1"/>
+      <x:c r="BT2" s="1"/>
+      <x:c r="BU2" s="1"/>
+      <x:c r="BV2" s="1"/>
+      <x:c r="BW2" s="1"/>
+      <x:c r="BX2" s="1"/>
+      <x:c r="BY2" s="1"/>
+      <x:c r="BZ2" s="1"/>
+      <x:c r="CA2" s="1"/>
+      <x:c r="CB2" s="1"/>
+      <x:c r="CC2" s="1"/>
+      <x:c r="CD2" s="1"/>
+      <x:c r="CE2" s="1"/>
+      <x:c r="CF2" s="1"/>
+      <x:c r="CG2" s="1"/>
+      <x:c r="CH2" s="1"/>
+      <x:c r="CI2" s="1"/>
+      <x:c r="CJ2" s="1"/>
+      <x:c r="CK2" s="1"/>
+      <x:c r="CL2" s="1"/>
     </x:row>
     <x:row r="3" ht="13.5" customHeight="1">
-      <x:c r="A3" s="71" t="s">
+      <x:c r="A3" s="54" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B3" s="72"/>
-      <x:c r="C3" s="72"/>
-      <x:c r="D3" s="72"/>
-      <x:c r="E3" s="72"/>
-      <x:c r="F3" s="72"/>
-      <x:c r="G3" s="77" t="s">
+      <x:c r="B3" s="55"/>
+      <x:c r="C3" s="55"/>
+      <x:c r="D3" s="55"/>
+      <x:c r="E3" s="55"/>
+      <x:c r="F3" s="55"/>
+      <x:c r="G3" s="57" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H3" s="63"/>
-      <x:c r="I3" s="63"/>
-      <x:c r="J3" s="63"/>
-      <x:c r="K3" s="63"/>
-      <x:c r="L3" s="63"/>
-      <x:c r="M3" s="63"/>
-      <x:c r="N3" s="63"/>
-      <x:c r="O3" s="63" t="s">
+      <x:c r="H3" s="46"/>
+      <x:c r="I3" s="46"/>
+      <x:c r="J3" s="46"/>
+      <x:c r="K3" s="46"/>
+      <x:c r="L3" s="46"/>
+      <x:c r="M3" s="46"/>
+      <x:c r="N3" s="46"/>
+      <x:c r="O3" s="46" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P3" s="63"/>
-      <x:c r="Q3" s="63" t="s">
+      <x:c r="P3" s="46"/>
+      <x:c r="Q3" s="46" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="R3" s="63"/>
-      <x:c r="S3" s="63"/>
-      <x:c r="T3" s="63"/>
-      <x:c r="U3" s="63"/>
-      <x:c r="V3" s="63"/>
-      <x:c r="W3" s="63"/>
-      <x:c r="X3" s="63"/>
-      <x:c r="Y3" s="63"/>
-      <x:c r="Z3" s="63"/>
-      <x:c r="AA3" s="63"/>
-      <x:c r="AB3" s="63"/>
-      <x:c r="AC3" s="63"/>
-      <x:c r="AD3" s="63"/>
-      <x:c r="AE3" s="63"/>
-      <x:c r="AF3" s="63"/>
-      <x:c r="AG3" s="63"/>
-      <x:c r="AH3" s="63"/>
-      <x:c r="AI3" s="63"/>
-      <x:c r="AJ3" s="63"/>
-      <x:c r="AK3" s="63"/>
-      <x:c r="AL3" s="63"/>
-      <x:c r="AM3" s="63"/>
-      <x:c r="AN3" s="63"/>
-      <x:c r="AO3" s="63"/>
-      <x:c r="AP3" s="63"/>
-      <x:c r="AQ3" s="63"/>
-      <x:c r="AR3" s="63"/>
-      <x:c r="AS3" s="63"/>
-      <x:c r="AT3" s="63"/>
-      <x:c r="AU3" s="63"/>
-      <x:c r="AV3" s="63"/>
-      <x:c r="AW3" s="63"/>
-      <x:c r="AX3" s="63"/>
-      <x:c r="AY3" s="63"/>
-      <x:c r="AZ3" s="63"/>
-      <x:c r="BA3" s="63"/>
-      <x:c r="BB3" s="63"/>
-      <x:c r="BC3" s="63"/>
-      <x:c r="BD3" s="63"/>
-      <x:c r="BE3" s="63"/>
-      <x:c r="BF3" s="63"/>
-      <x:c r="BG3" s="63"/>
-      <x:c r="BH3" s="63"/>
-      <x:c r="BI3" s="63"/>
-      <x:c r="BJ3" s="63"/>
-      <x:c r="BK3" s="63"/>
-      <x:c r="BL3" s="63"/>
-      <x:c r="BM3" s="63"/>
-      <x:c r="BN3" s="63"/>
-      <x:c r="BO3" s="63"/>
-      <x:c r="BP3" s="63"/>
-      <x:c r="BQ3" s="63"/>
-      <x:c r="BR3" s="63"/>
-      <x:c r="BS3" s="63"/>
-      <x:c r="BT3" s="63"/>
-      <x:c r="BU3" s="63"/>
-      <x:c r="BV3" s="63"/>
-      <x:c r="BW3" s="63"/>
-      <x:c r="BX3" s="63"/>
-      <x:c r="BY3" s="63"/>
-      <x:c r="BZ3" s="63"/>
-      <x:c r="CA3" s="63"/>
-      <x:c r="CB3" s="63"/>
-      <x:c r="CC3" s="63"/>
-      <x:c r="CD3" s="63"/>
-      <x:c r="CE3" s="63"/>
-      <x:c r="CF3" s="63"/>
-      <x:c r="CG3" s="63"/>
-      <x:c r="CH3" s="63"/>
-      <x:c r="CI3" s="63"/>
-      <x:c r="CJ3" s="63"/>
-      <x:c r="CK3" s="63"/>
-      <x:c r="CL3" s="78"/>
+      <x:c r="R3" s="46"/>
+      <x:c r="S3" s="46"/>
+      <x:c r="T3" s="46"/>
+      <x:c r="U3" s="46"/>
+      <x:c r="V3" s="46"/>
+      <x:c r="W3" s="46"/>
+      <x:c r="X3" s="46"/>
+      <x:c r="Y3" s="46"/>
+      <x:c r="Z3" s="46"/>
+      <x:c r="AA3" s="46"/>
+      <x:c r="AB3" s="46"/>
+      <x:c r="AC3" s="46"/>
+      <x:c r="AD3" s="46"/>
+      <x:c r="AE3" s="46"/>
+      <x:c r="AF3" s="46"/>
+      <x:c r="AG3" s="46"/>
+      <x:c r="AH3" s="46"/>
+      <x:c r="AI3" s="46"/>
+      <x:c r="AJ3" s="46"/>
+      <x:c r="AK3" s="46"/>
+      <x:c r="AL3" s="46"/>
+      <x:c r="AM3" s="46"/>
+      <x:c r="AN3" s="46"/>
+      <x:c r="AO3" s="46"/>
+      <x:c r="AP3" s="46"/>
+      <x:c r="AQ3" s="46"/>
+      <x:c r="AR3" s="46"/>
+      <x:c r="AS3" s="46"/>
+      <x:c r="AT3" s="46"/>
+      <x:c r="AU3" s="46"/>
+      <x:c r="AV3" s="46"/>
+      <x:c r="AW3" s="46"/>
+      <x:c r="AX3" s="46"/>
+      <x:c r="AY3" s="46"/>
+      <x:c r="AZ3" s="46"/>
+      <x:c r="BA3" s="46"/>
+      <x:c r="BB3" s="46"/>
+      <x:c r="BC3" s="46"/>
+      <x:c r="BD3" s="46"/>
+      <x:c r="BE3" s="46"/>
+      <x:c r="BF3" s="46"/>
+      <x:c r="BG3" s="46"/>
+      <x:c r="BH3" s="46"/>
+      <x:c r="BI3" s="46"/>
+      <x:c r="BJ3" s="46"/>
+      <x:c r="BK3" s="46"/>
+      <x:c r="BL3" s="46"/>
+      <x:c r="BM3" s="46"/>
+      <x:c r="BN3" s="46"/>
+      <x:c r="BO3" s="46"/>
+      <x:c r="BP3" s="46"/>
+      <x:c r="BQ3" s="46"/>
+      <x:c r="BR3" s="46"/>
+      <x:c r="BS3" s="46"/>
+      <x:c r="BT3" s="46"/>
+      <x:c r="BU3" s="46"/>
+      <x:c r="BV3" s="46"/>
+      <x:c r="BW3" s="46"/>
+      <x:c r="BX3" s="46"/>
+      <x:c r="BY3" s="46"/>
+      <x:c r="BZ3" s="46"/>
+      <x:c r="CA3" s="46"/>
+      <x:c r="CB3" s="46"/>
+      <x:c r="CC3" s="46"/>
+      <x:c r="CD3" s="46"/>
+      <x:c r="CE3" s="46"/>
+      <x:c r="CF3" s="46"/>
+      <x:c r="CG3" s="46"/>
+      <x:c r="CH3" s="46"/>
+      <x:c r="CI3" s="46"/>
+      <x:c r="CJ3" s="46"/>
+      <x:c r="CK3" s="46"/>
+      <x:c r="CL3" s="58"/>
     </x:row>
     <x:row r="4" ht="13.5" customHeight="1">
-      <x:c r="A4" s="73"/>
-      <x:c r="B4" s="74"/>
-      <x:c r="C4" s="74"/>
-      <x:c r="D4" s="74"/>
-      <x:c r="E4" s="74"/>
-      <x:c r="F4" s="74"/>
-      <x:c r="G4" s="79" t="s">
+      <x:c r="A4" s="56"/>
+      <x:c r="B4" s="53"/>
+      <x:c r="C4" s="53"/>
+      <x:c r="D4" s="53"/>
+      <x:c r="E4" s="53"/>
+      <x:c r="F4" s="53"/>
+      <x:c r="G4" s="59" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H4" s="80"/>
-      <x:c r="I4" s="80"/>
-      <x:c r="J4" s="80"/>
-      <x:c r="K4" s="80"/>
-      <x:c r="L4" s="80"/>
-      <x:c r="M4" s="80"/>
-      <x:c r="N4" s="80"/>
-      <x:c r="O4" s="80" t="s">
+      <x:c r="H4" s="45"/>
+      <x:c r="I4" s="45"/>
+      <x:c r="J4" s="45"/>
+      <x:c r="K4" s="45"/>
+      <x:c r="L4" s="45"/>
+      <x:c r="M4" s="45"/>
+      <x:c r="N4" s="45"/>
+      <x:c r="O4" s="45" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P4" s="80"/>
-      <x:c r="Q4" s="80" t="s">
+      <x:c r="P4" s="45"/>
+      <x:c r="Q4" s="45" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="R4" s="80"/>
-      <x:c r="S4" s="80"/>
-      <x:c r="T4" s="80"/>
-      <x:c r="U4" s="80"/>
-      <x:c r="V4" s="80"/>
-      <x:c r="W4" s="80"/>
-      <x:c r="X4" s="80"/>
-      <x:c r="Y4" s="80"/>
-      <x:c r="Z4" s="80"/>
-      <x:c r="AA4" s="80"/>
-      <x:c r="AB4" s="80"/>
-      <x:c r="AC4" s="80"/>
-      <x:c r="AD4" s="80"/>
-      <x:c r="AE4" s="80"/>
-      <x:c r="AF4" s="80"/>
-      <x:c r="AG4" s="80"/>
-      <x:c r="AH4" s="80"/>
-      <x:c r="AI4" s="80"/>
-      <x:c r="AJ4" s="80"/>
-      <x:c r="AK4" s="80"/>
-      <x:c r="AL4" s="80"/>
-      <x:c r="AM4" s="80"/>
-      <x:c r="AN4" s="80"/>
-      <x:c r="AO4" s="80"/>
-      <x:c r="AP4" s="80"/>
-      <x:c r="AQ4" s="80"/>
-      <x:c r="AR4" s="80"/>
-      <x:c r="AS4" s="80"/>
-      <x:c r="AT4" s="80"/>
-      <x:c r="AU4" s="80"/>
-      <x:c r="AV4" s="80"/>
-      <x:c r="AW4" s="80"/>
-      <x:c r="AX4" s="80"/>
-      <x:c r="AY4" s="80"/>
-      <x:c r="AZ4" s="80"/>
-      <x:c r="BA4" s="80"/>
-      <x:c r="BB4" s="80"/>
-      <x:c r="BC4" s="80"/>
-      <x:c r="BD4" s="80"/>
-      <x:c r="BE4" s="80"/>
-      <x:c r="BF4" s="80"/>
-      <x:c r="BG4" s="80"/>
-      <x:c r="BH4" s="80"/>
-      <x:c r="BI4" s="80"/>
-      <x:c r="BJ4" s="80"/>
-      <x:c r="BK4" s="80"/>
-      <x:c r="BL4" s="80"/>
-      <x:c r="BM4" s="80"/>
-      <x:c r="BN4" s="80"/>
-      <x:c r="BO4" s="80"/>
-      <x:c r="BP4" s="80"/>
-      <x:c r="BQ4" s="80"/>
-      <x:c r="BR4" s="80"/>
-      <x:c r="BS4" s="80"/>
-      <x:c r="BT4" s="80"/>
-      <x:c r="BU4" s="80"/>
-      <x:c r="BV4" s="80"/>
-      <x:c r="BW4" s="80"/>
-      <x:c r="BX4" s="80"/>
-      <x:c r="BY4" s="80"/>
-      <x:c r="BZ4" s="80"/>
-      <x:c r="CA4" s="80"/>
-      <x:c r="CB4" s="80"/>
-      <x:c r="CC4" s="80"/>
-      <x:c r="CD4" s="80"/>
-      <x:c r="CE4" s="80"/>
-      <x:c r="CF4" s="80"/>
-      <x:c r="CG4" s="80"/>
-      <x:c r="CH4" s="80"/>
-      <x:c r="CI4" s="80"/>
-      <x:c r="CJ4" s="80"/>
-      <x:c r="CK4" s="80"/>
-      <x:c r="CL4" s="81"/>
+      <x:c r="R4" s="45"/>
+      <x:c r="S4" s="45"/>
+      <x:c r="T4" s="45"/>
+      <x:c r="U4" s="45"/>
+      <x:c r="V4" s="45"/>
+      <x:c r="W4" s="45"/>
+      <x:c r="X4" s="45"/>
+      <x:c r="Y4" s="45"/>
+      <x:c r="Z4" s="45"/>
+      <x:c r="AA4" s="45"/>
+      <x:c r="AB4" s="45"/>
+      <x:c r="AC4" s="45"/>
+      <x:c r="AD4" s="45"/>
+      <x:c r="AE4" s="45"/>
+      <x:c r="AF4" s="45"/>
+      <x:c r="AG4" s="45"/>
+      <x:c r="AH4" s="45"/>
+      <x:c r="AI4" s="45"/>
+      <x:c r="AJ4" s="45"/>
+      <x:c r="AK4" s="45"/>
+      <x:c r="AL4" s="45"/>
+      <x:c r="AM4" s="45"/>
+      <x:c r="AN4" s="45"/>
+      <x:c r="AO4" s="45"/>
+      <x:c r="AP4" s="45"/>
+      <x:c r="AQ4" s="45"/>
+      <x:c r="AR4" s="45"/>
+      <x:c r="AS4" s="45"/>
+      <x:c r="AT4" s="45"/>
+      <x:c r="AU4" s="45"/>
+      <x:c r="AV4" s="45"/>
+      <x:c r="AW4" s="45"/>
+      <x:c r="AX4" s="45"/>
+      <x:c r="AY4" s="45"/>
+      <x:c r="AZ4" s="45"/>
+      <x:c r="BA4" s="45"/>
+      <x:c r="BB4" s="45"/>
+      <x:c r="BC4" s="45"/>
+      <x:c r="BD4" s="45"/>
+      <x:c r="BE4" s="45"/>
+      <x:c r="BF4" s="45"/>
+      <x:c r="BG4" s="45"/>
+      <x:c r="BH4" s="45"/>
+      <x:c r="BI4" s="45"/>
+      <x:c r="BJ4" s="45"/>
+      <x:c r="BK4" s="45"/>
+      <x:c r="BL4" s="45"/>
+      <x:c r="BM4" s="45"/>
+      <x:c r="BN4" s="45"/>
+      <x:c r="BO4" s="45"/>
+      <x:c r="BP4" s="45"/>
+      <x:c r="BQ4" s="45"/>
+      <x:c r="BR4" s="45"/>
+      <x:c r="BS4" s="45"/>
+      <x:c r="BT4" s="45"/>
+      <x:c r="BU4" s="45"/>
+      <x:c r="BV4" s="45"/>
+      <x:c r="BW4" s="45"/>
+      <x:c r="BX4" s="45"/>
+      <x:c r="BY4" s="45"/>
+      <x:c r="BZ4" s="45"/>
+      <x:c r="CA4" s="45"/>
+      <x:c r="CB4" s="45"/>
+      <x:c r="CC4" s="45"/>
+      <x:c r="CD4" s="45"/>
+      <x:c r="CE4" s="45"/>
+      <x:c r="CF4" s="45"/>
+      <x:c r="CG4" s="45"/>
+      <x:c r="CH4" s="45"/>
+      <x:c r="CI4" s="45"/>
+      <x:c r="CJ4" s="45"/>
+      <x:c r="CK4" s="45"/>
+      <x:c r="CL4" s="60"/>
     </x:row>
     <x:row r="5" ht="13.5" customHeight="1">
-      <x:c r="A5" s="67" t="s">
+      <x:c r="A5" s="50" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B5" s="68"/>
-      <x:c r="C5" s="68"/>
-      <x:c r="D5" s="68"/>
-      <x:c r="E5" s="68"/>
-      <x:c r="F5" s="68"/>
-      <x:c r="G5" s="64"/>
-      <x:c r="H5" s="65"/>
-      <x:c r="I5" s="65"/>
-      <x:c r="J5" s="65"/>
-      <x:c r="K5" s="65"/>
-      <x:c r="L5" s="65"/>
-      <x:c r="M5" s="65"/>
-      <x:c r="N5" s="65"/>
-      <x:c r="O5" s="65"/>
-      <x:c r="P5" s="65"/>
-      <x:c r="Q5" s="65" t="s">
+      <x:c r="B5" s="51"/>
+      <x:c r="C5" s="51"/>
+      <x:c r="D5" s="51"/>
+      <x:c r="E5" s="51"/>
+      <x:c r="F5" s="51"/>
+      <x:c r="G5" s="47"/>
+      <x:c r="H5" s="48"/>
+      <x:c r="I5" s="48"/>
+      <x:c r="J5" s="48"/>
+      <x:c r="K5" s="48"/>
+      <x:c r="L5" s="48"/>
+      <x:c r="M5" s="48"/>
+      <x:c r="N5" s="48"/>
+      <x:c r="O5" s="48"/>
+      <x:c r="P5" s="48"/>
+      <x:c r="Q5" s="48" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="R5" s="65"/>
-      <x:c r="S5" s="65"/>
-      <x:c r="T5" s="65"/>
-      <x:c r="U5" s="65"/>
-      <x:c r="V5" s="65"/>
-      <x:c r="W5" s="65"/>
-      <x:c r="X5" s="65"/>
-      <x:c r="Y5" s="65"/>
-      <x:c r="Z5" s="65"/>
-      <x:c r="AA5" s="65"/>
-      <x:c r="AB5" s="65"/>
-      <x:c r="AC5" s="65"/>
-      <x:c r="AD5" s="65"/>
-      <x:c r="AE5" s="65"/>
-      <x:c r="AF5" s="65"/>
-      <x:c r="AG5" s="65"/>
-      <x:c r="AH5" s="65"/>
-      <x:c r="AI5" s="65"/>
-      <x:c r="AJ5" s="65"/>
-      <x:c r="AK5" s="65"/>
-      <x:c r="AL5" s="65"/>
-      <x:c r="AM5" s="65"/>
-      <x:c r="AN5" s="65"/>
-      <x:c r="AO5" s="65"/>
-      <x:c r="AP5" s="65"/>
-      <x:c r="AQ5" s="65"/>
-      <x:c r="AR5" s="65"/>
-      <x:c r="AS5" s="65"/>
-      <x:c r="AT5" s="65"/>
-      <x:c r="AU5" s="65"/>
-      <x:c r="AV5" s="65"/>
-      <x:c r="AW5" s="65"/>
-      <x:c r="AX5" s="65"/>
-      <x:c r="AY5" s="65"/>
-      <x:c r="AZ5" s="65"/>
-      <x:c r="BA5" s="65"/>
-      <x:c r="BB5" s="65"/>
-      <x:c r="BC5" s="65"/>
-      <x:c r="BD5" s="65"/>
-      <x:c r="BE5" s="65"/>
-      <x:c r="BF5" s="65"/>
-      <x:c r="BG5" s="65"/>
-      <x:c r="BH5" s="65"/>
-      <x:c r="BI5" s="65"/>
-      <x:c r="BJ5" s="65"/>
-      <x:c r="BK5" s="65"/>
-      <x:c r="BL5" s="65"/>
-      <x:c r="BM5" s="65"/>
-      <x:c r="BN5" s="65"/>
-      <x:c r="BO5" s="65"/>
-      <x:c r="BP5" s="65"/>
-      <x:c r="BQ5" s="65"/>
-      <x:c r="BR5" s="65"/>
-      <x:c r="BS5" s="65"/>
-      <x:c r="BT5" s="65"/>
-      <x:c r="BU5" s="65"/>
-      <x:c r="BV5" s="65"/>
-      <x:c r="BW5" s="65"/>
-      <x:c r="BX5" s="65"/>
-      <x:c r="BY5" s="65"/>
-      <x:c r="BZ5" s="65"/>
-      <x:c r="CA5" s="65"/>
-      <x:c r="CB5" s="65"/>
-      <x:c r="CC5" s="65"/>
-      <x:c r="CD5" s="65"/>
-      <x:c r="CE5" s="65"/>
-      <x:c r="CF5" s="65"/>
-      <x:c r="CG5" s="65"/>
-      <x:c r="CH5" s="65"/>
-      <x:c r="CI5" s="65"/>
-      <x:c r="CJ5" s="65"/>
-      <x:c r="CK5" s="65"/>
-      <x:c r="CL5" s="66"/>
+      <x:c r="R5" s="48"/>
+      <x:c r="S5" s="48"/>
+      <x:c r="T5" s="48"/>
+      <x:c r="U5" s="48"/>
+      <x:c r="V5" s="48"/>
+      <x:c r="W5" s="48"/>
+      <x:c r="X5" s="48"/>
+      <x:c r="Y5" s="48"/>
+      <x:c r="Z5" s="48"/>
+      <x:c r="AA5" s="48"/>
+      <x:c r="AB5" s="48"/>
+      <x:c r="AC5" s="48"/>
+      <x:c r="AD5" s="48"/>
+      <x:c r="AE5" s="48"/>
+      <x:c r="AF5" s="48"/>
+      <x:c r="AG5" s="48"/>
+      <x:c r="AH5" s="48"/>
+      <x:c r="AI5" s="48"/>
+      <x:c r="AJ5" s="48"/>
+      <x:c r="AK5" s="48"/>
+      <x:c r="AL5" s="48"/>
+      <x:c r="AM5" s="48"/>
+      <x:c r="AN5" s="48"/>
+      <x:c r="AO5" s="48"/>
+      <x:c r="AP5" s="48"/>
+      <x:c r="AQ5" s="48"/>
+      <x:c r="AR5" s="48"/>
+      <x:c r="AS5" s="48"/>
+      <x:c r="AT5" s="48"/>
+      <x:c r="AU5" s="48"/>
+      <x:c r="AV5" s="48"/>
+      <x:c r="AW5" s="48"/>
+      <x:c r="AX5" s="48"/>
+      <x:c r="AY5" s="48"/>
+      <x:c r="AZ5" s="48"/>
+      <x:c r="BA5" s="48"/>
+      <x:c r="BB5" s="48"/>
+      <x:c r="BC5" s="48"/>
+      <x:c r="BD5" s="48"/>
+      <x:c r="BE5" s="48"/>
+      <x:c r="BF5" s="48"/>
+      <x:c r="BG5" s="48"/>
+      <x:c r="BH5" s="48"/>
+      <x:c r="BI5" s="48"/>
+      <x:c r="BJ5" s="48"/>
+      <x:c r="BK5" s="48"/>
+      <x:c r="BL5" s="48"/>
+      <x:c r="BM5" s="48"/>
+      <x:c r="BN5" s="48"/>
+      <x:c r="BO5" s="48"/>
+      <x:c r="BP5" s="48"/>
+      <x:c r="BQ5" s="48"/>
+      <x:c r="BR5" s="48"/>
+      <x:c r="BS5" s="48"/>
+      <x:c r="BT5" s="48"/>
+      <x:c r="BU5" s="48"/>
+      <x:c r="BV5" s="48"/>
+      <x:c r="BW5" s="48"/>
+      <x:c r="BX5" s="48"/>
+      <x:c r="BY5" s="48"/>
+      <x:c r="BZ5" s="48"/>
+      <x:c r="CA5" s="48"/>
+      <x:c r="CB5" s="48"/>
+      <x:c r="CC5" s="48"/>
+      <x:c r="CD5" s="48"/>
+      <x:c r="CE5" s="48"/>
+      <x:c r="CF5" s="48"/>
+      <x:c r="CG5" s="48"/>
+      <x:c r="CH5" s="48"/>
+      <x:c r="CI5" s="48"/>
+      <x:c r="CJ5" s="48"/>
+      <x:c r="CK5" s="48"/>
+      <x:c r="CL5" s="49"/>
     </x:row>
     <x:row r="6" ht="13.5" customHeight="1">
-      <x:c r="A6" s="63" t="str">
-        <x:v>＜UNION ALL＞</x:v>
-      </x:c>
-      <x:c r="B6" s="63"/>
-      <x:c r="C6" s="63"/>
-      <x:c r="D6" s="63"/>
-      <x:c r="E6" s="63"/>
-      <x:c r="F6" s="63"/>
-      <x:c r="G6" s="63"/>
-      <x:c r="H6" s="63"/>
-      <x:c r="I6" s="63"/>
-      <x:c r="J6" s="63"/>
-      <x:c r="K6" s="63"/>
-      <x:c r="L6" s="63"/>
-      <x:c r="M6" s="63"/>
-      <x:c r="N6" s="63"/>
-      <x:c r="O6" s="63"/>
-      <x:c r="P6" s="63"/>
-      <x:c r="Q6" s="63"/>
-      <x:c r="R6" s="63"/>
-      <x:c r="S6" s="63"/>
-      <x:c r="T6" s="63"/>
-      <x:c r="U6" s="63"/>
-      <x:c r="V6" s="63"/>
-      <x:c r="W6" s="63"/>
-      <x:c r="X6" s="63"/>
-      <x:c r="Y6" s="63"/>
-      <x:c r="Z6" s="63"/>
-      <x:c r="AA6" s="63"/>
-      <x:c r="AB6" s="63"/>
-      <x:c r="AC6" s="63"/>
-      <x:c r="AD6" s="63"/>
-      <x:c r="AE6" s="63"/>
-      <x:c r="AF6" s="63"/>
-      <x:c r="AG6" s="63"/>
-      <x:c r="AH6" s="63"/>
-      <x:c r="AI6" s="63"/>
-      <x:c r="AJ6" s="63"/>
-      <x:c r="AK6" s="63"/>
-      <x:c r="AL6" s="63"/>
-      <x:c r="AM6" s="63"/>
-      <x:c r="AN6" s="63"/>
-      <x:c r="AO6" s="63"/>
-      <x:c r="AP6" s="63"/>
-      <x:c r="AQ6" s="63"/>
-      <x:c r="AR6" s="63"/>
-      <x:c r="AS6" s="63"/>
-      <x:c r="AT6" s="63"/>
-      <x:c r="AU6" s="63"/>
-      <x:c r="AV6" s="63"/>
-      <x:c r="AW6" s="63"/>
-      <x:c r="AX6" s="63"/>
-      <x:c r="AY6" s="63"/>
-      <x:c r="AZ6" s="63"/>
-      <x:c r="BA6" s="63"/>
-      <x:c r="BB6" s="63"/>
-      <x:c r="BC6" s="63"/>
-      <x:c r="BD6" s="63"/>
-      <x:c r="BE6" s="63"/>
-      <x:c r="BF6" s="63"/>
-      <x:c r="BG6" s="63"/>
-      <x:c r="BH6" s="63"/>
-      <x:c r="BI6" s="63"/>
-      <x:c r="BJ6" s="63"/>
-      <x:c r="BK6" s="63"/>
-      <x:c r="BL6" s="63"/>
-      <x:c r="BM6" s="63"/>
-      <x:c r="BN6" s="63"/>
-      <x:c r="BO6" s="63"/>
-      <x:c r="BP6" s="63"/>
-      <x:c r="BQ6" s="63"/>
-      <x:c r="BR6" s="63"/>
-      <x:c r="BS6" s="63"/>
-      <x:c r="BT6" s="63"/>
-      <x:c r="BU6" s="63"/>
-      <x:c r="BV6" s="63"/>
-      <x:c r="BW6" s="63"/>
-      <x:c r="BX6" s="63"/>
-      <x:c r="BY6" s="63"/>
-      <x:c r="BZ6" s="63"/>
-      <x:c r="CA6" s="63"/>
-      <x:c r="CB6" s="63"/>
-      <x:c r="CC6" s="63"/>
-      <x:c r="CD6" s="63"/>
-      <x:c r="CE6" s="63"/>
-      <x:c r="CF6" s="63"/>
-      <x:c r="CG6" s="63"/>
-      <x:c r="CH6" s="63"/>
-      <x:c r="CI6" s="63"/>
-      <x:c r="CJ6" s="63"/>
-      <x:c r="CK6" s="63"/>
-      <x:c r="CL6" s="63"/>
+      <x:c r="A6" s="46" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="B6" s="46"/>
+      <x:c r="C6" s="46"/>
+      <x:c r="D6" s="46"/>
+      <x:c r="E6" s="46"/>
+      <x:c r="F6" s="46"/>
+      <x:c r="G6" s="46"/>
+      <x:c r="H6" s="46"/>
+      <x:c r="I6" s="46"/>
+      <x:c r="J6" s="46"/>
+      <x:c r="K6" s="46"/>
+      <x:c r="L6" s="46"/>
+      <x:c r="M6" s="46"/>
+      <x:c r="N6" s="46"/>
+      <x:c r="O6" s="46"/>
+      <x:c r="P6" s="46"/>
+      <x:c r="Q6" s="46"/>
+      <x:c r="R6" s="46"/>
+      <x:c r="S6" s="46"/>
+      <x:c r="T6" s="46"/>
+      <x:c r="U6" s="46"/>
+      <x:c r="V6" s="46"/>
+      <x:c r="W6" s="46"/>
+      <x:c r="X6" s="46"/>
+      <x:c r="Y6" s="46"/>
+      <x:c r="Z6" s="46"/>
+      <x:c r="AA6" s="46"/>
+      <x:c r="AB6" s="46"/>
+      <x:c r="AC6" s="46"/>
+      <x:c r="AD6" s="46"/>
+      <x:c r="AE6" s="46"/>
+      <x:c r="AF6" s="46"/>
+      <x:c r="AG6" s="46"/>
+      <x:c r="AH6" s="46"/>
+      <x:c r="AI6" s="46"/>
+      <x:c r="AJ6" s="46"/>
+      <x:c r="AK6" s="46"/>
+      <x:c r="AL6" s="46"/>
+      <x:c r="AM6" s="46"/>
+      <x:c r="AN6" s="46"/>
+      <x:c r="AO6" s="46"/>
+      <x:c r="AP6" s="46"/>
+      <x:c r="AQ6" s="46"/>
+      <x:c r="AR6" s="46"/>
+      <x:c r="AS6" s="46"/>
+      <x:c r="AT6" s="46"/>
+      <x:c r="AU6" s="46"/>
+      <x:c r="AV6" s="46"/>
+      <x:c r="AW6" s="46"/>
+      <x:c r="AX6" s="46"/>
+      <x:c r="AY6" s="46"/>
+      <x:c r="AZ6" s="46"/>
+      <x:c r="BA6" s="46"/>
+      <x:c r="BB6" s="46"/>
+      <x:c r="BC6" s="46"/>
+      <x:c r="BD6" s="46"/>
+      <x:c r="BE6" s="46"/>
+      <x:c r="BF6" s="46"/>
+      <x:c r="BG6" s="46"/>
+      <x:c r="BH6" s="46"/>
+      <x:c r="BI6" s="46"/>
+      <x:c r="BJ6" s="46"/>
+      <x:c r="BK6" s="46"/>
+      <x:c r="BL6" s="46"/>
+      <x:c r="BM6" s="46"/>
+      <x:c r="BN6" s="46"/>
+      <x:c r="BO6" s="46"/>
+      <x:c r="BP6" s="46"/>
+      <x:c r="BQ6" s="46"/>
+      <x:c r="BR6" s="46"/>
+      <x:c r="BS6" s="46"/>
+      <x:c r="BT6" s="46"/>
+      <x:c r="BU6" s="46"/>
+      <x:c r="BV6" s="46"/>
+      <x:c r="BW6" s="46"/>
+      <x:c r="BX6" s="46"/>
+      <x:c r="BY6" s="46"/>
+      <x:c r="BZ6" s="46"/>
+      <x:c r="CA6" s="46"/>
+      <x:c r="CB6" s="46"/>
+      <x:c r="CC6" s="46"/>
+      <x:c r="CD6" s="46"/>
+      <x:c r="CE6" s="46"/>
+      <x:c r="CF6" s="46"/>
+      <x:c r="CG6" s="46"/>
+      <x:c r="CH6" s="46"/>
+      <x:c r="CI6" s="46"/>
+      <x:c r="CJ6" s="46"/>
+      <x:c r="CK6" s="46"/>
+      <x:c r="CL6" s="46"/>
     </x:row>
     <x:row r="7" ht="13.5" customHeight="1">
-      <x:c r="A7" s="71" t="s">
+      <x:c r="A7" s="54" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" s="72"/>
-      <x:c r="C7" s="72"/>
-      <x:c r="D7" s="72"/>
-      <x:c r="E7" s="72"/>
-      <x:c r="F7" s="72"/>
-      <x:c r="G7" s="77" t="s">
+      <x:c r="B7" s="55"/>
+      <x:c r="C7" s="55"/>
+      <x:c r="D7" s="55"/>
+      <x:c r="E7" s="55"/>
+      <x:c r="F7" s="55"/>
+      <x:c r="G7" s="57" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H7" s="63"/>
-      <x:c r="I7" s="63"/>
-      <x:c r="J7" s="63"/>
-      <x:c r="K7" s="63"/>
-      <x:c r="L7" s="63"/>
-      <x:c r="M7" s="63"/>
-      <x:c r="N7" s="63"/>
-      <x:c r="O7" s="63" t="s">
+      <x:c r="H7" s="46"/>
+      <x:c r="I7" s="46"/>
+      <x:c r="J7" s="46"/>
+      <x:c r="K7" s="46"/>
+      <x:c r="L7" s="46"/>
+      <x:c r="M7" s="46"/>
+      <x:c r="N7" s="46"/>
+      <x:c r="O7" s="46" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P7" s="63"/>
-      <x:c r="Q7" s="63" t="s">
+      <x:c r="P7" s="46"/>
+      <x:c r="Q7" s="46" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="R7" s="63"/>
-      <x:c r="S7" s="63"/>
-      <x:c r="T7" s="63"/>
-      <x:c r="U7" s="63"/>
-      <x:c r="V7" s="63"/>
-      <x:c r="W7" s="63"/>
-      <x:c r="X7" s="63"/>
-      <x:c r="Y7" s="63"/>
-      <x:c r="Z7" s="63"/>
-      <x:c r="AA7" s="63"/>
-      <x:c r="AB7" s="63"/>
-      <x:c r="AC7" s="63"/>
-      <x:c r="AD7" s="63"/>
-      <x:c r="AE7" s="63"/>
-      <x:c r="AF7" s="63"/>
-      <x:c r="AG7" s="63"/>
-      <x:c r="AH7" s="63"/>
-      <x:c r="AI7" s="63"/>
-      <x:c r="AJ7" s="63"/>
-      <x:c r="AK7" s="63"/>
-      <x:c r="AL7" s="63"/>
-      <x:c r="AM7" s="63"/>
-      <x:c r="AN7" s="63"/>
-      <x:c r="AO7" s="63"/>
-      <x:c r="AP7" s="63"/>
-      <x:c r="AQ7" s="63"/>
-      <x:c r="AR7" s="63"/>
-      <x:c r="AS7" s="63"/>
-      <x:c r="AT7" s="63"/>
-      <x:c r="AU7" s="63"/>
-      <x:c r="AV7" s="63"/>
-      <x:c r="AW7" s="63"/>
-      <x:c r="AX7" s="63"/>
-      <x:c r="AY7" s="63"/>
-      <x:c r="AZ7" s="63"/>
-      <x:c r="BA7" s="63"/>
-      <x:c r="BB7" s="63"/>
-      <x:c r="BC7" s="63"/>
-      <x:c r="BD7" s="63"/>
-      <x:c r="BE7" s="63"/>
-      <x:c r="BF7" s="63"/>
-      <x:c r="BG7" s="63"/>
-      <x:c r="BH7" s="63"/>
-      <x:c r="BI7" s="63"/>
-      <x:c r="BJ7" s="63"/>
-      <x:c r="BK7" s="63"/>
-      <x:c r="BL7" s="63"/>
-      <x:c r="BM7" s="63"/>
-      <x:c r="BN7" s="63"/>
-      <x:c r="BO7" s="63"/>
-      <x:c r="BP7" s="63"/>
-      <x:c r="BQ7" s="63"/>
-      <x:c r="BR7" s="63"/>
-      <x:c r="BS7" s="63"/>
-      <x:c r="BT7" s="63"/>
-      <x:c r="BU7" s="63"/>
-      <x:c r="BV7" s="63"/>
-      <x:c r="BW7" s="63"/>
-      <x:c r="BX7" s="63"/>
-      <x:c r="BY7" s="63"/>
-      <x:c r="BZ7" s="63"/>
-      <x:c r="CA7" s="63"/>
-      <x:c r="CB7" s="63"/>
-      <x:c r="CC7" s="63"/>
-      <x:c r="CD7" s="63"/>
-      <x:c r="CE7" s="63"/>
-      <x:c r="CF7" s="63"/>
-      <x:c r="CG7" s="63"/>
-      <x:c r="CH7" s="63"/>
-      <x:c r="CI7" s="63"/>
-      <x:c r="CJ7" s="63"/>
-      <x:c r="CK7" s="63"/>
-      <x:c r="CL7" s="78"/>
+      <x:c r="R7" s="46"/>
+      <x:c r="S7" s="46"/>
+      <x:c r="T7" s="46"/>
+      <x:c r="U7" s="46"/>
+      <x:c r="V7" s="46"/>
+      <x:c r="W7" s="46"/>
+      <x:c r="X7" s="46"/>
+      <x:c r="Y7" s="46"/>
+      <x:c r="Z7" s="46"/>
+      <x:c r="AA7" s="46"/>
+      <x:c r="AB7" s="46"/>
+      <x:c r="AC7" s="46"/>
+      <x:c r="AD7" s="46"/>
+      <x:c r="AE7" s="46"/>
+      <x:c r="AF7" s="46"/>
+      <x:c r="AG7" s="46"/>
+      <x:c r="AH7" s="46"/>
+      <x:c r="AI7" s="46"/>
+      <x:c r="AJ7" s="46"/>
+      <x:c r="AK7" s="46"/>
+      <x:c r="AL7" s="46"/>
+      <x:c r="AM7" s="46"/>
+      <x:c r="AN7" s="46"/>
+      <x:c r="AO7" s="46"/>
+      <x:c r="AP7" s="46"/>
+      <x:c r="AQ7" s="46"/>
+      <x:c r="AR7" s="46"/>
+      <x:c r="AS7" s="46"/>
+      <x:c r="AT7" s="46"/>
+      <x:c r="AU7" s="46"/>
+      <x:c r="AV7" s="46"/>
+      <x:c r="AW7" s="46"/>
+      <x:c r="AX7" s="46"/>
+      <x:c r="AY7" s="46"/>
+      <x:c r="AZ7" s="46"/>
+      <x:c r="BA7" s="46"/>
+      <x:c r="BB7" s="46"/>
+      <x:c r="BC7" s="46"/>
+      <x:c r="BD7" s="46"/>
+      <x:c r="BE7" s="46"/>
+      <x:c r="BF7" s="46"/>
+      <x:c r="BG7" s="46"/>
+      <x:c r="BH7" s="46"/>
+      <x:c r="BI7" s="46"/>
+      <x:c r="BJ7" s="46"/>
+      <x:c r="BK7" s="46"/>
+      <x:c r="BL7" s="46"/>
+      <x:c r="BM7" s="46"/>
+      <x:c r="BN7" s="46"/>
+      <x:c r="BO7" s="46"/>
+      <x:c r="BP7" s="46"/>
+      <x:c r="BQ7" s="46"/>
+      <x:c r="BR7" s="46"/>
+      <x:c r="BS7" s="46"/>
+      <x:c r="BT7" s="46"/>
+      <x:c r="BU7" s="46"/>
+      <x:c r="BV7" s="46"/>
+      <x:c r="BW7" s="46"/>
+      <x:c r="BX7" s="46"/>
+      <x:c r="BY7" s="46"/>
+      <x:c r="BZ7" s="46"/>
+      <x:c r="CA7" s="46"/>
+      <x:c r="CB7" s="46"/>
+      <x:c r="CC7" s="46"/>
+      <x:c r="CD7" s="46"/>
+      <x:c r="CE7" s="46"/>
+      <x:c r="CF7" s="46"/>
+      <x:c r="CG7" s="46"/>
+      <x:c r="CH7" s="46"/>
+      <x:c r="CI7" s="46"/>
+      <x:c r="CJ7" s="46"/>
+      <x:c r="CK7" s="46"/>
+      <x:c r="CL7" s="58"/>
     </x:row>
     <x:row r="8" ht="13.5" customHeight="1">
-      <x:c r="A8" s="73"/>
-      <x:c r="B8" s="74"/>
-      <x:c r="C8" s="74"/>
-      <x:c r="D8" s="74"/>
-      <x:c r="E8" s="74"/>
-      <x:c r="F8" s="74"/>
-      <x:c r="G8" s="79" t="s">
+      <x:c r="A8" s="56"/>
+      <x:c r="B8" s="53"/>
+      <x:c r="C8" s="53"/>
+      <x:c r="D8" s="53"/>
+      <x:c r="E8" s="53"/>
+      <x:c r="F8" s="53"/>
+      <x:c r="G8" s="59" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H8" s="80"/>
-      <x:c r="I8" s="80"/>
-      <x:c r="J8" s="80"/>
-      <x:c r="K8" s="80"/>
-      <x:c r="L8" s="80"/>
-      <x:c r="M8" s="80"/>
-      <x:c r="N8" s="80"/>
-      <x:c r="O8" s="80" t="s">
+      <x:c r="H8" s="45"/>
+      <x:c r="I8" s="45"/>
+      <x:c r="J8" s="45"/>
+      <x:c r="K8" s="45"/>
+      <x:c r="L8" s="45"/>
+      <x:c r="M8" s="45"/>
+      <x:c r="N8" s="45"/>
+      <x:c r="O8" s="45" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P8" s="80"/>
-      <x:c r="Q8" s="80" t="str">
-        <x:v>TRIM(tb2.氏名)</x:v>
-      </x:c>
-      <x:c r="R8" s="80"/>
-      <x:c r="S8" s="80"/>
-      <x:c r="T8" s="80"/>
-      <x:c r="U8" s="80"/>
-      <x:c r="V8" s="80"/>
-      <x:c r="W8" s="80"/>
-      <x:c r="X8" s="80"/>
-      <x:c r="Y8" s="80"/>
-      <x:c r="Z8" s="80"/>
-      <x:c r="AA8" s="80"/>
-      <x:c r="AB8" s="80"/>
-      <x:c r="AC8" s="80"/>
-      <x:c r="AD8" s="80"/>
-      <x:c r="AE8" s="80"/>
-      <x:c r="AF8" s="80"/>
-      <x:c r="AG8" s="80"/>
-      <x:c r="AH8" s="80"/>
-      <x:c r="AI8" s="80"/>
-      <x:c r="AJ8" s="80"/>
-      <x:c r="AK8" s="80"/>
-      <x:c r="AL8" s="80"/>
-      <x:c r="AM8" s="80"/>
-      <x:c r="AN8" s="80"/>
-      <x:c r="AO8" s="80"/>
-      <x:c r="AP8" s="80"/>
-      <x:c r="AQ8" s="80"/>
-      <x:c r="AR8" s="80"/>
-      <x:c r="AS8" s="80"/>
-      <x:c r="AT8" s="80"/>
-      <x:c r="AU8" s="80"/>
-      <x:c r="AV8" s="80"/>
-      <x:c r="AW8" s="80"/>
-      <x:c r="AX8" s="80"/>
-      <x:c r="AY8" s="80"/>
-      <x:c r="AZ8" s="80"/>
-      <x:c r="BA8" s="80"/>
-      <x:c r="BB8" s="80"/>
-      <x:c r="BC8" s="80"/>
-      <x:c r="BD8" s="80"/>
-      <x:c r="BE8" s="80"/>
-      <x:c r="BF8" s="80"/>
-      <x:c r="BG8" s="80"/>
-      <x:c r="BH8" s="80"/>
-      <x:c r="BI8" s="80"/>
-      <x:c r="BJ8" s="80"/>
-      <x:c r="BK8" s="80"/>
-      <x:c r="BL8" s="80"/>
-      <x:c r="BM8" s="80"/>
-      <x:c r="BN8" s="80"/>
-      <x:c r="BO8" s="80"/>
-      <x:c r="BP8" s="80"/>
-      <x:c r="BQ8" s="80"/>
-      <x:c r="BR8" s="80"/>
-      <x:c r="BS8" s="80"/>
-      <x:c r="BT8" s="80"/>
-      <x:c r="BU8" s="80"/>
-      <x:c r="BV8" s="80"/>
-      <x:c r="BW8" s="80"/>
-      <x:c r="BX8" s="80"/>
-      <x:c r="BY8" s="80"/>
-      <x:c r="BZ8" s="80"/>
-      <x:c r="CA8" s="80"/>
-      <x:c r="CB8" s="80"/>
-      <x:c r="CC8" s="80"/>
-      <x:c r="CD8" s="80"/>
-      <x:c r="CE8" s="80"/>
-      <x:c r="CF8" s="80"/>
-      <x:c r="CG8" s="80"/>
-      <x:c r="CH8" s="80"/>
-      <x:c r="CI8" s="80"/>
-      <x:c r="CJ8" s="80"/>
-      <x:c r="CK8" s="80"/>
-      <x:c r="CL8" s="81"/>
+      <x:c r="P8" s="45"/>
+      <x:c r="Q8" s="45" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="R8" s="45"/>
+      <x:c r="S8" s="45"/>
+      <x:c r="T8" s="45"/>
+      <x:c r="U8" s="45"/>
+      <x:c r="V8" s="45"/>
+      <x:c r="W8" s="45"/>
+      <x:c r="X8" s="45"/>
+      <x:c r="Y8" s="45"/>
+      <x:c r="Z8" s="45"/>
+      <x:c r="AA8" s="45"/>
+      <x:c r="AB8" s="45"/>
+      <x:c r="AC8" s="45"/>
+      <x:c r="AD8" s="45"/>
+      <x:c r="AE8" s="45"/>
+      <x:c r="AF8" s="45"/>
+      <x:c r="AG8" s="45"/>
+      <x:c r="AH8" s="45"/>
+      <x:c r="AI8" s="45"/>
+      <x:c r="AJ8" s="45"/>
+      <x:c r="AK8" s="45"/>
+      <x:c r="AL8" s="45"/>
+      <x:c r="AM8" s="45"/>
+      <x:c r="AN8" s="45"/>
+      <x:c r="AO8" s="45"/>
+      <x:c r="AP8" s="45"/>
+      <x:c r="AQ8" s="45"/>
+      <x:c r="AR8" s="45"/>
+      <x:c r="AS8" s="45"/>
+      <x:c r="AT8" s="45"/>
+      <x:c r="AU8" s="45"/>
+      <x:c r="AV8" s="45"/>
+      <x:c r="AW8" s="45"/>
+      <x:c r="AX8" s="45"/>
+      <x:c r="AY8" s="45"/>
+      <x:c r="AZ8" s="45"/>
+      <x:c r="BA8" s="45"/>
+      <x:c r="BB8" s="45"/>
+      <x:c r="BC8" s="45"/>
+      <x:c r="BD8" s="45"/>
+      <x:c r="BE8" s="45"/>
+      <x:c r="BF8" s="45"/>
+      <x:c r="BG8" s="45"/>
+      <x:c r="BH8" s="45"/>
+      <x:c r="BI8" s="45"/>
+      <x:c r="BJ8" s="45"/>
+      <x:c r="BK8" s="45"/>
+      <x:c r="BL8" s="45"/>
+      <x:c r="BM8" s="45"/>
+      <x:c r="BN8" s="45"/>
+      <x:c r="BO8" s="45"/>
+      <x:c r="BP8" s="45"/>
+      <x:c r="BQ8" s="45"/>
+      <x:c r="BR8" s="45"/>
+      <x:c r="BS8" s="45"/>
+      <x:c r="BT8" s="45"/>
+      <x:c r="BU8" s="45"/>
+      <x:c r="BV8" s="45"/>
+      <x:c r="BW8" s="45"/>
+      <x:c r="BX8" s="45"/>
+      <x:c r="BY8" s="45"/>
+      <x:c r="BZ8" s="45"/>
+      <x:c r="CA8" s="45"/>
+      <x:c r="CB8" s="45"/>
+      <x:c r="CC8" s="45"/>
+      <x:c r="CD8" s="45"/>
+      <x:c r="CE8" s="45"/>
+      <x:c r="CF8" s="45"/>
+      <x:c r="CG8" s="45"/>
+      <x:c r="CH8" s="45"/>
+      <x:c r="CI8" s="45"/>
+      <x:c r="CJ8" s="45"/>
+      <x:c r="CK8" s="45"/>
+      <x:c r="CL8" s="60"/>
     </x:row>
     <x:row r="9" ht="13.5" customHeight="1">
-      <x:c r="A9" s="67" t="s">
+      <x:c r="A9" s="50" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="68"/>
-      <x:c r="C9" s="68"/>
-      <x:c r="D9" s="68"/>
-      <x:c r="E9" s="68"/>
-      <x:c r="F9" s="68"/>
-      <x:c r="G9" s="64"/>
-      <x:c r="H9" s="65"/>
-      <x:c r="I9" s="65"/>
-      <x:c r="J9" s="65"/>
-      <x:c r="K9" s="65"/>
-      <x:c r="L9" s="65"/>
-      <x:c r="M9" s="65"/>
-      <x:c r="N9" s="65"/>
-      <x:c r="O9" s="65"/>
-      <x:c r="P9" s="65"/>
-      <x:c r="Q9" s="65" t="str">
-        <x:v>tb2.状態 = 'INACTIVE'</x:v>
-      </x:c>
-      <x:c r="R9" s="65"/>
-      <x:c r="S9" s="65"/>
-      <x:c r="T9" s="65"/>
-      <x:c r="U9" s="65"/>
-      <x:c r="V9" s="65"/>
-      <x:c r="W9" s="65"/>
-      <x:c r="X9" s="65"/>
-      <x:c r="Y9" s="65"/>
-      <x:c r="Z9" s="65"/>
-      <x:c r="AA9" s="65"/>
-      <x:c r="AB9" s="65"/>
-      <x:c r="AC9" s="65"/>
-      <x:c r="AD9" s="65"/>
-      <x:c r="AE9" s="65"/>
-      <x:c r="AF9" s="65"/>
-      <x:c r="AG9" s="65"/>
-      <x:c r="AH9" s="65"/>
-      <x:c r="AI9" s="65"/>
-      <x:c r="AJ9" s="65"/>
-      <x:c r="AK9" s="65"/>
-      <x:c r="AL9" s="65"/>
-      <x:c r="AM9" s="65"/>
-      <x:c r="AN9" s="65"/>
-      <x:c r="AO9" s="65"/>
-      <x:c r="AP9" s="65"/>
-      <x:c r="AQ9" s="65"/>
-      <x:c r="AR9" s="65"/>
-      <x:c r="AS9" s="65"/>
-      <x:c r="AT9" s="65"/>
-      <x:c r="AU9" s="65"/>
-      <x:c r="AV9" s="65"/>
-      <x:c r="AW9" s="65"/>
-      <x:c r="AX9" s="65"/>
-      <x:c r="AY9" s="65"/>
-      <x:c r="AZ9" s="65"/>
-      <x:c r="BA9" s="65"/>
-      <x:c r="BB9" s="65"/>
-      <x:c r="BC9" s="65"/>
-      <x:c r="BD9" s="65"/>
-      <x:c r="BE9" s="65"/>
-      <x:c r="BF9" s="65"/>
-      <x:c r="BG9" s="65"/>
-      <x:c r="BH9" s="65"/>
-      <x:c r="BI9" s="65"/>
-      <x:c r="BJ9" s="65"/>
-      <x:c r="BK9" s="65"/>
-      <x:c r="BL9" s="65"/>
-      <x:c r="BM9" s="65"/>
-      <x:c r="BN9" s="65"/>
-      <x:c r="BO9" s="65"/>
-      <x:c r="BP9" s="65"/>
-      <x:c r="BQ9" s="65"/>
-      <x:c r="BR9" s="65"/>
-      <x:c r="BS9" s="65"/>
-      <x:c r="BT9" s="65"/>
-      <x:c r="BU9" s="65"/>
-      <x:c r="BV9" s="65"/>
-      <x:c r="BW9" s="65"/>
-      <x:c r="BX9" s="65"/>
-      <x:c r="BY9" s="65"/>
-      <x:c r="BZ9" s="65"/>
-      <x:c r="CA9" s="65"/>
-      <x:c r="CB9" s="65"/>
-      <x:c r="CC9" s="65"/>
-      <x:c r="CD9" s="65"/>
-      <x:c r="CE9" s="65"/>
-      <x:c r="CF9" s="65"/>
-      <x:c r="CG9" s="65"/>
-      <x:c r="CH9" s="65"/>
-      <x:c r="CI9" s="65"/>
-      <x:c r="CJ9" s="65"/>
-      <x:c r="CK9" s="65"/>
-      <x:c r="CL9" s="66"/>
+      <x:c r="B9" s="51"/>
+      <x:c r="C9" s="51"/>
+      <x:c r="D9" s="51"/>
+      <x:c r="E9" s="51"/>
+      <x:c r="F9" s="51"/>
+      <x:c r="G9" s="47"/>
+      <x:c r="H9" s="48"/>
+      <x:c r="I9" s="48"/>
+      <x:c r="J9" s="48"/>
+      <x:c r="K9" s="48"/>
+      <x:c r="L9" s="48"/>
+      <x:c r="M9" s="48"/>
+      <x:c r="N9" s="48"/>
+      <x:c r="O9" s="48"/>
+      <x:c r="P9" s="48"/>
+      <x:c r="Q9" s="48" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="R9" s="48"/>
+      <x:c r="S9" s="48"/>
+      <x:c r="T9" s="48"/>
+      <x:c r="U9" s="48"/>
+      <x:c r="V9" s="48"/>
+      <x:c r="W9" s="48"/>
+      <x:c r="X9" s="48"/>
+      <x:c r="Y9" s="48"/>
+      <x:c r="Z9" s="48"/>
+      <x:c r="AA9" s="48"/>
+      <x:c r="AB9" s="48"/>
+      <x:c r="AC9" s="48"/>
+      <x:c r="AD9" s="48"/>
+      <x:c r="AE9" s="48"/>
+      <x:c r="AF9" s="48"/>
+      <x:c r="AG9" s="48"/>
+      <x:c r="AH9" s="48"/>
+      <x:c r="AI9" s="48"/>
+      <x:c r="AJ9" s="48"/>
+      <x:c r="AK9" s="48"/>
+      <x:c r="AL9" s="48"/>
+      <x:c r="AM9" s="48"/>
+      <x:c r="AN9" s="48"/>
+      <x:c r="AO9" s="48"/>
+      <x:c r="AP9" s="48"/>
+      <x:c r="AQ9" s="48"/>
+      <x:c r="AR9" s="48"/>
+      <x:c r="AS9" s="48"/>
+      <x:c r="AT9" s="48"/>
+      <x:c r="AU9" s="48"/>
+      <x:c r="AV9" s="48"/>
+      <x:c r="AW9" s="48"/>
+      <x:c r="AX9" s="48"/>
+      <x:c r="AY9" s="48"/>
+      <x:c r="AZ9" s="48"/>
+      <x:c r="BA9" s="48"/>
+      <x:c r="BB9" s="48"/>
+      <x:c r="BC9" s="48"/>
+      <x:c r="BD9" s="48"/>
+      <x:c r="BE9" s="48"/>
+      <x:c r="BF9" s="48"/>
+      <x:c r="BG9" s="48"/>
+      <x:c r="BH9" s="48"/>
+      <x:c r="BI9" s="48"/>
+      <x:c r="BJ9" s="48"/>
+      <x:c r="BK9" s="48"/>
+      <x:c r="BL9" s="48"/>
+      <x:c r="BM9" s="48"/>
+      <x:c r="BN9" s="48"/>
+      <x:c r="BO9" s="48"/>
+      <x:c r="BP9" s="48"/>
+      <x:c r="BQ9" s="48"/>
+      <x:c r="BR9" s="48"/>
+      <x:c r="BS9" s="48"/>
+      <x:c r="BT9" s="48"/>
+      <x:c r="BU9" s="48"/>
+      <x:c r="BV9" s="48"/>
+      <x:c r="BW9" s="48"/>
+      <x:c r="BX9" s="48"/>
+      <x:c r="BY9" s="48"/>
+      <x:c r="BZ9" s="48"/>
+      <x:c r="CA9" s="48"/>
+      <x:c r="CB9" s="48"/>
+      <x:c r="CC9" s="48"/>
+      <x:c r="CD9" s="48"/>
+      <x:c r="CE9" s="48"/>
+      <x:c r="CF9" s="48"/>
+      <x:c r="CG9" s="48"/>
+      <x:c r="CH9" s="48"/>
+      <x:c r="CI9" s="48"/>
+      <x:c r="CJ9" s="48"/>
+      <x:c r="CK9" s="48"/>
+      <x:c r="CL9" s="49"/>
     </x:row>
     <x:row r="10" ht="13.5" customHeight="1">
-      <x:c r="A10" s="61"/>
-      <x:c r="B10" s="61"/>
-      <x:c r="C10" s="61"/>
-      <x:c r="D10" s="61"/>
-      <x:c r="E10" s="61"/>
-      <x:c r="F10" s="61"/>
-      <x:c r="G10" s="61"/>
-      <x:c r="H10" s="61"/>
-      <x:c r="I10" s="61"/>
-      <x:c r="J10" s="61"/>
-      <x:c r="K10" s="61"/>
-      <x:c r="L10" s="61"/>
-      <x:c r="M10" s="61"/>
-      <x:c r="N10" s="61"/>
-      <x:c r="O10" s="61"/>
-      <x:c r="P10" s="61"/>
-      <x:c r="Q10" s="61"/>
-      <x:c r="R10" s="61"/>
-      <x:c r="S10" s="61"/>
-      <x:c r="T10" s="61"/>
-      <x:c r="U10" s="61"/>
-      <x:c r="V10" s="61"/>
-      <x:c r="W10" s="61"/>
-      <x:c r="X10" s="61"/>
-      <x:c r="Y10" s="61"/>
-      <x:c r="Z10" s="61"/>
-      <x:c r="AA10" s="61"/>
-      <x:c r="AB10" s="61"/>
-      <x:c r="AC10" s="61"/>
-      <x:c r="AD10" s="61"/>
-      <x:c r="AE10" s="61"/>
-      <x:c r="AF10" s="61"/>
-      <x:c r="AG10" s="61"/>
-      <x:c r="AH10" s="61"/>
-      <x:c r="AI10" s="61"/>
-      <x:c r="AJ10" s="61"/>
-      <x:c r="AK10" s="61"/>
-      <x:c r="AL10" s="61"/>
-      <x:c r="AM10" s="61"/>
-      <x:c r="AN10" s="61"/>
-      <x:c r="AO10" s="61"/>
-      <x:c r="AP10" s="61"/>
-      <x:c r="AQ10" s="61"/>
-      <x:c r="AR10" s="61"/>
-      <x:c r="AS10" s="61"/>
-      <x:c r="AT10" s="61"/>
-      <x:c r="AU10" s="61"/>
-      <x:c r="AV10" s="61"/>
-      <x:c r="AW10" s="61"/>
-      <x:c r="AX10" s="61"/>
-      <x:c r="AY10" s="61"/>
-      <x:c r="AZ10" s="61"/>
-      <x:c r="BA10" s="61"/>
-      <x:c r="BB10" s="61"/>
-      <x:c r="BC10" s="61"/>
-      <x:c r="BD10" s="61"/>
-      <x:c r="BE10" s="61"/>
-      <x:c r="BF10" s="61"/>
-      <x:c r="BG10" s="61"/>
-      <x:c r="BH10" s="61"/>
-      <x:c r="BI10" s="61"/>
-      <x:c r="BJ10" s="61"/>
-      <x:c r="BK10" s="61"/>
-      <x:c r="BL10" s="61"/>
-      <x:c r="BM10" s="61"/>
-      <x:c r="BN10" s="61"/>
-      <x:c r="BO10" s="61"/>
-      <x:c r="BP10" s="61"/>
-      <x:c r="BQ10" s="61"/>
-      <x:c r="BR10" s="61"/>
-      <x:c r="BS10" s="61"/>
-      <x:c r="BT10" s="61"/>
-      <x:c r="BU10" s="61"/>
-      <x:c r="BV10" s="61"/>
-      <x:c r="BW10" s="61"/>
-      <x:c r="BX10" s="61"/>
-      <x:c r="BY10" s="61"/>
-      <x:c r="BZ10" s="61"/>
-      <x:c r="CA10" s="61"/>
-      <x:c r="CB10" s="61"/>
-      <x:c r="CC10" s="61"/>
-      <x:c r="CD10" s="61"/>
-      <x:c r="CE10" s="61"/>
-      <x:c r="CF10" s="61"/>
-      <x:c r="CG10" s="61"/>
-      <x:c r="CH10" s="61"/>
-      <x:c r="CI10" s="61"/>
-      <x:c r="CJ10" s="61"/>
-      <x:c r="CK10" s="61"/>
-      <x:c r="CL10" s="61"/>
+      <x:c r="A10" s="1"/>
+      <x:c r="B10" s="1"/>
+      <x:c r="C10" s="1"/>
+      <x:c r="D10" s="1"/>
+      <x:c r="E10" s="1"/>
+      <x:c r="F10" s="1"/>
+      <x:c r="G10" s="1"/>
+      <x:c r="H10" s="1"/>
+      <x:c r="I10" s="1"/>
+      <x:c r="J10" s="1"/>
+      <x:c r="K10" s="1"/>
+      <x:c r="L10" s="1"/>
+      <x:c r="M10" s="1"/>
+      <x:c r="N10" s="1"/>
+      <x:c r="O10" s="1"/>
+      <x:c r="P10" s="1"/>
+      <x:c r="Q10" s="1"/>
+      <x:c r="R10" s="1"/>
+      <x:c r="S10" s="1"/>
+      <x:c r="T10" s="1"/>
+      <x:c r="U10" s="1"/>
+      <x:c r="V10" s="1"/>
+      <x:c r="W10" s="1"/>
+      <x:c r="X10" s="1"/>
+      <x:c r="Y10" s="1"/>
+      <x:c r="Z10" s="1"/>
+      <x:c r="AA10" s="1"/>
+      <x:c r="AB10" s="1"/>
+      <x:c r="AC10" s="1"/>
+      <x:c r="AD10" s="1"/>
+      <x:c r="AE10" s="1"/>
+      <x:c r="AF10" s="1"/>
+      <x:c r="AG10" s="1"/>
+      <x:c r="AH10" s="1"/>
+      <x:c r="AI10" s="1"/>
+      <x:c r="AJ10" s="1"/>
+      <x:c r="AK10" s="1"/>
+      <x:c r="AL10" s="1"/>
+      <x:c r="AM10" s="1"/>
+      <x:c r="AN10" s="1"/>
+      <x:c r="AO10" s="1"/>
+      <x:c r="AP10" s="1"/>
+      <x:c r="AQ10" s="1"/>
+      <x:c r="AR10" s="1"/>
+      <x:c r="AS10" s="1"/>
+      <x:c r="AT10" s="1"/>
+      <x:c r="AU10" s="1"/>
+      <x:c r="AV10" s="1"/>
+      <x:c r="AW10" s="1"/>
+      <x:c r="AX10" s="1"/>
+      <x:c r="AY10" s="1"/>
+      <x:c r="AZ10" s="1"/>
+      <x:c r="BA10" s="1"/>
+      <x:c r="BB10" s="1"/>
+      <x:c r="BC10" s="1"/>
+      <x:c r="BD10" s="1"/>
+      <x:c r="BE10" s="1"/>
+      <x:c r="BF10" s="1"/>
+      <x:c r="BG10" s="1"/>
+      <x:c r="BH10" s="1"/>
+      <x:c r="BI10" s="1"/>
+      <x:c r="BJ10" s="1"/>
+      <x:c r="BK10" s="1"/>
+      <x:c r="BL10" s="1"/>
+      <x:c r="BM10" s="1"/>
+      <x:c r="BN10" s="1"/>
+      <x:c r="BO10" s="1"/>
+      <x:c r="BP10" s="1"/>
+      <x:c r="BQ10" s="1"/>
+      <x:c r="BR10" s="1"/>
+      <x:c r="BS10" s="1"/>
+      <x:c r="BT10" s="1"/>
+      <x:c r="BU10" s="1"/>
+      <x:c r="BV10" s="1"/>
+      <x:c r="BW10" s="1"/>
+      <x:c r="BX10" s="1"/>
+      <x:c r="BY10" s="1"/>
+      <x:c r="BZ10" s="1"/>
+      <x:c r="CA10" s="1"/>
+      <x:c r="CB10" s="1"/>
+      <x:c r="CC10" s="1"/>
+      <x:c r="CD10" s="1"/>
+      <x:c r="CE10" s="1"/>
+      <x:c r="CF10" s="1"/>
+      <x:c r="CG10" s="1"/>
+      <x:c r="CH10" s="1"/>
+      <x:c r="CI10" s="1"/>
+      <x:c r="CJ10" s="1"/>
+      <x:c r="CK10" s="1"/>
+      <x:c r="CL10" s="1"/>
     </x:row>
     <x:row r="11" ht="13.5" customHeight="1">
-      <x:c r="A11" s="61" t="str">
-        <x:v>＜データ移送表＞</x:v>
-      </x:c>
-      <x:c r="B11" s="61"/>
-      <x:c r="C11" s="61"/>
-      <x:c r="D11" s="61"/>
-      <x:c r="E11" s="61"/>
-      <x:c r="F11" s="61"/>
-      <x:c r="G11" s="61"/>
-      <x:c r="H11" s="61"/>
-      <x:c r="I11" s="61"/>
-      <x:c r="J11" s="61"/>
-      <x:c r="K11" s="61"/>
-      <x:c r="L11" s="61"/>
-      <x:c r="M11" s="61"/>
-      <x:c r="N11" s="61"/>
-      <x:c r="O11" s="61"/>
-      <x:c r="P11" s="61"/>
-      <x:c r="Q11" s="61"/>
-      <x:c r="R11" s="61"/>
-      <x:c r="S11" s="61"/>
-      <x:c r="T11" s="61"/>
-      <x:c r="U11" s="61"/>
-      <x:c r="V11" s="61"/>
-      <x:c r="W11" s="61"/>
-      <x:c r="X11" s="61"/>
-      <x:c r="Y11" s="61"/>
-      <x:c r="Z11" s="61"/>
-      <x:c r="AA11" s="61"/>
-      <x:c r="AB11" s="61"/>
-      <x:c r="AC11" s="61"/>
-      <x:c r="AD11" s="61"/>
-      <x:c r="AE11" s="61"/>
-      <x:c r="AF11" s="61"/>
-      <x:c r="AG11" s="61"/>
-      <x:c r="AH11" s="61"/>
-      <x:c r="AI11" s="61"/>
-      <x:c r="AJ11" s="61"/>
-      <x:c r="AK11" s="61"/>
-      <x:c r="AL11" s="61"/>
-      <x:c r="AM11" s="61"/>
-      <x:c r="AN11" s="61"/>
-      <x:c r="AO11" s="61"/>
-      <x:c r="AP11" s="61"/>
-      <x:c r="AQ11" s="61"/>
-      <x:c r="AR11" s="61"/>
-      <x:c r="AS11" s="61"/>
-      <x:c r="AT11" s="61"/>
-      <x:c r="AU11" s="61"/>
-      <x:c r="AV11" s="61"/>
-      <x:c r="AW11" s="61"/>
-      <x:c r="AX11" s="61"/>
-      <x:c r="AY11" s="61"/>
-      <x:c r="AZ11" s="61"/>
-      <x:c r="BA11" s="61"/>
-      <x:c r="BB11" s="61"/>
-      <x:c r="BC11" s="61"/>
-      <x:c r="BD11" s="61"/>
-      <x:c r="BE11" s="61"/>
-      <x:c r="BF11" s="61"/>
-      <x:c r="BG11" s="61"/>
-      <x:c r="BH11" s="61"/>
-      <x:c r="BI11" s="61"/>
-      <x:c r="BJ11" s="61"/>
-      <x:c r="BK11" s="61"/>
-      <x:c r="BL11" s="61"/>
-      <x:c r="BM11" s="61"/>
-      <x:c r="BN11" s="61"/>
-      <x:c r="BO11" s="61"/>
-      <x:c r="BP11" s="61"/>
-      <x:c r="BQ11" s="61"/>
-      <x:c r="BR11" s="61"/>
-      <x:c r="BS11" s="61"/>
-      <x:c r="BT11" s="61"/>
-      <x:c r="BU11" s="61"/>
-      <x:c r="BV11" s="61"/>
-      <x:c r="BW11" s="61"/>
-      <x:c r="BX11" s="61"/>
-      <x:c r="BY11" s="61"/>
-      <x:c r="BZ11" s="61"/>
-      <x:c r="CA11" s="61"/>
-      <x:c r="CB11" s="61"/>
-      <x:c r="CC11" s="61"/>
-      <x:c r="CD11" s="61"/>
-      <x:c r="CE11" s="61"/>
-      <x:c r="CF11" s="61"/>
-      <x:c r="CG11" s="61"/>
-      <x:c r="CH11" s="61"/>
-      <x:c r="CI11" s="61"/>
-      <x:c r="CJ11" s="61"/>
-      <x:c r="CK11" s="61"/>
-      <x:c r="CL11" s="61"/>
+      <x:c r="A11" s="1" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B11" s="1"/>
+      <x:c r="C11" s="1"/>
+      <x:c r="D11" s="1"/>
+      <x:c r="E11" s="1"/>
+      <x:c r="F11" s="1"/>
+      <x:c r="G11" s="1"/>
+      <x:c r="H11" s="1"/>
+      <x:c r="I11" s="1"/>
+      <x:c r="J11" s="1"/>
+      <x:c r="K11" s="1"/>
+      <x:c r="L11" s="1"/>
+      <x:c r="M11" s="1"/>
+      <x:c r="N11" s="1"/>
+      <x:c r="O11" s="1"/>
+      <x:c r="P11" s="1"/>
+      <x:c r="Q11" s="1"/>
+      <x:c r="R11" s="1"/>
+      <x:c r="S11" s="1"/>
+      <x:c r="T11" s="1"/>
+      <x:c r="U11" s="1"/>
+      <x:c r="V11" s="1"/>
+      <x:c r="W11" s="1"/>
+      <x:c r="X11" s="1"/>
+      <x:c r="Y11" s="1"/>
+      <x:c r="Z11" s="1"/>
+      <x:c r="AA11" s="1"/>
+      <x:c r="AB11" s="1"/>
+      <x:c r="AC11" s="1"/>
+      <x:c r="AD11" s="1"/>
+      <x:c r="AE11" s="1"/>
+      <x:c r="AF11" s="1"/>
+      <x:c r="AG11" s="1"/>
+      <x:c r="AH11" s="1"/>
+      <x:c r="AI11" s="1"/>
+      <x:c r="AJ11" s="1"/>
+      <x:c r="AK11" s="1"/>
+      <x:c r="AL11" s="1"/>
+      <x:c r="AM11" s="1"/>
+      <x:c r="AN11" s="1"/>
+      <x:c r="AO11" s="1"/>
+      <x:c r="AP11" s="1"/>
+      <x:c r="AQ11" s="1"/>
+      <x:c r="AR11" s="1"/>
+      <x:c r="AS11" s="1"/>
+      <x:c r="AT11" s="1"/>
+      <x:c r="AU11" s="1"/>
+      <x:c r="AV11" s="1"/>
+      <x:c r="AW11" s="1"/>
+      <x:c r="AX11" s="1"/>
+      <x:c r="AY11" s="1"/>
+      <x:c r="AZ11" s="1"/>
+      <x:c r="BA11" s="1"/>
+      <x:c r="BB11" s="1"/>
+      <x:c r="BC11" s="1"/>
+      <x:c r="BD11" s="1"/>
+      <x:c r="BE11" s="1"/>
+      <x:c r="BF11" s="1"/>
+      <x:c r="BG11" s="1"/>
+      <x:c r="BH11" s="1"/>
+      <x:c r="BI11" s="1"/>
+      <x:c r="BJ11" s="1"/>
+      <x:c r="BK11" s="1"/>
+      <x:c r="BL11" s="1"/>
+      <x:c r="BM11" s="1"/>
+      <x:c r="BN11" s="1"/>
+      <x:c r="BO11" s="1"/>
+      <x:c r="BP11" s="1"/>
+      <x:c r="BQ11" s="1"/>
+      <x:c r="BR11" s="1"/>
+      <x:c r="BS11" s="1"/>
+      <x:c r="BT11" s="1"/>
+      <x:c r="BU11" s="1"/>
+      <x:c r="BV11" s="1"/>
+      <x:c r="BW11" s="1"/>
+      <x:c r="BX11" s="1"/>
+      <x:c r="BY11" s="1"/>
+      <x:c r="BZ11" s="1"/>
+      <x:c r="CA11" s="1"/>
+      <x:c r="CB11" s="1"/>
+      <x:c r="CC11" s="1"/>
+      <x:c r="CD11" s="1"/>
+      <x:c r="CE11" s="1"/>
+      <x:c r="CF11" s="1"/>
+      <x:c r="CG11" s="1"/>
+      <x:c r="CH11" s="1"/>
+      <x:c r="CI11" s="1"/>
+      <x:c r="CJ11" s="1"/>
+      <x:c r="CK11" s="1"/>
+      <x:c r="CL11" s="1"/>
     </x:row>
     <x:row r="12" ht="13.5" customHeight="1">
-      <x:c r="A12" s="61" t="str">
-        <x:v>参照テーブル: ユーザーアーカイブ</x:v>
-      </x:c>
-      <x:c r="B12" s="61"/>
-      <x:c r="C12" s="61"/>
-      <x:c r="D12" s="61"/>
-      <x:c r="E12" s="61"/>
-      <x:c r="F12" s="61"/>
-      <x:c r="G12" s="61"/>
-      <x:c r="H12" s="61"/>
-      <x:c r="I12" s="61"/>
-      <x:c r="J12" s="61"/>
-      <x:c r="K12" s="61"/>
-      <x:c r="L12" s="61"/>
-      <x:c r="M12" s="61"/>
-      <x:c r="N12" s="61"/>
-      <x:c r="O12" s="61"/>
-      <x:c r="P12" s="61"/>
-      <x:c r="Q12" s="61"/>
-      <x:c r="R12" s="61"/>
-      <x:c r="S12" s="61"/>
-      <x:c r="T12" s="61"/>
-      <x:c r="U12" s="61"/>
-      <x:c r="V12" s="61"/>
-      <x:c r="W12" s="61"/>
-      <x:c r="X12" s="61"/>
-      <x:c r="Y12" s="61"/>
-      <x:c r="Z12" s="61"/>
-      <x:c r="AA12" s="61"/>
-      <x:c r="AB12" s="61"/>
-      <x:c r="AC12" s="61"/>
-      <x:c r="AD12" s="61"/>
-      <x:c r="AE12" s="61"/>
-      <x:c r="AF12" s="61"/>
-      <x:c r="AG12" s="61"/>
-      <x:c r="AH12" s="61"/>
-      <x:c r="AI12" s="61"/>
-      <x:c r="AJ12" s="61"/>
-      <x:c r="AK12" s="61"/>
-      <x:c r="AL12" s="61"/>
-      <x:c r="AM12" s="61"/>
-      <x:c r="AN12" s="61"/>
-      <x:c r="AO12" s="61"/>
-      <x:c r="AP12" s="61"/>
-      <x:c r="AQ12" s="61"/>
-      <x:c r="AR12" s="61"/>
-      <x:c r="AS12" s="61"/>
-      <x:c r="AT12" s="61"/>
-      <x:c r="AU12" s="61"/>
-      <x:c r="AV12" s="61"/>
-      <x:c r="AW12" s="61"/>
-      <x:c r="AX12" s="61"/>
-      <x:c r="AY12" s="61"/>
-      <x:c r="AZ12" s="61"/>
-      <x:c r="BA12" s="61"/>
-      <x:c r="BB12" s="61"/>
-      <x:c r="BC12" s="61"/>
-      <x:c r="BD12" s="61"/>
-      <x:c r="BE12" s="61"/>
-      <x:c r="BF12" s="61"/>
-      <x:c r="BG12" s="61"/>
-      <x:c r="BH12" s="61"/>
-      <x:c r="BI12" s="61"/>
-      <x:c r="BJ12" s="61"/>
-      <x:c r="BK12" s="61"/>
-      <x:c r="BL12" s="61"/>
-      <x:c r="BM12" s="61"/>
-      <x:c r="BN12" s="61"/>
-      <x:c r="BO12" s="61"/>
-      <x:c r="BP12" s="61"/>
-      <x:c r="BQ12" s="61"/>
-      <x:c r="BR12" s="61"/>
-      <x:c r="BS12" s="61"/>
-      <x:c r="BT12" s="61"/>
-      <x:c r="BU12" s="61"/>
-      <x:c r="BV12" s="61"/>
-      <x:c r="BW12" s="61"/>
-      <x:c r="BX12" s="61"/>
-      <x:c r="BY12" s="61"/>
-      <x:c r="BZ12" s="61"/>
-      <x:c r="CA12" s="61"/>
-      <x:c r="CB12" s="61"/>
-      <x:c r="CC12" s="61"/>
-      <x:c r="CD12" s="61"/>
-      <x:c r="CE12" s="61"/>
-      <x:c r="CF12" s="61"/>
-      <x:c r="CG12" s="61"/>
-      <x:c r="CH12" s="61"/>
-      <x:c r="CI12" s="61"/>
-      <x:c r="CJ12" s="61"/>
-      <x:c r="CK12" s="61"/>
-      <x:c r="CL12" s="61"/>
+      <x:c r="A12" s="1" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B12" s="1"/>
+      <x:c r="C12" s="1"/>
+      <x:c r="D12" s="1"/>
+      <x:c r="E12" s="1"/>
+      <x:c r="F12" s="1"/>
+      <x:c r="G12" s="1"/>
+      <x:c r="H12" s="1"/>
+      <x:c r="I12" s="1"/>
+      <x:c r="J12" s="1"/>
+      <x:c r="K12" s="1"/>
+      <x:c r="L12" s="1"/>
+      <x:c r="M12" s="1"/>
+      <x:c r="N12" s="1"/>
+      <x:c r="O12" s="1"/>
+      <x:c r="P12" s="1"/>
+      <x:c r="Q12" s="1"/>
+      <x:c r="R12" s="1"/>
+      <x:c r="S12" s="1"/>
+      <x:c r="T12" s="1"/>
+      <x:c r="U12" s="1"/>
+      <x:c r="V12" s="1"/>
+      <x:c r="W12" s="1"/>
+      <x:c r="X12" s="1"/>
+      <x:c r="Y12" s="1"/>
+      <x:c r="Z12" s="1"/>
+      <x:c r="AA12" s="1"/>
+      <x:c r="AB12" s="1"/>
+      <x:c r="AC12" s="1"/>
+      <x:c r="AD12" s="1"/>
+      <x:c r="AE12" s="1"/>
+      <x:c r="AF12" s="1"/>
+      <x:c r="AG12" s="1"/>
+      <x:c r="AH12" s="1"/>
+      <x:c r="AI12" s="1"/>
+      <x:c r="AJ12" s="1"/>
+      <x:c r="AK12" s="1"/>
+      <x:c r="AL12" s="1"/>
+      <x:c r="AM12" s="1"/>
+      <x:c r="AN12" s="1"/>
+      <x:c r="AO12" s="1"/>
+      <x:c r="AP12" s="1"/>
+      <x:c r="AQ12" s="1"/>
+      <x:c r="AR12" s="1"/>
+      <x:c r="AS12" s="1"/>
+      <x:c r="AT12" s="1"/>
+      <x:c r="AU12" s="1"/>
+      <x:c r="AV12" s="1"/>
+      <x:c r="AW12" s="1"/>
+      <x:c r="AX12" s="1"/>
+      <x:c r="AY12" s="1"/>
+      <x:c r="AZ12" s="1"/>
+      <x:c r="BA12" s="1"/>
+      <x:c r="BB12" s="1"/>
+      <x:c r="BC12" s="1"/>
+      <x:c r="BD12" s="1"/>
+      <x:c r="BE12" s="1"/>
+      <x:c r="BF12" s="1"/>
+      <x:c r="BG12" s="1"/>
+      <x:c r="BH12" s="1"/>
+      <x:c r="BI12" s="1"/>
+      <x:c r="BJ12" s="1"/>
+      <x:c r="BK12" s="1"/>
+      <x:c r="BL12" s="1"/>
+      <x:c r="BM12" s="1"/>
+      <x:c r="BN12" s="1"/>
+      <x:c r="BO12" s="1"/>
+      <x:c r="BP12" s="1"/>
+      <x:c r="BQ12" s="1"/>
+      <x:c r="BR12" s="1"/>
+      <x:c r="BS12" s="1"/>
+      <x:c r="BT12" s="1"/>
+      <x:c r="BU12" s="1"/>
+      <x:c r="BV12" s="1"/>
+      <x:c r="BW12" s="1"/>
+      <x:c r="BX12" s="1"/>
+      <x:c r="BY12" s="1"/>
+      <x:c r="BZ12" s="1"/>
+      <x:c r="CA12" s="1"/>
+      <x:c r="CB12" s="1"/>
+      <x:c r="CC12" s="1"/>
+      <x:c r="CD12" s="1"/>
+      <x:c r="CE12" s="1"/>
+      <x:c r="CF12" s="1"/>
+      <x:c r="CG12" s="1"/>
+      <x:c r="CH12" s="1"/>
+      <x:c r="CI12" s="1"/>
+      <x:c r="CJ12" s="1"/>
+      <x:c r="CK12" s="1"/>
+      <x:c r="CL12" s="1"/>
     </x:row>
     <x:row r="13" ht="13.5" customHeight="1">
-      <x:c r="A13" s="63" t="str">
-        <x:v>＜移送パターン1＞</x:v>
-      </x:c>
-      <x:c r="B13" s="63"/>
-      <x:c r="C13" s="63"/>
-      <x:c r="D13" s="63"/>
-      <x:c r="E13" s="63"/>
-      <x:c r="F13" s="63"/>
-      <x:c r="G13" s="63"/>
-      <x:c r="H13" s="63"/>
-      <x:c r="I13" s="63"/>
-      <x:c r="J13" s="63"/>
-      <x:c r="K13" s="63"/>
-      <x:c r="L13" s="63"/>
-      <x:c r="M13" s="63"/>
-      <x:c r="N13" s="63"/>
-      <x:c r="O13" s="63"/>
-      <x:c r="P13" s="63"/>
-      <x:c r="Q13" s="63"/>
-      <x:c r="R13" s="63"/>
-      <x:c r="S13" s="63"/>
-      <x:c r="T13" s="63"/>
-      <x:c r="U13" s="63"/>
-      <x:c r="V13" s="63"/>
-      <x:c r="W13" s="63"/>
-      <x:c r="X13" s="63"/>
-      <x:c r="Y13" s="63"/>
-      <x:c r="Z13" s="63"/>
-      <x:c r="AA13" s="63"/>
-      <x:c r="AB13" s="63"/>
-      <x:c r="AC13" s="63"/>
-      <x:c r="AD13" s="63"/>
-      <x:c r="AE13" s="63"/>
-      <x:c r="AF13" s="63"/>
-      <x:c r="AG13" s="63"/>
-      <x:c r="AH13" s="63"/>
-      <x:c r="AI13" s="63"/>
-      <x:c r="AJ13" s="63"/>
-      <x:c r="AK13" s="63"/>
-      <x:c r="AL13" s="63"/>
-      <x:c r="AM13" s="63"/>
-      <x:c r="AN13" s="63"/>
-      <x:c r="AO13" s="63"/>
-      <x:c r="AP13" s="63"/>
-      <x:c r="AQ13" s="63"/>
-      <x:c r="AR13" s="63"/>
-      <x:c r="AS13" s="63"/>
-      <x:c r="AT13" s="63"/>
-      <x:c r="AU13" s="63"/>
-      <x:c r="AV13" s="63"/>
-      <x:c r="AW13" s="63"/>
-      <x:c r="AX13" s="63"/>
-      <x:c r="AY13" s="63"/>
-      <x:c r="AZ13" s="63"/>
-      <x:c r="BA13" s="63"/>
-      <x:c r="BB13" s="63"/>
-      <x:c r="BC13" s="63"/>
-      <x:c r="BD13" s="63"/>
-      <x:c r="BE13" s="63"/>
-      <x:c r="BF13" s="63"/>
-      <x:c r="BG13" s="63"/>
-      <x:c r="BH13" s="63"/>
-      <x:c r="BI13" s="63"/>
-      <x:c r="BJ13" s="63"/>
-      <x:c r="BK13" s="63"/>
-      <x:c r="BL13" s="63"/>
-      <x:c r="BM13" s="63"/>
-      <x:c r="BN13" s="63"/>
-      <x:c r="BO13" s="63"/>
-      <x:c r="BP13" s="63"/>
-      <x:c r="BQ13" s="63"/>
-      <x:c r="BR13" s="63"/>
-      <x:c r="BS13" s="63"/>
-      <x:c r="BT13" s="63"/>
-      <x:c r="BU13" s="63"/>
-      <x:c r="BV13" s="63"/>
-      <x:c r="BW13" s="63"/>
-      <x:c r="BX13" s="63"/>
-      <x:c r="BY13" s="63"/>
-      <x:c r="BZ13" s="63"/>
-      <x:c r="CA13" s="63"/>
-      <x:c r="CB13" s="63"/>
-      <x:c r="CC13" s="63"/>
-      <x:c r="CD13" s="63"/>
-      <x:c r="CE13" s="63"/>
-      <x:c r="CF13" s="63"/>
-      <x:c r="CG13" s="63"/>
-      <x:c r="CH13" s="63"/>
-      <x:c r="CI13" s="63"/>
-      <x:c r="CJ13" s="63"/>
-      <x:c r="CK13" s="63"/>
-      <x:c r="CL13" s="63"/>
+      <x:c r="A13" s="62" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="B13" s="61"/>
+      <x:c r="C13" s="61"/>
+      <x:c r="D13" s="61"/>
+      <x:c r="E13" s="61"/>
+      <x:c r="F13" s="61"/>
+      <x:c r="G13" s="61"/>
+      <x:c r="H13" s="61"/>
+      <x:c r="I13" s="61"/>
+      <x:c r="J13" s="61"/>
+      <x:c r="K13" s="61"/>
+      <x:c r="L13" s="61"/>
+      <x:c r="M13" s="61"/>
+      <x:c r="N13" s="61"/>
+      <x:c r="O13" s="61"/>
+      <x:c r="P13" s="61"/>
+      <x:c r="Q13" s="61"/>
+      <x:c r="R13" s="61"/>
+      <x:c r="S13" s="61"/>
+      <x:c r="T13" s="61"/>
+      <x:c r="U13" s="61"/>
+      <x:c r="V13" s="61"/>
+      <x:c r="W13" s="61"/>
+      <x:c r="X13" s="61"/>
+      <x:c r="Y13" s="61"/>
+      <x:c r="Z13" s="61"/>
+      <x:c r="AA13" s="61"/>
+      <x:c r="AB13" s="61"/>
+      <x:c r="AC13" s="61"/>
+      <x:c r="AD13" s="61"/>
+      <x:c r="AE13" s="61"/>
+      <x:c r="AF13" s="61"/>
+      <x:c r="AG13" s="61"/>
+      <x:c r="AH13" s="61"/>
+      <x:c r="AI13" s="61"/>
+      <x:c r="AJ13" s="61"/>
+      <x:c r="AK13" s="61"/>
+      <x:c r="AL13" s="61"/>
+      <x:c r="AM13" s="61"/>
+      <x:c r="AN13" s="61"/>
+      <x:c r="AO13" s="61"/>
+      <x:c r="AP13" s="61"/>
+      <x:c r="AQ13" s="61"/>
+      <x:c r="AR13" s="61"/>
+      <x:c r="AS13" s="61"/>
+      <x:c r="AT13" s="61"/>
+      <x:c r="AU13" s="61"/>
+      <x:c r="AV13" s="61"/>
+      <x:c r="AW13" s="61"/>
+      <x:c r="AX13" s="61"/>
+      <x:c r="AY13" s="61"/>
+      <x:c r="AZ13" s="61"/>
+      <x:c r="BA13" s="61"/>
+      <x:c r="BB13" s="61"/>
+      <x:c r="BC13" s="61"/>
+      <x:c r="BD13" s="61"/>
+      <x:c r="BE13" s="61"/>
+      <x:c r="BF13" s="61"/>
+      <x:c r="BG13" s="61"/>
+      <x:c r="BH13" s="61"/>
+      <x:c r="BI13" s="61"/>
+      <x:c r="BJ13" s="61"/>
+      <x:c r="BK13" s="61"/>
+      <x:c r="BL13" s="61"/>
+      <x:c r="BM13" s="61"/>
+      <x:c r="BN13" s="61"/>
+      <x:c r="BO13" s="61"/>
+      <x:c r="BP13" s="61"/>
+      <x:c r="BQ13" s="61"/>
+      <x:c r="BR13" s="61"/>
+      <x:c r="BS13" s="61"/>
+      <x:c r="BT13" s="61"/>
+      <x:c r="BU13" s="61"/>
+      <x:c r="BV13" s="61"/>
+      <x:c r="BW13" s="61"/>
+      <x:c r="BX13" s="61"/>
+      <x:c r="BY13" s="61"/>
+      <x:c r="BZ13" s="61"/>
+      <x:c r="CA13" s="61"/>
+      <x:c r="CB13" s="61"/>
+      <x:c r="CC13" s="61"/>
+      <x:c r="CD13" s="61"/>
+      <x:c r="CE13" s="61"/>
+      <x:c r="CF13" s="61"/>
+      <x:c r="CG13" s="61"/>
+      <x:c r="CH13" s="61"/>
+      <x:c r="CI13" s="61"/>
+      <x:c r="CJ13" s="61"/>
+      <x:c r="CK13" s="61"/>
+      <x:c r="CL13" s="61"/>
     </x:row>
     <x:row r="14" ht="13.5" customHeight="1">
-      <x:c r="A14" s="67" t="str">
-        <x:v>項目</x:v>
-      </x:c>
-      <x:c r="B14" s="68"/>
-      <x:c r="C14" s="68"/>
-      <x:c r="D14" s="68"/>
-      <x:c r="E14" s="68"/>
-      <x:c r="F14" s="68"/>
-      <x:c r="G14" s="68"/>
-      <x:c r="H14" s="68"/>
-      <x:c r="I14" s="68"/>
-      <x:c r="J14" s="68"/>
-      <x:c r="K14" s="68"/>
-      <x:c r="L14" s="68"/>
-      <x:c r="M14" s="68"/>
-      <x:c r="N14" s="68"/>
-      <x:c r="O14" s="68"/>
-      <x:c r="P14" s="68"/>
-      <x:c r="Q14" s="68"/>
-      <x:c r="R14" s="68"/>
-      <x:c r="S14" s="67" t="str">
-        <x:v>移送元</x:v>
-      </x:c>
-      <x:c r="T14" s="68"/>
-      <x:c r="U14" s="68"/>
-      <x:c r="V14" s="68"/>
-      <x:c r="W14" s="68"/>
-      <x:c r="X14" s="68"/>
-      <x:c r="Y14" s="68"/>
-      <x:c r="Z14" s="68"/>
-      <x:c r="AA14" s="68"/>
-      <x:c r="AB14" s="68"/>
-      <x:c r="AC14" s="68"/>
-      <x:c r="AD14" s="68"/>
-      <x:c r="AE14" s="68"/>
-      <x:c r="AF14" s="68"/>
-      <x:c r="AG14" s="68"/>
-      <x:c r="AH14" s="68"/>
-      <x:c r="AI14" s="68"/>
-      <x:c r="AJ14" s="68"/>
-      <x:c r="AK14" s="67" t="str">
-        <x:v>移送方法ほか</x:v>
-      </x:c>
-      <x:c r="AL14" s="68"/>
-      <x:c r="AM14" s="68"/>
-      <x:c r="AN14" s="68"/>
-      <x:c r="AO14" s="68"/>
-      <x:c r="AP14" s="68"/>
-      <x:c r="AQ14" s="68"/>
-      <x:c r="AR14" s="68"/>
-      <x:c r="AS14" s="68"/>
-      <x:c r="AT14" s="68"/>
-      <x:c r="AU14" s="68"/>
-      <x:c r="AV14" s="68"/>
-      <x:c r="AW14" s="68"/>
-      <x:c r="AX14" s="68"/>
-      <x:c r="AY14" s="68"/>
-      <x:c r="AZ14" s="68"/>
-      <x:c r="BA14" s="68"/>
-      <x:c r="BB14" s="68"/>
-      <x:c r="BC14" s="68"/>
-      <x:c r="BD14" s="68"/>
-      <x:c r="BE14" s="68"/>
-      <x:c r="BF14" s="68"/>
-      <x:c r="BG14" s="68"/>
-      <x:c r="BH14" s="68"/>
-      <x:c r="BI14" s="68"/>
-      <x:c r="BJ14" s="68"/>
-      <x:c r="BK14" s="68"/>
-      <x:c r="BL14" s="68"/>
-      <x:c r="BM14" s="68"/>
-      <x:c r="BN14" s="68"/>
-      <x:c r="BO14" s="68"/>
-      <x:c r="BP14" s="68"/>
-      <x:c r="BQ14" s="68"/>
-      <x:c r="BR14" s="68"/>
-      <x:c r="BS14" s="68"/>
-      <x:c r="BT14" s="68"/>
-      <x:c r="BU14" s="68"/>
-      <x:c r="BV14" s="68"/>
-      <x:c r="BW14" s="68"/>
-      <x:c r="BX14" s="68"/>
-      <x:c r="BY14" s="68"/>
-      <x:c r="BZ14" s="68"/>
-      <x:c r="CA14" s="68"/>
-      <x:c r="CB14" s="68"/>
-      <x:c r="CC14" s="68"/>
-      <x:c r="CD14" s="68"/>
-      <x:c r="CE14" s="68"/>
-      <x:c r="CF14" s="68"/>
-      <x:c r="CG14" s="68"/>
-      <x:c r="CH14" s="68"/>
-      <x:c r="CI14" s="68"/>
-      <x:c r="CJ14" s="68"/>
-      <x:c r="CK14" s="68"/>
-      <x:c r="CL14" s="69"/>
+      <x:c r="A14" s="50" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B14" s="51"/>
+      <x:c r="C14" s="51"/>
+      <x:c r="D14" s="51"/>
+      <x:c r="E14" s="51"/>
+      <x:c r="F14" s="51"/>
+      <x:c r="G14" s="51"/>
+      <x:c r="H14" s="51"/>
+      <x:c r="I14" s="51"/>
+      <x:c r="J14" s="51"/>
+      <x:c r="K14" s="51"/>
+      <x:c r="L14" s="51"/>
+      <x:c r="M14" s="51"/>
+      <x:c r="N14" s="51"/>
+      <x:c r="O14" s="51"/>
+      <x:c r="P14" s="51"/>
+      <x:c r="Q14" s="51"/>
+      <x:c r="R14" s="51"/>
+      <x:c r="S14" s="50" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="T14" s="51"/>
+      <x:c r="U14" s="51"/>
+      <x:c r="V14" s="51"/>
+      <x:c r="W14" s="51"/>
+      <x:c r="X14" s="51"/>
+      <x:c r="Y14" s="51"/>
+      <x:c r="Z14" s="51"/>
+      <x:c r="AA14" s="51"/>
+      <x:c r="AB14" s="51"/>
+      <x:c r="AC14" s="51"/>
+      <x:c r="AD14" s="51"/>
+      <x:c r="AE14" s="51"/>
+      <x:c r="AF14" s="51"/>
+      <x:c r="AG14" s="51"/>
+      <x:c r="AH14" s="51"/>
+      <x:c r="AI14" s="51"/>
+      <x:c r="AJ14" s="51"/>
+      <x:c r="AK14" s="50" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="AL14" s="51"/>
+      <x:c r="AM14" s="51"/>
+      <x:c r="AN14" s="51"/>
+      <x:c r="AO14" s="51"/>
+      <x:c r="AP14" s="51"/>
+      <x:c r="AQ14" s="51"/>
+      <x:c r="AR14" s="51"/>
+      <x:c r="AS14" s="51"/>
+      <x:c r="AT14" s="51"/>
+      <x:c r="AU14" s="51"/>
+      <x:c r="AV14" s="51"/>
+      <x:c r="AW14" s="51"/>
+      <x:c r="AX14" s="51"/>
+      <x:c r="AY14" s="51"/>
+      <x:c r="AZ14" s="51"/>
+      <x:c r="BA14" s="51"/>
+      <x:c r="BB14" s="51"/>
+      <x:c r="BC14" s="51"/>
+      <x:c r="BD14" s="51"/>
+      <x:c r="BE14" s="51"/>
+      <x:c r="BF14" s="51"/>
+      <x:c r="BG14" s="51"/>
+      <x:c r="BH14" s="51"/>
+      <x:c r="BI14" s="51"/>
+      <x:c r="BJ14" s="51"/>
+      <x:c r="BK14" s="51"/>
+      <x:c r="BL14" s="51"/>
+      <x:c r="BM14" s="51"/>
+      <x:c r="BN14" s="51"/>
+      <x:c r="BO14" s="51"/>
+      <x:c r="BP14" s="51"/>
+      <x:c r="BQ14" s="51"/>
+      <x:c r="BR14" s="51"/>
+      <x:c r="BS14" s="51"/>
+      <x:c r="BT14" s="51"/>
+      <x:c r="BU14" s="51"/>
+      <x:c r="BV14" s="51"/>
+      <x:c r="BW14" s="51"/>
+      <x:c r="BX14" s="51"/>
+      <x:c r="BY14" s="51"/>
+      <x:c r="BZ14" s="51"/>
+      <x:c r="CA14" s="51"/>
+      <x:c r="CB14" s="51"/>
+      <x:c r="CC14" s="51"/>
+      <x:c r="CD14" s="51"/>
+      <x:c r="CE14" s="51"/>
+      <x:c r="CF14" s="51"/>
+      <x:c r="CG14" s="51"/>
+      <x:c r="CH14" s="51"/>
+      <x:c r="CI14" s="51"/>
+      <x:c r="CJ14" s="51"/>
+      <x:c r="CK14" s="51"/>
+      <x:c r="CL14" s="52"/>
     </x:row>
     <x:row r="15" ht="13.5" customHeight="1">
-      <x:c r="A15" s="64" t="str">
-        <x:v>ユーザーID</x:v>
-      </x:c>
-      <x:c r="B15" s="65"/>
-      <x:c r="C15" s="65"/>
-      <x:c r="D15" s="65"/>
-      <x:c r="E15" s="65"/>
-      <x:c r="F15" s="65"/>
-      <x:c r="G15" s="65"/>
-      <x:c r="H15" s="65"/>
-      <x:c r="I15" s="65"/>
-      <x:c r="J15" s="65"/>
-      <x:c r="K15" s="65"/>
-      <x:c r="L15" s="65"/>
-      <x:c r="M15" s="65"/>
-      <x:c r="N15" s="65"/>
-      <x:c r="O15" s="65"/>
-      <x:c r="P15" s="65"/>
-      <x:c r="Q15" s="65"/>
-      <x:c r="R15" s="65"/>
-      <x:c r="S15" s="64" t="str">
-        <x:v>tb1.ユーザーID</x:v>
-      </x:c>
-      <x:c r="T15" s="65"/>
-      <x:c r="U15" s="65"/>
-      <x:c r="V15" s="65"/>
-      <x:c r="W15" s="65"/>
-      <x:c r="X15" s="65"/>
-      <x:c r="Y15" s="65"/>
-      <x:c r="Z15" s="65"/>
-      <x:c r="AA15" s="65"/>
-      <x:c r="AB15" s="65"/>
-      <x:c r="AC15" s="65"/>
-      <x:c r="AD15" s="65"/>
-      <x:c r="AE15" s="65"/>
-      <x:c r="AF15" s="65"/>
-      <x:c r="AG15" s="65"/>
-      <x:c r="AH15" s="65"/>
-      <x:c r="AI15" s="65"/>
-      <x:c r="AJ15" s="65"/>
-      <x:c r="AK15" s="64"/>
-      <x:c r="AL15" s="65"/>
-      <x:c r="AM15" s="65"/>
-      <x:c r="AN15" s="65"/>
-      <x:c r="AO15" s="65"/>
-      <x:c r="AP15" s="65"/>
-      <x:c r="AQ15" s="65"/>
-      <x:c r="AR15" s="65"/>
-      <x:c r="AS15" s="65"/>
-      <x:c r="AT15" s="65"/>
-      <x:c r="AU15" s="65"/>
-      <x:c r="AV15" s="65"/>
-      <x:c r="AW15" s="65"/>
-      <x:c r="AX15" s="65"/>
-      <x:c r="AY15" s="65"/>
-      <x:c r="AZ15" s="65"/>
-      <x:c r="BA15" s="65"/>
-      <x:c r="BB15" s="65"/>
-      <x:c r="BC15" s="65"/>
-      <x:c r="BD15" s="65"/>
-      <x:c r="BE15" s="65"/>
-      <x:c r="BF15" s="65"/>
-      <x:c r="BG15" s="65"/>
-      <x:c r="BH15" s="65"/>
-      <x:c r="BI15" s="65"/>
-      <x:c r="BJ15" s="65"/>
-      <x:c r="BK15" s="65"/>
-      <x:c r="BL15" s="65"/>
-      <x:c r="BM15" s="65"/>
-      <x:c r="BN15" s="65"/>
-      <x:c r="BO15" s="65"/>
-      <x:c r="BP15" s="65"/>
-      <x:c r="BQ15" s="65"/>
-      <x:c r="BR15" s="65"/>
-      <x:c r="BS15" s="65"/>
-      <x:c r="BT15" s="65"/>
-      <x:c r="BU15" s="65"/>
-      <x:c r="BV15" s="65"/>
-      <x:c r="BW15" s="65"/>
-      <x:c r="BX15" s="65"/>
-      <x:c r="BY15" s="65"/>
-      <x:c r="BZ15" s="65"/>
-      <x:c r="CA15" s="65"/>
-      <x:c r="CB15" s="65"/>
-      <x:c r="CC15" s="65"/>
-      <x:c r="CD15" s="65"/>
-      <x:c r="CE15" s="65"/>
-      <x:c r="CF15" s="65"/>
-      <x:c r="CG15" s="65"/>
-      <x:c r="CH15" s="65"/>
-      <x:c r="CI15" s="65"/>
-      <x:c r="CJ15" s="65"/>
-      <x:c r="CK15" s="65"/>
-      <x:c r="CL15" s="66"/>
+      <x:c r="A15" s="47" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B15" s="48"/>
+      <x:c r="C15" s="48"/>
+      <x:c r="D15" s="48"/>
+      <x:c r="E15" s="48"/>
+      <x:c r="F15" s="48"/>
+      <x:c r="G15" s="48"/>
+      <x:c r="H15" s="48"/>
+      <x:c r="I15" s="48"/>
+      <x:c r="J15" s="48"/>
+      <x:c r="K15" s="48"/>
+      <x:c r="L15" s="48"/>
+      <x:c r="M15" s="48"/>
+      <x:c r="N15" s="48"/>
+      <x:c r="O15" s="48"/>
+      <x:c r="P15" s="48"/>
+      <x:c r="Q15" s="48"/>
+      <x:c r="R15" s="48"/>
+      <x:c r="S15" s="47" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T15" s="48"/>
+      <x:c r="U15" s="48"/>
+      <x:c r="V15" s="48"/>
+      <x:c r="W15" s="48"/>
+      <x:c r="X15" s="48"/>
+      <x:c r="Y15" s="48"/>
+      <x:c r="Z15" s="48"/>
+      <x:c r="AA15" s="48"/>
+      <x:c r="AB15" s="48"/>
+      <x:c r="AC15" s="48"/>
+      <x:c r="AD15" s="48"/>
+      <x:c r="AE15" s="48"/>
+      <x:c r="AF15" s="48"/>
+      <x:c r="AG15" s="48"/>
+      <x:c r="AH15" s="48"/>
+      <x:c r="AI15" s="48"/>
+      <x:c r="AJ15" s="48"/>
+      <x:c r="AK15" s="47"/>
+      <x:c r="AL15" s="48"/>
+      <x:c r="AM15" s="48"/>
+      <x:c r="AN15" s="48"/>
+      <x:c r="AO15" s="48"/>
+      <x:c r="AP15" s="48"/>
+      <x:c r="AQ15" s="48"/>
+      <x:c r="AR15" s="48"/>
+      <x:c r="AS15" s="48"/>
+      <x:c r="AT15" s="48"/>
+      <x:c r="AU15" s="48"/>
+      <x:c r="AV15" s="48"/>
+      <x:c r="AW15" s="48"/>
+      <x:c r="AX15" s="48"/>
+      <x:c r="AY15" s="48"/>
+      <x:c r="AZ15" s="48"/>
+      <x:c r="BA15" s="48"/>
+      <x:c r="BB15" s="48"/>
+      <x:c r="BC15" s="48"/>
+      <x:c r="BD15" s="48"/>
+      <x:c r="BE15" s="48"/>
+      <x:c r="BF15" s="48"/>
+      <x:c r="BG15" s="48"/>
+      <x:c r="BH15" s="48"/>
+      <x:c r="BI15" s="48"/>
+      <x:c r="BJ15" s="48"/>
+      <x:c r="BK15" s="48"/>
+      <x:c r="BL15" s="48"/>
+      <x:c r="BM15" s="48"/>
+      <x:c r="BN15" s="48"/>
+      <x:c r="BO15" s="48"/>
+      <x:c r="BP15" s="48"/>
+      <x:c r="BQ15" s="48"/>
+      <x:c r="BR15" s="48"/>
+      <x:c r="BS15" s="48"/>
+      <x:c r="BT15" s="48"/>
+      <x:c r="BU15" s="48"/>
+      <x:c r="BV15" s="48"/>
+      <x:c r="BW15" s="48"/>
+      <x:c r="BX15" s="48"/>
+      <x:c r="BY15" s="48"/>
+      <x:c r="BZ15" s="48"/>
+      <x:c r="CA15" s="48"/>
+      <x:c r="CB15" s="48"/>
+      <x:c r="CC15" s="48"/>
+      <x:c r="CD15" s="48"/>
+      <x:c r="CE15" s="48"/>
+      <x:c r="CF15" s="48"/>
+      <x:c r="CG15" s="48"/>
+      <x:c r="CH15" s="48"/>
+      <x:c r="CI15" s="48"/>
+      <x:c r="CJ15" s="48"/>
+      <x:c r="CK15" s="48"/>
+      <x:c r="CL15" s="49"/>
     </x:row>
     <x:row r="16" ht="13.5" customHeight="1">
-      <x:c r="A16" s="64" t="str">
-        <x:v>氏名</x:v>
-      </x:c>
-      <x:c r="B16" s="65"/>
-      <x:c r="C16" s="65"/>
-      <x:c r="D16" s="65"/>
-      <x:c r="E16" s="65"/>
-      <x:c r="F16" s="65"/>
-      <x:c r="G16" s="65"/>
-      <x:c r="H16" s="65"/>
-      <x:c r="I16" s="65"/>
-      <x:c r="J16" s="65"/>
-      <x:c r="K16" s="65"/>
-      <x:c r="L16" s="65"/>
-      <x:c r="M16" s="65"/>
-      <x:c r="N16" s="65"/>
-      <x:c r="O16" s="65"/>
-      <x:c r="P16" s="65"/>
-      <x:c r="Q16" s="65"/>
-      <x:c r="R16" s="65"/>
-      <x:c r="S16" s="64" t="str">
-        <x:v>tb1.氏名</x:v>
-      </x:c>
-      <x:c r="T16" s="65"/>
-      <x:c r="U16" s="65"/>
-      <x:c r="V16" s="65"/>
-      <x:c r="W16" s="65"/>
-      <x:c r="X16" s="65"/>
-      <x:c r="Y16" s="65"/>
-      <x:c r="Z16" s="65"/>
-      <x:c r="AA16" s="65"/>
-      <x:c r="AB16" s="65"/>
-      <x:c r="AC16" s="65"/>
-      <x:c r="AD16" s="65"/>
-      <x:c r="AE16" s="65"/>
-      <x:c r="AF16" s="65"/>
-      <x:c r="AG16" s="65"/>
-      <x:c r="AH16" s="65"/>
-      <x:c r="AI16" s="65"/>
-      <x:c r="AJ16" s="65"/>
-      <x:c r="AK16" s="64"/>
-      <x:c r="AL16" s="65"/>
-      <x:c r="AM16" s="65"/>
-      <x:c r="AN16" s="65"/>
-      <x:c r="AO16" s="65"/>
-      <x:c r="AP16" s="65"/>
-      <x:c r="AQ16" s="65"/>
-      <x:c r="AR16" s="65"/>
-      <x:c r="AS16" s="65"/>
-      <x:c r="AT16" s="65"/>
-      <x:c r="AU16" s="65"/>
-      <x:c r="AV16" s="65"/>
-      <x:c r="AW16" s="65"/>
-      <x:c r="AX16" s="65"/>
-      <x:c r="AY16" s="65"/>
-      <x:c r="AZ16" s="65"/>
-      <x:c r="BA16" s="65"/>
-      <x:c r="BB16" s="65"/>
-      <x:c r="BC16" s="65"/>
-      <x:c r="BD16" s="65"/>
-      <x:c r="BE16" s="65"/>
-      <x:c r="BF16" s="65"/>
-      <x:c r="BG16" s="65"/>
-      <x:c r="BH16" s="65"/>
-      <x:c r="BI16" s="65"/>
-      <x:c r="BJ16" s="65"/>
-      <x:c r="BK16" s="65"/>
-      <x:c r="BL16" s="65"/>
-      <x:c r="BM16" s="65"/>
-      <x:c r="BN16" s="65"/>
-      <x:c r="BO16" s="65"/>
-      <x:c r="BP16" s="65"/>
-      <x:c r="BQ16" s="65"/>
-      <x:c r="BR16" s="65"/>
-      <x:c r="BS16" s="65"/>
-      <x:c r="BT16" s="65"/>
-      <x:c r="BU16" s="65"/>
-      <x:c r="BV16" s="65"/>
-      <x:c r="BW16" s="65"/>
-      <x:c r="BX16" s="65"/>
-      <x:c r="BY16" s="65"/>
-      <x:c r="BZ16" s="65"/>
-      <x:c r="CA16" s="65"/>
-      <x:c r="CB16" s="65"/>
-      <x:c r="CC16" s="65"/>
-      <x:c r="CD16" s="65"/>
-      <x:c r="CE16" s="65"/>
-      <x:c r="CF16" s="65"/>
-      <x:c r="CG16" s="65"/>
-      <x:c r="CH16" s="65"/>
-      <x:c r="CI16" s="65"/>
-      <x:c r="CJ16" s="65"/>
-      <x:c r="CK16" s="65"/>
-      <x:c r="CL16" s="66"/>
+      <x:c r="A16" s="47" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B16" s="48"/>
+      <x:c r="C16" s="48"/>
+      <x:c r="D16" s="48"/>
+      <x:c r="E16" s="48"/>
+      <x:c r="F16" s="48"/>
+      <x:c r="G16" s="48"/>
+      <x:c r="H16" s="48"/>
+      <x:c r="I16" s="48"/>
+      <x:c r="J16" s="48"/>
+      <x:c r="K16" s="48"/>
+      <x:c r="L16" s="48"/>
+      <x:c r="M16" s="48"/>
+      <x:c r="N16" s="48"/>
+      <x:c r="O16" s="48"/>
+      <x:c r="P16" s="48"/>
+      <x:c r="Q16" s="48"/>
+      <x:c r="R16" s="48"/>
+      <x:c r="S16" s="47" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="T16" s="48"/>
+      <x:c r="U16" s="48"/>
+      <x:c r="V16" s="48"/>
+      <x:c r="W16" s="48"/>
+      <x:c r="X16" s="48"/>
+      <x:c r="Y16" s="48"/>
+      <x:c r="Z16" s="48"/>
+      <x:c r="AA16" s="48"/>
+      <x:c r="AB16" s="48"/>
+      <x:c r="AC16" s="48"/>
+      <x:c r="AD16" s="48"/>
+      <x:c r="AE16" s="48"/>
+      <x:c r="AF16" s="48"/>
+      <x:c r="AG16" s="48"/>
+      <x:c r="AH16" s="48"/>
+      <x:c r="AI16" s="48"/>
+      <x:c r="AJ16" s="48"/>
+      <x:c r="AK16" s="47"/>
+      <x:c r="AL16" s="48"/>
+      <x:c r="AM16" s="48"/>
+      <x:c r="AN16" s="48"/>
+      <x:c r="AO16" s="48"/>
+      <x:c r="AP16" s="48"/>
+      <x:c r="AQ16" s="48"/>
+      <x:c r="AR16" s="48"/>
+      <x:c r="AS16" s="48"/>
+      <x:c r="AT16" s="48"/>
+      <x:c r="AU16" s="48"/>
+      <x:c r="AV16" s="48"/>
+      <x:c r="AW16" s="48"/>
+      <x:c r="AX16" s="48"/>
+      <x:c r="AY16" s="48"/>
+      <x:c r="AZ16" s="48"/>
+      <x:c r="BA16" s="48"/>
+      <x:c r="BB16" s="48"/>
+      <x:c r="BC16" s="48"/>
+      <x:c r="BD16" s="48"/>
+      <x:c r="BE16" s="48"/>
+      <x:c r="BF16" s="48"/>
+      <x:c r="BG16" s="48"/>
+      <x:c r="BH16" s="48"/>
+      <x:c r="BI16" s="48"/>
+      <x:c r="BJ16" s="48"/>
+      <x:c r="BK16" s="48"/>
+      <x:c r="BL16" s="48"/>
+      <x:c r="BM16" s="48"/>
+      <x:c r="BN16" s="48"/>
+      <x:c r="BO16" s="48"/>
+      <x:c r="BP16" s="48"/>
+      <x:c r="BQ16" s="48"/>
+      <x:c r="BR16" s="48"/>
+      <x:c r="BS16" s="48"/>
+      <x:c r="BT16" s="48"/>
+      <x:c r="BU16" s="48"/>
+      <x:c r="BV16" s="48"/>
+      <x:c r="BW16" s="48"/>
+      <x:c r="BX16" s="48"/>
+      <x:c r="BY16" s="48"/>
+      <x:c r="BZ16" s="48"/>
+      <x:c r="CA16" s="48"/>
+      <x:c r="CB16" s="48"/>
+      <x:c r="CC16" s="48"/>
+      <x:c r="CD16" s="48"/>
+      <x:c r="CE16" s="48"/>
+      <x:c r="CF16" s="48"/>
+      <x:c r="CG16" s="48"/>
+      <x:c r="CH16" s="48"/>
+      <x:c r="CI16" s="48"/>
+      <x:c r="CJ16" s="48"/>
+      <x:c r="CK16" s="48"/>
+      <x:c r="CL16" s="49"/>
     </x:row>
     <x:row r="17" ht="13.5" customHeight="1">
-      <x:c r="A17" s="63" t="str">
-        <x:v>＜移送パターン2＞</x:v>
-      </x:c>
-      <x:c r="B17" s="63"/>
-      <x:c r="C17" s="63"/>
-      <x:c r="D17" s="63"/>
-      <x:c r="E17" s="63"/>
-      <x:c r="F17" s="63"/>
-      <x:c r="G17" s="63"/>
-      <x:c r="H17" s="63"/>
-      <x:c r="I17" s="63"/>
-      <x:c r="J17" s="63"/>
-      <x:c r="K17" s="63"/>
-      <x:c r="L17" s="63"/>
-      <x:c r="M17" s="63"/>
-      <x:c r="N17" s="63"/>
-      <x:c r="O17" s="63"/>
-      <x:c r="P17" s="63"/>
-      <x:c r="Q17" s="63"/>
-      <x:c r="R17" s="63"/>
-      <x:c r="S17" s="63"/>
-      <x:c r="T17" s="63"/>
-      <x:c r="U17" s="63"/>
-      <x:c r="V17" s="63"/>
-      <x:c r="W17" s="63"/>
-      <x:c r="X17" s="63"/>
-      <x:c r="Y17" s="63"/>
-      <x:c r="Z17" s="63"/>
-      <x:c r="AA17" s="63"/>
-      <x:c r="AB17" s="63"/>
-      <x:c r="AC17" s="63"/>
-      <x:c r="AD17" s="63"/>
-      <x:c r="AE17" s="63"/>
-      <x:c r="AF17" s="63"/>
-      <x:c r="AG17" s="63"/>
-      <x:c r="AH17" s="63"/>
-      <x:c r="AI17" s="63"/>
-      <x:c r="AJ17" s="63"/>
-      <x:c r="AK17" s="63"/>
-      <x:c r="AL17" s="63"/>
-      <x:c r="AM17" s="63"/>
-      <x:c r="AN17" s="63"/>
-      <x:c r="AO17" s="63"/>
-      <x:c r="AP17" s="63"/>
-      <x:c r="AQ17" s="63"/>
-      <x:c r="AR17" s="63"/>
-      <x:c r="AS17" s="63"/>
-      <x:c r="AT17" s="63"/>
-      <x:c r="AU17" s="63"/>
-      <x:c r="AV17" s="63"/>
-      <x:c r="AW17" s="63"/>
-      <x:c r="AX17" s="63"/>
-      <x:c r="AY17" s="63"/>
-      <x:c r="AZ17" s="63"/>
-      <x:c r="BA17" s="63"/>
-      <x:c r="BB17" s="63"/>
-      <x:c r="BC17" s="63"/>
-      <x:c r="BD17" s="63"/>
-      <x:c r="BE17" s="63"/>
-      <x:c r="BF17" s="63"/>
-      <x:c r="BG17" s="63"/>
-      <x:c r="BH17" s="63"/>
-      <x:c r="BI17" s="63"/>
-      <x:c r="BJ17" s="63"/>
-      <x:c r="BK17" s="63"/>
-      <x:c r="BL17" s="63"/>
-      <x:c r="BM17" s="63"/>
-      <x:c r="BN17" s="63"/>
-      <x:c r="BO17" s="63"/>
-      <x:c r="BP17" s="63"/>
-      <x:c r="BQ17" s="63"/>
-      <x:c r="BR17" s="63"/>
-      <x:c r="BS17" s="63"/>
-      <x:c r="BT17" s="63"/>
-      <x:c r="BU17" s="63"/>
-      <x:c r="BV17" s="63"/>
-      <x:c r="BW17" s="63"/>
-      <x:c r="BX17" s="63"/>
-      <x:c r="BY17" s="63"/>
-      <x:c r="BZ17" s="63"/>
-      <x:c r="CA17" s="63"/>
-      <x:c r="CB17" s="63"/>
-      <x:c r="CC17" s="63"/>
-      <x:c r="CD17" s="63"/>
-      <x:c r="CE17" s="63"/>
-      <x:c r="CF17" s="63"/>
-      <x:c r="CG17" s="63"/>
-      <x:c r="CH17" s="63"/>
-      <x:c r="CI17" s="63"/>
-      <x:c r="CJ17" s="63"/>
-      <x:c r="CK17" s="63"/>
-      <x:c r="CL17" s="63"/>
+      <x:c r="A17" s="46" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="B17" s="48"/>
+      <x:c r="C17" s="48"/>
+      <x:c r="D17" s="48"/>
+      <x:c r="E17" s="48"/>
+      <x:c r="F17" s="48"/>
+      <x:c r="G17" s="48"/>
+      <x:c r="H17" s="48"/>
+      <x:c r="I17" s="48"/>
+      <x:c r="J17" s="48"/>
+      <x:c r="K17" s="48"/>
+      <x:c r="L17" s="48"/>
+      <x:c r="M17" s="48"/>
+      <x:c r="N17" s="48"/>
+      <x:c r="O17" s="48"/>
+      <x:c r="P17" s="48"/>
+      <x:c r="Q17" s="48"/>
+      <x:c r="R17" s="48"/>
+      <x:c r="S17" s="48"/>
+      <x:c r="T17" s="48"/>
+      <x:c r="U17" s="48"/>
+      <x:c r="V17" s="48"/>
+      <x:c r="W17" s="48"/>
+      <x:c r="X17" s="48"/>
+      <x:c r="Y17" s="48"/>
+      <x:c r="Z17" s="48"/>
+      <x:c r="AA17" s="48"/>
+      <x:c r="AB17" s="48"/>
+      <x:c r="AC17" s="48"/>
+      <x:c r="AD17" s="48"/>
+      <x:c r="AE17" s="48"/>
+      <x:c r="AF17" s="48"/>
+      <x:c r="AG17" s="48"/>
+      <x:c r="AH17" s="48"/>
+      <x:c r="AI17" s="48"/>
+      <x:c r="AJ17" s="48"/>
+      <x:c r="AK17" s="48"/>
+      <x:c r="AL17" s="48"/>
+      <x:c r="AM17" s="48"/>
+      <x:c r="AN17" s="48"/>
+      <x:c r="AO17" s="48"/>
+      <x:c r="AP17" s="48"/>
+      <x:c r="AQ17" s="48"/>
+      <x:c r="AR17" s="48"/>
+      <x:c r="AS17" s="48"/>
+      <x:c r="AT17" s="48"/>
+      <x:c r="AU17" s="48"/>
+      <x:c r="AV17" s="48"/>
+      <x:c r="AW17" s="48"/>
+      <x:c r="AX17" s="48"/>
+      <x:c r="AY17" s="48"/>
+      <x:c r="AZ17" s="48"/>
+      <x:c r="BA17" s="48"/>
+      <x:c r="BB17" s="48"/>
+      <x:c r="BC17" s="48"/>
+      <x:c r="BD17" s="48"/>
+      <x:c r="BE17" s="48"/>
+      <x:c r="BF17" s="48"/>
+      <x:c r="BG17" s="48"/>
+      <x:c r="BH17" s="48"/>
+      <x:c r="BI17" s="48"/>
+      <x:c r="BJ17" s="48"/>
+      <x:c r="BK17" s="48"/>
+      <x:c r="BL17" s="48"/>
+      <x:c r="BM17" s="48"/>
+      <x:c r="BN17" s="48"/>
+      <x:c r="BO17" s="48"/>
+      <x:c r="BP17" s="48"/>
+      <x:c r="BQ17" s="48"/>
+      <x:c r="BR17" s="48"/>
+      <x:c r="BS17" s="48"/>
+      <x:c r="BT17" s="48"/>
+      <x:c r="BU17" s="48"/>
+      <x:c r="BV17" s="48"/>
+      <x:c r="BW17" s="48"/>
+      <x:c r="BX17" s="48"/>
+      <x:c r="BY17" s="48"/>
+      <x:c r="BZ17" s="48"/>
+      <x:c r="CA17" s="48"/>
+      <x:c r="CB17" s="48"/>
+      <x:c r="CC17" s="48"/>
+      <x:c r="CD17" s="48"/>
+      <x:c r="CE17" s="48"/>
+      <x:c r="CF17" s="48"/>
+      <x:c r="CG17" s="48"/>
+      <x:c r="CH17" s="48"/>
+      <x:c r="CI17" s="48"/>
+      <x:c r="CJ17" s="48"/>
+      <x:c r="CK17" s="48"/>
+      <x:c r="CL17" s="48"/>
     </x:row>
     <x:row r="18" ht="13.5" customHeight="1">
-      <x:c r="A18" s="67" t="str">
-        <x:v>項目</x:v>
-      </x:c>
-      <x:c r="B18" s="68"/>
-      <x:c r="C18" s="68"/>
-      <x:c r="D18" s="68"/>
-      <x:c r="E18" s="68"/>
-      <x:c r="F18" s="68"/>
-      <x:c r="G18" s="68"/>
-      <x:c r="H18" s="68"/>
-      <x:c r="I18" s="68"/>
-      <x:c r="J18" s="68"/>
-      <x:c r="K18" s="68"/>
-      <x:c r="L18" s="68"/>
-      <x:c r="M18" s="68"/>
-      <x:c r="N18" s="68"/>
-      <x:c r="O18" s="68"/>
-      <x:c r="P18" s="68"/>
-      <x:c r="Q18" s="68"/>
-      <x:c r="R18" s="68"/>
-      <x:c r="S18" s="67" t="str">
-        <x:v>移送元</x:v>
-      </x:c>
-      <x:c r="T18" s="68"/>
-      <x:c r="U18" s="68"/>
-      <x:c r="V18" s="68"/>
-      <x:c r="W18" s="68"/>
-      <x:c r="X18" s="68"/>
-      <x:c r="Y18" s="68"/>
-      <x:c r="Z18" s="68"/>
-      <x:c r="AA18" s="68"/>
-      <x:c r="AB18" s="68"/>
-      <x:c r="AC18" s="68"/>
-      <x:c r="AD18" s="68"/>
-      <x:c r="AE18" s="68"/>
-      <x:c r="AF18" s="68"/>
-      <x:c r="AG18" s="68"/>
-      <x:c r="AH18" s="68"/>
-      <x:c r="AI18" s="68"/>
-      <x:c r="AJ18" s="68"/>
-      <x:c r="AK18" s="67" t="str">
-        <x:v>移送方法ほか</x:v>
-      </x:c>
-      <x:c r="AL18" s="68"/>
-      <x:c r="AM18" s="68"/>
-      <x:c r="AN18" s="68"/>
-      <x:c r="AO18" s="68"/>
-      <x:c r="AP18" s="68"/>
-      <x:c r="AQ18" s="68"/>
-      <x:c r="AR18" s="68"/>
-      <x:c r="AS18" s="68"/>
-      <x:c r="AT18" s="68"/>
-      <x:c r="AU18" s="68"/>
-      <x:c r="AV18" s="68"/>
-      <x:c r="AW18" s="68"/>
-      <x:c r="AX18" s="68"/>
-      <x:c r="AY18" s="68"/>
-      <x:c r="AZ18" s="68"/>
-      <x:c r="BA18" s="68"/>
-      <x:c r="BB18" s="68"/>
-      <x:c r="BC18" s="68"/>
-      <x:c r="BD18" s="68"/>
-      <x:c r="BE18" s="68"/>
-      <x:c r="BF18" s="68"/>
-      <x:c r="BG18" s="68"/>
-      <x:c r="BH18" s="68"/>
-      <x:c r="BI18" s="68"/>
-      <x:c r="BJ18" s="68"/>
-      <x:c r="BK18" s="68"/>
-      <x:c r="BL18" s="68"/>
-      <x:c r="BM18" s="68"/>
-      <x:c r="BN18" s="68"/>
-      <x:c r="BO18" s="68"/>
-      <x:c r="BP18" s="68"/>
-      <x:c r="BQ18" s="68"/>
-      <x:c r="BR18" s="68"/>
-      <x:c r="BS18" s="68"/>
-      <x:c r="BT18" s="68"/>
-      <x:c r="BU18" s="68"/>
-      <x:c r="BV18" s="68"/>
-      <x:c r="BW18" s="68"/>
-      <x:c r="BX18" s="68"/>
-      <x:c r="BY18" s="68"/>
-      <x:c r="BZ18" s="68"/>
-      <x:c r="CA18" s="68"/>
-      <x:c r="CB18" s="68"/>
-      <x:c r="CC18" s="68"/>
-      <x:c r="CD18" s="68"/>
-      <x:c r="CE18" s="68"/>
-      <x:c r="CF18" s="68"/>
-      <x:c r="CG18" s="68"/>
-      <x:c r="CH18" s="68"/>
-      <x:c r="CI18" s="68"/>
-      <x:c r="CJ18" s="68"/>
-      <x:c r="CK18" s="68"/>
-      <x:c r="CL18" s="69"/>
+      <x:c r="A18" s="50" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B18" s="51"/>
+      <x:c r="C18" s="51"/>
+      <x:c r="D18" s="51"/>
+      <x:c r="E18" s="51"/>
+      <x:c r="F18" s="51"/>
+      <x:c r="G18" s="51"/>
+      <x:c r="H18" s="51"/>
+      <x:c r="I18" s="51"/>
+      <x:c r="J18" s="51"/>
+      <x:c r="K18" s="51"/>
+      <x:c r="L18" s="51"/>
+      <x:c r="M18" s="51"/>
+      <x:c r="N18" s="51"/>
+      <x:c r="O18" s="51"/>
+      <x:c r="P18" s="51"/>
+      <x:c r="Q18" s="51"/>
+      <x:c r="R18" s="51"/>
+      <x:c r="S18" s="50" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="T18" s="51"/>
+      <x:c r="U18" s="51"/>
+      <x:c r="V18" s="51"/>
+      <x:c r="W18" s="51"/>
+      <x:c r="X18" s="51"/>
+      <x:c r="Y18" s="51"/>
+      <x:c r="Z18" s="51"/>
+      <x:c r="AA18" s="51"/>
+      <x:c r="AB18" s="51"/>
+      <x:c r="AC18" s="51"/>
+      <x:c r="AD18" s="51"/>
+      <x:c r="AE18" s="51"/>
+      <x:c r="AF18" s="51"/>
+      <x:c r="AG18" s="51"/>
+      <x:c r="AH18" s="51"/>
+      <x:c r="AI18" s="51"/>
+      <x:c r="AJ18" s="51"/>
+      <x:c r="AK18" s="50" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="AL18" s="51"/>
+      <x:c r="AM18" s="51"/>
+      <x:c r="AN18" s="51"/>
+      <x:c r="AO18" s="51"/>
+      <x:c r="AP18" s="51"/>
+      <x:c r="AQ18" s="51"/>
+      <x:c r="AR18" s="51"/>
+      <x:c r="AS18" s="51"/>
+      <x:c r="AT18" s="51"/>
+      <x:c r="AU18" s="51"/>
+      <x:c r="AV18" s="51"/>
+      <x:c r="AW18" s="51"/>
+      <x:c r="AX18" s="51"/>
+      <x:c r="AY18" s="51"/>
+      <x:c r="AZ18" s="51"/>
+      <x:c r="BA18" s="51"/>
+      <x:c r="BB18" s="51"/>
+      <x:c r="BC18" s="51"/>
+      <x:c r="BD18" s="51"/>
+      <x:c r="BE18" s="51"/>
+      <x:c r="BF18" s="51"/>
+      <x:c r="BG18" s="51"/>
+      <x:c r="BH18" s="51"/>
+      <x:c r="BI18" s="51"/>
+      <x:c r="BJ18" s="51"/>
+      <x:c r="BK18" s="51"/>
+      <x:c r="BL18" s="51"/>
+      <x:c r="BM18" s="51"/>
+      <x:c r="BN18" s="51"/>
+      <x:c r="BO18" s="51"/>
+      <x:c r="BP18" s="51"/>
+      <x:c r="BQ18" s="51"/>
+      <x:c r="BR18" s="51"/>
+      <x:c r="BS18" s="51"/>
+      <x:c r="BT18" s="51"/>
+      <x:c r="BU18" s="51"/>
+      <x:c r="BV18" s="51"/>
+      <x:c r="BW18" s="51"/>
+      <x:c r="BX18" s="51"/>
+      <x:c r="BY18" s="51"/>
+      <x:c r="BZ18" s="51"/>
+      <x:c r="CA18" s="51"/>
+      <x:c r="CB18" s="51"/>
+      <x:c r="CC18" s="51"/>
+      <x:c r="CD18" s="51"/>
+      <x:c r="CE18" s="51"/>
+      <x:c r="CF18" s="51"/>
+      <x:c r="CG18" s="51"/>
+      <x:c r="CH18" s="51"/>
+      <x:c r="CI18" s="51"/>
+      <x:c r="CJ18" s="51"/>
+      <x:c r="CK18" s="51"/>
+      <x:c r="CL18" s="52"/>
     </x:row>
     <x:row r="19" ht="13.5" customHeight="1">
-      <x:c r="A19" s="64" t="str">
-        <x:v>ユーザーID</x:v>
-      </x:c>
-      <x:c r="B19" s="65"/>
-      <x:c r="C19" s="65"/>
-      <x:c r="D19" s="65"/>
-      <x:c r="E19" s="65"/>
-      <x:c r="F19" s="65"/>
-      <x:c r="G19" s="65"/>
-      <x:c r="H19" s="65"/>
-      <x:c r="I19" s="65"/>
-      <x:c r="J19" s="65"/>
-      <x:c r="K19" s="65"/>
-      <x:c r="L19" s="65"/>
-      <x:c r="M19" s="65"/>
-      <x:c r="N19" s="65"/>
-      <x:c r="O19" s="65"/>
-      <x:c r="P19" s="65"/>
-      <x:c r="Q19" s="65"/>
-      <x:c r="R19" s="65"/>
-      <x:c r="S19" s="64" t="str">
-        <x:v>tb2.ユーザーID</x:v>
-      </x:c>
-      <x:c r="T19" s="65"/>
-      <x:c r="U19" s="65"/>
-      <x:c r="V19" s="65"/>
-      <x:c r="W19" s="65"/>
-      <x:c r="X19" s="65"/>
-      <x:c r="Y19" s="65"/>
-      <x:c r="Z19" s="65"/>
-      <x:c r="AA19" s="65"/>
-      <x:c r="AB19" s="65"/>
-      <x:c r="AC19" s="65"/>
-      <x:c r="AD19" s="65"/>
-      <x:c r="AE19" s="65"/>
-      <x:c r="AF19" s="65"/>
-      <x:c r="AG19" s="65"/>
-      <x:c r="AH19" s="65"/>
-      <x:c r="AI19" s="65"/>
-      <x:c r="AJ19" s="65"/>
-      <x:c r="AK19" s="64"/>
-      <x:c r="AL19" s="65"/>
-      <x:c r="AM19" s="65"/>
-      <x:c r="AN19" s="65"/>
-      <x:c r="AO19" s="65"/>
-      <x:c r="AP19" s="65"/>
-      <x:c r="AQ19" s="65"/>
-      <x:c r="AR19" s="65"/>
-      <x:c r="AS19" s="65"/>
-      <x:c r="AT19" s="65"/>
-      <x:c r="AU19" s="65"/>
-      <x:c r="AV19" s="65"/>
-      <x:c r="AW19" s="65"/>
-      <x:c r="AX19" s="65"/>
-      <x:c r="AY19" s="65"/>
-      <x:c r="AZ19" s="65"/>
-      <x:c r="BA19" s="65"/>
-      <x:c r="BB19" s="65"/>
-      <x:c r="BC19" s="65"/>
-      <x:c r="BD19" s="65"/>
-      <x:c r="BE19" s="65"/>
-      <x:c r="BF19" s="65"/>
-      <x:c r="BG19" s="65"/>
-      <x:c r="BH19" s="65"/>
-      <x:c r="BI19" s="65"/>
-      <x:c r="BJ19" s="65"/>
-      <x:c r="BK19" s="65"/>
-      <x:c r="BL19" s="65"/>
-      <x:c r="BM19" s="65"/>
-      <x:c r="BN19" s="65"/>
-      <x:c r="BO19" s="65"/>
-      <x:c r="BP19" s="65"/>
-      <x:c r="BQ19" s="65"/>
-      <x:c r="BR19" s="65"/>
-      <x:c r="BS19" s="65"/>
-      <x:c r="BT19" s="65"/>
-      <x:c r="BU19" s="65"/>
-      <x:c r="BV19" s="65"/>
-      <x:c r="BW19" s="65"/>
-      <x:c r="BX19" s="65"/>
-      <x:c r="BY19" s="65"/>
-      <x:c r="BZ19" s="65"/>
-      <x:c r="CA19" s="65"/>
-      <x:c r="CB19" s="65"/>
-      <x:c r="CC19" s="65"/>
-      <x:c r="CD19" s="65"/>
-      <x:c r="CE19" s="65"/>
-      <x:c r="CF19" s="65"/>
-      <x:c r="CG19" s="65"/>
-      <x:c r="CH19" s="65"/>
-      <x:c r="CI19" s="65"/>
-      <x:c r="CJ19" s="65"/>
-      <x:c r="CK19" s="65"/>
-      <x:c r="CL19" s="66"/>
+      <x:c r="A19" s="47" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B19" s="48"/>
+      <x:c r="C19" s="48"/>
+      <x:c r="D19" s="48"/>
+      <x:c r="E19" s="48"/>
+      <x:c r="F19" s="48"/>
+      <x:c r="G19" s="48"/>
+      <x:c r="H19" s="48"/>
+      <x:c r="I19" s="48"/>
+      <x:c r="J19" s="48"/>
+      <x:c r="K19" s="48"/>
+      <x:c r="L19" s="48"/>
+      <x:c r="M19" s="48"/>
+      <x:c r="N19" s="48"/>
+      <x:c r="O19" s="48"/>
+      <x:c r="P19" s="48"/>
+      <x:c r="Q19" s="48"/>
+      <x:c r="R19" s="48"/>
+      <x:c r="S19" s="47" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="T19" s="48"/>
+      <x:c r="U19" s="48"/>
+      <x:c r="V19" s="48"/>
+      <x:c r="W19" s="48"/>
+      <x:c r="X19" s="48"/>
+      <x:c r="Y19" s="48"/>
+      <x:c r="Z19" s="48"/>
+      <x:c r="AA19" s="48"/>
+      <x:c r="AB19" s="48"/>
+      <x:c r="AC19" s="48"/>
+      <x:c r="AD19" s="48"/>
+      <x:c r="AE19" s="48"/>
+      <x:c r="AF19" s="48"/>
+      <x:c r="AG19" s="48"/>
+      <x:c r="AH19" s="48"/>
+      <x:c r="AI19" s="48"/>
+      <x:c r="AJ19" s="48"/>
+      <x:c r="AK19" s="47"/>
+      <x:c r="AL19" s="48"/>
+      <x:c r="AM19" s="48"/>
+      <x:c r="AN19" s="48"/>
+      <x:c r="AO19" s="48"/>
+      <x:c r="AP19" s="48"/>
+      <x:c r="AQ19" s="48"/>
+      <x:c r="AR19" s="48"/>
+      <x:c r="AS19" s="48"/>
+      <x:c r="AT19" s="48"/>
+      <x:c r="AU19" s="48"/>
+      <x:c r="AV19" s="48"/>
+      <x:c r="AW19" s="48"/>
+      <x:c r="AX19" s="48"/>
+      <x:c r="AY19" s="48"/>
+      <x:c r="AZ19" s="48"/>
+      <x:c r="BA19" s="48"/>
+      <x:c r="BB19" s="48"/>
+      <x:c r="BC19" s="48"/>
+      <x:c r="BD19" s="48"/>
+      <x:c r="BE19" s="48"/>
+      <x:c r="BF19" s="48"/>
+      <x:c r="BG19" s="48"/>
+      <x:c r="BH19" s="48"/>
+      <x:c r="BI19" s="48"/>
+      <x:c r="BJ19" s="48"/>
+      <x:c r="BK19" s="48"/>
+      <x:c r="BL19" s="48"/>
+      <x:c r="BM19" s="48"/>
+      <x:c r="BN19" s="48"/>
+      <x:c r="BO19" s="48"/>
+      <x:c r="BP19" s="48"/>
+      <x:c r="BQ19" s="48"/>
+      <x:c r="BR19" s="48"/>
+      <x:c r="BS19" s="48"/>
+      <x:c r="BT19" s="48"/>
+      <x:c r="BU19" s="48"/>
+      <x:c r="BV19" s="48"/>
+      <x:c r="BW19" s="48"/>
+      <x:c r="BX19" s="48"/>
+      <x:c r="BY19" s="48"/>
+      <x:c r="BZ19" s="48"/>
+      <x:c r="CA19" s="48"/>
+      <x:c r="CB19" s="48"/>
+      <x:c r="CC19" s="48"/>
+      <x:c r="CD19" s="48"/>
+      <x:c r="CE19" s="48"/>
+      <x:c r="CF19" s="48"/>
+      <x:c r="CG19" s="48"/>
+      <x:c r="CH19" s="48"/>
+      <x:c r="CI19" s="48"/>
+      <x:c r="CJ19" s="48"/>
+      <x:c r="CK19" s="48"/>
+      <x:c r="CL19" s="49"/>
     </x:row>
     <x:row r="20" ht="13.5" customHeight="1">
-      <x:c r="A20" s="64" t="str">
-        <x:v>氏名</x:v>
-      </x:c>
-      <x:c r="B20" s="65"/>
-      <x:c r="C20" s="65"/>
-      <x:c r="D20" s="65"/>
-      <x:c r="E20" s="65"/>
-      <x:c r="F20" s="65"/>
-      <x:c r="G20" s="65"/>
-      <x:c r="H20" s="65"/>
-      <x:c r="I20" s="65"/>
-      <x:c r="J20" s="65"/>
-      <x:c r="K20" s="65"/>
-      <x:c r="L20" s="65"/>
-      <x:c r="M20" s="65"/>
-      <x:c r="N20" s="65"/>
-      <x:c r="O20" s="65"/>
-      <x:c r="P20" s="65"/>
-      <x:c r="Q20" s="65"/>
-      <x:c r="R20" s="65"/>
-      <x:c r="S20" s="64" t="str">
-        <x:v>tb2.氏名</x:v>
-      </x:c>
-      <x:c r="T20" s="65"/>
-      <x:c r="U20" s="65"/>
-      <x:c r="V20" s="65"/>
-      <x:c r="W20" s="65"/>
-      <x:c r="X20" s="65"/>
-      <x:c r="Y20" s="65"/>
-      <x:c r="Z20" s="65"/>
-      <x:c r="AA20" s="65"/>
-      <x:c r="AB20" s="65"/>
-      <x:c r="AC20" s="65"/>
-      <x:c r="AD20" s="65"/>
-      <x:c r="AE20" s="65"/>
-      <x:c r="AF20" s="65"/>
-      <x:c r="AG20" s="65"/>
-      <x:c r="AH20" s="65"/>
-      <x:c r="AI20" s="65"/>
-      <x:c r="AJ20" s="65"/>
-      <x:c r="AK20" s="64" t="str">
-        <x:v>TRIM(tb2.氏名)</x:v>
-      </x:c>
-      <x:c r="AL20" s="65"/>
-      <x:c r="AM20" s="65"/>
-      <x:c r="AN20" s="65"/>
-      <x:c r="AO20" s="65"/>
-      <x:c r="AP20" s="65"/>
-      <x:c r="AQ20" s="65"/>
-      <x:c r="AR20" s="65"/>
-      <x:c r="AS20" s="65"/>
-      <x:c r="AT20" s="65"/>
-      <x:c r="AU20" s="65"/>
-      <x:c r="AV20" s="65"/>
-      <x:c r="AW20" s="65"/>
-      <x:c r="AX20" s="65"/>
-      <x:c r="AY20" s="65"/>
-      <x:c r="AZ20" s="65"/>
-      <x:c r="BA20" s="65"/>
-      <x:c r="BB20" s="65"/>
-      <x:c r="BC20" s="65"/>
-      <x:c r="BD20" s="65"/>
-      <x:c r="BE20" s="65"/>
-      <x:c r="BF20" s="65"/>
-      <x:c r="BG20" s="65"/>
-      <x:c r="BH20" s="65"/>
-      <x:c r="BI20" s="65"/>
-      <x:c r="BJ20" s="65"/>
-      <x:c r="BK20" s="65"/>
-      <x:c r="BL20" s="65"/>
-      <x:c r="BM20" s="65"/>
-      <x:c r="BN20" s="65"/>
-      <x:c r="BO20" s="65"/>
-      <x:c r="BP20" s="65"/>
-      <x:c r="BQ20" s="65"/>
-      <x:c r="BR20" s="65"/>
-      <x:c r="BS20" s="65"/>
-      <x:c r="BT20" s="65"/>
-      <x:c r="BU20" s="65"/>
-      <x:c r="BV20" s="65"/>
-      <x:c r="BW20" s="65"/>
-      <x:c r="BX20" s="65"/>
-      <x:c r="BY20" s="65"/>
-      <x:c r="BZ20" s="65"/>
-      <x:c r="CA20" s="65"/>
-      <x:c r="CB20" s="65"/>
-      <x:c r="CC20" s="65"/>
-      <x:c r="CD20" s="65"/>
-      <x:c r="CE20" s="65"/>
-      <x:c r="CF20" s="65"/>
-      <x:c r="CG20" s="65"/>
-      <x:c r="CH20" s="65"/>
-      <x:c r="CI20" s="65"/>
-      <x:c r="CJ20" s="65"/>
-      <x:c r="CK20" s="65"/>
-      <x:c r="CL20" s="66"/>
+      <x:c r="A20" s="47" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B20" s="48"/>
+      <x:c r="C20" s="48"/>
+      <x:c r="D20" s="48"/>
+      <x:c r="E20" s="48"/>
+      <x:c r="F20" s="48"/>
+      <x:c r="G20" s="48"/>
+      <x:c r="H20" s="48"/>
+      <x:c r="I20" s="48"/>
+      <x:c r="J20" s="48"/>
+      <x:c r="K20" s="48"/>
+      <x:c r="L20" s="48"/>
+      <x:c r="M20" s="48"/>
+      <x:c r="N20" s="48"/>
+      <x:c r="O20" s="48"/>
+      <x:c r="P20" s="48"/>
+      <x:c r="Q20" s="48"/>
+      <x:c r="R20" s="48"/>
+      <x:c r="S20" s="47" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="T20" s="48"/>
+      <x:c r="U20" s="48"/>
+      <x:c r="V20" s="48"/>
+      <x:c r="W20" s="48"/>
+      <x:c r="X20" s="48"/>
+      <x:c r="Y20" s="48"/>
+      <x:c r="Z20" s="48"/>
+      <x:c r="AA20" s="48"/>
+      <x:c r="AB20" s="48"/>
+      <x:c r="AC20" s="48"/>
+      <x:c r="AD20" s="48"/>
+      <x:c r="AE20" s="48"/>
+      <x:c r="AF20" s="48"/>
+      <x:c r="AG20" s="48"/>
+      <x:c r="AH20" s="48"/>
+      <x:c r="AI20" s="48"/>
+      <x:c r="AJ20" s="48"/>
+      <x:c r="AK20" s="47" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="AL20" s="48"/>
+      <x:c r="AM20" s="48"/>
+      <x:c r="AN20" s="48"/>
+      <x:c r="AO20" s="48"/>
+      <x:c r="AP20" s="48"/>
+      <x:c r="AQ20" s="48"/>
+      <x:c r="AR20" s="48"/>
+      <x:c r="AS20" s="48"/>
+      <x:c r="AT20" s="48"/>
+      <x:c r="AU20" s="48"/>
+      <x:c r="AV20" s="48"/>
+      <x:c r="AW20" s="48"/>
+      <x:c r="AX20" s="48"/>
+      <x:c r="AY20" s="48"/>
+      <x:c r="AZ20" s="48"/>
+      <x:c r="BA20" s="48"/>
+      <x:c r="BB20" s="48"/>
+      <x:c r="BC20" s="48"/>
+      <x:c r="BD20" s="48"/>
+      <x:c r="BE20" s="48"/>
+      <x:c r="BF20" s="48"/>
+      <x:c r="BG20" s="48"/>
+      <x:c r="BH20" s="48"/>
+      <x:c r="BI20" s="48"/>
+      <x:c r="BJ20" s="48"/>
+      <x:c r="BK20" s="48"/>
+      <x:c r="BL20" s="48"/>
+      <x:c r="BM20" s="48"/>
+      <x:c r="BN20" s="48"/>
+      <x:c r="BO20" s="48"/>
+      <x:c r="BP20" s="48"/>
+      <x:c r="BQ20" s="48"/>
+      <x:c r="BR20" s="48"/>
+      <x:c r="BS20" s="48"/>
+      <x:c r="BT20" s="48"/>
+      <x:c r="BU20" s="48"/>
+      <x:c r="BV20" s="48"/>
+      <x:c r="BW20" s="48"/>
+      <x:c r="BX20" s="48"/>
+      <x:c r="BY20" s="48"/>
+      <x:c r="BZ20" s="48"/>
+      <x:c r="CA20" s="48"/>
+      <x:c r="CB20" s="48"/>
+      <x:c r="CC20" s="48"/>
+      <x:c r="CD20" s="48"/>
+      <x:c r="CE20" s="48"/>
+      <x:c r="CF20" s="48"/>
+      <x:c r="CG20" s="48"/>
+      <x:c r="CH20" s="48"/>
+      <x:c r="CI20" s="48"/>
+      <x:c r="CJ20" s="48"/>
+      <x:c r="CK20" s="48"/>
+      <x:c r="CL20" s="49"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
